--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8899FC7-3E4D-8546-A0D6-44ACC3B38C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7F620D0-2F07-A440-A8B0-9FB7F2D77D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="22800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3495" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3515" uniqueCount="932">
   <si>
     <t>First name</t>
   </si>
@@ -2306,6 +2306,9 @@
     <t>WBJQTZTS-1</t>
   </si>
   <si>
+    <t>ELLKZQVY-1</t>
+  </si>
+  <si>
     <t>Margaret</t>
   </si>
   <si>
@@ -2613,6 +2616,15 @@
   </si>
   <si>
     <t>XTOCLHPM-1</t>
+  </si>
+  <si>
+    <t>Kelsie</t>
+  </si>
+  <si>
+    <t>Costa</t>
+  </si>
+  <si>
+    <t>ECYOPUVX-1</t>
   </si>
   <si>
     <t>Dalia</t>
@@ -3176,12 +3188,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O349"/>
+  <dimension ref="A1:O351"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="10" width="15" customWidth="1"/>
     <col min="11" max="13" width="15" style="1" customWidth="1"/>
-    <col min="14" max="15" width="15" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -13365,7 +13378,7 @@
         <v>21</v>
       </c>
       <c r="J217" t="s">
-        <v>455</v>
+        <v>34</v>
       </c>
       <c r="K217" s="1">
         <v>46161</v>
@@ -14023,7 +14036,7 @@
         <v>21</v>
       </c>
       <c r="J231" t="s">
-        <v>595</v>
+        <v>34</v>
       </c>
       <c r="K231" s="1">
         <v>46163</v>
@@ -14070,7 +14083,7 @@
         <v>69</v>
       </c>
       <c r="J232" t="s">
-        <v>595</v>
+        <v>34</v>
       </c>
       <c r="K232" s="1">
         <v>46164</v>
@@ -14164,7 +14177,7 @@
         <v>69</v>
       </c>
       <c r="J234" t="s">
-        <v>595</v>
+        <v>455</v>
       </c>
       <c r="K234" s="1">
         <v>46159</v>
@@ -14211,7 +14224,7 @@
         <v>21</v>
       </c>
       <c r="J235" t="s">
-        <v>595</v>
+        <v>455</v>
       </c>
       <c r="K235" s="1">
         <v>46161</v>
@@ -14414,7 +14427,7 @@
         <v>4</v>
       </c>
       <c r="O239" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.2">
@@ -15668,7 +15681,7 @@
         <v>69</v>
       </c>
       <c r="J266" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K266" s="1">
         <v>46141</v>
@@ -16044,7 +16057,7 @@
         <v>21</v>
       </c>
       <c r="J274" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K274" s="1">
         <v>46104</v>
@@ -16270,7 +16283,7 @@
         <v>17</v>
       </c>
       <c r="G279">
-        <v>4309</v>
+        <v>6212</v>
       </c>
       <c r="H279" t="s">
         <v>748</v>
@@ -16288,10 +16301,10 @@
         <v>46198</v>
       </c>
       <c r="M279" s="1">
-        <v>46205</v>
+        <v>46208</v>
       </c>
       <c r="N279">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O279" t="s">
         <v>17</v>
@@ -16534,28 +16547,28 @@
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
+        <v>742</v>
+      </c>
+      <c r="B285" t="s">
+        <v>743</v>
+      </c>
+      <c r="C285" t="s">
+        <v>155</v>
+      </c>
+      <c r="D285" t="s">
+        <v>39</v>
+      </c>
+      <c r="E285" t="s">
+        <v>19</v>
+      </c>
+      <c r="F285" t="s">
+        <v>17</v>
+      </c>
+      <c r="G285">
+        <v>1524.8</v>
+      </c>
+      <c r="H285" t="s">
         <v>763</v>
-      </c>
-      <c r="B285" t="s">
-        <v>764</v>
-      </c>
-      <c r="C285" t="s">
-        <v>58</v>
-      </c>
-      <c r="D285" t="s">
-        <v>36</v>
-      </c>
-      <c r="E285" t="s">
-        <v>40</v>
-      </c>
-      <c r="F285" t="s">
-        <v>434</v>
-      </c>
-      <c r="G285">
-        <v>4918.13</v>
-      </c>
-      <c r="H285" t="s">
-        <v>765</v>
       </c>
       <c r="I285" t="s">
         <v>21</v>
@@ -16564,16 +16577,16 @@
         <v>595</v>
       </c>
       <c r="K285" s="1">
-        <v>46094</v>
+        <v>46170</v>
       </c>
       <c r="L285" s="1">
-        <v>46204</v>
+        <v>46202</v>
       </c>
       <c r="M285" s="1">
-        <v>46211</v>
+        <v>46203</v>
       </c>
       <c r="N285">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O285" t="s">
         <v>17</v>
@@ -16581,10 +16594,10 @@
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B286" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C286" t="s">
         <v>58</v>
@@ -16596,92 +16609,92 @@
         <v>40</v>
       </c>
       <c r="F286" t="s">
-        <v>306</v>
+        <v>434</v>
       </c>
       <c r="G286">
-        <v>0</v>
+        <v>4918.13</v>
       </c>
       <c r="H286" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="I286" t="s">
         <v>21</v>
       </c>
       <c r="J286" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K286" s="1">
-        <v>46132</v>
+        <v>46094</v>
       </c>
       <c r="L286" s="1">
         <v>46204</v>
       </c>
       <c r="M286" s="1">
-        <v>46294</v>
+        <v>46211</v>
       </c>
       <c r="N286">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="O286" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
+        <v>767</v>
+      </c>
+      <c r="B287" t="s">
+        <v>768</v>
+      </c>
+      <c r="C287" t="s">
+        <v>58</v>
+      </c>
+      <c r="D287" t="s">
+        <v>36</v>
+      </c>
+      <c r="E287" t="s">
+        <v>40</v>
+      </c>
+      <c r="F287" t="s">
+        <v>306</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="H287" t="s">
         <v>769</v>
       </c>
-      <c r="B287" t="s">
-        <v>770</v>
-      </c>
-      <c r="C287" t="s">
-        <v>73</v>
-      </c>
-      <c r="D287" t="s">
-        <v>74</v>
-      </c>
-      <c r="E287" t="s">
-        <v>40</v>
-      </c>
-      <c r="F287" t="s">
-        <v>75</v>
-      </c>
-      <c r="G287">
-        <v>4536</v>
-      </c>
-      <c r="H287" t="s">
-        <v>771</v>
-      </c>
       <c r="I287" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J287" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K287" s="1">
-        <v>46154</v>
+        <v>46132</v>
       </c>
       <c r="L287" s="1">
         <v>46204</v>
       </c>
       <c r="M287" s="1">
-        <v>46211</v>
+        <v>46294</v>
       </c>
       <c r="N287">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="O287" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B288" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C288" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D288" t="s">
         <v>74</v>
@@ -16693,10 +16706,10 @@
         <v>75</v>
       </c>
       <c r="G288">
-        <v>2880</v>
+        <v>4536</v>
       </c>
       <c r="H288" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="I288" t="s">
         <v>69</v>
@@ -16708,13 +16721,13 @@
         <v>46154</v>
       </c>
       <c r="L288" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="M288" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="N288">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O288" t="s">
         <v>17</v>
@@ -16722,16 +16735,16 @@
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B289" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C289" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="D289" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="E289" t="s">
         <v>40</v>
@@ -16740,28 +16753,28 @@
         <v>75</v>
       </c>
       <c r="G289">
-        <v>13546.77</v>
+        <v>2880</v>
       </c>
       <c r="H289" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I289" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J289" t="s">
         <v>595</v>
       </c>
       <c r="K289" s="1">
-        <v>46108</v>
+        <v>46154</v>
       </c>
       <c r="L289" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="M289" s="1">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="N289">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O289" t="s">
         <v>17</v>
@@ -16769,63 +16782,63 @@
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
+        <v>776</v>
+      </c>
+      <c r="B290" t="s">
+        <v>777</v>
+      </c>
+      <c r="C290" t="s">
+        <v>155</v>
+      </c>
+      <c r="D290" t="s">
+        <v>39</v>
+      </c>
+      <c r="E290" t="s">
+        <v>40</v>
+      </c>
+      <c r="F290" t="s">
+        <v>75</v>
+      </c>
+      <c r="G290">
+        <v>13546.77</v>
+      </c>
+      <c r="H290" t="s">
         <v>778</v>
       </c>
-      <c r="B290" t="s">
-        <v>779</v>
-      </c>
-      <c r="C290" t="s">
-        <v>105</v>
-      </c>
-      <c r="D290" t="s">
-        <v>66</v>
-      </c>
-      <c r="E290" t="s">
-        <v>40</v>
-      </c>
-      <c r="F290" t="s">
-        <v>390</v>
-      </c>
-      <c r="G290">
-        <v>2025.78</v>
-      </c>
-      <c r="H290" t="s">
-        <v>780</v>
-      </c>
       <c r="I290" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J290" t="s">
         <v>595</v>
       </c>
       <c r="K290" s="1">
-        <v>46079</v>
+        <v>46108</v>
       </c>
       <c r="L290" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="M290" s="1">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="N290">
         <v>6</v>
       </c>
       <c r="O290" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B291" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C291" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="D291" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E291" t="s">
         <v>40</v>
@@ -16834,10 +16847,10 @@
         <v>390</v>
       </c>
       <c r="G291">
-        <v>4311.7299999999996</v>
+        <v>2025.78</v>
       </c>
       <c r="H291" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="I291" t="s">
         <v>69</v>
@@ -16846,63 +16859,63 @@
         <v>595</v>
       </c>
       <c r="K291" s="1">
-        <v>46165</v>
+        <v>46079</v>
       </c>
       <c r="L291" s="1">
         <v>46207</v>
       </c>
       <c r="M291" s="1">
-        <v>46214</v>
+        <v>46213</v>
       </c>
       <c r="N291">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O291" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="292" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
+        <v>782</v>
+      </c>
+      <c r="B292" t="s">
+        <v>783</v>
+      </c>
+      <c r="C292" t="s">
+        <v>71</v>
+      </c>
+      <c r="D292" t="s">
+        <v>70</v>
+      </c>
+      <c r="E292" t="s">
+        <v>40</v>
+      </c>
+      <c r="F292" t="s">
+        <v>390</v>
+      </c>
+      <c r="G292">
+        <v>4311.7299999999996</v>
+      </c>
+      <c r="H292" t="s">
         <v>784</v>
       </c>
-      <c r="B292" t="s">
-        <v>785</v>
-      </c>
-      <c r="C292" t="s">
-        <v>318</v>
-      </c>
-      <c r="D292" t="s">
-        <v>36</v>
-      </c>
-      <c r="E292" t="s">
-        <v>40</v>
-      </c>
-      <c r="F292" t="s">
-        <v>434</v>
-      </c>
-      <c r="G292">
-        <v>4596</v>
-      </c>
-      <c r="H292" t="s">
-        <v>786</v>
-      </c>
       <c r="I292" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J292" t="s">
         <v>595</v>
       </c>
       <c r="K292" s="1">
-        <v>46101</v>
+        <v>46165</v>
       </c>
       <c r="L292" s="1">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="M292" s="1">
-        <v>46212</v>
+        <v>46214</v>
       </c>
       <c r="N292">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O292" t="s">
         <v>17</v>
@@ -16910,13 +16923,13 @@
     </row>
     <row r="293" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B293" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C293" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D293" t="s">
         <v>36</v>
@@ -16928,10 +16941,10 @@
         <v>434</v>
       </c>
       <c r="G293">
-        <v>8882.44</v>
+        <v>4596</v>
       </c>
       <c r="H293" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="I293" t="s">
         <v>320</v>
@@ -16940,204 +16953,204 @@
         <v>595</v>
       </c>
       <c r="K293" s="1">
-        <v>46122</v>
+        <v>46101</v>
       </c>
       <c r="L293" s="1">
         <v>46208</v>
       </c>
       <c r="M293" s="1">
-        <v>46215</v>
+        <v>46212</v>
       </c>
       <c r="N293">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O293" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="294" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
+        <v>788</v>
+      </c>
+      <c r="B294" t="s">
+        <v>789</v>
+      </c>
+      <c r="C294" t="s">
+        <v>321</v>
+      </c>
+      <c r="D294" t="s">
+        <v>36</v>
+      </c>
+      <c r="E294" t="s">
+        <v>40</v>
+      </c>
+      <c r="F294" t="s">
+        <v>434</v>
+      </c>
+      <c r="G294">
+        <v>8882.44</v>
+      </c>
+      <c r="H294" t="s">
         <v>790</v>
       </c>
-      <c r="B294" t="s">
-        <v>791</v>
-      </c>
-      <c r="C294" t="s">
-        <v>17</v>
-      </c>
-      <c r="D294" t="s">
-        <v>17</v>
-      </c>
-      <c r="E294" t="s">
-        <v>40</v>
-      </c>
-      <c r="F294" t="s">
-        <v>75</v>
-      </c>
-      <c r="G294">
-        <v>15723.48</v>
-      </c>
-      <c r="H294" t="s">
-        <v>792</v>
-      </c>
       <c r="I294" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J294" t="s">
         <v>595</v>
       </c>
       <c r="K294" s="1">
-        <v>46132</v>
+        <v>46122</v>
       </c>
       <c r="L294" s="1">
         <v>46208</v>
       </c>
       <c r="M294" s="1">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="N294">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O294" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="295" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>56</v>
+        <v>791</v>
       </c>
       <c r="B295" t="s">
+        <v>792</v>
+      </c>
+      <c r="C295" t="s">
+        <v>17</v>
+      </c>
+      <c r="D295" t="s">
+        <v>17</v>
+      </c>
+      <c r="E295" t="s">
+        <v>40</v>
+      </c>
+      <c r="F295" t="s">
+        <v>75</v>
+      </c>
+      <c r="G295">
+        <v>15723.48</v>
+      </c>
+      <c r="H295" t="s">
         <v>793</v>
       </c>
-      <c r="C295" t="s">
-        <v>83</v>
-      </c>
-      <c r="D295" t="s">
-        <v>74</v>
-      </c>
-      <c r="E295" t="s">
-        <v>40</v>
-      </c>
-      <c r="F295" t="s">
-        <v>434</v>
-      </c>
-      <c r="G295">
-        <v>6006.72</v>
-      </c>
-      <c r="H295" t="s">
-        <v>794</v>
-      </c>
       <c r="I295" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J295" t="s">
         <v>595</v>
       </c>
       <c r="K295" s="1">
-        <v>46091</v>
+        <v>46132</v>
       </c>
       <c r="L295" s="1">
-        <v>46210</v>
+        <v>46208</v>
       </c>
       <c r="M295" s="1">
-        <v>46218</v>
+        <v>46214</v>
       </c>
       <c r="N295">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O295" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="296" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
+        <v>56</v>
+      </c>
+      <c r="B296" t="s">
+        <v>794</v>
+      </c>
+      <c r="C296" t="s">
+        <v>83</v>
+      </c>
+      <c r="D296" t="s">
+        <v>74</v>
+      </c>
+      <c r="E296" t="s">
+        <v>40</v>
+      </c>
+      <c r="F296" t="s">
+        <v>434</v>
+      </c>
+      <c r="G296">
+        <v>6006.72</v>
+      </c>
+      <c r="H296" t="s">
         <v>795</v>
       </c>
-      <c r="B296" t="s">
-        <v>796</v>
-      </c>
-      <c r="C296" t="s">
-        <v>17</v>
-      </c>
-      <c r="D296" t="s">
-        <v>17</v>
-      </c>
-      <c r="E296" t="s">
-        <v>40</v>
-      </c>
-      <c r="F296" t="s">
-        <v>125</v>
-      </c>
-      <c r="G296">
-        <v>2575.1999999999998</v>
-      </c>
-      <c r="H296" t="s">
-        <v>797</v>
-      </c>
       <c r="I296" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J296" t="s">
         <v>595</v>
       </c>
       <c r="K296" s="1">
-        <v>46106</v>
+        <v>46091</v>
       </c>
       <c r="L296" s="1">
         <v>46210</v>
       </c>
       <c r="M296" s="1">
-        <v>46214</v>
+        <v>46218</v>
       </c>
       <c r="N296">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O296" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="297" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
+        <v>796</v>
+      </c>
+      <c r="B297" t="s">
+        <v>797</v>
+      </c>
+      <c r="C297" t="s">
+        <v>17</v>
+      </c>
+      <c r="D297" t="s">
+        <v>17</v>
+      </c>
+      <c r="E297" t="s">
+        <v>40</v>
+      </c>
+      <c r="F297" t="s">
+        <v>125</v>
+      </c>
+      <c r="G297">
+        <v>2575.1999999999998</v>
+      </c>
+      <c r="H297" t="s">
         <v>798</v>
       </c>
-      <c r="B297" t="s">
-        <v>799</v>
-      </c>
-      <c r="C297" t="s">
-        <v>27</v>
-      </c>
-      <c r="D297" t="s">
-        <v>28</v>
-      </c>
-      <c r="E297" t="s">
-        <v>40</v>
-      </c>
-      <c r="F297" t="s">
-        <v>75</v>
-      </c>
-      <c r="G297">
-        <v>25725</v>
-      </c>
-      <c r="H297" t="s">
-        <v>800</v>
-      </c>
       <c r="I297" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J297" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K297" s="1">
-        <v>46062</v>
+        <v>46106</v>
       </c>
       <c r="L297" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="M297" s="1">
-        <v>46242</v>
+        <v>46214</v>
       </c>
       <c r="N297">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="O297" t="s">
         <v>17</v>
@@ -17145,16 +17158,16 @@
     </row>
     <row r="298" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B298" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C298" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D298" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E298" t="s">
         <v>40</v>
@@ -17163,7 +17176,7 @@
         <v>75</v>
       </c>
       <c r="G298">
-        <v>20559.599999999999</v>
+        <v>25725</v>
       </c>
       <c r="H298" t="s">
         <v>801</v>
@@ -17175,7 +17188,7 @@
         <v>22</v>
       </c>
       <c r="K298" s="1">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="L298" s="1">
         <v>46211</v>
@@ -17192,16 +17205,16 @@
     </row>
     <row r="299" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B299" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C299" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D299" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E299" t="s">
         <v>40</v>
@@ -17210,7 +17223,7 @@
         <v>75</v>
       </c>
       <c r="G299">
-        <v>23149</v>
+        <v>20559.599999999999</v>
       </c>
       <c r="H299" t="s">
         <v>802</v>
@@ -17228,10 +17241,10 @@
         <v>46211</v>
       </c>
       <c r="M299" s="1">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="N299">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="O299" t="s">
         <v>17</v>
@@ -17239,46 +17252,46 @@
     </row>
     <row r="300" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
+        <v>799</v>
+      </c>
+      <c r="B300" t="s">
+        <v>800</v>
+      </c>
+      <c r="C300" t="s">
+        <v>27</v>
+      </c>
+      <c r="D300" t="s">
+        <v>28</v>
+      </c>
+      <c r="E300" t="s">
+        <v>40</v>
+      </c>
+      <c r="F300" t="s">
+        <v>75</v>
+      </c>
+      <c r="G300">
+        <v>23149</v>
+      </c>
+      <c r="H300" t="s">
         <v>803</v>
-      </c>
-      <c r="B300" t="s">
-        <v>804</v>
-      </c>
-      <c r="C300" t="s">
-        <v>155</v>
-      </c>
-      <c r="D300" t="s">
-        <v>39</v>
-      </c>
-      <c r="E300" t="s">
-        <v>225</v>
-      </c>
-      <c r="F300" t="s">
-        <v>17</v>
-      </c>
-      <c r="G300">
-        <v>41988</v>
-      </c>
-      <c r="H300" t="s">
-        <v>805</v>
       </c>
       <c r="I300" t="s">
         <v>21</v>
       </c>
       <c r="J300" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K300" s="1">
-        <v>46160</v>
+        <v>46063</v>
       </c>
       <c r="L300" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="M300" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="N300">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O300" t="s">
         <v>17</v>
@@ -17286,16 +17299,16 @@
     </row>
     <row r="301" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B301" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C301" t="s">
-        <v>212</v>
+        <v>155</v>
       </c>
       <c r="D301" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E301" t="s">
         <v>225</v>
@@ -17304,10 +17317,10 @@
         <v>17</v>
       </c>
       <c r="G301">
-        <v>9035</v>
+        <v>41988</v>
       </c>
       <c r="H301" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="I301" t="s">
         <v>21</v>
@@ -17316,16 +17329,16 @@
         <v>595</v>
       </c>
       <c r="K301" s="1">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="L301" s="1">
         <v>46212</v>
       </c>
       <c r="M301" s="1">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="N301">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O301" t="s">
         <v>17</v>
@@ -17333,46 +17346,46 @@
     </row>
     <row r="302" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
+        <v>807</v>
+      </c>
+      <c r="B302" t="s">
+        <v>808</v>
+      </c>
+      <c r="C302" t="s">
+        <v>212</v>
+      </c>
+      <c r="D302" t="s">
+        <v>24</v>
+      </c>
+      <c r="E302" t="s">
+        <v>225</v>
+      </c>
+      <c r="F302" t="s">
+        <v>17</v>
+      </c>
+      <c r="G302">
+        <v>9035</v>
+      </c>
+      <c r="H302" t="s">
         <v>809</v>
       </c>
-      <c r="B302" t="s">
-        <v>810</v>
-      </c>
-      <c r="C302" t="s">
-        <v>105</v>
-      </c>
-      <c r="D302" t="s">
-        <v>66</v>
-      </c>
-      <c r="E302" t="s">
-        <v>40</v>
-      </c>
-      <c r="F302" t="s">
-        <v>75</v>
-      </c>
-      <c r="G302">
-        <v>2621.7</v>
-      </c>
-      <c r="H302" t="s">
-        <v>811</v>
-      </c>
       <c r="I302" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J302" t="s">
         <v>595</v>
       </c>
       <c r="K302" s="1">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="L302" s="1">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="M302" s="1">
-        <v>46220</v>
+        <v>46229</v>
       </c>
       <c r="N302">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="O302" t="s">
         <v>17</v>
@@ -17380,46 +17393,46 @@
     </row>
     <row r="303" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
+        <v>810</v>
+      </c>
+      <c r="B303" t="s">
+        <v>811</v>
+      </c>
+      <c r="C303" t="s">
+        <v>105</v>
+      </c>
+      <c r="D303" t="s">
+        <v>66</v>
+      </c>
+      <c r="E303" t="s">
+        <v>40</v>
+      </c>
+      <c r="F303" t="s">
+        <v>75</v>
+      </c>
+      <c r="G303">
+        <v>2621.7</v>
+      </c>
+      <c r="H303" t="s">
         <v>812</v>
       </c>
-      <c r="B303" t="s">
-        <v>813</v>
-      </c>
-      <c r="C303" t="s">
-        <v>318</v>
-      </c>
-      <c r="D303" t="s">
-        <v>36</v>
-      </c>
-      <c r="E303" t="s">
-        <v>40</v>
-      </c>
-      <c r="F303" t="s">
-        <v>125</v>
-      </c>
-      <c r="G303">
-        <v>8446.34</v>
-      </c>
-      <c r="H303" t="s">
-        <v>814</v>
-      </c>
       <c r="I303" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J303" t="s">
         <v>595</v>
       </c>
       <c r="K303" s="1">
-        <v>46106</v>
+        <v>46166</v>
       </c>
       <c r="L303" s="1">
-        <v>46215</v>
+        <v>46213</v>
       </c>
       <c r="M303" s="1">
-        <v>46229</v>
+        <v>46220</v>
       </c>
       <c r="N303">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O303" t="s">
         <v>17</v>
@@ -17427,46 +17440,46 @@
     </row>
     <row r="304" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
+        <v>813</v>
+      </c>
+      <c r="B304" t="s">
+        <v>814</v>
+      </c>
+      <c r="C304" t="s">
+        <v>318</v>
+      </c>
+      <c r="D304" t="s">
+        <v>36</v>
+      </c>
+      <c r="E304" t="s">
+        <v>40</v>
+      </c>
+      <c r="F304" t="s">
+        <v>125</v>
+      </c>
+      <c r="G304">
+        <v>8446.34</v>
+      </c>
+      <c r="H304" t="s">
         <v>815</v>
       </c>
-      <c r="B304" t="s">
-        <v>816</v>
-      </c>
-      <c r="C304" t="s">
-        <v>73</v>
-      </c>
-      <c r="D304" t="s">
-        <v>74</v>
-      </c>
-      <c r="E304" t="s">
-        <v>40</v>
-      </c>
-      <c r="F304" t="s">
-        <v>75</v>
-      </c>
-      <c r="G304">
-        <v>12127.4</v>
-      </c>
-      <c r="H304" t="s">
-        <v>817</v>
-      </c>
       <c r="I304" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J304" t="s">
         <v>595</v>
       </c>
       <c r="K304" s="1">
-        <v>46120</v>
+        <v>46106</v>
       </c>
       <c r="L304" s="1">
         <v>46215</v>
       </c>
       <c r="M304" s="1">
-        <v>46235</v>
+        <v>46229</v>
       </c>
       <c r="N304">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O304" t="s">
         <v>17</v>
@@ -17474,46 +17487,46 @@
     </row>
     <row r="305" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>697</v>
+        <v>816</v>
       </c>
       <c r="B305" t="s">
+        <v>817</v>
+      </c>
+      <c r="C305" t="s">
+        <v>73</v>
+      </c>
+      <c r="D305" t="s">
+        <v>74</v>
+      </c>
+      <c r="E305" t="s">
+        <v>40</v>
+      </c>
+      <c r="F305" t="s">
+        <v>75</v>
+      </c>
+      <c r="G305">
+        <v>12127.4</v>
+      </c>
+      <c r="H305" t="s">
         <v>818</v>
       </c>
-      <c r="C305" t="s">
-        <v>17</v>
-      </c>
-      <c r="D305" t="s">
-        <v>17</v>
-      </c>
-      <c r="E305" t="s">
-        <v>40</v>
-      </c>
-      <c r="F305" t="s">
-        <v>434</v>
-      </c>
-      <c r="G305">
-        <v>4802.3999999999996</v>
-      </c>
-      <c r="H305" t="s">
-        <v>819</v>
-      </c>
       <c r="I305" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J305" t="s">
         <v>595</v>
       </c>
       <c r="K305" s="1">
-        <v>46126</v>
+        <v>46120</v>
       </c>
       <c r="L305" s="1">
-        <v>46216</v>
+        <v>46215</v>
       </c>
       <c r="M305" s="1">
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="N305">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="O305" t="s">
         <v>17</v>
@@ -17521,28 +17534,28 @@
     </row>
     <row r="306" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
+        <v>697</v>
+      </c>
+      <c r="B306" t="s">
+        <v>819</v>
+      </c>
+      <c r="C306" t="s">
+        <v>17</v>
+      </c>
+      <c r="D306" t="s">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>40</v>
+      </c>
+      <c r="F306" t="s">
+        <v>434</v>
+      </c>
+      <c r="G306">
+        <v>4802.3999999999996</v>
+      </c>
+      <c r="H306" t="s">
         <v>820</v>
-      </c>
-      <c r="B306" t="s">
-        <v>821</v>
-      </c>
-      <c r="C306" t="s">
-        <v>321</v>
-      </c>
-      <c r="D306" t="s">
-        <v>36</v>
-      </c>
-      <c r="E306" t="s">
-        <v>40</v>
-      </c>
-      <c r="F306" t="s">
-        <v>75</v>
-      </c>
-      <c r="G306">
-        <v>16844.400000000001</v>
-      </c>
-      <c r="H306" t="s">
-        <v>822</v>
       </c>
       <c r="I306" t="s">
         <v>320</v>
@@ -17551,16 +17564,16 @@
         <v>595</v>
       </c>
       <c r="K306" s="1">
-        <v>46129</v>
+        <v>46126</v>
       </c>
       <c r="L306" s="1">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="M306" s="1">
-        <v>46235</v>
+        <v>46220</v>
       </c>
       <c r="N306">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="O306" t="s">
         <v>17</v>
@@ -17568,16 +17581,16 @@
     </row>
     <row r="307" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>373</v>
+        <v>821</v>
       </c>
       <c r="B307" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C307" t="s">
-        <v>25</v>
+        <v>321</v>
       </c>
       <c r="D307" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E307" t="s">
         <v>40</v>
@@ -17586,28 +17599,28 @@
         <v>75</v>
       </c>
       <c r="G307">
-        <v>4078.8</v>
+        <v>16844.400000000001</v>
       </c>
       <c r="H307" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I307" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J307" t="s">
         <v>595</v>
       </c>
       <c r="K307" s="1">
-        <v>46078</v>
+        <v>46129</v>
       </c>
       <c r="L307" s="1">
-        <v>46222</v>
+        <v>46218</v>
       </c>
       <c r="M307" s="1">
-        <v>46227</v>
+        <v>46235</v>
       </c>
       <c r="N307">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O307" t="s">
         <v>17</v>
@@ -17615,25 +17628,25 @@
     </row>
     <row r="308" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="B308" t="s">
-        <v>622</v>
+        <v>824</v>
       </c>
       <c r="C308" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D308" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E308" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F308" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="G308">
-        <v>6036</v>
+        <v>4078.8</v>
       </c>
       <c r="H308" t="s">
         <v>825</v>
@@ -17645,16 +17658,16 @@
         <v>595</v>
       </c>
       <c r="K308" s="1">
-        <v>46165</v>
+        <v>46078</v>
       </c>
       <c r="L308" s="1">
         <v>46222</v>
       </c>
       <c r="M308" s="1">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="N308">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O308" t="s">
         <v>17</v>
@@ -17662,46 +17675,46 @@
     </row>
     <row r="309" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
+        <v>669</v>
+      </c>
+      <c r="B309" t="s">
+        <v>622</v>
+      </c>
+      <c r="C309" t="s">
+        <v>27</v>
+      </c>
+      <c r="D309" t="s">
+        <v>28</v>
+      </c>
+      <c r="E309" t="s">
+        <v>19</v>
+      </c>
+      <c r="F309" t="s">
+        <v>17</v>
+      </c>
+      <c r="G309">
+        <v>6036</v>
+      </c>
+      <c r="H309" t="s">
         <v>826</v>
-      </c>
-      <c r="B309" t="s">
-        <v>827</v>
-      </c>
-      <c r="C309" t="s">
-        <v>17</v>
-      </c>
-      <c r="D309" t="s">
-        <v>17</v>
-      </c>
-      <c r="E309" t="s">
-        <v>40</v>
-      </c>
-      <c r="F309" t="s">
-        <v>75</v>
-      </c>
-      <c r="G309">
-        <v>29900.97</v>
-      </c>
-      <c r="H309" t="s">
-        <v>828</v>
       </c>
       <c r="I309" t="s">
         <v>21</v>
       </c>
       <c r="J309" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K309" s="1">
-        <v>46111</v>
+        <v>46165</v>
       </c>
       <c r="L309" s="1">
-        <v>46226</v>
+        <v>46222</v>
       </c>
       <c r="M309" s="1">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="N309">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O309" t="s">
         <v>17</v>
@@ -17709,16 +17722,16 @@
     </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B310" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C310" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="D310" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="E310" t="s">
         <v>40</v>
@@ -17727,28 +17740,28 @@
         <v>75</v>
       </c>
       <c r="G310">
-        <v>1731.6</v>
+        <v>29900.97</v>
       </c>
       <c r="H310" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="I310" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J310" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K310" s="1">
-        <v>46056</v>
+        <v>46111</v>
       </c>
       <c r="L310" s="1">
-        <v>46229</v>
+        <v>46226</v>
       </c>
       <c r="M310" s="1">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="N310">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O310" t="s">
         <v>17</v>
@@ -17756,16 +17769,16 @@
     </row>
     <row r="311" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B311" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C311" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="D311" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="E311" t="s">
         <v>40</v>
@@ -17774,28 +17787,28 @@
         <v>75</v>
       </c>
       <c r="G311">
-        <v>3983.66</v>
+        <v>1731.6</v>
       </c>
       <c r="H311" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="I311" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J311" t="s">
         <v>595</v>
       </c>
       <c r="K311" s="1">
-        <v>46092</v>
+        <v>46056</v>
       </c>
       <c r="L311" s="1">
         <v>46229</v>
       </c>
       <c r="M311" s="1">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="N311">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O311" t="s">
         <v>17</v>
@@ -17803,78 +17816,78 @@
     </row>
     <row r="312" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>586</v>
+        <v>833</v>
       </c>
       <c r="B312" t="s">
+        <v>834</v>
+      </c>
+      <c r="C312" t="s">
+        <v>58</v>
+      </c>
+      <c r="D312" t="s">
+        <v>36</v>
+      </c>
+      <c r="E312" t="s">
+        <v>40</v>
+      </c>
+      <c r="F312" t="s">
+        <v>75</v>
+      </c>
+      <c r="G312">
+        <v>3983.66</v>
+      </c>
+      <c r="H312" t="s">
         <v>835</v>
       </c>
-      <c r="C312" t="s">
-        <v>83</v>
-      </c>
-      <c r="D312" t="s">
-        <v>74</v>
-      </c>
-      <c r="E312" t="s">
-        <v>40</v>
-      </c>
-      <c r="F312" t="s">
-        <v>125</v>
-      </c>
-      <c r="G312">
-        <v>2110.48</v>
-      </c>
-      <c r="H312" t="s">
-        <v>836</v>
-      </c>
       <c r="I312" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J312" t="s">
         <v>595</v>
       </c>
       <c r="K312" s="1">
-        <v>46163</v>
+        <v>46092</v>
       </c>
       <c r="L312" s="1">
         <v>46229</v>
       </c>
       <c r="M312" s="1">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="N312">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O312" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="313" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
+        <v>586</v>
+      </c>
+      <c r="B313" t="s">
+        <v>836</v>
+      </c>
+      <c r="C313" t="s">
+        <v>83</v>
+      </c>
+      <c r="D313" t="s">
+        <v>74</v>
+      </c>
+      <c r="E313" t="s">
+        <v>40</v>
+      </c>
+      <c r="F313" t="s">
+        <v>125</v>
+      </c>
+      <c r="G313">
+        <v>2110.48</v>
+      </c>
+      <c r="H313" t="s">
         <v>837</v>
       </c>
-      <c r="B313" t="s">
-        <v>31</v>
-      </c>
-      <c r="C313" t="s">
-        <v>318</v>
-      </c>
-      <c r="D313" t="s">
-        <v>36</v>
-      </c>
-      <c r="E313" t="s">
-        <v>40</v>
-      </c>
-      <c r="F313" t="s">
-        <v>41</v>
-      </c>
-      <c r="G313">
-        <v>5446</v>
-      </c>
-      <c r="H313" t="s">
-        <v>838</v>
-      </c>
       <c r="I313" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J313" t="s">
         <v>595</v>
@@ -17892,48 +17905,48 @@
         <v>4</v>
       </c>
       <c r="O313" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="314" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
+        <v>838</v>
+      </c>
+      <c r="B314" t="s">
+        <v>31</v>
+      </c>
+      <c r="C314" t="s">
+        <v>318</v>
+      </c>
+      <c r="D314" t="s">
+        <v>36</v>
+      </c>
+      <c r="E314" t="s">
+        <v>40</v>
+      </c>
+      <c r="F314" t="s">
+        <v>41</v>
+      </c>
+      <c r="G314">
+        <v>5446</v>
+      </c>
+      <c r="H314" t="s">
         <v>839</v>
       </c>
-      <c r="B314" t="s">
-        <v>840</v>
-      </c>
-      <c r="C314" t="s">
-        <v>334</v>
-      </c>
-      <c r="D314" t="s">
-        <v>333</v>
-      </c>
-      <c r="E314" t="s">
-        <v>40</v>
-      </c>
-      <c r="F314" t="s">
-        <v>434</v>
-      </c>
-      <c r="G314">
-        <v>1302.2</v>
-      </c>
-      <c r="H314" t="s">
-        <v>841</v>
-      </c>
       <c r="I314" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J314" t="s">
         <v>22</v>
       </c>
       <c r="K314" s="1">
-        <v>46031</v>
+        <v>46163</v>
       </c>
       <c r="L314" s="1">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="M314" s="1">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="N314">
         <v>4</v>
@@ -17944,28 +17957,28 @@
     </row>
     <row r="315" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
+        <v>840</v>
+      </c>
+      <c r="B315" t="s">
+        <v>841</v>
+      </c>
+      <c r="C315" t="s">
+        <v>334</v>
+      </c>
+      <c r="D315" t="s">
+        <v>333</v>
+      </c>
+      <c r="E315" t="s">
+        <v>40</v>
+      </c>
+      <c r="F315" t="s">
+        <v>434</v>
+      </c>
+      <c r="G315">
+        <v>1302.2</v>
+      </c>
+      <c r="H315" t="s">
         <v>842</v>
-      </c>
-      <c r="B315" t="s">
-        <v>843</v>
-      </c>
-      <c r="C315" t="s">
-        <v>73</v>
-      </c>
-      <c r="D315" t="s">
-        <v>74</v>
-      </c>
-      <c r="E315" t="s">
-        <v>40</v>
-      </c>
-      <c r="F315" t="s">
-        <v>75</v>
-      </c>
-      <c r="G315">
-        <v>4013.08</v>
-      </c>
-      <c r="H315" t="s">
-        <v>844</v>
       </c>
       <c r="I315" t="s">
         <v>69</v>
@@ -17974,16 +17987,16 @@
         <v>22</v>
       </c>
       <c r="K315" s="1">
-        <v>46109</v>
+        <v>46031</v>
       </c>
       <c r="L315" s="1">
+        <v>46230</v>
+      </c>
+      <c r="M315" s="1">
         <v>46234</v>
       </c>
-      <c r="M315" s="1">
-        <v>46241</v>
-      </c>
       <c r="N315">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O315" t="s">
         <v>17</v>
@@ -17991,16 +18004,16 @@
     </row>
     <row r="316" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B316" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C316" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D316" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E316" t="s">
         <v>40</v>
@@ -18009,7 +18022,7 @@
         <v>75</v>
       </c>
       <c r="G316">
-        <v>1977.13</v>
+        <v>4013.08</v>
       </c>
       <c r="H316" t="s">
         <v>845</v>
@@ -18038,16 +18051,16 @@
     </row>
     <row r="317" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B317" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C317" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="D317" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E317" t="s">
         <v>40</v>
@@ -18056,7 +18069,7 @@
         <v>75</v>
       </c>
       <c r="G317">
-        <v>3610.33</v>
+        <v>1977.13</v>
       </c>
       <c r="H317" t="s">
         <v>846</v>
@@ -18085,28 +18098,28 @@
     </row>
     <row r="318" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>23</v>
+        <v>843</v>
       </c>
       <c r="B318" t="s">
+        <v>844</v>
+      </c>
+      <c r="C318" t="s">
+        <v>71</v>
+      </c>
+      <c r="D318" t="s">
+        <v>70</v>
+      </c>
+      <c r="E318" t="s">
+        <v>40</v>
+      </c>
+      <c r="F318" t="s">
+        <v>75</v>
+      </c>
+      <c r="G318">
+        <v>3610.33</v>
+      </c>
+      <c r="H318" t="s">
         <v>847</v>
-      </c>
-      <c r="C318" t="s">
-        <v>67</v>
-      </c>
-      <c r="D318" t="s">
-        <v>66</v>
-      </c>
-      <c r="E318" t="s">
-        <v>40</v>
-      </c>
-      <c r="F318" t="s">
-        <v>848</v>
-      </c>
-      <c r="G318">
-        <v>704.8</v>
-      </c>
-      <c r="H318" t="s">
-        <v>849</v>
       </c>
       <c r="I318" t="s">
         <v>69</v>
@@ -18115,16 +18128,16 @@
         <v>22</v>
       </c>
       <c r="K318" s="1">
-        <v>46073</v>
+        <v>46109</v>
       </c>
       <c r="L318" s="1">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="M318" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="N318">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O318" t="s">
         <v>17</v>
@@ -18132,46 +18145,46 @@
     </row>
     <row r="319" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
+        <v>23</v>
+      </c>
+      <c r="B319" t="s">
+        <v>848</v>
+      </c>
+      <c r="C319" t="s">
+        <v>67</v>
+      </c>
+      <c r="D319" t="s">
+        <v>66</v>
+      </c>
+      <c r="E319" t="s">
+        <v>40</v>
+      </c>
+      <c r="F319" t="s">
+        <v>849</v>
+      </c>
+      <c r="G319">
+        <v>704.8</v>
+      </c>
+      <c r="H319" t="s">
         <v>850</v>
       </c>
-      <c r="B319" t="s">
-        <v>851</v>
-      </c>
-      <c r="C319" t="s">
-        <v>177</v>
-      </c>
-      <c r="D319" t="s">
-        <v>24</v>
-      </c>
-      <c r="E319" t="s">
-        <v>40</v>
-      </c>
-      <c r="F319" t="s">
-        <v>75</v>
-      </c>
-      <c r="G319">
-        <v>6948.03</v>
-      </c>
-      <c r="H319" t="s">
-        <v>852</v>
-      </c>
       <c r="I319" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J319" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K319" s="1">
-        <v>46081</v>
+        <v>46073</v>
       </c>
       <c r="L319" s="1">
         <v>46235</v>
       </c>
       <c r="M319" s="1">
-        <v>46249</v>
+        <v>46238</v>
       </c>
       <c r="N319">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O319" t="s">
         <v>17</v>
@@ -18179,140 +18192,140 @@
     </row>
     <row r="320" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>509</v>
+        <v>851</v>
       </c>
       <c r="B320" t="s">
-        <v>468</v>
+        <v>852</v>
       </c>
       <c r="C320" t="s">
-        <v>334</v>
+        <v>177</v>
       </c>
       <c r="D320" t="s">
-        <v>333</v>
+        <v>24</v>
       </c>
       <c r="E320" t="s">
         <v>40</v>
       </c>
       <c r="F320" t="s">
-        <v>411</v>
+        <v>75</v>
       </c>
       <c r="G320">
-        <v>24500</v>
+        <v>6948.03</v>
       </c>
       <c r="H320" t="s">
         <v>853</v>
       </c>
       <c r="I320" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J320" t="s">
         <v>595</v>
       </c>
       <c r="K320" s="1">
-        <v>46094</v>
+        <v>46081</v>
       </c>
       <c r="L320" s="1">
         <v>46235</v>
       </c>
       <c r="M320" s="1">
-        <v>46375</v>
+        <v>46249</v>
       </c>
       <c r="N320">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="O320" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="321" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
+        <v>509</v>
+      </c>
+      <c r="B321" t="s">
+        <v>468</v>
+      </c>
+      <c r="C321" t="s">
+        <v>334</v>
+      </c>
+      <c r="D321" t="s">
+        <v>333</v>
+      </c>
+      <c r="E321" t="s">
+        <v>40</v>
+      </c>
+      <c r="F321" t="s">
+        <v>411</v>
+      </c>
+      <c r="G321">
+        <v>24500</v>
+      </c>
+      <c r="H321" t="s">
         <v>854</v>
       </c>
-      <c r="B321" t="s">
-        <v>855</v>
-      </c>
-      <c r="C321" t="s">
-        <v>321</v>
-      </c>
-      <c r="D321" t="s">
-        <v>36</v>
-      </c>
-      <c r="E321" t="s">
-        <v>40</v>
-      </c>
-      <c r="F321" t="s">
-        <v>637</v>
-      </c>
-      <c r="G321">
-        <v>4591</v>
-      </c>
-      <c r="H321" t="s">
-        <v>856</v>
-      </c>
       <c r="I321" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J321" t="s">
         <v>595</v>
       </c>
       <c r="K321" s="1">
-        <v>46112</v>
+        <v>46094</v>
       </c>
       <c r="L321" s="1">
-        <v>46236</v>
+        <v>46235</v>
       </c>
       <c r="M321" s="1">
-        <v>46240</v>
+        <v>46375</v>
       </c>
       <c r="N321">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="O321" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="322" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
+        <v>855</v>
+      </c>
+      <c r="B322" t="s">
+        <v>856</v>
+      </c>
+      <c r="C322" t="s">
+        <v>321</v>
+      </c>
+      <c r="D322" t="s">
+        <v>36</v>
+      </c>
+      <c r="E322" t="s">
+        <v>40</v>
+      </c>
+      <c r="F322" t="s">
+        <v>637</v>
+      </c>
+      <c r="G322">
+        <v>4591</v>
+      </c>
+      <c r="H322" t="s">
         <v>857</v>
       </c>
-      <c r="B322" t="s">
-        <v>858</v>
-      </c>
-      <c r="C322" t="s">
-        <v>71</v>
-      </c>
-      <c r="D322" t="s">
-        <v>70</v>
-      </c>
-      <c r="E322" t="s">
-        <v>40</v>
-      </c>
-      <c r="F322" t="s">
-        <v>75</v>
-      </c>
-      <c r="G322">
-        <v>3621.6</v>
-      </c>
-      <c r="H322" t="s">
-        <v>859</v>
-      </c>
       <c r="I322" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J322" t="s">
         <v>595</v>
       </c>
       <c r="K322" s="1">
-        <v>46145</v>
+        <v>46112</v>
       </c>
       <c r="L322" s="1">
         <v>46236</v>
       </c>
       <c r="M322" s="1">
-        <v>46243</v>
+        <v>46240</v>
       </c>
       <c r="N322">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O322" t="s">
         <v>17</v>
@@ -18320,10 +18333,10 @@
     </row>
     <row r="323" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B323" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C323" t="s">
         <v>71</v>
@@ -18338,28 +18351,28 @@
         <v>75</v>
       </c>
       <c r="G323">
-        <v>1611.82</v>
+        <v>3621.6</v>
       </c>
       <c r="H323" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="I323" t="s">
         <v>69</v>
       </c>
       <c r="J323" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K323" s="1">
-        <v>46131</v>
+        <v>46145</v>
       </c>
       <c r="L323" s="1">
-        <v>46241</v>
+        <v>46236</v>
       </c>
       <c r="M323" s="1">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="N323">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O323" t="s">
         <v>17</v>
@@ -18367,46 +18380,46 @@
     </row>
     <row r="324" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
+        <v>861</v>
+      </c>
+      <c r="B324" t="s">
+        <v>862</v>
+      </c>
+      <c r="C324" t="s">
+        <v>71</v>
+      </c>
+      <c r="D324" t="s">
+        <v>70</v>
+      </c>
+      <c r="E324" t="s">
+        <v>40</v>
+      </c>
+      <c r="F324" t="s">
+        <v>75</v>
+      </c>
+      <c r="G324">
+        <v>1611.82</v>
+      </c>
+      <c r="H324" t="s">
         <v>863</v>
-      </c>
-      <c r="B324" t="s">
-        <v>864</v>
-      </c>
-      <c r="C324" t="s">
-        <v>67</v>
-      </c>
-      <c r="D324" t="s">
-        <v>66</v>
-      </c>
-      <c r="E324" t="s">
-        <v>40</v>
-      </c>
-      <c r="F324" t="s">
-        <v>434</v>
-      </c>
-      <c r="G324">
-        <v>1627.68</v>
-      </c>
-      <c r="H324" t="s">
-        <v>865</v>
       </c>
       <c r="I324" t="s">
         <v>69</v>
       </c>
       <c r="J324" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K324" s="1">
-        <v>46046</v>
+        <v>46131</v>
       </c>
       <c r="L324" s="1">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="M324" s="1">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="N324">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O324" t="s">
         <v>17</v>
@@ -18414,46 +18427,46 @@
     </row>
     <row r="325" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
+        <v>864</v>
+      </c>
+      <c r="B325" t="s">
+        <v>865</v>
+      </c>
+      <c r="C325" t="s">
+        <v>67</v>
+      </c>
+      <c r="D325" t="s">
+        <v>66</v>
+      </c>
+      <c r="E325" t="s">
+        <v>40</v>
+      </c>
+      <c r="F325" t="s">
+        <v>434</v>
+      </c>
+      <c r="G325">
+        <v>1627.68</v>
+      </c>
+      <c r="H325" t="s">
         <v>866</v>
       </c>
-      <c r="B325" t="s">
-        <v>867</v>
-      </c>
-      <c r="C325" t="s">
-        <v>321</v>
-      </c>
-      <c r="D325" t="s">
-        <v>36</v>
-      </c>
-      <c r="E325" t="s">
-        <v>40</v>
-      </c>
-      <c r="F325" t="s">
-        <v>125</v>
-      </c>
-      <c r="G325">
-        <v>11002.2</v>
-      </c>
-      <c r="H325" t="s">
-        <v>868</v>
-      </c>
       <c r="I325" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J325" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K325" s="1">
-        <v>46141</v>
+        <v>46046</v>
       </c>
       <c r="L325" s="1">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="M325" s="1">
-        <v>46257</v>
+        <v>46248</v>
       </c>
       <c r="N325">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O325" t="s">
         <v>17</v>
@@ -18461,13 +18474,13 @@
     </row>
     <row r="326" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B326" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C326" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D326" t="s">
         <v>36</v>
@@ -18479,39 +18492,39 @@
         <v>434</v>
       </c>
       <c r="G326">
-        <v>4336.2</v>
+        <v>7268.08</v>
       </c>
       <c r="H326" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="I326" t="s">
         <v>320</v>
       </c>
       <c r="J326" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K326" s="1">
-        <v>46158</v>
+        <v>46169</v>
       </c>
       <c r="L326" s="1">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="M326" s="1">
-        <v>46252</v>
+        <v>46250</v>
       </c>
       <c r="N326">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O326" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="327" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B327" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C327" t="s">
         <v>321</v>
@@ -18523,10 +18536,10 @@
         <v>40</v>
       </c>
       <c r="F327" t="s">
-        <v>434</v>
+        <v>125</v>
       </c>
       <c r="G327">
-        <v>7399.35</v>
+        <v>11002.2</v>
       </c>
       <c r="H327" t="s">
         <v>872</v>
@@ -18535,130 +18548,130 @@
         <v>320</v>
       </c>
       <c r="J327" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K327" s="1">
-        <v>46160</v>
+        <v>46141</v>
       </c>
       <c r="L327" s="1">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="M327" s="1">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="N327">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O327" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="328" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>251</v>
+        <v>873</v>
       </c>
       <c r="B328" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C328" t="s">
-        <v>17</v>
+        <v>321</v>
       </c>
       <c r="D328" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E328" t="s">
         <v>40</v>
       </c>
       <c r="F328" t="s">
-        <v>75</v>
+        <v>434</v>
       </c>
       <c r="G328">
-        <v>8665</v>
+        <v>4336.2</v>
       </c>
       <c r="H328" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="I328" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J328" t="s">
         <v>22</v>
       </c>
       <c r="K328" s="1">
-        <v>46030</v>
+        <v>46158</v>
       </c>
       <c r="L328" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="M328" s="1">
-        <v>46262</v>
+        <v>46252</v>
       </c>
       <c r="N328">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O328" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="329" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B329" t="s">
+        <v>874</v>
+      </c>
+      <c r="C329" t="s">
+        <v>321</v>
+      </c>
+      <c r="D329" t="s">
+        <v>36</v>
+      </c>
+      <c r="E329" t="s">
+        <v>40</v>
+      </c>
+      <c r="F329" t="s">
+        <v>434</v>
+      </c>
+      <c r="G329">
+        <v>7399.35</v>
+      </c>
+      <c r="H329" t="s">
         <v>876</v>
       </c>
-      <c r="C329" t="s">
-        <v>67</v>
-      </c>
-      <c r="D329" t="s">
-        <v>66</v>
-      </c>
-      <c r="E329" t="s">
-        <v>40</v>
-      </c>
-      <c r="F329" t="s">
-        <v>75</v>
-      </c>
-      <c r="G329">
-        <v>980</v>
-      </c>
-      <c r="H329" t="s">
-        <v>877</v>
-      </c>
       <c r="I329" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J329" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K329" s="1">
-        <v>46048</v>
+        <v>46160</v>
       </c>
       <c r="L329" s="1">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="M329" s="1">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="N329">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O329" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="330" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>763</v>
+        <v>251</v>
       </c>
       <c r="B330" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C330" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="D330" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="E330" t="s">
         <v>40</v>
@@ -18667,28 +18680,28 @@
         <v>75</v>
       </c>
       <c r="G330">
-        <v>982.77</v>
+        <v>8665</v>
       </c>
       <c r="H330" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I330" t="s">
         <v>69</v>
       </c>
       <c r="J330" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K330" s="1">
-        <v>46115</v>
+        <v>46030</v>
       </c>
       <c r="L330" s="1">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="M330" s="1">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="N330">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O330" t="s">
         <v>17</v>
@@ -18696,16 +18709,16 @@
     </row>
     <row r="331" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
+        <v>879</v>
+      </c>
+      <c r="B331" t="s">
         <v>880</v>
       </c>
-      <c r="B331" t="s">
-        <v>881</v>
-      </c>
       <c r="C331" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D331" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E331" t="s">
         <v>40</v>
@@ -18714,28 +18727,28 @@
         <v>75</v>
       </c>
       <c r="G331">
-        <v>2599.9499999999998</v>
+        <v>980</v>
       </c>
       <c r="H331" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="I331" t="s">
         <v>69</v>
       </c>
       <c r="J331" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K331" s="1">
-        <v>46139</v>
+        <v>46048</v>
       </c>
       <c r="L331" s="1">
-        <v>46259</v>
+        <v>46251</v>
       </c>
       <c r="M331" s="1">
-        <v>46264</v>
+        <v>46254</v>
       </c>
       <c r="N331">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O331" t="s">
         <v>17</v>
@@ -18743,96 +18756,96 @@
     </row>
     <row r="332" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
+        <v>764</v>
+      </c>
+      <c r="B332" t="s">
+        <v>882</v>
+      </c>
+      <c r="C332" t="s">
+        <v>105</v>
+      </c>
+      <c r="D332" t="s">
+        <v>66</v>
+      </c>
+      <c r="E332" t="s">
+        <v>40</v>
+      </c>
+      <c r="F332" t="s">
+        <v>75</v>
+      </c>
+      <c r="G332">
+        <v>982.77</v>
+      </c>
+      <c r="H332" t="s">
         <v>883</v>
       </c>
-      <c r="B332" t="s">
-        <v>884</v>
-      </c>
-      <c r="C332" t="s">
-        <v>17</v>
-      </c>
-      <c r="D332" t="s">
-        <v>17</v>
-      </c>
-      <c r="E332" t="s">
-        <v>40</v>
-      </c>
-      <c r="F332" t="s">
-        <v>306</v>
-      </c>
-      <c r="G332">
-        <v>0</v>
-      </c>
-      <c r="H332" t="s">
-        <v>885</v>
-      </c>
       <c r="I332" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J332" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K332" s="1">
-        <v>46140</v>
+        <v>46115</v>
       </c>
       <c r="L332" s="1">
-        <v>46266</v>
+        <v>46252</v>
       </c>
       <c r="M332" s="1">
-        <v>46556</v>
+        <v>46255</v>
       </c>
       <c r="N332">
-        <v>290</v>
+        <v>3</v>
       </c>
       <c r="O332" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="333" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B333" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C333" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D333" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="E333" t="s">
         <v>40</v>
       </c>
       <c r="F333" t="s">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="G333">
-        <v>62837.27</v>
+        <v>2599.9499999999998</v>
       </c>
       <c r="H333" t="s">
         <v>886</v>
       </c>
       <c r="I333" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J333" t="s">
         <v>595</v>
       </c>
       <c r="K333" s="1">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="L333" s="1">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="M333" s="1">
-        <v>46555</v>
+        <v>46264</v>
       </c>
       <c r="N333">
-        <v>289</v>
+        <v>5</v>
       </c>
       <c r="O333" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="334" spans="1:15" x14ac:dyDescent="0.2">
@@ -18843,134 +18856,134 @@
         <v>888</v>
       </c>
       <c r="C334" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="D334" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="E334" t="s">
         <v>40</v>
       </c>
       <c r="F334" t="s">
-        <v>75</v>
+        <v>306</v>
       </c>
       <c r="G334">
-        <v>974.7</v>
+        <v>0</v>
       </c>
       <c r="H334" t="s">
         <v>889</v>
       </c>
       <c r="I334" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J334" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K334" s="1">
-        <v>46069</v>
+        <v>46140</v>
       </c>
       <c r="L334" s="1">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="M334" s="1">
-        <v>46271</v>
+        <v>46556</v>
       </c>
       <c r="N334">
-        <v>3</v>
+        <v>290</v>
       </c>
       <c r="O334" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="335" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
+        <v>887</v>
+      </c>
+      <c r="B335" t="s">
+        <v>888</v>
+      </c>
+      <c r="C335" t="s">
+        <v>25</v>
+      </c>
+      <c r="D335" t="s">
+        <v>24</v>
+      </c>
+      <c r="E335" t="s">
+        <v>40</v>
+      </c>
+      <c r="F335" t="s">
+        <v>306</v>
+      </c>
+      <c r="G335">
+        <v>62837.27</v>
+      </c>
+      <c r="H335" t="s">
         <v>890</v>
       </c>
-      <c r="B335" t="s">
-        <v>891</v>
-      </c>
-      <c r="C335" t="s">
-        <v>105</v>
-      </c>
-      <c r="D335" t="s">
-        <v>66</v>
-      </c>
-      <c r="E335" t="s">
-        <v>40</v>
-      </c>
-      <c r="F335" t="s">
-        <v>75</v>
-      </c>
-      <c r="G335">
-        <v>1092.96</v>
-      </c>
-      <c r="H335" t="s">
-        <v>892</v>
-      </c>
       <c r="I335" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J335" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K335" s="1">
-        <v>46085</v>
+        <v>46140</v>
       </c>
       <c r="L335" s="1">
-        <v>46272</v>
+        <v>46266</v>
       </c>
       <c r="M335" s="1">
-        <v>46275</v>
+        <v>46555</v>
       </c>
       <c r="N335">
-        <v>3</v>
+        <v>289</v>
       </c>
       <c r="O335" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="336" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>803</v>
+        <v>891</v>
       </c>
       <c r="B336" t="s">
+        <v>892</v>
+      </c>
+      <c r="C336" t="s">
+        <v>67</v>
+      </c>
+      <c r="D336" t="s">
+        <v>66</v>
+      </c>
+      <c r="E336" t="s">
+        <v>40</v>
+      </c>
+      <c r="F336" t="s">
+        <v>75</v>
+      </c>
+      <c r="G336">
+        <v>974.7</v>
+      </c>
+      <c r="H336" t="s">
         <v>893</v>
       </c>
-      <c r="C336" t="s">
-        <v>321</v>
-      </c>
-      <c r="D336" t="s">
-        <v>36</v>
-      </c>
-      <c r="E336" t="s">
-        <v>40</v>
-      </c>
-      <c r="F336" t="s">
-        <v>125</v>
-      </c>
-      <c r="G336">
-        <v>1892</v>
-      </c>
-      <c r="H336" t="s">
-        <v>894</v>
-      </c>
       <c r="I336" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J336" t="s">
         <v>595</v>
       </c>
       <c r="K336" s="1">
-        <v>46108</v>
+        <v>46069</v>
       </c>
       <c r="L336" s="1">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="M336" s="1">
-        <v>46279</v>
+        <v>46271</v>
       </c>
       <c r="N336">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O336" t="s">
         <v>17</v>
@@ -18978,28 +18991,28 @@
     </row>
     <row r="337" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
+        <v>894</v>
+      </c>
+      <c r="B337" t="s">
         <v>895</v>
       </c>
-      <c r="B337" t="s">
+      <c r="C337" t="s">
+        <v>105</v>
+      </c>
+      <c r="D337" t="s">
+        <v>66</v>
+      </c>
+      <c r="E337" t="s">
+        <v>40</v>
+      </c>
+      <c r="F337" t="s">
+        <v>75</v>
+      </c>
+      <c r="G337">
+        <v>1092.96</v>
+      </c>
+      <c r="H337" t="s">
         <v>896</v>
-      </c>
-      <c r="C337" t="s">
-        <v>71</v>
-      </c>
-      <c r="D337" t="s">
-        <v>70</v>
-      </c>
-      <c r="E337" t="s">
-        <v>40</v>
-      </c>
-      <c r="F337" t="s">
-        <v>306</v>
-      </c>
-      <c r="G337">
-        <v>1594268</v>
-      </c>
-      <c r="H337" t="s">
-        <v>897</v>
       </c>
       <c r="I337" t="s">
         <v>69</v>
@@ -19008,66 +19021,66 @@
         <v>22</v>
       </c>
       <c r="K337" s="1">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="L337" s="1">
-        <v>46284</v>
+        <v>46272</v>
       </c>
       <c r="M337" s="1">
-        <v>46544</v>
+        <v>46275</v>
       </c>
       <c r="N337">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="O337" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="338" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>895</v>
+        <v>804</v>
       </c>
       <c r="B338" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C338" t="s">
-        <v>71</v>
+        <v>321</v>
       </c>
       <c r="D338" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="E338" t="s">
         <v>40</v>
       </c>
       <c r="F338" t="s">
-        <v>306</v>
+        <v>125</v>
       </c>
       <c r="G338">
-        <v>81900</v>
+        <v>1892</v>
       </c>
       <c r="H338" t="s">
         <v>898</v>
       </c>
       <c r="I338" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J338" t="s">
         <v>595</v>
       </c>
       <c r="K338" s="1">
-        <v>46078</v>
+        <v>46108</v>
       </c>
       <c r="L338" s="1">
-        <v>46284</v>
+        <v>46275</v>
       </c>
       <c r="M338" s="1">
-        <v>46544</v>
+        <v>46279</v>
       </c>
       <c r="N338">
-        <v>260</v>
+        <v>4</v>
       </c>
       <c r="O338" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="339" spans="1:15" x14ac:dyDescent="0.2">
@@ -19075,13 +19088,13 @@
         <v>899</v>
       </c>
       <c r="B339" t="s">
-        <v>305</v>
+        <v>900</v>
       </c>
       <c r="C339" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D339" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E339" t="s">
         <v>40</v>
@@ -19090,19 +19103,19 @@
         <v>306</v>
       </c>
       <c r="G339">
-        <v>40957.800000000003</v>
+        <v>1594268</v>
       </c>
       <c r="H339" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="I339" t="s">
         <v>69</v>
       </c>
       <c r="J339" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K339" s="1">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="L339" s="1">
         <v>46284</v>
@@ -19119,16 +19132,16 @@
     </row>
     <row r="340" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B340" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C340" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="D340" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E340" t="s">
         <v>40</v>
@@ -19137,10 +19150,10 @@
         <v>306</v>
       </c>
       <c r="G340">
-        <v>41080</v>
+        <v>81900</v>
       </c>
       <c r="H340" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I340" t="s">
         <v>69</v>
@@ -19149,7 +19162,7 @@
         <v>595</v>
       </c>
       <c r="K340" s="1">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="L340" s="1">
         <v>46284</v>
@@ -19166,49 +19179,49 @@
     </row>
     <row r="341" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>63</v>
+        <v>903</v>
       </c>
       <c r="B341" t="s">
-        <v>31</v>
+        <v>305</v>
       </c>
       <c r="C341" t="s">
-        <v>212</v>
+        <v>67</v>
       </c>
       <c r="D341" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E341" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F341" t="s">
-        <v>17</v>
+        <v>306</v>
       </c>
       <c r="G341">
-        <v>1487</v>
+        <v>40957.800000000003</v>
       </c>
       <c r="H341" t="s">
         <v>904</v>
       </c>
       <c r="I341" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J341" t="s">
         <v>595</v>
       </c>
       <c r="K341" s="1">
-        <v>46099</v>
+        <v>46084</v>
       </c>
       <c r="L341" s="1">
-        <v>46286</v>
+        <v>46284</v>
       </c>
       <c r="M341" s="1">
-        <v>46290</v>
+        <v>46544</v>
       </c>
       <c r="N341">
-        <v>4</v>
+        <v>260</v>
       </c>
       <c r="O341" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="342" spans="1:15" x14ac:dyDescent="0.2">
@@ -19219,87 +19232,87 @@
         <v>906</v>
       </c>
       <c r="C342" t="s">
-        <v>321</v>
+        <v>105</v>
       </c>
       <c r="D342" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="E342" t="s">
         <v>40</v>
       </c>
       <c r="F342" t="s">
-        <v>434</v>
+        <v>306</v>
       </c>
       <c r="G342">
-        <v>13630.5</v>
+        <v>41080</v>
       </c>
       <c r="H342" t="s">
         <v>907</v>
       </c>
       <c r="I342" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J342" t="s">
         <v>595</v>
       </c>
       <c r="K342" s="1">
-        <v>46144</v>
+        <v>46134</v>
       </c>
       <c r="L342" s="1">
-        <v>46286</v>
+        <v>46284</v>
       </c>
       <c r="M342" s="1">
-        <v>46301</v>
+        <v>46544</v>
       </c>
       <c r="N342">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="O342" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="343" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
+        <v>63</v>
+      </c>
+      <c r="B343" t="s">
+        <v>31</v>
+      </c>
+      <c r="C343" t="s">
+        <v>212</v>
+      </c>
+      <c r="D343" t="s">
+        <v>24</v>
+      </c>
+      <c r="E343" t="s">
+        <v>19</v>
+      </c>
+      <c r="F343" t="s">
+        <v>17</v>
+      </c>
+      <c r="G343">
+        <v>1487</v>
+      </c>
+      <c r="H343" t="s">
         <v>908</v>
       </c>
-      <c r="B343" t="s">
-        <v>909</v>
-      </c>
-      <c r="C343" t="s">
-        <v>73</v>
-      </c>
-      <c r="D343" t="s">
-        <v>74</v>
-      </c>
-      <c r="E343" t="s">
-        <v>40</v>
-      </c>
-      <c r="F343" t="s">
-        <v>75</v>
-      </c>
-      <c r="G343">
-        <v>918</v>
-      </c>
-      <c r="H343" t="s">
-        <v>910</v>
-      </c>
       <c r="I343" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J343" t="s">
         <v>595</v>
       </c>
       <c r="K343" s="1">
-        <v>46075</v>
+        <v>46099</v>
       </c>
       <c r="L343" s="1">
+        <v>46286</v>
+      </c>
+      <c r="M343" s="1">
         <v>46290</v>
       </c>
-      <c r="M343" s="1">
-        <v>46293</v>
-      </c>
       <c r="N343">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O343" t="s">
         <v>17</v>
@@ -19307,46 +19320,46 @@
     </row>
     <row r="344" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>373</v>
+        <v>909</v>
       </c>
       <c r="B344" t="s">
+        <v>910</v>
+      </c>
+      <c r="C344" t="s">
+        <v>321</v>
+      </c>
+      <c r="D344" t="s">
+        <v>36</v>
+      </c>
+      <c r="E344" t="s">
+        <v>40</v>
+      </c>
+      <c r="F344" t="s">
+        <v>434</v>
+      </c>
+      <c r="G344">
+        <v>13630.5</v>
+      </c>
+      <c r="H344" t="s">
         <v>911</v>
       </c>
-      <c r="C344" t="s">
-        <v>17</v>
-      </c>
-      <c r="D344" t="s">
-        <v>17</v>
-      </c>
-      <c r="E344" t="s">
-        <v>40</v>
-      </c>
-      <c r="F344" t="s">
-        <v>125</v>
-      </c>
-      <c r="G344">
-        <v>1395.99</v>
-      </c>
-      <c r="H344" t="s">
-        <v>912</v>
-      </c>
       <c r="I344" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J344" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K344" s="1">
-        <v>45989</v>
+        <v>46144</v>
       </c>
       <c r="L344" s="1">
-        <v>46330</v>
+        <v>46286</v>
       </c>
       <c r="M344" s="1">
-        <v>46333</v>
+        <v>46301</v>
       </c>
       <c r="N344">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O344" t="s">
         <v>17</v>
@@ -19354,46 +19367,46 @@
     </row>
     <row r="345" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
+        <v>912</v>
+      </c>
+      <c r="B345" t="s">
         <v>913</v>
       </c>
-      <c r="B345" t="s">
+      <c r="C345" t="s">
+        <v>73</v>
+      </c>
+      <c r="D345" t="s">
+        <v>74</v>
+      </c>
+      <c r="E345" t="s">
+        <v>40</v>
+      </c>
+      <c r="F345" t="s">
+        <v>75</v>
+      </c>
+      <c r="G345">
+        <v>918</v>
+      </c>
+      <c r="H345" t="s">
         <v>914</v>
       </c>
-      <c r="C345" t="s">
-        <v>346</v>
-      </c>
-      <c r="D345" t="s">
-        <v>344</v>
-      </c>
-      <c r="E345" t="s">
-        <v>40</v>
-      </c>
-      <c r="F345" t="s">
-        <v>125</v>
-      </c>
-      <c r="G345">
-        <v>1872.8</v>
-      </c>
-      <c r="H345" t="s">
-        <v>915</v>
-      </c>
       <c r="I345" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J345" t="s">
         <v>595</v>
       </c>
       <c r="K345" s="1">
-        <v>46120</v>
+        <v>46075</v>
       </c>
       <c r="L345" s="1">
-        <v>46375</v>
+        <v>46290</v>
       </c>
       <c r="M345" s="1">
-        <v>46379</v>
+        <v>46293</v>
       </c>
       <c r="N345">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O345" t="s">
         <v>17</v>
@@ -19401,16 +19414,16 @@
     </row>
     <row r="346" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>916</v>
+        <v>373</v>
       </c>
       <c r="B346" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C346" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="D346" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="E346" t="s">
         <v>40</v>
@@ -19419,28 +19432,28 @@
         <v>125</v>
       </c>
       <c r="G346">
-        <v>3370</v>
+        <v>1395.99</v>
       </c>
       <c r="H346" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="I346" t="s">
         <v>69</v>
       </c>
       <c r="J346" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K346" s="1">
-        <v>46106</v>
+        <v>45989</v>
       </c>
       <c r="L346" s="1">
-        <v>46385</v>
+        <v>46330</v>
       </c>
       <c r="M346" s="1">
-        <v>46389</v>
+        <v>46333</v>
       </c>
       <c r="N346">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O346" t="s">
         <v>17</v>
@@ -19448,10 +19461,10 @@
     </row>
     <row r="347" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B347" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C347" t="s">
         <v>346</v>
@@ -19466,10 +19479,10 @@
         <v>125</v>
       </c>
       <c r="G347">
-        <v>1272</v>
+        <v>1872.8</v>
       </c>
       <c r="H347" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="I347" t="s">
         <v>320</v>
@@ -19481,13 +19494,13 @@
         <v>46120</v>
       </c>
       <c r="L347" s="1">
-        <v>46385</v>
+        <v>46375</v>
       </c>
       <c r="M347" s="1">
-        <v>46388</v>
+        <v>46379</v>
       </c>
       <c r="N347">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O347" t="s">
         <v>17</v>
@@ -19495,13 +19508,13 @@
     </row>
     <row r="348" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B348" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C348" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D348" t="s">
         <v>74</v>
@@ -19513,10 +19526,10 @@
         <v>125</v>
       </c>
       <c r="G348">
-        <v>2300</v>
+        <v>3370</v>
       </c>
       <c r="H348" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="I348" t="s">
         <v>69</v>
@@ -19525,13 +19538,13 @@
         <v>595</v>
       </c>
       <c r="K348" s="1">
-        <v>46141</v>
+        <v>46106</v>
       </c>
       <c r="L348" s="1">
-        <v>46582</v>
+        <v>46385</v>
       </c>
       <c r="M348" s="1">
-        <v>46586</v>
+        <v>46389</v>
       </c>
       <c r="N348">
         <v>4</v>
@@ -19542,16 +19555,16 @@
     </row>
     <row r="349" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B349" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C349" t="s">
-        <v>83</v>
+        <v>346</v>
       </c>
       <c r="D349" t="s">
-        <v>74</v>
+        <v>344</v>
       </c>
       <c r="E349" t="s">
         <v>40</v>
@@ -19560,30 +19573,124 @@
         <v>125</v>
       </c>
       <c r="G349">
+        <v>1272</v>
+      </c>
+      <c r="H349" t="s">
+        <v>925</v>
+      </c>
+      <c r="I349" t="s">
+        <v>320</v>
+      </c>
+      <c r="J349" t="s">
+        <v>595</v>
+      </c>
+      <c r="K349" s="1">
+        <v>46120</v>
+      </c>
+      <c r="L349" s="1">
+        <v>46385</v>
+      </c>
+      <c r="M349" s="1">
+        <v>46388</v>
+      </c>
+      <c r="N349">
+        <v>3</v>
+      </c>
+      <c r="O349" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="350" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A350" t="s">
+        <v>926</v>
+      </c>
+      <c r="B350" t="s">
+        <v>927</v>
+      </c>
+      <c r="C350" t="s">
+        <v>83</v>
+      </c>
+      <c r="D350" t="s">
+        <v>74</v>
+      </c>
+      <c r="E350" t="s">
+        <v>40</v>
+      </c>
+      <c r="F350" t="s">
+        <v>125</v>
+      </c>
+      <c r="G350">
+        <v>2300</v>
+      </c>
+      <c r="H350" t="s">
+        <v>928</v>
+      </c>
+      <c r="I350" t="s">
+        <v>69</v>
+      </c>
+      <c r="J350" t="s">
+        <v>595</v>
+      </c>
+      <c r="K350" s="1">
+        <v>46141</v>
+      </c>
+      <c r="L350" s="1">
+        <v>46582</v>
+      </c>
+      <c r="M350" s="1">
+        <v>46586</v>
+      </c>
+      <c r="N350">
+        <v>4</v>
+      </c>
+      <c r="O350" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="351" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A351" t="s">
+        <v>929</v>
+      </c>
+      <c r="B351" t="s">
+        <v>930</v>
+      </c>
+      <c r="C351" t="s">
+        <v>83</v>
+      </c>
+      <c r="D351" t="s">
+        <v>74</v>
+      </c>
+      <c r="E351" t="s">
+        <v>40</v>
+      </c>
+      <c r="F351" t="s">
+        <v>125</v>
+      </c>
+      <c r="G351">
         <v>4829.9399999999996</v>
       </c>
-      <c r="H349" t="s">
-        <v>927</v>
-      </c>
-      <c r="I349" t="s">
+      <c r="H351" t="s">
+        <v>931</v>
+      </c>
+      <c r="I351" t="s">
         <v>69</v>
       </c>
-      <c r="J349" t="s">
+      <c r="J351" t="s">
         <v>22</v>
       </c>
-      <c r="K349" s="1">
+      <c r="K351" s="1">
         <v>46147</v>
       </c>
-      <c r="L349" s="1">
+      <c r="L351" s="1">
         <v>46744</v>
       </c>
-      <c r="M349" s="1">
+      <c r="M351" s="1">
         <v>46753</v>
       </c>
-      <c r="N349">
+      <c r="N351">
         <v>9</v>
       </c>
-      <c r="O349" t="s">
+      <c r="O351" t="s">
         <v>17</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7F620D0-2F07-A440-A8B0-9FB7F2D77D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65EF83BE-49A5-9445-8823-A8F8B6597087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="22800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3515" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3565" uniqueCount="943">
   <si>
     <t>First name</t>
   </si>
@@ -2066,6 +2066,9 @@
     <t>LZGTFJNU-1</t>
   </si>
   <si>
+    <t>JMFMFTRQ-1</t>
+  </si>
+  <si>
     <t>Yevhenii</t>
   </si>
   <si>
@@ -2075,6 +2078,15 @@
     <t>CQTFJMJO-1</t>
   </si>
   <si>
+    <t>Haly-Mat</t>
+  </si>
+  <si>
+    <t>Said</t>
+  </si>
+  <si>
+    <t>PSVWXHLZ-1</t>
+  </si>
+  <si>
     <t>Mohammad</t>
   </si>
   <si>
@@ -2138,6 +2150,15 @@
     <t>NHCYWTJA-1</t>
   </si>
   <si>
+    <t>Chanika</t>
+  </si>
+  <si>
+    <t>Simms</t>
+  </si>
+  <si>
+    <t>NGHBJFBL-1</t>
+  </si>
+  <si>
     <t>Manjul</t>
   </si>
   <si>
@@ -2489,6 +2510,15 @@
     <t>ZITOIOCT-1</t>
   </si>
   <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>Golda</t>
+  </si>
+  <si>
+    <t>BFIYBJBM-1</t>
+  </si>
+  <si>
     <t>Inkster</t>
   </si>
   <si>
@@ -2646,6 +2676,9 @@
   </si>
   <si>
     <t>RERLYAOB-1</t>
+  </si>
+  <si>
+    <t>EXGZHTNK-1</t>
   </si>
   <si>
     <t>Al-Malki</t>
@@ -3188,13 +3221,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O351"/>
+  <dimension ref="A1:O356"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="10" width="15" customWidth="1"/>
     <col min="11" max="13" width="15" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="15.6640625" customWidth="1"/>
+    <col min="14" max="15" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -14224,7 +14256,7 @@
         <v>21</v>
       </c>
       <c r="J235" t="s">
-        <v>455</v>
+        <v>34</v>
       </c>
       <c r="K235" s="1">
         <v>46161</v>
@@ -14412,7 +14444,7 @@
         <v>69</v>
       </c>
       <c r="J239" t="s">
-        <v>595</v>
+        <v>455</v>
       </c>
       <c r="K239" s="1">
         <v>46159</v>
@@ -14521,7 +14553,7 @@
         <v>1</v>
       </c>
       <c r="O241" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.2">
@@ -14996,16 +15028,16 @@
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>683</v>
+        <v>633</v>
       </c>
       <c r="B252" t="s">
-        <v>684</v>
+        <v>632</v>
       </c>
       <c r="C252" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D252" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="E252" t="s">
         <v>225</v>
@@ -15014,28 +15046,28 @@
         <v>17</v>
       </c>
       <c r="G252">
-        <v>12213</v>
+        <v>2060</v>
       </c>
       <c r="H252" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I252" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J252" t="s">
         <v>595</v>
       </c>
       <c r="K252" s="1">
-        <v>46131</v>
+        <v>46170</v>
       </c>
       <c r="L252" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="M252" s="1">
-        <v>46186</v>
+        <v>46181</v>
       </c>
       <c r="N252">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O252" t="s">
         <v>17</v>
@@ -15043,43 +15075,43 @@
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
+        <v>684</v>
+      </c>
+      <c r="B253" t="s">
+        <v>685</v>
+      </c>
+      <c r="C253" t="s">
+        <v>58</v>
+      </c>
+      <c r="D253" t="s">
+        <v>36</v>
+      </c>
+      <c r="E253" t="s">
+        <v>225</v>
+      </c>
+      <c r="F253" t="s">
+        <v>17</v>
+      </c>
+      <c r="G253">
+        <v>12213</v>
+      </c>
+      <c r="H253" t="s">
         <v>686</v>
-      </c>
-      <c r="B253" t="s">
-        <v>687</v>
-      </c>
-      <c r="C253" t="s">
-        <v>32</v>
-      </c>
-      <c r="D253" t="s">
-        <v>18</v>
-      </c>
-      <c r="E253" t="s">
-        <v>40</v>
-      </c>
-      <c r="F253" t="s">
-        <v>75</v>
-      </c>
-      <c r="G253">
-        <v>8718.44</v>
-      </c>
-      <c r="H253" t="s">
-        <v>688</v>
       </c>
       <c r="I253" t="s">
         <v>21</v>
       </c>
       <c r="J253" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K253" s="1">
-        <v>46080</v>
+        <v>46131</v>
       </c>
       <c r="L253" s="1">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="M253" s="1">
-        <v>46189</v>
+        <v>46186</v>
       </c>
       <c r="N253">
         <v>9</v>
@@ -15090,16 +15122,16 @@
     </row>
     <row r="254" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B254" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C254" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="D254" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E254" t="s">
         <v>40</v>
@@ -15108,28 +15140,28 @@
         <v>75</v>
       </c>
       <c r="G254">
-        <v>4871.9799999999996</v>
+        <v>766.8</v>
       </c>
       <c r="H254" t="s">
         <v>689</v>
       </c>
       <c r="I254" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J254" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K254" s="1">
-        <v>46080</v>
+        <v>46171</v>
       </c>
       <c r="L254" s="1">
-        <v>46180</v>
+        <v>46179</v>
       </c>
       <c r="M254" s="1">
-        <v>46189</v>
+        <v>46182</v>
       </c>
       <c r="N254">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O254" t="s">
         <v>17</v>
@@ -15137,16 +15169,16 @@
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B255" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C255" t="s">
-        <v>212</v>
+        <v>32</v>
       </c>
       <c r="D255" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E255" t="s">
         <v>40</v>
@@ -15155,10 +15187,10 @@
         <v>75</v>
       </c>
       <c r="G255">
-        <v>4871.9799999999996</v>
+        <v>8718.44</v>
       </c>
       <c r="H255" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="I255" t="s">
         <v>21</v>
@@ -15184,25 +15216,25 @@
     </row>
     <row r="256" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
+        <v>690</v>
+      </c>
+      <c r="B256" t="s">
         <v>691</v>
       </c>
-      <c r="B256" t="s">
-        <v>692</v>
-      </c>
       <c r="C256" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="D256" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E256" t="s">
         <v>40</v>
       </c>
       <c r="F256" t="s">
-        <v>571</v>
+        <v>75</v>
       </c>
       <c r="G256">
-        <v>12534.62</v>
+        <v>4871.9799999999996</v>
       </c>
       <c r="H256" t="s">
         <v>693</v>
@@ -15214,16 +15246,16 @@
         <v>22</v>
       </c>
       <c r="K256" s="1">
-        <v>46148</v>
+        <v>46080</v>
       </c>
       <c r="L256" s="1">
         <v>46180</v>
       </c>
       <c r="M256" s="1">
-        <v>46187</v>
+        <v>46189</v>
       </c>
       <c r="N256">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O256" t="s">
         <v>17</v>
@@ -15231,93 +15263,93 @@
     </row>
     <row r="257" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B257" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C257" t="s">
-        <v>25</v>
+        <v>212</v>
       </c>
       <c r="D257" t="s">
         <v>24</v>
       </c>
       <c r="E257" t="s">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="F257" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="G257">
-        <v>1832</v>
+        <v>4871.9799999999996</v>
       </c>
       <c r="H257" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="I257" t="s">
         <v>21</v>
       </c>
       <c r="J257" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K257" s="1">
-        <v>46161</v>
+        <v>46080</v>
       </c>
       <c r="L257" s="1">
         <v>46180</v>
       </c>
       <c r="M257" s="1">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="N257">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O257" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="258" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
+        <v>695</v>
+      </c>
+      <c r="B258" t="s">
+        <v>696</v>
+      </c>
+      <c r="C258" t="s">
+        <v>151</v>
+      </c>
+      <c r="D258" t="s">
+        <v>39</v>
+      </c>
+      <c r="E258" t="s">
+        <v>40</v>
+      </c>
+      <c r="F258" t="s">
+        <v>571</v>
+      </c>
+      <c r="G258">
+        <v>12534.62</v>
+      </c>
+      <c r="H258" t="s">
         <v>697</v>
       </c>
-      <c r="B258" t="s">
-        <v>698</v>
-      </c>
-      <c r="C258" t="s">
-        <v>105</v>
-      </c>
-      <c r="D258" t="s">
-        <v>66</v>
-      </c>
-      <c r="E258" t="s">
-        <v>40</v>
-      </c>
-      <c r="F258" t="s">
-        <v>75</v>
-      </c>
-      <c r="G258">
-        <v>2505.6</v>
-      </c>
-      <c r="H258" t="s">
-        <v>699</v>
-      </c>
       <c r="I258" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J258" t="s">
         <v>22</v>
       </c>
       <c r="K258" s="1">
-        <v>46051</v>
+        <v>46148</v>
       </c>
       <c r="L258" s="1">
-        <v>46181</v>
+        <v>46180</v>
       </c>
       <c r="M258" s="1">
-        <v>46189</v>
+        <v>46187</v>
       </c>
       <c r="N258">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O258" t="s">
         <v>17</v>
@@ -15325,49 +15357,49 @@
     </row>
     <row r="259" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B259" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C259" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E259" t="s">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="F259" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="G259">
-        <v>2613.6</v>
+        <v>1832</v>
       </c>
       <c r="H259" t="s">
         <v>700</v>
       </c>
       <c r="I259" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J259" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K259" s="1">
-        <v>46071</v>
+        <v>46161</v>
       </c>
       <c r="L259" s="1">
-        <v>46181</v>
+        <v>46180</v>
       </c>
       <c r="M259" s="1">
-        <v>46189</v>
+        <v>46184</v>
       </c>
       <c r="N259">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O259" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="260" spans="1:15" x14ac:dyDescent="0.2">
@@ -15378,40 +15410,40 @@
         <v>702</v>
       </c>
       <c r="C260" t="s">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="D260" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E260" t="s">
         <v>40</v>
       </c>
       <c r="F260" t="s">
-        <v>390</v>
+        <v>75</v>
       </c>
       <c r="G260">
-        <v>1419.44</v>
+        <v>2505.6</v>
       </c>
       <c r="H260" t="s">
         <v>703</v>
       </c>
       <c r="I260" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J260" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K260" s="1">
-        <v>46161</v>
+        <v>46051</v>
       </c>
       <c r="L260" s="1">
         <v>46181</v>
       </c>
       <c r="M260" s="1">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="N260">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O260" t="s">
         <v>17</v>
@@ -15419,16 +15451,16 @@
     </row>
     <row r="261" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B261" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C261" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D261" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="E261" t="s">
         <v>40</v>
@@ -15437,57 +15469,57 @@
         <v>75</v>
       </c>
       <c r="G261">
-        <v>6317.1</v>
+        <v>2613.6</v>
       </c>
       <c r="H261" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="I261" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J261" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K261" s="1">
-        <v>46165</v>
+        <v>46071</v>
       </c>
       <c r="L261" s="1">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="M261" s="1">
         <v>46189</v>
       </c>
       <c r="N261">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O261" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="262" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
+        <v>705</v>
+      </c>
+      <c r="B262" t="s">
+        <v>706</v>
+      </c>
+      <c r="C262" t="s">
+        <v>212</v>
+      </c>
+      <c r="D262" t="s">
+        <v>24</v>
+      </c>
+      <c r="E262" t="s">
+        <v>40</v>
+      </c>
+      <c r="F262" t="s">
+        <v>390</v>
+      </c>
+      <c r="G262">
+        <v>1419.44</v>
+      </c>
+      <c r="H262" t="s">
         <v>707</v>
-      </c>
-      <c r="B262" t="s">
-        <v>708</v>
-      </c>
-      <c r="C262" t="s">
-        <v>151</v>
-      </c>
-      <c r="D262" t="s">
-        <v>39</v>
-      </c>
-      <c r="E262" t="s">
-        <v>225</v>
-      </c>
-      <c r="F262" t="s">
-        <v>17</v>
-      </c>
-      <c r="G262">
-        <v>7428</v>
-      </c>
-      <c r="H262" t="s">
-        <v>709</v>
       </c>
       <c r="I262" t="s">
         <v>21</v>
@@ -15496,13 +15528,13 @@
         <v>595</v>
       </c>
       <c r="K262" s="1">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="L262" s="1">
-        <v>46186</v>
+        <v>46181</v>
       </c>
       <c r="M262" s="1">
-        <v>46190</v>
+        <v>46185</v>
       </c>
       <c r="N262">
         <v>4</v>
@@ -15513,90 +15545,90 @@
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>107</v>
+        <v>708</v>
       </c>
       <c r="B263" t="s">
-        <v>108</v>
+        <v>709</v>
       </c>
       <c r="C263" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="D263" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E263" t="s">
         <v>40</v>
       </c>
       <c r="F263" t="s">
-        <v>390</v>
+        <v>75</v>
       </c>
       <c r="G263">
-        <v>1942.62</v>
+        <v>6317.1</v>
       </c>
       <c r="H263" t="s">
         <v>710</v>
       </c>
       <c r="I263" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J263" t="s">
         <v>595</v>
       </c>
       <c r="K263" s="1">
-        <v>46109</v>
+        <v>46165</v>
       </c>
       <c r="L263" s="1">
-        <v>46187</v>
+        <v>46182</v>
       </c>
       <c r="M263" s="1">
-        <v>46193</v>
+        <v>46189</v>
       </c>
       <c r="N263">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O263" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>43</v>
+        <v>711</v>
       </c>
       <c r="B264" t="s">
-        <v>43</v>
+        <v>712</v>
       </c>
       <c r="C264" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="D264" t="s">
         <v>66</v>
       </c>
       <c r="E264" t="s">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="F264" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="G264">
-        <v>1230</v>
+        <v>750.6</v>
       </c>
       <c r="H264" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="I264" t="s">
         <v>69</v>
       </c>
       <c r="J264" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K264" s="1">
-        <v>46059</v>
+        <v>46170</v>
       </c>
       <c r="L264" s="1">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="M264" s="1">
-        <v>46191</v>
+        <v>46186</v>
       </c>
       <c r="N264">
         <v>3</v>
@@ -15607,46 +15639,46 @@
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B265" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C265" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="D265" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="E265" t="s">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="F265" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="G265">
-        <v>3979.21</v>
+        <v>7428</v>
       </c>
       <c r="H265" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="I265" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J265" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K265" s="1">
-        <v>46101</v>
+        <v>46154</v>
       </c>
       <c r="L265" s="1">
-        <v>46188</v>
+        <v>46186</v>
       </c>
       <c r="M265" s="1">
-        <v>46199</v>
+        <v>46190</v>
       </c>
       <c r="N265">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O265" t="s">
         <v>17</v>
@@ -15654,25 +15686,25 @@
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>715</v>
+        <v>107</v>
       </c>
       <c r="B266" t="s">
-        <v>716</v>
+        <v>108</v>
       </c>
       <c r="C266" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="D266" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E266" t="s">
         <v>40</v>
       </c>
       <c r="F266" t="s">
-        <v>75</v>
+        <v>390</v>
       </c>
       <c r="G266">
-        <v>6416.09</v>
+        <v>1942.62</v>
       </c>
       <c r="H266" t="s">
         <v>717</v>
@@ -15681,19 +15713,19 @@
         <v>69</v>
       </c>
       <c r="J266" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K266" s="1">
-        <v>46141</v>
+        <v>46109</v>
       </c>
       <c r="L266" s="1">
-        <v>46188</v>
+        <v>46187</v>
       </c>
       <c r="M266" s="1">
-        <v>46198</v>
+        <v>46193</v>
       </c>
       <c r="N266">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O266" t="s">
         <v>17</v>
@@ -15701,46 +15733,46 @@
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
+        <v>43</v>
+      </c>
+      <c r="B267" t="s">
+        <v>43</v>
+      </c>
+      <c r="C267" t="s">
+        <v>67</v>
+      </c>
+      <c r="D267" t="s">
+        <v>66</v>
+      </c>
+      <c r="E267" t="s">
+        <v>225</v>
+      </c>
+      <c r="F267" t="s">
+        <v>17</v>
+      </c>
+      <c r="G267">
+        <v>1230</v>
+      </c>
+      <c r="H267" t="s">
         <v>718</v>
       </c>
-      <c r="B267" t="s">
-        <v>719</v>
-      </c>
-      <c r="C267" t="s">
-        <v>32</v>
-      </c>
-      <c r="D267" t="s">
-        <v>18</v>
-      </c>
-      <c r="E267" t="s">
-        <v>40</v>
-      </c>
-      <c r="F267" t="s">
-        <v>434</v>
-      </c>
-      <c r="G267">
-        <v>8458.17</v>
-      </c>
-      <c r="H267" t="s">
-        <v>720</v>
-      </c>
       <c r="I267" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J267" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K267" s="1">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="L267" s="1">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="M267" s="1">
-        <v>46196</v>
+        <v>46191</v>
       </c>
       <c r="N267">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O267" t="s">
         <v>17</v>
@@ -15748,46 +15780,46 @@
     </row>
     <row r="268" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
+        <v>719</v>
+      </c>
+      <c r="B268" t="s">
+        <v>720</v>
+      </c>
+      <c r="C268" t="s">
+        <v>105</v>
+      </c>
+      <c r="D268" t="s">
+        <v>66</v>
+      </c>
+      <c r="E268" t="s">
+        <v>40</v>
+      </c>
+      <c r="F268" t="s">
+        <v>75</v>
+      </c>
+      <c r="G268">
+        <v>3979.21</v>
+      </c>
+      <c r="H268" t="s">
         <v>721</v>
       </c>
-      <c r="B268" t="s">
-        <v>636</v>
-      </c>
-      <c r="C268" t="s">
-        <v>321</v>
-      </c>
-      <c r="D268" t="s">
-        <v>36</v>
-      </c>
-      <c r="E268" t="s">
-        <v>225</v>
-      </c>
-      <c r="F268" t="s">
-        <v>17</v>
-      </c>
-      <c r="G268">
-        <v>5712</v>
-      </c>
-      <c r="H268" t="s">
-        <v>722</v>
-      </c>
       <c r="I268" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J268" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K268" s="1">
-        <v>46139</v>
+        <v>46101</v>
       </c>
       <c r="L268" s="1">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="M268" s="1">
-        <v>46194</v>
+        <v>46199</v>
       </c>
       <c r="N268">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O268" t="s">
         <v>17</v>
@@ -15795,13 +15827,13 @@
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>91</v>
+        <v>722</v>
       </c>
       <c r="B269" t="s">
         <v>723</v>
       </c>
       <c r="C269" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D269" t="s">
         <v>74</v>
@@ -15810,10 +15842,10 @@
         <v>40</v>
       </c>
       <c r="F269" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="G269">
-        <v>3680</v>
+        <v>6416.09</v>
       </c>
       <c r="H269" t="s">
         <v>724</v>
@@ -15822,22 +15854,22 @@
         <v>69</v>
       </c>
       <c r="J269" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K269" s="1">
-        <v>46156</v>
+        <v>46141</v>
       </c>
       <c r="L269" s="1">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="M269" s="1">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="N269">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O269" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.2">
@@ -15848,19 +15880,19 @@
         <v>726</v>
       </c>
       <c r="C270" t="s">
-        <v>212</v>
+        <v>32</v>
       </c>
       <c r="D270" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E270" t="s">
         <v>40</v>
       </c>
       <c r="F270" t="s">
-        <v>75</v>
+        <v>434</v>
       </c>
       <c r="G270">
-        <v>2877.3</v>
+        <v>8458.17</v>
       </c>
       <c r="H270" t="s">
         <v>727</v>
@@ -15872,16 +15904,16 @@
         <v>595</v>
       </c>
       <c r="K270" s="1">
-        <v>46165</v>
+        <v>46057</v>
       </c>
       <c r="L270" s="1">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="M270" s="1">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="N270">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O270" t="s">
         <v>17</v>
@@ -15889,46 +15921,46 @@
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>23</v>
+        <v>728</v>
       </c>
       <c r="B271" t="s">
-        <v>23</v>
+        <v>636</v>
       </c>
       <c r="C271" t="s">
-        <v>17</v>
+        <v>321</v>
       </c>
       <c r="D271" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E271" t="s">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="F271" t="s">
-        <v>567</v>
+        <v>17</v>
       </c>
       <c r="G271">
-        <v>2123.1999999999998</v>
+        <v>5712</v>
       </c>
       <c r="H271" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I271" t="s">
         <v>320</v>
       </c>
       <c r="J271" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K271" s="1">
-        <v>46101</v>
+        <v>46139</v>
       </c>
       <c r="L271" s="1">
-        <v>46193</v>
+        <v>46189</v>
       </c>
       <c r="M271" s="1">
-        <v>46196</v>
+        <v>46194</v>
       </c>
       <c r="N271">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O271" t="s">
         <v>17</v>
@@ -15936,60 +15968,60 @@
     </row>
     <row r="272" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="B272" t="s">
-        <v>23</v>
+        <v>730</v>
       </c>
       <c r="C272" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="D272" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="E272" t="s">
         <v>40</v>
       </c>
       <c r="F272" t="s">
-        <v>567</v>
+        <v>125</v>
       </c>
       <c r="G272">
-        <v>4009.6</v>
+        <v>3680</v>
       </c>
       <c r="H272" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="I272" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J272" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K272" s="1">
-        <v>46101</v>
+        <v>46156</v>
       </c>
       <c r="L272" s="1">
-        <v>46193</v>
+        <v>46190</v>
       </c>
       <c r="M272" s="1">
-        <v>46198</v>
+        <v>46195</v>
       </c>
       <c r="N272">
         <v>5</v>
       </c>
       <c r="O272" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B273" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C273" t="s">
-        <v>25</v>
+        <v>212</v>
       </c>
       <c r="D273" t="s">
         <v>24</v>
@@ -16001,10 +16033,10 @@
         <v>75</v>
       </c>
       <c r="G273">
-        <v>10082.58</v>
+        <v>2877.3</v>
       </c>
       <c r="H273" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="I273" t="s">
         <v>21</v>
@@ -16013,63 +16045,63 @@
         <v>595</v>
       </c>
       <c r="K273" s="1">
-        <v>46098</v>
+        <v>46165</v>
       </c>
       <c r="L273" s="1">
-        <v>46194</v>
+        <v>46190</v>
       </c>
       <c r="M273" s="1">
-        <v>46214</v>
+        <v>46195</v>
       </c>
       <c r="N273">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O273" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>733</v>
+        <v>23</v>
       </c>
       <c r="B274" t="s">
-        <v>734</v>
+        <v>23</v>
       </c>
       <c r="C274" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="D274" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E274" t="s">
         <v>40</v>
       </c>
       <c r="F274" t="s">
-        <v>75</v>
+        <v>567</v>
       </c>
       <c r="G274">
-        <v>3425.01</v>
+        <v>2123.1999999999998</v>
       </c>
       <c r="H274" t="s">
         <v>735</v>
       </c>
       <c r="I274" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J274" t="s">
         <v>22</v>
       </c>
       <c r="K274" s="1">
-        <v>46104</v>
+        <v>46101</v>
       </c>
       <c r="L274" s="1">
-        <v>46194</v>
+        <v>46193</v>
       </c>
       <c r="M274" s="1">
-        <v>46199</v>
+        <v>46196</v>
       </c>
       <c r="N274">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O274" t="s">
         <v>17</v>
@@ -16077,43 +16109,43 @@
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
+        <v>23</v>
+      </c>
+      <c r="B275" t="s">
+        <v>23</v>
+      </c>
+      <c r="C275" t="s">
+        <v>17</v>
+      </c>
+      <c r="D275" t="s">
+        <v>17</v>
+      </c>
+      <c r="E275" t="s">
+        <v>40</v>
+      </c>
+      <c r="F275" t="s">
+        <v>567</v>
+      </c>
+      <c r="G275">
+        <v>4009.6</v>
+      </c>
+      <c r="H275" t="s">
         <v>736</v>
-      </c>
-      <c r="B275" t="s">
-        <v>737</v>
-      </c>
-      <c r="C275" t="s">
-        <v>321</v>
-      </c>
-      <c r="D275" t="s">
-        <v>36</v>
-      </c>
-      <c r="E275" t="s">
-        <v>40</v>
-      </c>
-      <c r="F275" t="s">
-        <v>125</v>
-      </c>
-      <c r="G275">
-        <v>3522.4</v>
-      </c>
-      <c r="H275" t="s">
-        <v>738</v>
       </c>
       <c r="I275" t="s">
         <v>320</v>
       </c>
       <c r="J275" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K275" s="1">
-        <v>46106</v>
+        <v>46101</v>
       </c>
       <c r="L275" s="1">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="M275" s="1">
-        <v>46201</v>
+        <v>46198</v>
       </c>
       <c r="N275">
         <v>5</v>
@@ -16124,46 +16156,46 @@
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
+        <v>737</v>
+      </c>
+      <c r="B276" t="s">
+        <v>738</v>
+      </c>
+      <c r="C276" t="s">
+        <v>25</v>
+      </c>
+      <c r="D276" t="s">
+        <v>24</v>
+      </c>
+      <c r="E276" t="s">
+        <v>40</v>
+      </c>
+      <c r="F276" t="s">
+        <v>75</v>
+      </c>
+      <c r="G276">
+        <v>10082.58</v>
+      </c>
+      <c r="H276" t="s">
         <v>739</v>
       </c>
-      <c r="B276" t="s">
-        <v>740</v>
-      </c>
-      <c r="C276" t="s">
-        <v>17</v>
-      </c>
-      <c r="D276" t="s">
-        <v>17</v>
-      </c>
-      <c r="E276" t="s">
-        <v>40</v>
-      </c>
-      <c r="F276" t="s">
-        <v>125</v>
-      </c>
-      <c r="G276">
-        <v>2364.9899999999998</v>
-      </c>
-      <c r="H276" t="s">
-        <v>741</v>
-      </c>
       <c r="I276" t="s">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="J276" t="s">
         <v>595</v>
       </c>
       <c r="K276" s="1">
-        <v>46106</v>
+        <v>46098</v>
       </c>
       <c r="L276" s="1">
-        <v>46197</v>
+        <v>46194</v>
       </c>
       <c r="M276" s="1">
-        <v>46200</v>
+        <v>46214</v>
       </c>
       <c r="N276">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="O276" t="s">
         <v>35</v>
@@ -16171,43 +16203,43 @@
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
+        <v>740</v>
+      </c>
+      <c r="B277" t="s">
+        <v>741</v>
+      </c>
+      <c r="C277" t="s">
+        <v>58</v>
+      </c>
+      <c r="D277" t="s">
+        <v>36</v>
+      </c>
+      <c r="E277" t="s">
+        <v>40</v>
+      </c>
+      <c r="F277" t="s">
+        <v>75</v>
+      </c>
+      <c r="G277">
+        <v>3425.01</v>
+      </c>
+      <c r="H277" t="s">
         <v>742</v>
-      </c>
-      <c r="B277" t="s">
-        <v>743</v>
-      </c>
-      <c r="C277" t="s">
-        <v>155</v>
-      </c>
-      <c r="D277" t="s">
-        <v>39</v>
-      </c>
-      <c r="E277" t="s">
-        <v>225</v>
-      </c>
-      <c r="F277" t="s">
-        <v>17</v>
-      </c>
-      <c r="G277">
-        <v>7624</v>
-      </c>
-      <c r="H277" t="s">
-        <v>744</v>
       </c>
       <c r="I277" t="s">
         <v>21</v>
       </c>
       <c r="J277" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K277" s="1">
-        <v>46163</v>
+        <v>46104</v>
       </c>
       <c r="L277" s="1">
-        <v>46197</v>
+        <v>46194</v>
       </c>
       <c r="M277" s="1">
-        <v>46202</v>
+        <v>46199</v>
       </c>
       <c r="N277">
         <v>5</v>
@@ -16218,46 +16250,46 @@
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
+        <v>743</v>
+      </c>
+      <c r="B278" t="s">
+        <v>744</v>
+      </c>
+      <c r="C278" t="s">
+        <v>321</v>
+      </c>
+      <c r="D278" t="s">
+        <v>36</v>
+      </c>
+      <c r="E278" t="s">
+        <v>40</v>
+      </c>
+      <c r="F278" t="s">
+        <v>125</v>
+      </c>
+      <c r="G278">
+        <v>3522.4</v>
+      </c>
+      <c r="H278" t="s">
         <v>745</v>
       </c>
-      <c r="B278" t="s">
-        <v>746</v>
-      </c>
-      <c r="C278" t="s">
-        <v>32</v>
-      </c>
-      <c r="D278" t="s">
-        <v>18</v>
-      </c>
-      <c r="E278" t="s">
-        <v>19</v>
-      </c>
-      <c r="F278" t="s">
-        <v>17</v>
-      </c>
-      <c r="G278">
-        <v>50279.45</v>
-      </c>
-      <c r="H278" t="s">
-        <v>747</v>
-      </c>
       <c r="I278" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J278" t="s">
         <v>595</v>
       </c>
       <c r="K278" s="1">
-        <v>46084</v>
+        <v>46106</v>
       </c>
       <c r="L278" s="1">
-        <v>46198</v>
+        <v>46196</v>
       </c>
       <c r="M278" s="1">
-        <v>46288</v>
+        <v>46201</v>
       </c>
       <c r="N278">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="O278" t="s">
         <v>17</v>
@@ -16265,75 +16297,75 @@
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>398</v>
+        <v>746</v>
       </c>
       <c r="B279" t="s">
-        <v>399</v>
+        <v>747</v>
       </c>
       <c r="C279" t="s">
-        <v>212</v>
+        <v>17</v>
       </c>
       <c r="D279" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E279" t="s">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="F279" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="G279">
-        <v>6212</v>
+        <v>2364.9899999999998</v>
       </c>
       <c r="H279" t="s">
         <v>748</v>
       </c>
       <c r="I279" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J279" t="s">
         <v>595</v>
       </c>
       <c r="K279" s="1">
-        <v>46132</v>
+        <v>46106</v>
       </c>
       <c r="L279" s="1">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="M279" s="1">
-        <v>46208</v>
+        <v>46200</v>
       </c>
       <c r="N279">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O279" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>358</v>
+        <v>749</v>
       </c>
       <c r="B280" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C280" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D280" t="s">
         <v>39</v>
       </c>
       <c r="E280" t="s">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="F280" t="s">
-        <v>306</v>
+        <v>17</v>
       </c>
       <c r="G280">
-        <v>59520</v>
+        <v>7624</v>
       </c>
       <c r="H280" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="I280" t="s">
         <v>21</v>
@@ -16342,63 +16374,63 @@
         <v>595</v>
       </c>
       <c r="K280" s="1">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="L280" s="1">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="M280" s="1">
-        <v>46228</v>
+        <v>46202</v>
       </c>
       <c r="N280">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O280" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B281" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C281" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="D281" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E281" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F281" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="G281">
-        <v>1779.3</v>
+        <v>50279.45</v>
       </c>
       <c r="H281" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="I281" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J281" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K281" s="1">
-        <v>46161</v>
+        <v>46084</v>
       </c>
       <c r="L281" s="1">
         <v>46198</v>
       </c>
       <c r="M281" s="1">
-        <v>46203</v>
+        <v>46288</v>
       </c>
       <c r="N281">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="O281" t="s">
         <v>17</v>
@@ -16406,46 +16438,46 @@
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>754</v>
+        <v>398</v>
       </c>
       <c r="B282" t="s">
+        <v>399</v>
+      </c>
+      <c r="C282" t="s">
+        <v>212</v>
+      </c>
+      <c r="D282" t="s">
+        <v>24</v>
+      </c>
+      <c r="E282" t="s">
+        <v>225</v>
+      </c>
+      <c r="F282" t="s">
+        <v>17</v>
+      </c>
+      <c r="G282">
+        <v>6212</v>
+      </c>
+      <c r="H282" t="s">
         <v>755</v>
       </c>
-      <c r="C282" t="s">
-        <v>71</v>
-      </c>
-      <c r="D282" t="s">
-        <v>70</v>
-      </c>
-      <c r="E282" t="s">
-        <v>40</v>
-      </c>
-      <c r="F282" t="s">
-        <v>390</v>
-      </c>
-      <c r="G282">
-        <v>2540.42</v>
-      </c>
-      <c r="H282" t="s">
-        <v>756</v>
-      </c>
       <c r="I282" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J282" t="s">
         <v>595</v>
       </c>
       <c r="K282" s="1">
-        <v>46047</v>
+        <v>46132</v>
       </c>
       <c r="L282" s="1">
-        <v>46200</v>
+        <v>46198</v>
       </c>
       <c r="M282" s="1">
-        <v>46205</v>
+        <v>46208</v>
       </c>
       <c r="N282">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O282" t="s">
         <v>17</v>
@@ -16453,93 +16485,93 @@
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
+        <v>358</v>
+      </c>
+      <c r="B283" t="s">
+        <v>756</v>
+      </c>
+      <c r="C283" t="s">
+        <v>151</v>
+      </c>
+      <c r="D283" t="s">
+        <v>39</v>
+      </c>
+      <c r="E283" t="s">
+        <v>40</v>
+      </c>
+      <c r="F283" t="s">
+        <v>306</v>
+      </c>
+      <c r="G283">
+        <v>59520</v>
+      </c>
+      <c r="H283" t="s">
         <v>757</v>
       </c>
-      <c r="B283" t="s">
-        <v>758</v>
-      </c>
-      <c r="C283" t="s">
-        <v>321</v>
-      </c>
-      <c r="D283" t="s">
-        <v>36</v>
-      </c>
-      <c r="E283" t="s">
-        <v>40</v>
-      </c>
-      <c r="F283" t="s">
-        <v>125</v>
-      </c>
-      <c r="G283">
-        <v>3148</v>
-      </c>
-      <c r="H283" t="s">
-        <v>759</v>
-      </c>
       <c r="I283" t="s">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="J283" t="s">
         <v>595</v>
       </c>
       <c r="K283" s="1">
-        <v>46106</v>
+        <v>46160</v>
       </c>
       <c r="L283" s="1">
-        <v>46201</v>
+        <v>46198</v>
       </c>
       <c r="M283" s="1">
-        <v>46206</v>
+        <v>46228</v>
       </c>
       <c r="N283">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O283" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="284" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
+        <v>758</v>
+      </c>
+      <c r="B284" t="s">
+        <v>759</v>
+      </c>
+      <c r="C284" t="s">
+        <v>105</v>
+      </c>
+      <c r="D284" t="s">
+        <v>66</v>
+      </c>
+      <c r="E284" t="s">
+        <v>40</v>
+      </c>
+      <c r="F284" t="s">
+        <v>75</v>
+      </c>
+      <c r="G284">
+        <v>1779.3</v>
+      </c>
+      <c r="H284" t="s">
         <v>760</v>
       </c>
-      <c r="B284" t="s">
-        <v>761</v>
-      </c>
-      <c r="C284" t="s">
-        <v>318</v>
-      </c>
-      <c r="D284" t="s">
-        <v>36</v>
-      </c>
-      <c r="E284" t="s">
-        <v>40</v>
-      </c>
-      <c r="F284" t="s">
-        <v>125</v>
-      </c>
-      <c r="G284">
-        <v>2744</v>
-      </c>
-      <c r="H284" t="s">
-        <v>762</v>
-      </c>
       <c r="I284" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J284" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K284" s="1">
-        <v>46106</v>
+        <v>46161</v>
       </c>
       <c r="L284" s="1">
-        <v>46202</v>
+        <v>46198</v>
       </c>
       <c r="M284" s="1">
-        <v>46206</v>
+        <v>46203</v>
       </c>
       <c r="N284">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O284" t="s">
         <v>17</v>
@@ -16547,46 +16579,46 @@
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>742</v>
+        <v>761</v>
       </c>
       <c r="B285" t="s">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="C285" t="s">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="D285" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="E285" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F285" t="s">
-        <v>17</v>
+        <v>390</v>
       </c>
       <c r="G285">
-        <v>1524.8</v>
+        <v>2540.42</v>
       </c>
       <c r="H285" t="s">
         <v>763</v>
       </c>
       <c r="I285" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J285" t="s">
         <v>595</v>
       </c>
       <c r="K285" s="1">
-        <v>46170</v>
+        <v>46047</v>
       </c>
       <c r="L285" s="1">
-        <v>46202</v>
+        <v>46200</v>
       </c>
       <c r="M285" s="1">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="N285">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O285" t="s">
         <v>17</v>
@@ -16600,7 +16632,7 @@
         <v>765</v>
       </c>
       <c r="C286" t="s">
-        <v>58</v>
+        <v>321</v>
       </c>
       <c r="D286" t="s">
         <v>36</v>
@@ -16609,31 +16641,31 @@
         <v>40</v>
       </c>
       <c r="F286" t="s">
-        <v>434</v>
+        <v>125</v>
       </c>
       <c r="G286">
-        <v>4918.13</v>
+        <v>3148</v>
       </c>
       <c r="H286" t="s">
         <v>766</v>
       </c>
       <c r="I286" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J286" t="s">
         <v>595</v>
       </c>
       <c r="K286" s="1">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="L286" s="1">
-        <v>46204</v>
+        <v>46201</v>
       </c>
       <c r="M286" s="1">
-        <v>46211</v>
+        <v>46206</v>
       </c>
       <c r="N286">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O286" t="s">
         <v>17</v>
@@ -16647,7 +16679,7 @@
         <v>768</v>
       </c>
       <c r="C287" t="s">
-        <v>58</v>
+        <v>318</v>
       </c>
       <c r="D287" t="s">
         <v>36</v>
@@ -16656,78 +16688,78 @@
         <v>40</v>
       </c>
       <c r="F287" t="s">
-        <v>306</v>
+        <v>125</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>2744</v>
       </c>
       <c r="H287" t="s">
         <v>769</v>
       </c>
       <c r="I287" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J287" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K287" s="1">
-        <v>46132</v>
+        <v>46106</v>
       </c>
       <c r="L287" s="1">
-        <v>46204</v>
+        <v>46202</v>
       </c>
       <c r="M287" s="1">
-        <v>46294</v>
+        <v>46206</v>
       </c>
       <c r="N287">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="O287" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
+        <v>749</v>
+      </c>
+      <c r="B288" t="s">
+        <v>750</v>
+      </c>
+      <c r="C288" t="s">
+        <v>155</v>
+      </c>
+      <c r="D288" t="s">
+        <v>39</v>
+      </c>
+      <c r="E288" t="s">
+        <v>19</v>
+      </c>
+      <c r="F288" t="s">
+        <v>17</v>
+      </c>
+      <c r="G288">
+        <v>1524.8</v>
+      </c>
+      <c r="H288" t="s">
         <v>770</v>
       </c>
-      <c r="B288" t="s">
-        <v>771</v>
-      </c>
-      <c r="C288" t="s">
-        <v>73</v>
-      </c>
-      <c r="D288" t="s">
-        <v>74</v>
-      </c>
-      <c r="E288" t="s">
-        <v>40</v>
-      </c>
-      <c r="F288" t="s">
-        <v>75</v>
-      </c>
-      <c r="G288">
-        <v>4536</v>
-      </c>
-      <c r="H288" t="s">
-        <v>772</v>
-      </c>
       <c r="I288" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J288" t="s">
         <v>595</v>
       </c>
       <c r="K288" s="1">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="L288" s="1">
-        <v>46204</v>
+        <v>46202</v>
       </c>
       <c r="M288" s="1">
-        <v>46211</v>
+        <v>46203</v>
       </c>
       <c r="N288">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O288" t="s">
         <v>17</v>
@@ -16735,46 +16767,46 @@
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
+        <v>771</v>
+      </c>
+      <c r="B289" t="s">
+        <v>772</v>
+      </c>
+      <c r="C289" t="s">
+        <v>58</v>
+      </c>
+      <c r="D289" t="s">
+        <v>36</v>
+      </c>
+      <c r="E289" t="s">
+        <v>40</v>
+      </c>
+      <c r="F289" t="s">
+        <v>434</v>
+      </c>
+      <c r="G289">
+        <v>4918.13</v>
+      </c>
+      <c r="H289" t="s">
         <v>773</v>
       </c>
-      <c r="B289" t="s">
-        <v>774</v>
-      </c>
-      <c r="C289" t="s">
-        <v>83</v>
-      </c>
-      <c r="D289" t="s">
-        <v>74</v>
-      </c>
-      <c r="E289" t="s">
-        <v>40</v>
-      </c>
-      <c r="F289" t="s">
-        <v>75</v>
-      </c>
-      <c r="G289">
-        <v>2880</v>
-      </c>
-      <c r="H289" t="s">
-        <v>775</v>
-      </c>
       <c r="I289" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J289" t="s">
         <v>595</v>
       </c>
       <c r="K289" s="1">
-        <v>46154</v>
+        <v>46094</v>
       </c>
       <c r="L289" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="M289" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="N289">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O289" t="s">
         <v>17</v>
@@ -16782,75 +16814,75 @@
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
+        <v>774</v>
+      </c>
+      <c r="B290" t="s">
+        <v>775</v>
+      </c>
+      <c r="C290" t="s">
+        <v>58</v>
+      </c>
+      <c r="D290" t="s">
+        <v>36</v>
+      </c>
+      <c r="E290" t="s">
+        <v>40</v>
+      </c>
+      <c r="F290" t="s">
+        <v>306</v>
+      </c>
+      <c r="G290">
+        <v>0</v>
+      </c>
+      <c r="H290" t="s">
         <v>776</v>
-      </c>
-      <c r="B290" t="s">
-        <v>777</v>
-      </c>
-      <c r="C290" t="s">
-        <v>155</v>
-      </c>
-      <c r="D290" t="s">
-        <v>39</v>
-      </c>
-      <c r="E290" t="s">
-        <v>40</v>
-      </c>
-      <c r="F290" t="s">
-        <v>75</v>
-      </c>
-      <c r="G290">
-        <v>13546.77</v>
-      </c>
-      <c r="H290" t="s">
-        <v>778</v>
       </c>
       <c r="I290" t="s">
         <v>21</v>
       </c>
       <c r="J290" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K290" s="1">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="L290" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="M290" s="1">
-        <v>46212</v>
+        <v>46294</v>
       </c>
       <c r="N290">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="O290" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
+        <v>777</v>
+      </c>
+      <c r="B291" t="s">
+        <v>778</v>
+      </c>
+      <c r="C291" t="s">
+        <v>73</v>
+      </c>
+      <c r="D291" t="s">
+        <v>74</v>
+      </c>
+      <c r="E291" t="s">
+        <v>40</v>
+      </c>
+      <c r="F291" t="s">
+        <v>75</v>
+      </c>
+      <c r="G291">
+        <v>4536</v>
+      </c>
+      <c r="H291" t="s">
         <v>779</v>
-      </c>
-      <c r="B291" t="s">
-        <v>780</v>
-      </c>
-      <c r="C291" t="s">
-        <v>105</v>
-      </c>
-      <c r="D291" t="s">
-        <v>66</v>
-      </c>
-      <c r="E291" t="s">
-        <v>40</v>
-      </c>
-      <c r="F291" t="s">
-        <v>390</v>
-      </c>
-      <c r="G291">
-        <v>2025.78</v>
-      </c>
-      <c r="H291" t="s">
-        <v>781</v>
       </c>
       <c r="I291" t="s">
         <v>69</v>
@@ -16859,45 +16891,45 @@
         <v>595</v>
       </c>
       <c r="K291" s="1">
-        <v>46079</v>
+        <v>46154</v>
       </c>
       <c r="L291" s="1">
-        <v>46207</v>
+        <v>46204</v>
       </c>
       <c r="M291" s="1">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="N291">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O291" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="292" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
+        <v>780</v>
+      </c>
+      <c r="B292" t="s">
+        <v>781</v>
+      </c>
+      <c r="C292" t="s">
+        <v>83</v>
+      </c>
+      <c r="D292" t="s">
+        <v>74</v>
+      </c>
+      <c r="E292" t="s">
+        <v>40</v>
+      </c>
+      <c r="F292" t="s">
+        <v>75</v>
+      </c>
+      <c r="G292">
+        <v>2880</v>
+      </c>
+      <c r="H292" t="s">
         <v>782</v>
-      </c>
-      <c r="B292" t="s">
-        <v>783</v>
-      </c>
-      <c r="C292" t="s">
-        <v>71</v>
-      </c>
-      <c r="D292" t="s">
-        <v>70</v>
-      </c>
-      <c r="E292" t="s">
-        <v>40</v>
-      </c>
-      <c r="F292" t="s">
-        <v>390</v>
-      </c>
-      <c r="G292">
-        <v>4311.7299999999996</v>
-      </c>
-      <c r="H292" t="s">
-        <v>784</v>
       </c>
       <c r="I292" t="s">
         <v>69</v>
@@ -16906,16 +16938,16 @@
         <v>595</v>
       </c>
       <c r="K292" s="1">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="L292" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="M292" s="1">
-        <v>46214</v>
+        <v>46209</v>
       </c>
       <c r="N292">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O292" t="s">
         <v>17</v>
@@ -16923,46 +16955,46 @@
     </row>
     <row r="293" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
+        <v>783</v>
+      </c>
+      <c r="B293" t="s">
+        <v>784</v>
+      </c>
+      <c r="C293" t="s">
+        <v>155</v>
+      </c>
+      <c r="D293" t="s">
+        <v>39</v>
+      </c>
+      <c r="E293" t="s">
+        <v>40</v>
+      </c>
+      <c r="F293" t="s">
+        <v>75</v>
+      </c>
+      <c r="G293">
+        <v>13546.77</v>
+      </c>
+      <c r="H293" t="s">
         <v>785</v>
       </c>
-      <c r="B293" t="s">
-        <v>786</v>
-      </c>
-      <c r="C293" t="s">
-        <v>318</v>
-      </c>
-      <c r="D293" t="s">
-        <v>36</v>
-      </c>
-      <c r="E293" t="s">
-        <v>40</v>
-      </c>
-      <c r="F293" t="s">
-        <v>434</v>
-      </c>
-      <c r="G293">
-        <v>4596</v>
-      </c>
-      <c r="H293" t="s">
-        <v>787</v>
-      </c>
       <c r="I293" t="s">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="J293" t="s">
         <v>595</v>
       </c>
       <c r="K293" s="1">
-        <v>46101</v>
+        <v>46108</v>
       </c>
       <c r="L293" s="1">
-        <v>46208</v>
+        <v>46206</v>
       </c>
       <c r="M293" s="1">
         <v>46212</v>
       </c>
       <c r="N293">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O293" t="s">
         <v>17</v>
@@ -16970,93 +17002,93 @@
     </row>
     <row r="294" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
+        <v>786</v>
+      </c>
+      <c r="B294" t="s">
+        <v>787</v>
+      </c>
+      <c r="C294" t="s">
+        <v>105</v>
+      </c>
+      <c r="D294" t="s">
+        <v>66</v>
+      </c>
+      <c r="E294" t="s">
+        <v>40</v>
+      </c>
+      <c r="F294" t="s">
+        <v>390</v>
+      </c>
+      <c r="G294">
+        <v>2025.78</v>
+      </c>
+      <c r="H294" t="s">
         <v>788</v>
       </c>
-      <c r="B294" t="s">
-        <v>789</v>
-      </c>
-      <c r="C294" t="s">
-        <v>321</v>
-      </c>
-      <c r="D294" t="s">
-        <v>36</v>
-      </c>
-      <c r="E294" t="s">
-        <v>40</v>
-      </c>
-      <c r="F294" t="s">
-        <v>434</v>
-      </c>
-      <c r="G294">
-        <v>8882.44</v>
-      </c>
-      <c r="H294" t="s">
-        <v>790</v>
-      </c>
       <c r="I294" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J294" t="s">
         <v>595</v>
       </c>
       <c r="K294" s="1">
-        <v>46122</v>
+        <v>46079</v>
       </c>
       <c r="L294" s="1">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="M294" s="1">
-        <v>46215</v>
+        <v>46213</v>
       </c>
       <c r="N294">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O294" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="295" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
+        <v>789</v>
+      </c>
+      <c r="B295" t="s">
+        <v>790</v>
+      </c>
+      <c r="C295" t="s">
+        <v>71</v>
+      </c>
+      <c r="D295" t="s">
+        <v>70</v>
+      </c>
+      <c r="E295" t="s">
+        <v>40</v>
+      </c>
+      <c r="F295" t="s">
+        <v>390</v>
+      </c>
+      <c r="G295">
+        <v>4311.7299999999996</v>
+      </c>
+      <c r="H295" t="s">
         <v>791</v>
       </c>
-      <c r="B295" t="s">
-        <v>792</v>
-      </c>
-      <c r="C295" t="s">
-        <v>17</v>
-      </c>
-      <c r="D295" t="s">
-        <v>17</v>
-      </c>
-      <c r="E295" t="s">
-        <v>40</v>
-      </c>
-      <c r="F295" t="s">
-        <v>75</v>
-      </c>
-      <c r="G295">
-        <v>15723.48</v>
-      </c>
-      <c r="H295" t="s">
-        <v>793</v>
-      </c>
       <c r="I295" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J295" t="s">
         <v>595</v>
       </c>
       <c r="K295" s="1">
-        <v>46132</v>
+        <v>46165</v>
       </c>
       <c r="L295" s="1">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="M295" s="1">
         <v>46214</v>
       </c>
       <c r="N295">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O295" t="s">
         <v>17</v>
@@ -17064,16 +17096,16 @@
     </row>
     <row r="296" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>56</v>
+        <v>792</v>
       </c>
       <c r="B296" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C296" t="s">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="D296" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="E296" t="s">
         <v>40</v>
@@ -17082,57 +17114,57 @@
         <v>434</v>
       </c>
       <c r="G296">
-        <v>6006.72</v>
+        <v>4596</v>
       </c>
       <c r="H296" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="I296" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J296" t="s">
         <v>595</v>
       </c>
       <c r="K296" s="1">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="L296" s="1">
-        <v>46210</v>
+        <v>46208</v>
       </c>
       <c r="M296" s="1">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="N296">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O296" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="297" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
+        <v>795</v>
+      </c>
+      <c r="B297" t="s">
         <v>796</v>
       </c>
-      <c r="B297" t="s">
+      <c r="C297" t="s">
+        <v>321</v>
+      </c>
+      <c r="D297" t="s">
+        <v>36</v>
+      </c>
+      <c r="E297" t="s">
+        <v>40</v>
+      </c>
+      <c r="F297" t="s">
+        <v>434</v>
+      </c>
+      <c r="G297">
+        <v>8882.44</v>
+      </c>
+      <c r="H297" t="s">
         <v>797</v>
-      </c>
-      <c r="C297" t="s">
-        <v>17</v>
-      </c>
-      <c r="D297" t="s">
-        <v>17</v>
-      </c>
-      <c r="E297" t="s">
-        <v>40</v>
-      </c>
-      <c r="F297" t="s">
-        <v>125</v>
-      </c>
-      <c r="G297">
-        <v>2575.1999999999998</v>
-      </c>
-      <c r="H297" t="s">
-        <v>798</v>
       </c>
       <c r="I297" t="s">
         <v>320</v>
@@ -17141,33 +17173,33 @@
         <v>595</v>
       </c>
       <c r="K297" s="1">
-        <v>46106</v>
+        <v>46122</v>
       </c>
       <c r="L297" s="1">
-        <v>46210</v>
+        <v>46208</v>
       </c>
       <c r="M297" s="1">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="N297">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O297" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="298" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
+        <v>798</v>
+      </c>
+      <c r="B298" t="s">
         <v>799</v>
       </c>
-      <c r="B298" t="s">
-        <v>800</v>
-      </c>
       <c r="C298" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D298" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E298" t="s">
         <v>40</v>
@@ -17176,28 +17208,28 @@
         <v>75</v>
       </c>
       <c r="G298">
-        <v>25725</v>
+        <v>15723.48</v>
       </c>
       <c r="H298" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="I298" t="s">
         <v>21</v>
       </c>
       <c r="J298" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K298" s="1">
-        <v>46062</v>
+        <v>46132</v>
       </c>
       <c r="L298" s="1">
-        <v>46211</v>
+        <v>46208</v>
       </c>
       <c r="M298" s="1">
-        <v>46242</v>
+        <v>46214</v>
       </c>
       <c r="N298">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="O298" t="s">
         <v>17</v>
@@ -17205,93 +17237,93 @@
     </row>
     <row r="299" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>799</v>
+        <v>56</v>
       </c>
       <c r="B299" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C299" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="D299" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="E299" t="s">
         <v>40</v>
       </c>
       <c r="F299" t="s">
-        <v>75</v>
+        <v>434</v>
       </c>
       <c r="G299">
-        <v>20559.599999999999</v>
+        <v>6006.72</v>
       </c>
       <c r="H299" t="s">
         <v>802</v>
       </c>
       <c r="I299" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J299" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K299" s="1">
-        <v>46063</v>
+        <v>46091</v>
       </c>
       <c r="L299" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="M299" s="1">
-        <v>46242</v>
+        <v>46218</v>
       </c>
       <c r="N299">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="O299" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="300" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B300" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C300" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D300" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E300" t="s">
         <v>40</v>
       </c>
       <c r="F300" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="G300">
-        <v>23149</v>
+        <v>2575.1999999999998</v>
       </c>
       <c r="H300" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="I300" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J300" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K300" s="1">
-        <v>46063</v>
+        <v>46106</v>
       </c>
       <c r="L300" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="M300" s="1">
-        <v>46238</v>
+        <v>46214</v>
       </c>
       <c r="N300">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="O300" t="s">
         <v>17</v>
@@ -17299,46 +17331,46 @@
     </row>
     <row r="301" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B301" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C301" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="D301" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E301" t="s">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="F301" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="G301">
-        <v>41988</v>
+        <v>25725</v>
       </c>
       <c r="H301" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="I301" t="s">
         <v>21</v>
       </c>
       <c r="J301" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K301" s="1">
-        <v>46160</v>
+        <v>46062</v>
       </c>
       <c r="L301" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="M301" s="1">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="N301">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="O301" t="s">
         <v>17</v>
@@ -17346,25 +17378,25 @@
     </row>
     <row r="302" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
+        <v>806</v>
+      </c>
+      <c r="B302" t="s">
         <v>807</v>
       </c>
-      <c r="B302" t="s">
-        <v>808</v>
-      </c>
       <c r="C302" t="s">
-        <v>212</v>
+        <v>25</v>
       </c>
       <c r="D302" t="s">
         <v>24</v>
       </c>
       <c r="E302" t="s">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="F302" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="G302">
-        <v>9035</v>
+        <v>20559.599999999999</v>
       </c>
       <c r="H302" t="s">
         <v>809</v>
@@ -17373,19 +17405,19 @@
         <v>21</v>
       </c>
       <c r="J302" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K302" s="1">
-        <v>46167</v>
+        <v>46063</v>
       </c>
       <c r="L302" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="M302" s="1">
-        <v>46229</v>
+        <v>46242</v>
       </c>
       <c r="N302">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="O302" t="s">
         <v>17</v>
@@ -17393,16 +17425,16 @@
     </row>
     <row r="303" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B303" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="C303" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="D303" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="E303" t="s">
         <v>40</v>
@@ -17411,28 +17443,28 @@
         <v>75</v>
       </c>
       <c r="G303">
-        <v>2621.7</v>
+        <v>23149</v>
       </c>
       <c r="H303" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="I303" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J303" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K303" s="1">
-        <v>46166</v>
+        <v>46063</v>
       </c>
       <c r="L303" s="1">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="M303" s="1">
-        <v>46220</v>
+        <v>46238</v>
       </c>
       <c r="N303">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="O303" t="s">
         <v>17</v>
@@ -17440,46 +17472,46 @@
     </row>
     <row r="304" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
+        <v>811</v>
+      </c>
+      <c r="B304" t="s">
+        <v>812</v>
+      </c>
+      <c r="C304" t="s">
+        <v>155</v>
+      </c>
+      <c r="D304" t="s">
+        <v>39</v>
+      </c>
+      <c r="E304" t="s">
+        <v>225</v>
+      </c>
+      <c r="F304" t="s">
+        <v>17</v>
+      </c>
+      <c r="G304">
+        <v>41988</v>
+      </c>
+      <c r="H304" t="s">
         <v>813</v>
       </c>
-      <c r="B304" t="s">
-        <v>814</v>
-      </c>
-      <c r="C304" t="s">
-        <v>318</v>
-      </c>
-      <c r="D304" t="s">
-        <v>36</v>
-      </c>
-      <c r="E304" t="s">
-        <v>40</v>
-      </c>
-      <c r="F304" t="s">
-        <v>125</v>
-      </c>
-      <c r="G304">
-        <v>8446.34</v>
-      </c>
-      <c r="H304" t="s">
-        <v>815</v>
-      </c>
       <c r="I304" t="s">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="J304" t="s">
         <v>595</v>
       </c>
       <c r="K304" s="1">
-        <v>46106</v>
+        <v>46160</v>
       </c>
       <c r="L304" s="1">
-        <v>46215</v>
+        <v>46212</v>
       </c>
       <c r="M304" s="1">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="N304">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="O304" t="s">
         <v>17</v>
@@ -17487,46 +17519,46 @@
     </row>
     <row r="305" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
+        <v>814</v>
+      </c>
+      <c r="B305" t="s">
+        <v>815</v>
+      </c>
+      <c r="C305" t="s">
+        <v>212</v>
+      </c>
+      <c r="D305" t="s">
+        <v>24</v>
+      </c>
+      <c r="E305" t="s">
+        <v>225</v>
+      </c>
+      <c r="F305" t="s">
+        <v>17</v>
+      </c>
+      <c r="G305">
+        <v>9035</v>
+      </c>
+      <c r="H305" t="s">
         <v>816</v>
       </c>
-      <c r="B305" t="s">
-        <v>817</v>
-      </c>
-      <c r="C305" t="s">
-        <v>73</v>
-      </c>
-      <c r="D305" t="s">
-        <v>74</v>
-      </c>
-      <c r="E305" t="s">
-        <v>40</v>
-      </c>
-      <c r="F305" t="s">
-        <v>75</v>
-      </c>
-      <c r="G305">
-        <v>12127.4</v>
-      </c>
-      <c r="H305" t="s">
-        <v>818</v>
-      </c>
       <c r="I305" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J305" t="s">
         <v>595</v>
       </c>
       <c r="K305" s="1">
-        <v>46120</v>
+        <v>46167</v>
       </c>
       <c r="L305" s="1">
-        <v>46215</v>
+        <v>46212</v>
       </c>
       <c r="M305" s="1">
-        <v>46235</v>
+        <v>46229</v>
       </c>
       <c r="N305">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="O305" t="s">
         <v>17</v>
@@ -17534,46 +17566,46 @@
     </row>
     <row r="306" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>697</v>
+        <v>817</v>
       </c>
       <c r="B306" t="s">
+        <v>818</v>
+      </c>
+      <c r="C306" t="s">
+        <v>105</v>
+      </c>
+      <c r="D306" t="s">
+        <v>66</v>
+      </c>
+      <c r="E306" t="s">
+        <v>40</v>
+      </c>
+      <c r="F306" t="s">
+        <v>75</v>
+      </c>
+      <c r="G306">
+        <v>2621.7</v>
+      </c>
+      <c r="H306" t="s">
         <v>819</v>
       </c>
-      <c r="C306" t="s">
-        <v>17</v>
-      </c>
-      <c r="D306" t="s">
-        <v>17</v>
-      </c>
-      <c r="E306" t="s">
-        <v>40</v>
-      </c>
-      <c r="F306" t="s">
-        <v>434</v>
-      </c>
-      <c r="G306">
-        <v>4802.3999999999996</v>
-      </c>
-      <c r="H306" t="s">
-        <v>820</v>
-      </c>
       <c r="I306" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J306" t="s">
         <v>595</v>
       </c>
       <c r="K306" s="1">
-        <v>46126</v>
+        <v>46166</v>
       </c>
       <c r="L306" s="1">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="M306" s="1">
         <v>46220</v>
       </c>
       <c r="N306">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O306" t="s">
         <v>17</v>
@@ -17581,13 +17613,13 @@
     </row>
     <row r="307" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
+        <v>820</v>
+      </c>
+      <c r="B307" t="s">
         <v>821</v>
       </c>
-      <c r="B307" t="s">
-        <v>822</v>
-      </c>
       <c r="C307" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D307" t="s">
         <v>36</v>
@@ -17596,13 +17628,13 @@
         <v>40</v>
       </c>
       <c r="F307" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="G307">
-        <v>16844.400000000001</v>
+        <v>8446.34</v>
       </c>
       <c r="H307" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I307" t="s">
         <v>320</v>
@@ -17611,16 +17643,16 @@
         <v>595</v>
       </c>
       <c r="K307" s="1">
-        <v>46129</v>
+        <v>46106</v>
       </c>
       <c r="L307" s="1">
-        <v>46218</v>
+        <v>46215</v>
       </c>
       <c r="M307" s="1">
-        <v>46235</v>
+        <v>46229</v>
       </c>
       <c r="N307">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O307" t="s">
         <v>17</v>
@@ -17628,16 +17660,16 @@
     </row>
     <row r="308" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>373</v>
+        <v>823</v>
       </c>
       <c r="B308" t="s">
         <v>824</v>
       </c>
       <c r="C308" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="D308" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="E308" t="s">
         <v>40</v>
@@ -17646,28 +17678,28 @@
         <v>75</v>
       </c>
       <c r="G308">
-        <v>4078.8</v>
+        <v>12127.4</v>
       </c>
       <c r="H308" t="s">
         <v>825</v>
       </c>
       <c r="I308" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J308" t="s">
         <v>595</v>
       </c>
       <c r="K308" s="1">
-        <v>46078</v>
+        <v>46120</v>
       </c>
       <c r="L308" s="1">
-        <v>46222</v>
+        <v>46215</v>
       </c>
       <c r="M308" s="1">
-        <v>46227</v>
+        <v>46235</v>
       </c>
       <c r="N308">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O308" t="s">
         <v>17</v>
@@ -17675,46 +17707,46 @@
     </row>
     <row r="309" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="B309" t="s">
-        <v>622</v>
+        <v>826</v>
       </c>
       <c r="C309" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D309" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E309" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F309" t="s">
-        <v>17</v>
+        <v>434</v>
       </c>
       <c r="G309">
-        <v>6036</v>
+        <v>4802.3999999999996</v>
       </c>
       <c r="H309" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I309" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J309" t="s">
         <v>595</v>
       </c>
       <c r="K309" s="1">
-        <v>46165</v>
+        <v>46126</v>
       </c>
       <c r="L309" s="1">
-        <v>46222</v>
+        <v>46216</v>
       </c>
       <c r="M309" s="1">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="N309">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O309" t="s">
         <v>17</v>
@@ -17722,16 +17754,16 @@
     </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B310" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C310" t="s">
-        <v>17</v>
+        <v>321</v>
       </c>
       <c r="D310" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E310" t="s">
         <v>40</v>
@@ -17740,28 +17772,28 @@
         <v>75</v>
       </c>
       <c r="G310">
-        <v>29900.97</v>
+        <v>16844.400000000001</v>
       </c>
       <c r="H310" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I310" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J310" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K310" s="1">
-        <v>46111</v>
+        <v>46129</v>
       </c>
       <c r="L310" s="1">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="M310" s="1">
-        <v>46241</v>
+        <v>46235</v>
       </c>
       <c r="N310">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O310" t="s">
         <v>17</v>
@@ -17769,28 +17801,28 @@
     </row>
     <row r="311" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B311" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C311" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D311" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E311" t="s">
         <v>40</v>
       </c>
       <c r="F311" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="G311">
-        <v>1731.6</v>
+        <v>2322</v>
       </c>
       <c r="H311" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="I311" t="s">
         <v>69</v>
@@ -17799,16 +17831,16 @@
         <v>595</v>
       </c>
       <c r="K311" s="1">
-        <v>46056</v>
+        <v>46170</v>
       </c>
       <c r="L311" s="1">
-        <v>46229</v>
+        <v>46218</v>
       </c>
       <c r="M311" s="1">
-        <v>46234</v>
+        <v>46222</v>
       </c>
       <c r="N311">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O311" t="s">
         <v>17</v>
@@ -17816,16 +17848,16 @@
     </row>
     <row r="312" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>833</v>
+        <v>373</v>
       </c>
       <c r="B312" t="s">
         <v>834</v>
       </c>
       <c r="C312" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D312" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E312" t="s">
         <v>40</v>
@@ -17834,7 +17866,7 @@
         <v>75</v>
       </c>
       <c r="G312">
-        <v>3983.66</v>
+        <v>4078.8</v>
       </c>
       <c r="H312" t="s">
         <v>835</v>
@@ -17846,16 +17878,16 @@
         <v>595</v>
       </c>
       <c r="K312" s="1">
-        <v>46092</v>
+        <v>46078</v>
       </c>
       <c r="L312" s="1">
-        <v>46229</v>
+        <v>46222</v>
       </c>
       <c r="M312" s="1">
-        <v>46235</v>
+        <v>46227</v>
       </c>
       <c r="N312">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O312" t="s">
         <v>17</v>
@@ -17863,93 +17895,93 @@
     </row>
     <row r="313" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>586</v>
+        <v>669</v>
       </c>
       <c r="B313" t="s">
+        <v>622</v>
+      </c>
+      <c r="C313" t="s">
+        <v>27</v>
+      </c>
+      <c r="D313" t="s">
+        <v>28</v>
+      </c>
+      <c r="E313" t="s">
+        <v>19</v>
+      </c>
+      <c r="F313" t="s">
+        <v>17</v>
+      </c>
+      <c r="G313">
+        <v>6036</v>
+      </c>
+      <c r="H313" t="s">
         <v>836</v>
       </c>
-      <c r="C313" t="s">
-        <v>83</v>
-      </c>
-      <c r="D313" t="s">
-        <v>74</v>
-      </c>
-      <c r="E313" t="s">
-        <v>40</v>
-      </c>
-      <c r="F313" t="s">
-        <v>125</v>
-      </c>
-      <c r="G313">
-        <v>2110.48</v>
-      </c>
-      <c r="H313" t="s">
-        <v>837</v>
-      </c>
       <c r="I313" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J313" t="s">
         <v>595</v>
       </c>
       <c r="K313" s="1">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="L313" s="1">
-        <v>46229</v>
+        <v>46222</v>
       </c>
       <c r="M313" s="1">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="N313">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O313" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="314" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
+        <v>837</v>
+      </c>
+      <c r="B314" t="s">
         <v>838</v>
       </c>
-      <c r="B314" t="s">
-        <v>31</v>
-      </c>
       <c r="C314" t="s">
-        <v>318</v>
+        <v>17</v>
       </c>
       <c r="D314" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E314" t="s">
         <v>40</v>
       </c>
       <c r="F314" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="G314">
-        <v>5446</v>
+        <v>29900.97</v>
       </c>
       <c r="H314" t="s">
         <v>839</v>
       </c>
       <c r="I314" t="s">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="J314" t="s">
         <v>22</v>
       </c>
       <c r="K314" s="1">
-        <v>46163</v>
+        <v>46111</v>
       </c>
       <c r="L314" s="1">
-        <v>46229</v>
+        <v>46226</v>
       </c>
       <c r="M314" s="1">
-        <v>46233</v>
+        <v>46241</v>
       </c>
       <c r="N314">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O314" t="s">
         <v>17</v>
@@ -17963,19 +17995,19 @@
         <v>841</v>
       </c>
       <c r="C315" t="s">
-        <v>334</v>
+        <v>105</v>
       </c>
       <c r="D315" t="s">
-        <v>333</v>
+        <v>66</v>
       </c>
       <c r="E315" t="s">
         <v>40</v>
       </c>
       <c r="F315" t="s">
-        <v>434</v>
+        <v>75</v>
       </c>
       <c r="G315">
-        <v>1302.2</v>
+        <v>1731.6</v>
       </c>
       <c r="H315" t="s">
         <v>842</v>
@@ -17987,16 +18019,16 @@
         <v>22</v>
       </c>
       <c r="K315" s="1">
-        <v>46031</v>
+        <v>46056</v>
       </c>
       <c r="L315" s="1">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="M315" s="1">
         <v>46234</v>
       </c>
       <c r="N315">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O315" t="s">
         <v>17</v>
@@ -18010,10 +18042,10 @@
         <v>844</v>
       </c>
       <c r="C316" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D316" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="E316" t="s">
         <v>40</v>
@@ -18022,28 +18054,28 @@
         <v>75</v>
       </c>
       <c r="G316">
-        <v>4013.08</v>
+        <v>3983.66</v>
       </c>
       <c r="H316" t="s">
         <v>845</v>
       </c>
       <c r="I316" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J316" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K316" s="1">
-        <v>46109</v>
+        <v>46092</v>
       </c>
       <c r="L316" s="1">
-        <v>46234</v>
+        <v>46229</v>
       </c>
       <c r="M316" s="1">
-        <v>46241</v>
+        <v>46235</v>
       </c>
       <c r="N316">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O316" t="s">
         <v>17</v>
@@ -18051,93 +18083,93 @@
     </row>
     <row r="317" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>843</v>
+        <v>586</v>
       </c>
       <c r="B317" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C317" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D317" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E317" t="s">
         <v>40</v>
       </c>
       <c r="F317" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="G317">
-        <v>1977.13</v>
+        <v>2110.48</v>
       </c>
       <c r="H317" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="I317" t="s">
         <v>69</v>
       </c>
       <c r="J317" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K317" s="1">
-        <v>46109</v>
+        <v>46163</v>
       </c>
       <c r="L317" s="1">
-        <v>46234</v>
+        <v>46229</v>
       </c>
       <c r="M317" s="1">
-        <v>46241</v>
+        <v>46233</v>
       </c>
       <c r="N317">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O317" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="318" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="B318" t="s">
-        <v>844</v>
+        <v>31</v>
       </c>
       <c r="C318" t="s">
-        <v>71</v>
+        <v>318</v>
       </c>
       <c r="D318" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="E318" t="s">
         <v>40</v>
       </c>
       <c r="F318" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="G318">
-        <v>3610.33</v>
+        <v>5446</v>
       </c>
       <c r="H318" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="I318" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J318" t="s">
         <v>22</v>
       </c>
       <c r="K318" s="1">
-        <v>46109</v>
+        <v>46163</v>
       </c>
       <c r="L318" s="1">
-        <v>46234</v>
+        <v>46229</v>
       </c>
       <c r="M318" s="1">
-        <v>46241</v>
+        <v>46233</v>
       </c>
       <c r="N318">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O318" t="s">
         <v>17</v>
@@ -18145,28 +18177,28 @@
     </row>
     <row r="319" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>23</v>
+        <v>850</v>
       </c>
       <c r="B319" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C319" t="s">
-        <v>67</v>
+        <v>334</v>
       </c>
       <c r="D319" t="s">
-        <v>66</v>
+        <v>333</v>
       </c>
       <c r="E319" t="s">
         <v>40</v>
       </c>
       <c r="F319" t="s">
-        <v>849</v>
+        <v>434</v>
       </c>
       <c r="G319">
-        <v>704.8</v>
+        <v>1302.2</v>
       </c>
       <c r="H319" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="I319" t="s">
         <v>69</v>
@@ -18175,16 +18207,16 @@
         <v>22</v>
       </c>
       <c r="K319" s="1">
-        <v>46073</v>
+        <v>46031</v>
       </c>
       <c r="L319" s="1">
-        <v>46235</v>
+        <v>46230</v>
       </c>
       <c r="M319" s="1">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="N319">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O319" t="s">
         <v>17</v>
@@ -18192,16 +18224,16 @@
     </row>
     <row r="320" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B320" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C320" t="s">
-        <v>177</v>
+        <v>73</v>
       </c>
       <c r="D320" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="E320" t="s">
         <v>40</v>
@@ -18210,28 +18242,28 @@
         <v>75</v>
       </c>
       <c r="G320">
-        <v>6948.03</v>
+        <v>4013.08</v>
       </c>
       <c r="H320" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="I320" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J320" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K320" s="1">
-        <v>46081</v>
+        <v>46109</v>
       </c>
       <c r="L320" s="1">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="M320" s="1">
-        <v>46249</v>
+        <v>46241</v>
       </c>
       <c r="N320">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O320" t="s">
         <v>17</v>
@@ -18239,93 +18271,93 @@
     </row>
     <row r="321" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>509</v>
+        <v>853</v>
       </c>
       <c r="B321" t="s">
-        <v>468</v>
+        <v>854</v>
       </c>
       <c r="C321" t="s">
-        <v>334</v>
+        <v>105</v>
       </c>
       <c r="D321" t="s">
-        <v>333</v>
+        <v>66</v>
       </c>
       <c r="E321" t="s">
         <v>40</v>
       </c>
       <c r="F321" t="s">
-        <v>411</v>
+        <v>75</v>
       </c>
       <c r="G321">
-        <v>24500</v>
+        <v>1977.13</v>
       </c>
       <c r="H321" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="I321" t="s">
         <v>69</v>
       </c>
       <c r="J321" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K321" s="1">
-        <v>46094</v>
+        <v>46109</v>
       </c>
       <c r="L321" s="1">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="M321" s="1">
-        <v>46375</v>
+        <v>46241</v>
       </c>
       <c r="N321">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="O321" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="322" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B322" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C322" t="s">
-        <v>321</v>
+        <v>71</v>
       </c>
       <c r="D322" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="E322" t="s">
         <v>40</v>
       </c>
       <c r="F322" t="s">
-        <v>637</v>
+        <v>75</v>
       </c>
       <c r="G322">
-        <v>4591</v>
+        <v>3610.33</v>
       </c>
       <c r="H322" t="s">
         <v>857</v>
       </c>
       <c r="I322" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J322" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K322" s="1">
-        <v>46112</v>
+        <v>46109</v>
       </c>
       <c r="L322" s="1">
-        <v>46236</v>
+        <v>46234</v>
       </c>
       <c r="M322" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="N322">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O322" t="s">
         <v>17</v>
@@ -18333,25 +18365,25 @@
     </row>
     <row r="323" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
+        <v>23</v>
+      </c>
+      <c r="B323" t="s">
         <v>858</v>
       </c>
-      <c r="B323" t="s">
+      <c r="C323" t="s">
+        <v>67</v>
+      </c>
+      <c r="D323" t="s">
+        <v>66</v>
+      </c>
+      <c r="E323" t="s">
+        <v>40</v>
+      </c>
+      <c r="F323" t="s">
         <v>859</v>
       </c>
-      <c r="C323" t="s">
-        <v>71</v>
-      </c>
-      <c r="D323" t="s">
-        <v>70</v>
-      </c>
-      <c r="E323" t="s">
-        <v>40</v>
-      </c>
-      <c r="F323" t="s">
-        <v>75</v>
-      </c>
       <c r="G323">
-        <v>3621.6</v>
+        <v>704.8</v>
       </c>
       <c r="H323" t="s">
         <v>860</v>
@@ -18360,19 +18392,19 @@
         <v>69</v>
       </c>
       <c r="J323" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K323" s="1">
-        <v>46145</v>
+        <v>46073</v>
       </c>
       <c r="L323" s="1">
-        <v>46236</v>
+        <v>46235</v>
       </c>
       <c r="M323" s="1">
-        <v>46243</v>
+        <v>46238</v>
       </c>
       <c r="N323">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O323" t="s">
         <v>17</v>
@@ -18386,10 +18418,10 @@
         <v>862</v>
       </c>
       <c r="C324" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="D324" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E324" t="s">
         <v>40</v>
@@ -18398,28 +18430,28 @@
         <v>75</v>
       </c>
       <c r="G324">
-        <v>1611.82</v>
+        <v>6948.03</v>
       </c>
       <c r="H324" t="s">
         <v>863</v>
       </c>
       <c r="I324" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J324" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K324" s="1">
-        <v>46131</v>
+        <v>46081</v>
       </c>
       <c r="L324" s="1">
-        <v>46241</v>
+        <v>46235</v>
       </c>
       <c r="M324" s="1">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="N324">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O324" t="s">
         <v>17</v>
@@ -18427,28 +18459,28 @@
     </row>
     <row r="325" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
+        <v>509</v>
+      </c>
+      <c r="B325" t="s">
+        <v>468</v>
+      </c>
+      <c r="C325" t="s">
+        <v>334</v>
+      </c>
+      <c r="D325" t="s">
+        <v>333</v>
+      </c>
+      <c r="E325" t="s">
+        <v>40</v>
+      </c>
+      <c r="F325" t="s">
+        <v>411</v>
+      </c>
+      <c r="G325">
+        <v>24500</v>
+      </c>
+      <c r="H325" t="s">
         <v>864</v>
-      </c>
-      <c r="B325" t="s">
-        <v>865</v>
-      </c>
-      <c r="C325" t="s">
-        <v>67</v>
-      </c>
-      <c r="D325" t="s">
-        <v>66</v>
-      </c>
-      <c r="E325" t="s">
-        <v>40</v>
-      </c>
-      <c r="F325" t="s">
-        <v>434</v>
-      </c>
-      <c r="G325">
-        <v>1627.68</v>
-      </c>
-      <c r="H325" t="s">
-        <v>866</v>
       </c>
       <c r="I325" t="s">
         <v>69</v>
@@ -18457,30 +18489,30 @@
         <v>595</v>
       </c>
       <c r="K325" s="1">
-        <v>46046</v>
+        <v>46094</v>
       </c>
       <c r="L325" s="1">
-        <v>46242</v>
+        <v>46235</v>
       </c>
       <c r="M325" s="1">
-        <v>46248</v>
+        <v>46375</v>
       </c>
       <c r="N325">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="O325" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="326" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B326" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C326" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D326" t="s">
         <v>36</v>
@@ -18489,13 +18521,13 @@
         <v>40</v>
       </c>
       <c r="F326" t="s">
-        <v>434</v>
+        <v>637</v>
       </c>
       <c r="G326">
-        <v>7268.08</v>
+        <v>4591</v>
       </c>
       <c r="H326" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="I326" t="s">
         <v>320</v>
@@ -18504,16 +18536,16 @@
         <v>595</v>
       </c>
       <c r="K326" s="1">
-        <v>46169</v>
+        <v>46112</v>
       </c>
       <c r="L326" s="1">
-        <v>46242</v>
+        <v>46236</v>
       </c>
       <c r="M326" s="1">
-        <v>46250</v>
+        <v>46240</v>
       </c>
       <c r="N326">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O326" t="s">
         <v>17</v>
@@ -18521,46 +18553,46 @@
     </row>
     <row r="327" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
+        <v>868</v>
+      </c>
+      <c r="B327" t="s">
+        <v>869</v>
+      </c>
+      <c r="C327" t="s">
+        <v>71</v>
+      </c>
+      <c r="D327" t="s">
+        <v>70</v>
+      </c>
+      <c r="E327" t="s">
+        <v>40</v>
+      </c>
+      <c r="F327" t="s">
+        <v>75</v>
+      </c>
+      <c r="G327">
+        <v>3621.6</v>
+      </c>
+      <c r="H327" t="s">
         <v>870</v>
       </c>
-      <c r="B327" t="s">
-        <v>871</v>
-      </c>
-      <c r="C327" t="s">
-        <v>321</v>
-      </c>
-      <c r="D327" t="s">
-        <v>36</v>
-      </c>
-      <c r="E327" t="s">
-        <v>40</v>
-      </c>
-      <c r="F327" t="s">
-        <v>125</v>
-      </c>
-      <c r="G327">
-        <v>11002.2</v>
-      </c>
-      <c r="H327" t="s">
-        <v>872</v>
-      </c>
       <c r="I327" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J327" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K327" s="1">
-        <v>46141</v>
+        <v>46145</v>
       </c>
       <c r="L327" s="1">
-        <v>46245</v>
+        <v>46236</v>
       </c>
       <c r="M327" s="1">
-        <v>46257</v>
+        <v>46243</v>
       </c>
       <c r="N327">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O327" t="s">
         <v>17</v>
@@ -18568,63 +18600,63 @@
     </row>
     <row r="328" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
+        <v>871</v>
+      </c>
+      <c r="B328" t="s">
+        <v>872</v>
+      </c>
+      <c r="C328" t="s">
+        <v>71</v>
+      </c>
+      <c r="D328" t="s">
+        <v>70</v>
+      </c>
+      <c r="E328" t="s">
+        <v>40</v>
+      </c>
+      <c r="F328" t="s">
+        <v>75</v>
+      </c>
+      <c r="G328">
+        <v>1611.82</v>
+      </c>
+      <c r="H328" t="s">
         <v>873</v>
       </c>
-      <c r="B328" t="s">
-        <v>874</v>
-      </c>
-      <c r="C328" t="s">
-        <v>321</v>
-      </c>
-      <c r="D328" t="s">
-        <v>36</v>
-      </c>
-      <c r="E328" t="s">
-        <v>40</v>
-      </c>
-      <c r="F328" t="s">
-        <v>434</v>
-      </c>
-      <c r="G328">
-        <v>4336.2</v>
-      </c>
-      <c r="H328" t="s">
-        <v>875</v>
-      </c>
       <c r="I328" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J328" t="s">
         <v>22</v>
       </c>
       <c r="K328" s="1">
-        <v>46158</v>
+        <v>46131</v>
       </c>
       <c r="L328" s="1">
-        <v>46247</v>
+        <v>46241</v>
       </c>
       <c r="M328" s="1">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="N328">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O328" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="329" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B329" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C329" t="s">
-        <v>321</v>
+        <v>67</v>
       </c>
       <c r="D329" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="E329" t="s">
         <v>40</v>
@@ -18633,75 +18665,75 @@
         <v>434</v>
       </c>
       <c r="G329">
-        <v>7399.35</v>
+        <v>1627.68</v>
       </c>
       <c r="H329" t="s">
         <v>876</v>
       </c>
       <c r="I329" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J329" t="s">
         <v>595</v>
       </c>
       <c r="K329" s="1">
-        <v>46160</v>
+        <v>46046</v>
       </c>
       <c r="L329" s="1">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="M329" s="1">
-        <v>46256</v>
+        <v>46248</v>
       </c>
       <c r="N329">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O329" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="330" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>251</v>
+        <v>877</v>
       </c>
       <c r="B330" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C330" t="s">
-        <v>17</v>
+        <v>318</v>
       </c>
       <c r="D330" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E330" t="s">
         <v>40</v>
       </c>
       <c r="F330" t="s">
-        <v>75</v>
+        <v>434</v>
       </c>
       <c r="G330">
-        <v>8665</v>
+        <v>7268.08</v>
       </c>
       <c r="H330" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="I330" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J330" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K330" s="1">
-        <v>46030</v>
+        <v>46169</v>
       </c>
       <c r="L330" s="1">
-        <v>46248</v>
+        <v>46242</v>
       </c>
       <c r="M330" s="1">
-        <v>46262</v>
+        <v>46250</v>
       </c>
       <c r="N330">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O330" t="s">
         <v>17</v>
@@ -18709,46 +18741,46 @@
     </row>
     <row r="331" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B331" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C331" t="s">
-        <v>67</v>
+        <v>321</v>
       </c>
       <c r="D331" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="E331" t="s">
         <v>40</v>
       </c>
       <c r="F331" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="G331">
-        <v>980</v>
+        <v>11002.2</v>
       </c>
       <c r="H331" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="I331" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J331" t="s">
         <v>22</v>
       </c>
       <c r="K331" s="1">
-        <v>46048</v>
+        <v>46141</v>
       </c>
       <c r="L331" s="1">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="M331" s="1">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="N331">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O331" t="s">
         <v>17</v>
@@ -18756,198 +18788,198 @@
     </row>
     <row r="332" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>764</v>
+        <v>883</v>
       </c>
       <c r="B332" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C332" t="s">
-        <v>105</v>
+        <v>321</v>
       </c>
       <c r="D332" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="E332" t="s">
         <v>40</v>
       </c>
       <c r="F332" t="s">
-        <v>75</v>
+        <v>434</v>
       </c>
       <c r="G332">
-        <v>982.77</v>
+        <v>4336.2</v>
       </c>
       <c r="H332" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="I332" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J332" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K332" s="1">
-        <v>46115</v>
+        <v>46158</v>
       </c>
       <c r="L332" s="1">
+        <v>46247</v>
+      </c>
+      <c r="M332" s="1">
         <v>46252</v>
       </c>
-      <c r="M332" s="1">
-        <v>46255</v>
-      </c>
       <c r="N332">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O332" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="333" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
+        <v>883</v>
+      </c>
+      <c r="B333" t="s">
         <v>884</v>
       </c>
-      <c r="B333" t="s">
-        <v>885</v>
-      </c>
       <c r="C333" t="s">
-        <v>71</v>
+        <v>321</v>
       </c>
       <c r="D333" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="E333" t="s">
         <v>40</v>
       </c>
       <c r="F333" t="s">
-        <v>75</v>
+        <v>434</v>
       </c>
       <c r="G333">
-        <v>2599.9499999999998</v>
+        <v>7399.35</v>
       </c>
       <c r="H333" t="s">
         <v>886</v>
       </c>
       <c r="I333" t="s">
-        <v>69</v>
+        <v>320</v>
       </c>
       <c r="J333" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K333" s="1">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="L333" s="1">
-        <v>46259</v>
+        <v>46247</v>
       </c>
       <c r="M333" s="1">
-        <v>46264</v>
+        <v>46256</v>
       </c>
       <c r="N333">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O333" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="334" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
+        <v>883</v>
+      </c>
+      <c r="B334" t="s">
+        <v>884</v>
+      </c>
+      <c r="C334" t="s">
+        <v>346</v>
+      </c>
+      <c r="D334" t="s">
+        <v>344</v>
+      </c>
+      <c r="E334" t="s">
+        <v>40</v>
+      </c>
+      <c r="F334" t="s">
+        <v>434</v>
+      </c>
+      <c r="G334">
+        <v>7398.81</v>
+      </c>
+      <c r="H334" t="s">
         <v>887</v>
       </c>
-      <c r="B334" t="s">
-        <v>888</v>
-      </c>
-      <c r="C334" t="s">
-        <v>17</v>
-      </c>
-      <c r="D334" t="s">
-        <v>17</v>
-      </c>
-      <c r="E334" t="s">
-        <v>40</v>
-      </c>
-      <c r="F334" t="s">
-        <v>306</v>
-      </c>
-      <c r="G334">
-        <v>0</v>
-      </c>
-      <c r="H334" t="s">
-        <v>889</v>
-      </c>
       <c r="I334" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J334" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K334" s="1">
-        <v>46140</v>
+        <v>46170</v>
       </c>
       <c r="L334" s="1">
-        <v>46266</v>
+        <v>46247</v>
       </c>
       <c r="M334" s="1">
-        <v>46556</v>
+        <v>46256</v>
       </c>
       <c r="N334">
-        <v>290</v>
+        <v>9</v>
       </c>
       <c r="O334" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="335" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>887</v>
+        <v>251</v>
       </c>
       <c r="B335" t="s">
         <v>888</v>
       </c>
       <c r="C335" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D335" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E335" t="s">
         <v>40</v>
       </c>
       <c r="F335" t="s">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="G335">
-        <v>62837.27</v>
+        <v>8665</v>
       </c>
       <c r="H335" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="I335" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="J335" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K335" s="1">
-        <v>46140</v>
+        <v>46030</v>
       </c>
       <c r="L335" s="1">
-        <v>46266</v>
+        <v>46248</v>
       </c>
       <c r="M335" s="1">
-        <v>46555</v>
+        <v>46262</v>
       </c>
       <c r="N335">
-        <v>289</v>
+        <v>14</v>
       </c>
       <c r="O335" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="336" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
+        <v>890</v>
+      </c>
+      <c r="B336" t="s">
         <v>891</v>
-      </c>
-      <c r="B336" t="s">
-        <v>892</v>
       </c>
       <c r="C336" t="s">
         <v>67</v>
@@ -18962,25 +18994,25 @@
         <v>75</v>
       </c>
       <c r="G336">
-        <v>974.7</v>
+        <v>980</v>
       </c>
       <c r="H336" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="I336" t="s">
         <v>69</v>
       </c>
       <c r="J336" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K336" s="1">
-        <v>46069</v>
+        <v>46048</v>
       </c>
       <c r="L336" s="1">
-        <v>46268</v>
+        <v>46251</v>
       </c>
       <c r="M336" s="1">
-        <v>46271</v>
+        <v>46254</v>
       </c>
       <c r="N336">
         <v>3</v>
@@ -18991,10 +19023,10 @@
     </row>
     <row r="337" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>894</v>
+        <v>771</v>
       </c>
       <c r="B337" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C337" t="s">
         <v>105</v>
@@ -19009,25 +19041,25 @@
         <v>75</v>
       </c>
       <c r="G337">
-        <v>1092.96</v>
+        <v>982.77</v>
       </c>
       <c r="H337" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="I337" t="s">
         <v>69</v>
       </c>
       <c r="J337" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K337" s="1">
-        <v>46085</v>
+        <v>46115</v>
       </c>
       <c r="L337" s="1">
-        <v>46272</v>
+        <v>46252</v>
       </c>
       <c r="M337" s="1">
-        <v>46275</v>
+        <v>46255</v>
       </c>
       <c r="N337">
         <v>3</v>
@@ -19038,46 +19070,46 @@
     </row>
     <row r="338" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>804</v>
+        <v>895</v>
       </c>
       <c r="B338" t="s">
+        <v>896</v>
+      </c>
+      <c r="C338" t="s">
+        <v>71</v>
+      </c>
+      <c r="D338" t="s">
+        <v>70</v>
+      </c>
+      <c r="E338" t="s">
+        <v>40</v>
+      </c>
+      <c r="F338" t="s">
+        <v>75</v>
+      </c>
+      <c r="G338">
+        <v>2599.9499999999998</v>
+      </c>
+      <c r="H338" t="s">
         <v>897</v>
       </c>
-      <c r="C338" t="s">
-        <v>321</v>
-      </c>
-      <c r="D338" t="s">
-        <v>36</v>
-      </c>
-      <c r="E338" t="s">
-        <v>40</v>
-      </c>
-      <c r="F338" t="s">
-        <v>125</v>
-      </c>
-      <c r="G338">
-        <v>1892</v>
-      </c>
-      <c r="H338" t="s">
-        <v>898</v>
-      </c>
       <c r="I338" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J338" t="s">
         <v>595</v>
       </c>
       <c r="K338" s="1">
-        <v>46108</v>
+        <v>46139</v>
       </c>
       <c r="L338" s="1">
-        <v>46275</v>
+        <v>46259</v>
       </c>
       <c r="M338" s="1">
-        <v>46279</v>
+        <v>46264</v>
       </c>
       <c r="N338">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O338" t="s">
         <v>17</v>
@@ -19085,16 +19117,16 @@
     </row>
     <row r="339" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
+        <v>898</v>
+      </c>
+      <c r="B339" t="s">
         <v>899</v>
       </c>
-      <c r="B339" t="s">
-        <v>900</v>
-      </c>
       <c r="C339" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="D339" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="E339" t="s">
         <v>40</v>
@@ -19103,28 +19135,28 @@
         <v>306</v>
       </c>
       <c r="G339">
-        <v>1594268</v>
+        <v>0</v>
       </c>
       <c r="H339" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="I339" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J339" t="s">
         <v>22</v>
       </c>
       <c r="K339" s="1">
-        <v>46078</v>
+        <v>46140</v>
       </c>
       <c r="L339" s="1">
-        <v>46284</v>
+        <v>46266</v>
       </c>
       <c r="M339" s="1">
-        <v>46544</v>
+        <v>46556</v>
       </c>
       <c r="N339">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="O339" t="s">
         <v>206</v>
@@ -19132,16 +19164,16 @@
     </row>
     <row r="340" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
+        <v>898</v>
+      </c>
+      <c r="B340" t="s">
         <v>899</v>
       </c>
-      <c r="B340" t="s">
-        <v>900</v>
-      </c>
       <c r="C340" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="D340" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E340" t="s">
         <v>40</v>
@@ -19150,28 +19182,28 @@
         <v>306</v>
       </c>
       <c r="G340">
-        <v>81900</v>
+        <v>62837.27</v>
       </c>
       <c r="H340" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I340" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J340" t="s">
         <v>595</v>
       </c>
       <c r="K340" s="1">
-        <v>46078</v>
+        <v>46140</v>
       </c>
       <c r="L340" s="1">
-        <v>46284</v>
+        <v>46266</v>
       </c>
       <c r="M340" s="1">
-        <v>46544</v>
+        <v>46555</v>
       </c>
       <c r="N340">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="O340" t="s">
         <v>206</v>
@@ -19179,10 +19211,10 @@
     </row>
     <row r="341" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
+        <v>902</v>
+      </c>
+      <c r="B341" t="s">
         <v>903</v>
-      </c>
-      <c r="B341" t="s">
-        <v>305</v>
       </c>
       <c r="C341" t="s">
         <v>67</v>
@@ -19194,10 +19226,10 @@
         <v>40</v>
       </c>
       <c r="F341" t="s">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="G341">
-        <v>40957.800000000003</v>
+        <v>974.7</v>
       </c>
       <c r="H341" t="s">
         <v>904</v>
@@ -19209,19 +19241,19 @@
         <v>595</v>
       </c>
       <c r="K341" s="1">
-        <v>46084</v>
+        <v>46069</v>
       </c>
       <c r="L341" s="1">
-        <v>46284</v>
+        <v>46268</v>
       </c>
       <c r="M341" s="1">
-        <v>46544</v>
+        <v>46271</v>
       </c>
       <c r="N341">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="O341" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="342" spans="1:15" x14ac:dyDescent="0.2">
@@ -19241,10 +19273,10 @@
         <v>40</v>
       </c>
       <c r="F342" t="s">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="G342">
-        <v>41080</v>
+        <v>1092.96</v>
       </c>
       <c r="H342" t="s">
         <v>907</v>
@@ -19253,63 +19285,63 @@
         <v>69</v>
       </c>
       <c r="J342" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K342" s="1">
-        <v>46134</v>
+        <v>46085</v>
       </c>
       <c r="L342" s="1">
-        <v>46284</v>
+        <v>46272</v>
       </c>
       <c r="M342" s="1">
-        <v>46544</v>
+        <v>46275</v>
       </c>
       <c r="N342">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="O342" t="s">
-        <v>206</v>
+        <v>17</v>
       </c>
     </row>
     <row r="343" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>63</v>
+        <v>811</v>
       </c>
       <c r="B343" t="s">
-        <v>31</v>
+        <v>908</v>
       </c>
       <c r="C343" t="s">
-        <v>212</v>
+        <v>321</v>
       </c>
       <c r="D343" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E343" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F343" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="G343">
-        <v>1487</v>
+        <v>1892</v>
       </c>
       <c r="H343" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="I343" t="s">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="J343" t="s">
         <v>595</v>
       </c>
       <c r="K343" s="1">
-        <v>46099</v>
+        <v>46108</v>
       </c>
       <c r="L343" s="1">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="M343" s="1">
-        <v>46290</v>
+        <v>46279</v>
       </c>
       <c r="N343">
         <v>4</v>
@@ -19320,75 +19352,75 @@
     </row>
     <row r="344" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B344" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C344" t="s">
-        <v>321</v>
+        <v>71</v>
       </c>
       <c r="D344" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="E344" t="s">
         <v>40</v>
       </c>
       <c r="F344" t="s">
-        <v>434</v>
+        <v>306</v>
       </c>
       <c r="G344">
-        <v>13630.5</v>
+        <v>1594268</v>
       </c>
       <c r="H344" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I344" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J344" t="s">
-        <v>595</v>
+        <v>22</v>
       </c>
       <c r="K344" s="1">
-        <v>46144</v>
+        <v>46078</v>
       </c>
       <c r="L344" s="1">
-        <v>46286</v>
+        <v>46284</v>
       </c>
       <c r="M344" s="1">
-        <v>46301</v>
+        <v>46544</v>
       </c>
       <c r="N344">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="O344" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="345" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B345" t="s">
+        <v>911</v>
+      </c>
+      <c r="C345" t="s">
+        <v>71</v>
+      </c>
+      <c r="D345" t="s">
+        <v>70</v>
+      </c>
+      <c r="E345" t="s">
+        <v>40</v>
+      </c>
+      <c r="F345" t="s">
+        <v>306</v>
+      </c>
+      <c r="G345">
+        <v>81900</v>
+      </c>
+      <c r="H345" t="s">
         <v>913</v>
-      </c>
-      <c r="C345" t="s">
-        <v>73</v>
-      </c>
-      <c r="D345" t="s">
-        <v>74</v>
-      </c>
-      <c r="E345" t="s">
-        <v>40</v>
-      </c>
-      <c r="F345" t="s">
-        <v>75</v>
-      </c>
-      <c r="G345">
-        <v>918</v>
-      </c>
-      <c r="H345" t="s">
-        <v>914</v>
       </c>
       <c r="I345" t="s">
         <v>69</v>
@@ -19397,154 +19429,154 @@
         <v>595</v>
       </c>
       <c r="K345" s="1">
-        <v>46075</v>
+        <v>46078</v>
       </c>
       <c r="L345" s="1">
-        <v>46290</v>
+        <v>46284</v>
       </c>
       <c r="M345" s="1">
-        <v>46293</v>
+        <v>46544</v>
       </c>
       <c r="N345">
-        <v>3</v>
+        <v>260</v>
       </c>
       <c r="O345" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="346" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>373</v>
+        <v>914</v>
       </c>
       <c r="B346" t="s">
+        <v>305</v>
+      </c>
+      <c r="C346" t="s">
+        <v>67</v>
+      </c>
+      <c r="D346" t="s">
+        <v>66</v>
+      </c>
+      <c r="E346" t="s">
+        <v>40</v>
+      </c>
+      <c r="F346" t="s">
+        <v>306</v>
+      </c>
+      <c r="G346">
+        <v>40957.800000000003</v>
+      </c>
+      <c r="H346" t="s">
         <v>915</v>
-      </c>
-      <c r="C346" t="s">
-        <v>17</v>
-      </c>
-      <c r="D346" t="s">
-        <v>17</v>
-      </c>
-      <c r="E346" t="s">
-        <v>40</v>
-      </c>
-      <c r="F346" t="s">
-        <v>125</v>
-      </c>
-      <c r="G346">
-        <v>1395.99</v>
-      </c>
-      <c r="H346" t="s">
-        <v>916</v>
       </c>
       <c r="I346" t="s">
         <v>69</v>
       </c>
       <c r="J346" t="s">
-        <v>22</v>
+        <v>595</v>
       </c>
       <c r="K346" s="1">
-        <v>45989</v>
+        <v>46084</v>
       </c>
       <c r="L346" s="1">
-        <v>46330</v>
+        <v>46284</v>
       </c>
       <c r="M346" s="1">
-        <v>46333</v>
+        <v>46544</v>
       </c>
       <c r="N346">
-        <v>3</v>
+        <v>260</v>
       </c>
       <c r="O346" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="347" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
+        <v>916</v>
+      </c>
+      <c r="B347" t="s">
         <v>917</v>
       </c>
-      <c r="B347" t="s">
+      <c r="C347" t="s">
+        <v>105</v>
+      </c>
+      <c r="D347" t="s">
+        <v>66</v>
+      </c>
+      <c r="E347" t="s">
+        <v>40</v>
+      </c>
+      <c r="F347" t="s">
+        <v>306</v>
+      </c>
+      <c r="G347">
+        <v>41080</v>
+      </c>
+      <c r="H347" t="s">
         <v>918</v>
       </c>
-      <c r="C347" t="s">
-        <v>346</v>
-      </c>
-      <c r="D347" t="s">
-        <v>344</v>
-      </c>
-      <c r="E347" t="s">
-        <v>40</v>
-      </c>
-      <c r="F347" t="s">
-        <v>125</v>
-      </c>
-      <c r="G347">
-        <v>1872.8</v>
-      </c>
-      <c r="H347" t="s">
-        <v>919</v>
-      </c>
       <c r="I347" t="s">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="J347" t="s">
         <v>595</v>
       </c>
       <c r="K347" s="1">
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="L347" s="1">
-        <v>46375</v>
+        <v>46284</v>
       </c>
       <c r="M347" s="1">
-        <v>46379</v>
+        <v>46544</v>
       </c>
       <c r="N347">
-        <v>4</v>
+        <v>260</v>
       </c>
       <c r="O347" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
     </row>
     <row r="348" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>920</v>
+        <v>63</v>
       </c>
       <c r="B348" t="s">
-        <v>921</v>
+        <v>31</v>
       </c>
       <c r="C348" t="s">
-        <v>73</v>
+        <v>212</v>
       </c>
       <c r="D348" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="E348" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F348" t="s">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="G348">
-        <v>3370</v>
+        <v>1487</v>
       </c>
       <c r="H348" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="I348" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="J348" t="s">
         <v>595</v>
       </c>
       <c r="K348" s="1">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="L348" s="1">
-        <v>46385</v>
+        <v>46286</v>
       </c>
       <c r="M348" s="1">
-        <v>46389</v>
+        <v>46290</v>
       </c>
       <c r="N348">
         <v>4</v>
@@ -19555,28 +19587,28 @@
     </row>
     <row r="349" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="B349" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C349" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="D349" t="s">
-        <v>344</v>
+        <v>36</v>
       </c>
       <c r="E349" t="s">
         <v>40</v>
       </c>
       <c r="F349" t="s">
-        <v>125</v>
+        <v>434</v>
       </c>
       <c r="G349">
-        <v>1272</v>
+        <v>13630.5</v>
       </c>
       <c r="H349" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="I349" t="s">
         <v>320</v>
@@ -19585,16 +19617,16 @@
         <v>595</v>
       </c>
       <c r="K349" s="1">
-        <v>46120</v>
+        <v>46144</v>
       </c>
       <c r="L349" s="1">
-        <v>46385</v>
+        <v>46286</v>
       </c>
       <c r="M349" s="1">
-        <v>46388</v>
+        <v>46301</v>
       </c>
       <c r="N349">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O349" t="s">
         <v>17</v>
@@ -19602,13 +19634,13 @@
     </row>
     <row r="350" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B350" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="C350" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D350" t="s">
         <v>74</v>
@@ -19617,13 +19649,13 @@
         <v>40</v>
       </c>
       <c r="F350" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="G350">
-        <v>2300</v>
+        <v>918</v>
       </c>
       <c r="H350" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="I350" t="s">
         <v>69</v>
@@ -19632,16 +19664,16 @@
         <v>595</v>
       </c>
       <c r="K350" s="1">
-        <v>46141</v>
+        <v>46075</v>
       </c>
       <c r="L350" s="1">
-        <v>46582</v>
+        <v>46290</v>
       </c>
       <c r="M350" s="1">
-        <v>46586</v>
+        <v>46293</v>
       </c>
       <c r="N350">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O350" t="s">
         <v>17</v>
@@ -19649,16 +19681,16 @@
     </row>
     <row r="351" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>929</v>
+        <v>373</v>
       </c>
       <c r="B351" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C351" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="D351" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="E351" t="s">
         <v>40</v>
@@ -19667,10 +19699,10 @@
         <v>125</v>
       </c>
       <c r="G351">
-        <v>4829.9399999999996</v>
+        <v>1395.99</v>
       </c>
       <c r="H351" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="I351" t="s">
         <v>69</v>
@@ -19679,18 +19711,253 @@
         <v>22</v>
       </c>
       <c r="K351" s="1">
+        <v>45989</v>
+      </c>
+      <c r="L351" s="1">
+        <v>46330</v>
+      </c>
+      <c r="M351" s="1">
+        <v>46333</v>
+      </c>
+      <c r="N351">
+        <v>3</v>
+      </c>
+      <c r="O351" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="352" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A352" t="s">
+        <v>928</v>
+      </c>
+      <c r="B352" t="s">
+        <v>929</v>
+      </c>
+      <c r="C352" t="s">
+        <v>346</v>
+      </c>
+      <c r="D352" t="s">
+        <v>344</v>
+      </c>
+      <c r="E352" t="s">
+        <v>40</v>
+      </c>
+      <c r="F352" t="s">
+        <v>125</v>
+      </c>
+      <c r="G352">
+        <v>1872.8</v>
+      </c>
+      <c r="H352" t="s">
+        <v>930</v>
+      </c>
+      <c r="I352" t="s">
+        <v>320</v>
+      </c>
+      <c r="J352" t="s">
+        <v>595</v>
+      </c>
+      <c r="K352" s="1">
+        <v>46120</v>
+      </c>
+      <c r="L352" s="1">
+        <v>46375</v>
+      </c>
+      <c r="M352" s="1">
+        <v>46379</v>
+      </c>
+      <c r="N352">
+        <v>4</v>
+      </c>
+      <c r="O352" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="353" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A353" t="s">
+        <v>931</v>
+      </c>
+      <c r="B353" t="s">
+        <v>932</v>
+      </c>
+      <c r="C353" t="s">
+        <v>73</v>
+      </c>
+      <c r="D353" t="s">
+        <v>74</v>
+      </c>
+      <c r="E353" t="s">
+        <v>40</v>
+      </c>
+      <c r="F353" t="s">
+        <v>125</v>
+      </c>
+      <c r="G353">
+        <v>3370</v>
+      </c>
+      <c r="H353" t="s">
+        <v>933</v>
+      </c>
+      <c r="I353" t="s">
+        <v>69</v>
+      </c>
+      <c r="J353" t="s">
+        <v>595</v>
+      </c>
+      <c r="K353" s="1">
+        <v>46106</v>
+      </c>
+      <c r="L353" s="1">
+        <v>46385</v>
+      </c>
+      <c r="M353" s="1">
+        <v>46389</v>
+      </c>
+      <c r="N353">
+        <v>4</v>
+      </c>
+      <c r="O353" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="354" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A354" t="s">
+        <v>934</v>
+      </c>
+      <c r="B354" t="s">
+        <v>935</v>
+      </c>
+      <c r="C354" t="s">
+        <v>346</v>
+      </c>
+      <c r="D354" t="s">
+        <v>344</v>
+      </c>
+      <c r="E354" t="s">
+        <v>40</v>
+      </c>
+      <c r="F354" t="s">
+        <v>125</v>
+      </c>
+      <c r="G354">
+        <v>1272</v>
+      </c>
+      <c r="H354" t="s">
+        <v>936</v>
+      </c>
+      <c r="I354" t="s">
+        <v>320</v>
+      </c>
+      <c r="J354" t="s">
+        <v>595</v>
+      </c>
+      <c r="K354" s="1">
+        <v>46120</v>
+      </c>
+      <c r="L354" s="1">
+        <v>46385</v>
+      </c>
+      <c r="M354" s="1">
+        <v>46388</v>
+      </c>
+      <c r="N354">
+        <v>3</v>
+      </c>
+      <c r="O354" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="355" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A355" t="s">
+        <v>937</v>
+      </c>
+      <c r="B355" t="s">
+        <v>938</v>
+      </c>
+      <c r="C355" t="s">
+        <v>83</v>
+      </c>
+      <c r="D355" t="s">
+        <v>74</v>
+      </c>
+      <c r="E355" t="s">
+        <v>40</v>
+      </c>
+      <c r="F355" t="s">
+        <v>125</v>
+      </c>
+      <c r="G355">
+        <v>2300</v>
+      </c>
+      <c r="H355" t="s">
+        <v>939</v>
+      </c>
+      <c r="I355" t="s">
+        <v>69</v>
+      </c>
+      <c r="J355" t="s">
+        <v>595</v>
+      </c>
+      <c r="K355" s="1">
+        <v>46141</v>
+      </c>
+      <c r="L355" s="1">
+        <v>46582</v>
+      </c>
+      <c r="M355" s="1">
+        <v>46586</v>
+      </c>
+      <c r="N355">
+        <v>4</v>
+      </c>
+      <c r="O355" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="356" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A356" t="s">
+        <v>940</v>
+      </c>
+      <c r="B356" t="s">
+        <v>941</v>
+      </c>
+      <c r="C356" t="s">
+        <v>83</v>
+      </c>
+      <c r="D356" t="s">
+        <v>74</v>
+      </c>
+      <c r="E356" t="s">
+        <v>40</v>
+      </c>
+      <c r="F356" t="s">
+        <v>125</v>
+      </c>
+      <c r="G356">
+        <v>4829.9399999999996</v>
+      </c>
+      <c r="H356" t="s">
+        <v>942</v>
+      </c>
+      <c r="I356" t="s">
+        <v>69</v>
+      </c>
+      <c r="J356" t="s">
+        <v>22</v>
+      </c>
+      <c r="K356" s="1">
         <v>46147</v>
       </c>
-      <c r="L351" s="1">
+      <c r="L356" s="1">
         <v>46744</v>
       </c>
-      <c r="M351" s="1">
+      <c r="M356" s="1">
         <v>46753</v>
       </c>
-      <c r="N351">
+      <c r="N356">
         <v>9</v>
       </c>
-      <c r="O351" t="s">
+      <c r="O356" t="s">
         <v>17</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14903" uniqueCount="2352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14934" uniqueCount="2359">
   <si>
     <t>First name</t>
   </si>
@@ -10303,7 +10303,8 @@
     <t>Pahwa</t>
   </si>
   <si>
-    <t xml:space="preserve">codes sent (auto)
+    <t xml:space="preserve">Post stay message sent (auto)
+codes sent (auto)
 approved
 early check-in
 KYC Status: Failed
@@ -10554,7 +10555,8 @@
     <t>HYWWNYET</t>
   </si>
   <si>
-    <t xml:space="preserve">extension WFCCECCT-1
+    <t xml:space="preserve">Post stay message sent (auto)
+extension WFCCECCT-1
 no midstay clean
 Check-in form:
 https://checkin.stayatslo.com/?id=PSGXQMDD-1</t>
@@ -10723,7 +10725,8 @@
     <t>Bonadiman</t>
   </si>
   <si>
-    <t xml:space="preserve">approved
+    <t xml:space="preserve">codes sent (auto)
+approved
 pass in idenfo
 KYC Status: Failed
 Person 1: Pass - SARAH MARIE BONADIMAN
@@ -10805,7 +10808,8 @@
     <t>YKNUIDHE</t>
   </si>
   <si>
-    <t xml:space="preserve">approved
+    <t xml:space="preserve">codes sent (auto)
+approved
 KYC Status: Pass
 Person 1: Pass - SAMUEL HERVE BAGOT
  (dob: 1973-02-21, doe: 2029-05-21)
@@ -10851,7 +10855,9 @@
     <t>BVSKDWEU</t>
   </si>
   <si>
-    <t xml:space="preserve">approved
+    <t xml:space="preserve">codes sent (auto)
+Form chased 17/06/2026 (auto)
+approved
 No ID Required
 Fully paid
 Check-in form:
@@ -10860,7 +10866,15 @@
 https://complimentary.stayatslo.com/?id=WKLGKAAU-1
 Arrival time: 15:00
 Check-out time: 11:00
-</t>
+Arrival time: 15:00
+Check out time: 11:00
+Flight/Train number:
+Special requests: 
+Accessibility needs: No, I do not have any accessibility needs
+Consent: false
+WhatsApp: true
+Terms: true
+Number of guests: 1</t>
   </si>
   <si>
     <t>GPO London</t>
@@ -10894,7 +10908,9 @@
     <t>XLXTLVYC</t>
   </si>
   <si>
-    <t xml:space="preserve">KYC Status: Failed
+    <t xml:space="preserve">approved
+passed in IDENFO
+KYC Status: Failed
 Person 1: Pass - CHARLOTTEGRACE MC CLURE
  (dob: 2002-12-06, doe: 2032-12-19)
 Person 2: Pass - ANNE WILLIAMS MC CLURE
@@ -10939,10 +10955,28 @@
     <t>Mahdi</t>
   </si>
   <si>
-    <t xml:space="preserve">placeholder
+    <t xml:space="preserve">approved
+NOTE: copied and pasted there checkin form from the last booking, returning guest
 https://cleanings.stayatslo.com/?id=UCUOMERL-1
 Check-in form:
-https://checkin.stayatslo.com/?id=UCUOMERL-1</t>
+https://checkin.stayatslo.com/?id=UCUOMERL-1
+KYC Status: Pass
+Person 1: Pass - ALJAWHRA W A M MAHDI
+ (dob: 1989-03-16, doe: 2032-12-25)
+Person 2: Pass - NAJLAA W A M MAHDI
+ (dob: 1994-03-09, doe: 2033-05-13)
+Checked at: 2026-05-25 09:55:31
+Arrival time: 15:00
+Check out time: 11:00
+Flight/Train number:
+Special requests: 
+Accessibility needs: No, I do not have any accessibility needs
+Consent: true
+WhatsApp: true
+Terms: true
+Number of guests: 2
+https://api.typeform.com/responses/files/4346cda70ca99a5c7660152676608ad76c452fccb9084578cb451718aabdd351/Najla_Mahdi_Passport.jpg (Passport)
+https://api.typeform.com/responses/files/11ede3c18adb8c5808e2344364df072977b4544b4b40a35ffbc1bbaf5d6073a9/PHOTO_2026_05_25_11_37_38.jpg (Passport)</t>
   </si>
   <si>
     <t>a347baba-0c55-46b6-acfb-9598ae9c4ff4-1</t>
@@ -11113,9 +11147,21 @@
     <t>UZXNOVMZ</t>
   </si>
   <si>
-    <t xml:space="preserve">placeholder
+    <t xml:space="preserve">approved
+returning guest from Elizabeth
+his ID is already in IDENFO
 Check-in form:
-https://checkin.stayatslo.com/?id=NATVRXCG-1</t>
+https://checkin.stayatslo.com/?id=NATVRXCG-1
+Check-in form:
+https://checkin.stayatslo.com/?id=ANEJPNBB-1
+Arrival time: 15:00
+Check out time: 11:00
+Flight/Train number:
+Special requests: Make beds and clean kitchen
+Accessibility needs: No, I do not have any accessibility needs
+Consent: true
+WhatsApp: true
+Terms: true</t>
   </si>
   <si>
     <t>46254b07-c0a3-47a2-b23f-7e075e38a21d-1</t>
@@ -11205,10 +11251,27 @@
     <t>Scott</t>
   </si>
   <si>
-    <t xml:space="preserve">placeholder
+    <t xml:space="preserve">KYC Status: Pass
+Person 1: Pass - PATRICIA NORA SCOTT
+29 RABY ROAD, WASHINGTON, NE38 OLT EUROPEAN-UNION-MODEL (dob: 1980-02-18, doe: 2028-05-10)
+Person 2: Pass - ELAINE PARKER
+37 BURNSIDE ROAD, ROWLANDS GILL, DEC32 NE39 2JZ (dob: 1980-01-09, doe: 2032-12-14)
+Checked at: 2026-06-16 16:30:57
+placeholder
 PRESS BOOKING
 Check-in form:
-https://checkin.stayatslo.com/?id=EBWKVOUS-1</t>
+https://checkin.stayatslo.com/?id=EBWKVOUS-1
+Arrival time: 15:00
+Check out time: 11:00
+Flight/Train number:
+Special requests: None
+Accessibility needs: No, I do not have any accessibility needs
+Consent: true
+WhatsApp: true
+Terms: true
+Number of guests: 2
+https://api.typeform.com/responses/files/b6d04b73dbcb7d8d6452fef3a22ca9db55f1b0d60c653149aa2c5d9388b224b0/image.jpg (Driver's license (UK))
+https://api.typeform.com/responses/files/41b9b3f4bdca444914b122aeed19ad6932499c6db047e33a044ba328e8583e7a/d6ce8ffa_d234_45f6_a5c5_aab2d2f89a18.jpeg (Driver's license (UK))</t>
   </si>
   <si>
     <t>EBWKVOUS-1</t>
@@ -11680,6 +11743,14 @@
   </si>
   <si>
     <t xml:space="preserve">KYC Status: Failed
+Person 1: Pass - LINDA KAYLENE RUSSELL
+ (dob: 1966-05-01, doe: 2036-02-11)
+Person 2: Pass - STEPHEN GLEN RUSSELL
+ (dob: 1971-12-20, doe: 2031-05-17)
+Person 3: Failed - Sorry, we couldn't detect any documents in the image you provided. Please ensure the document is clear and well-centered
+Person 4: Failed - Sorry, we couldn't detect any valid documents in the image you provided. Please ensure the document is clear and well-centered
+Checked at: 2026-06-17 14:40:50
+KYC Status: Failed
 Person 1: Failed - Sorry, we couldn't detect any documents in the image you provided. Please ensure the document is clear and well-centered
 Person 2: Failed - Sorry, we couldn't detect any valid documents in the image you provided. Please ensure the document is clear and well-centered
 Checked at: 2026-03-02 06:19:33
@@ -11696,7 +11767,18 @@
 Terms: true
 Number of guests: 2
 https://api.typeform.com/responses/files/bc7bec43012109250c24e18c5d89a866fb01453a80d7ba78a02e5fdb93669f91/IMG_20260302_0001.jpg (Passport)
-https://api.typeform.com/responses/files/77b6e7b90889884252cfd3e31168379a4f049da8ababd67d9176d4a0be6f913d/IMG_20260302_0002.jpg (Passport)</t>
+https://api.typeform.com/responses/files/77b6e7b90889884252cfd3e31168379a4f049da8ababd67d9176d4a0be6f913d/IMG_20260302_0002.jpg (Passport)
+Arrival time: 15:00
+Check out time: 09:00
+Flight/Train number:
+Special requests: 
+Accessibility needs: No, I do not have any accessibility needs
+Consent: false
+WhatsApp: true
+Terms: true
+Number of guests: 2
+https://api.typeform.com/responses/files/aef0251342dfa9d92a84cf1643b29284996d884b16eeb69c2f4a44242659e2af/IMG_20260302_0001.jpg (Passport)
+https://api.typeform.com/responses/files/59053dd40788ff16c00d233954f32073d0f0ffde3f3ba1cc0cc91d2ea47649de/IMG_20260302_0002.jpg (Passport)</t>
   </si>
   <si>
     <t>2402290198</t>
@@ -12301,6 +12383,29 @@
   </si>
   <si>
     <t>SAAKQSKM</t>
+  </si>
+  <si>
+    <t>Rami</t>
+  </si>
+  <si>
+    <t>Idriss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">placeholder
+Check-in form:
+https://checkin.stayatslo.com/?id=ILYHIXRJ-1</t>
+  </si>
+  <si>
+    <t>smoking preference: Non-Smoking, The amount the guest prepaid to Booking.com is GBP 15107.40</t>
+  </si>
+  <si>
+    <t>5659456532|1</t>
+  </si>
+  <si>
+    <t>ILYHIXRJ-1</t>
+  </si>
+  <si>
+    <t>ILYHIXRJ</t>
   </si>
   <si>
     <t>Martine</t>
@@ -13767,7 +13872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AY382"/>
+  <dimension ref="A1:AY383"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="11" width="15" customWidth="1"/>
@@ -46441,7 +46546,7 @@
         <v>112</v>
       </c>
       <c r="AJ211">
-        <v>-3497.17</v>
+        <v>0</v>
       </c>
       <c r="AK211" t="s">
         <v>64</v>
@@ -46751,7 +46856,7 @@
         <v>112</v>
       </c>
       <c r="AJ213">
-        <v>-2526.3</v>
+        <v>0</v>
       </c>
       <c r="AK213" t="s">
         <v>64</v>
@@ -47836,7 +47941,7 @@
         <v>63</v>
       </c>
       <c r="AJ220">
-        <v>-873</v>
+        <v>0</v>
       </c>
       <c r="AK220" t="s">
         <v>64</v>
@@ -49696,7 +49801,7 @@
         <v>112</v>
       </c>
       <c r="AJ232">
-        <v>-439.2</v>
+        <v>0</v>
       </c>
       <c r="AK232" t="s">
         <v>64</v>
@@ -55829,11 +55934,11 @@
       <c r="M272" s="2">
         <v>46186.626493055555</v>
       </c>
-      <c r="N272" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O272" s="2" t="s">
-        <v>53</v>
+      <c r="N272" s="1">
+        <v>46190</v>
+      </c>
+      <c r="O272" s="2">
+        <v>46190.45866898148</v>
       </c>
       <c r="P272" t="s">
         <v>95</v>
@@ -55878,7 +55983,7 @@
         <v>1699</v>
       </c>
       <c r="AD272" t="s">
-        <v>1051</v>
+        <v>85</v>
       </c>
       <c r="AE272" s="1">
         <v>46154</v>
@@ -56914,11 +57019,11 @@
       <c r="M279" s="2">
         <v>46188.62650462963</v>
       </c>
-      <c r="N279" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O279" s="2" t="s">
-        <v>53</v>
+      <c r="N279" s="1">
+        <v>46190</v>
+      </c>
+      <c r="O279" s="2">
+        <v>46190.45866898148</v>
       </c>
       <c r="P279" t="s">
         <v>67</v>
@@ -56963,7 +57068,7 @@
         <v>1741</v>
       </c>
       <c r="AD279" t="s">
-        <v>1051</v>
+        <v>85</v>
       </c>
       <c r="AE279" s="1">
         <v>46187</v>
@@ -57528,11 +57633,11 @@
       <c r="K283">
         <v>0</v>
       </c>
-      <c r="L283" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M283" s="2" t="s">
-        <v>53</v>
+      <c r="L283" s="1">
+        <v>46190</v>
+      </c>
+      <c r="M283" s="2">
+        <v>46190.62657407408</v>
       </c>
       <c r="N283" s="1" t="s">
         <v>53</v>
@@ -57583,7 +57688,7 @@
         <v>1764</v>
       </c>
       <c r="AD283" t="s">
-        <v>1361</v>
+        <v>1051</v>
       </c>
       <c r="AE283" s="1">
         <v>46156</v>
@@ -57838,11 +57943,11 @@
       <c r="K285">
         <v>0</v>
       </c>
-      <c r="L285" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M285" s="2" t="s">
-        <v>53</v>
+      <c r="L285" s="1">
+        <v>46190</v>
+      </c>
+      <c r="M285" s="2">
+        <v>46190.62657407408</v>
       </c>
       <c r="N285" s="1" t="s">
         <v>53</v>
@@ -57893,7 +57998,7 @@
         <v>1775</v>
       </c>
       <c r="AD285" t="s">
-        <v>1361</v>
+        <v>1051</v>
       </c>
       <c r="AE285" s="1">
         <v>46179</v>
@@ -58128,7 +58233,7 @@
         <v>53</v>
       </c>
       <c r="E287" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="F287" t="s">
         <v>1781</v>
@@ -60143,7 +60248,7 @@
         <v>53</v>
       </c>
       <c r="E300" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="F300" t="s">
         <v>1859</v>
@@ -63163,7 +63268,7 @@
         <v>1981</v>
       </c>
       <c r="AD319" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE319" s="1">
         <v>46101</v>
@@ -63181,7 +63286,7 @@
         <v>63</v>
       </c>
       <c r="AJ319">
-        <v>-4596</v>
+        <v>0</v>
       </c>
       <c r="AK319" t="s">
         <v>64</v>
@@ -63204,11 +63309,11 @@
       <c r="AQ319" t="s">
         <v>53</v>
       </c>
-      <c r="AR319" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS319" s="2" t="s">
-        <v>53</v>
+      <c r="AR319" s="1">
+        <v>46190</v>
+      </c>
+      <c r="AS319" s="2">
+        <v>46190.09048611111</v>
       </c>
       <c r="AT319" s="1" t="s">
         <v>53</v>
@@ -66188,7 +66293,7 @@
         <v>53</v>
       </c>
       <c r="E339" t="s">
-        <v>1079</v>
+        <v>165</v>
       </c>
       <c r="F339" t="s">
         <v>2100</v>
@@ -66221,13 +66326,13 @@
         <v>53</v>
       </c>
       <c r="P339" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="Q339" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="R339" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="S339" t="s">
         <v>2102</v>
@@ -66239,7 +66344,7 @@
         <v>190</v>
       </c>
       <c r="V339" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="W339" t="s">
         <v>53</v>
@@ -66251,37 +66356,37 @@
         <v>53</v>
       </c>
       <c r="Z339">
-        <v>1731.6</v>
+        <v>15107.4</v>
       </c>
       <c r="AA339" t="s">
         <v>2103</v>
       </c>
       <c r="AB339" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AC339" t="s">
         <v>2104</v>
       </c>
       <c r="AD339" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE339" s="1">
-        <v>46056</v>
+        <v>46190</v>
       </c>
       <c r="AF339" s="1">
-        <v>46229</v>
+        <v>46227</v>
       </c>
       <c r="AG339" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="AH339">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AI339" t="s">
         <v>112</v>
       </c>
       <c r="AJ339">
-        <v>0</v>
+        <v>-15107.4</v>
       </c>
       <c r="AK339" t="s">
         <v>64</v>
@@ -66290,7 +66395,7 @@
         <v>53</v>
       </c>
       <c r="AM339">
-        <v>259.74</v>
+        <v>2266.11</v>
       </c>
       <c r="AN339" t="s">
         <v>53</v>
@@ -66304,11 +66409,11 @@
       <c r="AQ339" t="s">
         <v>53</v>
       </c>
-      <c r="AR339" s="1">
-        <v>46171</v>
-      </c>
-      <c r="AS339" s="2">
-        <v>46171.14560185185</v>
+      <c r="AR339" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS339" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT339" s="1" t="s">
         <v>53</v>
@@ -66343,7 +66448,7 @@
         <v>53</v>
       </c>
       <c r="E340" t="s">
-        <v>461</v>
+        <v>1079</v>
       </c>
       <c r="F340" t="s">
         <v>2107</v>
@@ -66376,13 +66481,13 @@
         <v>53</v>
       </c>
       <c r="P340" t="s">
-        <v>73</v>
+        <v>177</v>
       </c>
       <c r="Q340" t="s">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="R340" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="S340" t="s">
         <v>2109</v>
@@ -66406,13 +66511,13 @@
         <v>53</v>
       </c>
       <c r="Z340">
-        <v>3983.66</v>
+        <v>1731.6</v>
       </c>
       <c r="AA340" t="s">
         <v>2110</v>
       </c>
       <c r="AB340" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AC340" t="s">
         <v>2111</v>
@@ -66421,16 +66526,16 @@
         <v>62</v>
       </c>
       <c r="AE340" s="1">
-        <v>46092</v>
+        <v>46056</v>
       </c>
       <c r="AF340" s="1">
         <v>46229</v>
       </c>
       <c r="AG340" s="1">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="AH340">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI340" t="s">
         <v>112</v>
@@ -66445,7 +66550,7 @@
         <v>53</v>
       </c>
       <c r="AM340">
-        <v>597.55</v>
+        <v>259.74</v>
       </c>
       <c r="AN340" t="s">
         <v>53</v>
@@ -66460,10 +66565,10 @@
         <v>53</v>
       </c>
       <c r="AR340" s="1">
-        <v>46187</v>
+        <v>46171</v>
       </c>
       <c r="AS340" s="2">
-        <v>46187.716319444444</v>
+        <v>46171.14560185185</v>
       </c>
       <c r="AT340" s="1" t="s">
         <v>53</v>
@@ -66486,10 +66591,10 @@
     </row>
     <row r="341" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>1339</v>
+        <v>2112</v>
       </c>
       <c r="B341" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C341" t="s">
         <v>53</v>
@@ -66498,22 +66603,22 @@
         <v>53</v>
       </c>
       <c r="E341" t="s">
-        <v>570</v>
+        <v>461</v>
       </c>
       <c r="F341" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="G341" t="s">
-        <v>53</v>
+        <v>2115</v>
       </c>
       <c r="H341" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I341">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J341">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K341">
         <v>0</v>
@@ -66531,25 +66636,25 @@
         <v>53</v>
       </c>
       <c r="P341" t="s">
-        <v>189</v>
+        <v>73</v>
       </c>
       <c r="Q341" t="s">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="R341" t="s">
-        <v>189</v>
+        <v>88</v>
       </c>
       <c r="S341" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="T341" t="s">
         <v>97</v>
       </c>
       <c r="U341" t="s">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="V341" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="W341" t="s">
         <v>53</v>
@@ -66561,37 +66666,37 @@
         <v>53</v>
       </c>
       <c r="Z341">
-        <v>2110.48</v>
+        <v>3983.66</v>
       </c>
       <c r="AA341" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="AB341" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AC341" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="AD341" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE341" s="1">
-        <v>46163</v>
+        <v>46092</v>
       </c>
       <c r="AF341" s="1">
         <v>46229</v>
       </c>
       <c r="AG341" s="1">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="AH341">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI341" t="s">
         <v>112</v>
       </c>
       <c r="AJ341">
-        <v>-2110.48</v>
+        <v>0</v>
       </c>
       <c r="AK341" t="s">
         <v>64</v>
@@ -66599,8 +66704,8 @@
       <c r="AL341" t="s">
         <v>53</v>
       </c>
-      <c r="AM341" t="s">
-        <v>53</v>
+      <c r="AM341">
+        <v>597.55</v>
       </c>
       <c r="AN341" t="s">
         <v>53</v>
@@ -66614,11 +66719,11 @@
       <c r="AQ341" t="s">
         <v>53</v>
       </c>
-      <c r="AR341" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS341" s="2" t="s">
-        <v>53</v>
+      <c r="AR341" s="1">
+        <v>46187</v>
+      </c>
+      <c r="AS341" s="2">
+        <v>46187.716319444444</v>
       </c>
       <c r="AT341" s="1" t="s">
         <v>53</v>
@@ -66627,7 +66732,7 @@
         <v>53</v>
       </c>
       <c r="AV341" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="AW341" t="s">
         <v>53</v>
@@ -66641,10 +66746,10 @@
     </row>
     <row r="342" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>2117</v>
+        <v>1339</v>
       </c>
       <c r="B342" t="s">
-        <v>79</v>
+        <v>2119</v>
       </c>
       <c r="C342" t="s">
         <v>53</v>
@@ -66653,25 +66758,25 @@
         <v>53</v>
       </c>
       <c r="E342" t="s">
-        <v>80</v>
+        <v>570</v>
       </c>
       <c r="F342" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="G342" t="s">
         <v>53</v>
       </c>
       <c r="H342" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I342">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J342">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K342">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L342" s="1" t="s">
         <v>53</v>
@@ -66686,49 +66791,49 @@
         <v>53</v>
       </c>
       <c r="P342" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="Q342" t="s">
-        <v>761</v>
+        <v>205</v>
       </c>
       <c r="R342" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="S342" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="T342" t="s">
         <v>97</v>
       </c>
       <c r="U342" t="s">
-        <v>98</v>
+        <v>300</v>
       </c>
       <c r="V342" t="s">
         <v>99</v>
       </c>
       <c r="W342" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="X342" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="Y342" t="s">
-        <v>1808</v>
+        <v>53</v>
       </c>
       <c r="Z342">
-        <v>5446</v>
+        <v>2110.48</v>
       </c>
       <c r="AA342" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="AB342" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC342" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="AD342" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE342" s="1">
         <v>46163</v>
@@ -66743,10 +66848,10 @@
         <v>4</v>
       </c>
       <c r="AI342" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ342">
-        <v>0</v>
+        <v>-2110.48</v>
       </c>
       <c r="AK342" t="s">
         <v>64</v>
@@ -66754,8 +66859,8 @@
       <c r="AL342" t="s">
         <v>53</v>
       </c>
-      <c r="AM342">
-        <v>1089.2</v>
+      <c r="AM342" t="s">
+        <v>53</v>
       </c>
       <c r="AN342" t="s">
         <v>53</v>
@@ -66769,11 +66874,11 @@
       <c r="AQ342" t="s">
         <v>53</v>
       </c>
-      <c r="AR342" s="1">
-        <v>46167</v>
-      </c>
-      <c r="AS342" s="2">
-        <v>46167.64277777778</v>
+      <c r="AR342" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS342" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT342" s="1" t="s">
         <v>53</v>
@@ -66782,7 +66887,7 @@
         <v>53</v>
       </c>
       <c r="AV342" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="AW342" t="s">
         <v>53</v>
@@ -66796,10 +66901,10 @@
     </row>
     <row r="343" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="B343" t="s">
-        <v>2123</v>
+        <v>79</v>
       </c>
       <c r="C343" t="s">
         <v>53</v>
@@ -66808,25 +66913,25 @@
         <v>53</v>
       </c>
       <c r="E343" t="s">
-        <v>1079</v>
+        <v>80</v>
       </c>
       <c r="F343" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="G343" t="s">
         <v>53</v>
       </c>
       <c r="H343" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I343">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J343">
         <v>2</v>
       </c>
       <c r="K343">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L343" s="1" t="s">
         <v>53</v>
@@ -66841,58 +66946,58 @@
         <v>53</v>
       </c>
       <c r="P343" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="Q343" t="s">
-        <v>787</v>
+        <v>761</v>
       </c>
       <c r="R343" t="s">
-        <v>786</v>
+        <v>88</v>
       </c>
       <c r="S343" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="T343" t="s">
         <v>97</v>
       </c>
       <c r="U343" t="s">
-        <v>1006</v>
+        <v>98</v>
       </c>
       <c r="V343" t="s">
         <v>99</v>
       </c>
       <c r="W343" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="X343" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="Y343" t="s">
-        <v>53</v>
+        <v>1808</v>
       </c>
       <c r="Z343">
-        <v>1302.2</v>
+        <v>5446</v>
       </c>
       <c r="AA343" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="AB343" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC343" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="AD343" t="s">
         <v>62</v>
       </c>
       <c r="AE343" s="1">
-        <v>46031</v>
+        <v>46163</v>
       </c>
       <c r="AF343" s="1">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AG343" s="1">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="AH343">
         <v>4</v>
@@ -66909,8 +67014,8 @@
       <c r="AL343" t="s">
         <v>53</v>
       </c>
-      <c r="AM343" t="s">
-        <v>53</v>
+      <c r="AM343">
+        <v>1089.2</v>
       </c>
       <c r="AN343" t="s">
         <v>53</v>
@@ -66925,10 +67030,10 @@
         <v>53</v>
       </c>
       <c r="AR343" s="1">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="AS343" s="2">
-        <v>46161.58596064815</v>
+        <v>46167.64277777778</v>
       </c>
       <c r="AT343" s="1" t="s">
         <v>53</v>
@@ -66951,10 +67056,10 @@
     </row>
     <row r="344" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="B344" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="C344" t="s">
         <v>53</v>
@@ -66963,16 +67068,16 @@
         <v>53</v>
       </c>
       <c r="E344" t="s">
-        <v>53</v>
+        <v>1079</v>
       </c>
       <c r="F344" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="G344" t="s">
-        <v>1641</v>
+        <v>53</v>
       </c>
       <c r="H344" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I344">
         <v>2</v>
@@ -66996,67 +67101,67 @@
         <v>53</v>
       </c>
       <c r="P344" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="Q344" t="s">
-        <v>408</v>
+        <v>787</v>
       </c>
       <c r="R344" t="s">
-        <v>67</v>
+        <v>786</v>
       </c>
       <c r="S344" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="T344" t="s">
         <v>97</v>
       </c>
       <c r="U344" t="s">
-        <v>907</v>
+        <v>1006</v>
       </c>
       <c r="V344" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="W344" t="s">
-        <v>2132</v>
+        <v>53</v>
       </c>
       <c r="X344" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="Y344" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z344">
+        <v>1302.2</v>
+      </c>
+      <c r="AA344" t="s">
         <v>2133</v>
       </c>
-      <c r="Z344">
-        <v>5546.1</v>
-      </c>
-      <c r="AA344" t="s">
+      <c r="AB344" t="s">
+        <v>180</v>
+      </c>
+      <c r="AC344" t="s">
         <v>2134</v>
       </c>
-      <c r="AB344" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC344" t="s">
-        <v>2135</v>
-      </c>
       <c r="AD344" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE344" s="1">
-        <v>46188</v>
+        <v>46031</v>
       </c>
       <c r="AF344" s="1">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="AG344" s="1">
-        <v>46249</v>
+        <v>46234</v>
       </c>
       <c r="AH344">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AI344" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ344">
-        <v>-5546.1</v>
+        <v>0</v>
       </c>
       <c r="AK344" t="s">
         <v>64</v>
@@ -67079,11 +67184,11 @@
       <c r="AQ344" t="s">
         <v>53</v>
       </c>
-      <c r="AR344" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS344" s="2" t="s">
-        <v>53</v>
+      <c r="AR344" s="1">
+        <v>46161</v>
+      </c>
+      <c r="AS344" s="2">
+        <v>46161.58596064815</v>
       </c>
       <c r="AT344" s="1" t="s">
         <v>53</v>
@@ -67106,37 +67211,37 @@
     </row>
     <row r="345" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B345" t="s">
         <v>2136</v>
       </c>
-      <c r="B345" t="s">
+      <c r="C345" t="s">
+        <v>53</v>
+      </c>
+      <c r="D345" t="s">
+        <v>53</v>
+      </c>
+      <c r="E345" t="s">
+        <v>53</v>
+      </c>
+      <c r="F345" t="s">
         <v>2137</v>
       </c>
-      <c r="C345" t="s">
-        <v>53</v>
-      </c>
-      <c r="D345" t="s">
-        <v>53</v>
-      </c>
-      <c r="E345" t="s">
-        <v>220</v>
-      </c>
-      <c r="F345" t="s">
-        <v>2138</v>
-      </c>
       <c r="G345" t="s">
-        <v>2139</v>
+        <v>1641</v>
       </c>
       <c r="H345" t="s">
         <v>86</v>
       </c>
       <c r="I345">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J345">
         <v>2</v>
       </c>
       <c r="K345">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L345" s="1" t="s">
         <v>53</v>
@@ -67151,67 +67256,67 @@
         <v>53</v>
       </c>
       <c r="P345" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="Q345" t="s">
-        <v>188</v>
+        <v>408</v>
       </c>
       <c r="R345" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="S345" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="T345" t="s">
         <v>97</v>
       </c>
       <c r="U345" t="s">
-        <v>190</v>
+        <v>907</v>
       </c>
       <c r="V345" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="W345" t="s">
-        <v>53</v>
+        <v>2139</v>
       </c>
       <c r="X345" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="Y345" t="s">
-        <v>53</v>
+        <v>2140</v>
       </c>
       <c r="Z345">
-        <v>4013.08</v>
+        <v>5546.1</v>
       </c>
       <c r="AA345" t="s">
         <v>2141</v>
       </c>
       <c r="AB345" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AC345" t="s">
         <v>2142</v>
       </c>
       <c r="AD345" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE345" s="1">
-        <v>46109</v>
+        <v>46188</v>
       </c>
       <c r="AF345" s="1">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="AG345" s="1">
-        <v>46241</v>
+        <v>46249</v>
       </c>
       <c r="AH345">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AI345" t="s">
         <v>112</v>
       </c>
       <c r="AJ345">
-        <v>0</v>
+        <v>-5546.1</v>
       </c>
       <c r="AK345" t="s">
         <v>64</v>
@@ -67219,8 +67324,8 @@
       <c r="AL345" t="s">
         <v>53</v>
       </c>
-      <c r="AM345">
-        <v>601.96</v>
+      <c r="AM345" t="s">
+        <v>53</v>
       </c>
       <c r="AN345" t="s">
         <v>53</v>
@@ -67234,11 +67339,11 @@
       <c r="AQ345" t="s">
         <v>53</v>
       </c>
-      <c r="AR345" s="1">
-        <v>46109</v>
-      </c>
-      <c r="AS345" s="2">
-        <v>46109.58243055556</v>
+      <c r="AR345" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS345" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT345" s="1" t="s">
         <v>53</v>
@@ -67261,10 +67366,10 @@
     </row>
     <row r="346" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>2136</v>
+        <v>2143</v>
       </c>
       <c r="B346" t="s">
-        <v>2137</v>
+        <v>2144</v>
       </c>
       <c r="C346" t="s">
         <v>53</v>
@@ -67276,22 +67381,22 @@
         <v>220</v>
       </c>
       <c r="F346" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="G346" t="s">
-        <v>1622</v>
+        <v>2146</v>
       </c>
       <c r="H346" t="s">
         <v>86</v>
       </c>
       <c r="I346">
+        <v>4</v>
+      </c>
+      <c r="J346">
         <v>2</v>
       </c>
-      <c r="J346">
-        <v>1</v>
-      </c>
       <c r="K346">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L346" s="1" t="s">
         <v>53</v>
@@ -67306,16 +67411,16 @@
         <v>53</v>
       </c>
       <c r="P346" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="Q346" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="R346" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="S346" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="T346" t="s">
         <v>97</v>
@@ -67336,16 +67441,16 @@
         <v>53</v>
       </c>
       <c r="Z346">
-        <v>1977.13</v>
+        <v>4013.08</v>
       </c>
       <c r="AA346" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="AB346" t="s">
         <v>180</v>
       </c>
       <c r="AC346" t="s">
-        <v>2142</v>
+        <v>2149</v>
       </c>
       <c r="AD346" t="s">
         <v>62</v>
@@ -67375,7 +67480,7 @@
         <v>53</v>
       </c>
       <c r="AM346">
-        <v>296.57</v>
+        <v>601.96</v>
       </c>
       <c r="AN346" t="s">
         <v>53</v>
@@ -67393,7 +67498,7 @@
         <v>46109</v>
       </c>
       <c r="AS346" s="2">
-        <v>46109.58244212963</v>
+        <v>46109.58243055556</v>
       </c>
       <c r="AT346" s="1" t="s">
         <v>53</v>
@@ -67416,10 +67521,10 @@
     </row>
     <row r="347" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>2136</v>
+        <v>2143</v>
       </c>
       <c r="B347" t="s">
-        <v>2137</v>
+        <v>2144</v>
       </c>
       <c r="C347" t="s">
         <v>53</v>
@@ -67431,7 +67536,7 @@
         <v>220</v>
       </c>
       <c r="F347" t="s">
-        <v>2146</v>
+        <v>2150</v>
       </c>
       <c r="G347" t="s">
         <v>1622</v>
@@ -67440,13 +67545,13 @@
         <v>86</v>
       </c>
       <c r="I347">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J347">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K347">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L347" s="1" t="s">
         <v>53</v>
@@ -67461,16 +67566,16 @@
         <v>53</v>
       </c>
       <c r="P347" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Q347" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="R347" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="S347" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="T347" t="s">
         <v>97</v>
@@ -67491,16 +67596,16 @@
         <v>53</v>
       </c>
       <c r="Z347">
-        <v>3610.33</v>
+        <v>1977.13</v>
       </c>
       <c r="AA347" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
       <c r="AB347" t="s">
         <v>180</v>
       </c>
       <c r="AC347" t="s">
-        <v>2142</v>
+        <v>2149</v>
       </c>
       <c r="AD347" t="s">
         <v>62</v>
@@ -67530,7 +67635,7 @@
         <v>53</v>
       </c>
       <c r="AM347">
-        <v>541.55</v>
+        <v>296.57</v>
       </c>
       <c r="AN347" t="s">
         <v>53</v>
@@ -67548,7 +67653,7 @@
         <v>46109</v>
       </c>
       <c r="AS347" s="2">
-        <v>46109.582453703704</v>
+        <v>46109.58244212963</v>
       </c>
       <c r="AT347" s="1" t="s">
         <v>53</v>
@@ -67571,10 +67676,10 @@
     </row>
     <row r="348" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>65</v>
+        <v>2143</v>
       </c>
       <c r="B348" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="C348" t="s">
         <v>53</v>
@@ -67583,25 +67688,25 @@
         <v>53</v>
       </c>
       <c r="E348" t="s">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="F348" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="G348" t="s">
-        <v>53</v>
+        <v>1622</v>
       </c>
       <c r="H348" t="s">
         <v>86</v>
       </c>
       <c r="I348">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J348">
         <v>2</v>
       </c>
       <c r="K348">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L348" s="1" t="s">
         <v>53</v>
@@ -67616,61 +67721,61 @@
         <v>53</v>
       </c>
       <c r="P348" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="Q348" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="R348" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="S348" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="T348" t="s">
         <v>97</v>
       </c>
       <c r="U348" t="s">
-        <v>2152</v>
+        <v>190</v>
       </c>
       <c r="V348" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="W348" t="s">
-        <v>2153</v>
+        <v>53</v>
       </c>
       <c r="X348" t="s">
-        <v>526</v>
+        <v>53</v>
       </c>
       <c r="Y348" t="s">
         <v>53</v>
       </c>
       <c r="Z348">
-        <v>704.8</v>
+        <v>3610.33</v>
       </c>
       <c r="AA348" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="AB348" t="s">
         <v>180</v>
       </c>
       <c r="AC348" t="s">
-        <v>2155</v>
+        <v>2149</v>
       </c>
       <c r="AD348" t="s">
         <v>62</v>
       </c>
       <c r="AE348" s="1">
-        <v>46073</v>
+        <v>46109</v>
       </c>
       <c r="AF348" s="1">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="AG348" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="AH348">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI348" t="s">
         <v>112</v>
@@ -67684,8 +67789,8 @@
       <c r="AL348" t="s">
         <v>53</v>
       </c>
-      <c r="AM348" t="s">
-        <v>53</v>
+      <c r="AM348">
+        <v>541.55</v>
       </c>
       <c r="AN348" t="s">
         <v>53</v>
@@ -67700,10 +67805,10 @@
         <v>53</v>
       </c>
       <c r="AR348" s="1">
-        <v>46086</v>
+        <v>46109</v>
       </c>
       <c r="AS348" s="2">
-        <v>46086.16619212963</v>
+        <v>46109.582453703704</v>
       </c>
       <c r="AT348" s="1" t="s">
         <v>53</v>
@@ -67726,25 +67831,25 @@
     </row>
     <row r="349" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
+        <v>65</v>
+      </c>
+      <c r="B349" t="s">
         <v>2156</v>
       </c>
-      <c r="B349" t="s">
+      <c r="C349" t="s">
+        <v>53</v>
+      </c>
+      <c r="D349" t="s">
+        <v>53</v>
+      </c>
+      <c r="E349" t="s">
+        <v>53</v>
+      </c>
+      <c r="F349" t="s">
         <v>2157</v>
       </c>
-      <c r="C349" t="s">
-        <v>53</v>
-      </c>
-      <c r="D349" t="s">
-        <v>53</v>
-      </c>
-      <c r="E349" t="s">
-        <v>461</v>
-      </c>
-      <c r="F349" t="s">
-        <v>2158</v>
-      </c>
       <c r="G349" t="s">
-        <v>2159</v>
+        <v>53</v>
       </c>
       <c r="H349" t="s">
         <v>86</v>
@@ -67753,10 +67858,10 @@
         <v>2</v>
       </c>
       <c r="J349">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K349">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L349" s="1" t="s">
         <v>53</v>
@@ -67771,43 +67876,43 @@
         <v>53</v>
       </c>
       <c r="P349" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="Q349" t="s">
-        <v>408</v>
+        <v>178</v>
       </c>
       <c r="R349" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="S349" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="T349" t="s">
         <v>97</v>
       </c>
       <c r="U349" t="s">
-        <v>190</v>
+        <v>2159</v>
       </c>
       <c r="V349" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="W349" t="s">
-        <v>53</v>
+        <v>2160</v>
       </c>
       <c r="X349" t="s">
-        <v>53</v>
+        <v>526</v>
       </c>
       <c r="Y349" t="s">
         <v>53</v>
       </c>
       <c r="Z349">
-        <v>6948.03</v>
+        <v>704.8</v>
       </c>
       <c r="AA349" t="s">
         <v>2161</v>
       </c>
       <c r="AB349" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AC349" t="s">
         <v>2162</v>
@@ -67816,16 +67921,16 @@
         <v>62</v>
       </c>
       <c r="AE349" s="1">
-        <v>46081</v>
+        <v>46073</v>
       </c>
       <c r="AF349" s="1">
         <v>46235</v>
       </c>
       <c r="AG349" s="1">
-        <v>46249</v>
+        <v>46238</v>
       </c>
       <c r="AH349">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AI349" t="s">
         <v>112</v>
@@ -67839,8 +67944,8 @@
       <c r="AL349" t="s">
         <v>53</v>
       </c>
-      <c r="AM349">
-        <v>1042.2</v>
+      <c r="AM349" t="s">
+        <v>53</v>
       </c>
       <c r="AN349" t="s">
         <v>53</v>
@@ -67855,10 +67960,10 @@
         <v>53</v>
       </c>
       <c r="AR349" s="1">
-        <v>46186</v>
+        <v>46086</v>
       </c>
       <c r="AS349" s="2">
-        <v>46186.88296296296</v>
+        <v>46086.16619212963</v>
       </c>
       <c r="AT349" s="1" t="s">
         <v>53</v>
@@ -67881,37 +67986,37 @@
     </row>
     <row r="350" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1166</v>
+        <v>2163</v>
       </c>
       <c r="B350" t="s">
-        <v>1078</v>
+        <v>2164</v>
       </c>
       <c r="C350" t="s">
         <v>53</v>
       </c>
       <c r="D350" t="s">
-        <v>988</v>
+        <v>53</v>
       </c>
       <c r="E350" t="s">
-        <v>159</v>
+        <v>461</v>
       </c>
       <c r="F350" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="G350" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H350" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J350">
         <v>1</v>
       </c>
       <c r="K350">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L350" s="1" t="s">
         <v>53</v>
@@ -67926,25 +68031,25 @@
         <v>53</v>
       </c>
       <c r="P350" t="s">
-        <v>786</v>
+        <v>67</v>
       </c>
       <c r="Q350" t="s">
-        <v>787</v>
+        <v>408</v>
       </c>
       <c r="R350" t="s">
-        <v>786</v>
+        <v>67</v>
       </c>
       <c r="S350" t="s">
-        <v>53</v>
+        <v>2167</v>
       </c>
       <c r="T350" t="s">
         <v>97</v>
       </c>
       <c r="U350" t="s">
-        <v>954</v>
+        <v>190</v>
       </c>
       <c r="V350" t="s">
-        <v>744</v>
+        <v>125</v>
       </c>
       <c r="W350" t="s">
         <v>53</v>
@@ -67956,37 +68061,37 @@
         <v>53</v>
       </c>
       <c r="Z350">
-        <v>24500</v>
+        <v>6948.03</v>
       </c>
       <c r="AA350" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="AB350" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AC350" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="AD350" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE350" s="1">
-        <v>46094</v>
+        <v>46081</v>
       </c>
       <c r="AF350" s="1">
         <v>46235</v>
       </c>
       <c r="AG350" s="1">
-        <v>46375</v>
+        <v>46249</v>
       </c>
       <c r="AH350">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="AI350" t="s">
         <v>112</v>
       </c>
       <c r="AJ350">
-        <v>-24500</v>
+        <v>0</v>
       </c>
       <c r="AK350" t="s">
         <v>64</v>
@@ -67994,8 +68099,8 @@
       <c r="AL350" t="s">
         <v>53</v>
       </c>
-      <c r="AM350" t="s">
-        <v>53</v>
+      <c r="AM350">
+        <v>1042.2</v>
       </c>
       <c r="AN350" t="s">
         <v>53</v>
@@ -68009,11 +68114,11 @@
       <c r="AQ350" t="s">
         <v>53</v>
       </c>
-      <c r="AR350" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS350" s="2" t="s">
-        <v>53</v>
+      <c r="AR350" s="1">
+        <v>46186</v>
+      </c>
+      <c r="AS350" s="2">
+        <v>46186.88296296296</v>
       </c>
       <c r="AT350" s="1" t="s">
         <v>53</v>
@@ -68022,10 +68127,10 @@
         <v>53</v>
       </c>
       <c r="AV350" t="s">
-        <v>479</v>
+        <v>53</v>
       </c>
       <c r="AW350" t="s">
-        <v>2167</v>
+        <v>53</v>
       </c>
       <c r="AX350" t="s">
         <v>53</v>
@@ -68036,34 +68141,34 @@
     </row>
     <row r="351" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>2168</v>
+        <v>1166</v>
       </c>
       <c r="B351" t="s">
-        <v>2169</v>
+        <v>1078</v>
       </c>
       <c r="C351" t="s">
         <v>53</v>
       </c>
       <c r="D351" t="s">
-        <v>53</v>
+        <v>988</v>
       </c>
       <c r="E351" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="F351" t="s">
         <v>2170</v>
       </c>
       <c r="G351" t="s">
-        <v>53</v>
+        <v>2171</v>
       </c>
       <c r="H351" t="s">
         <v>53</v>
       </c>
       <c r="I351">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J351">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K351">
         <v>0</v>
@@ -68081,25 +68186,25 @@
         <v>53</v>
       </c>
       <c r="P351" t="s">
-        <v>88</v>
+        <v>786</v>
       </c>
       <c r="Q351" t="s">
-        <v>766</v>
+        <v>787</v>
       </c>
       <c r="R351" t="s">
-        <v>88</v>
+        <v>786</v>
       </c>
       <c r="S351" t="s">
-        <v>2171</v>
+        <v>53</v>
       </c>
       <c r="T351" t="s">
         <v>97</v>
       </c>
       <c r="U351" t="s">
-        <v>1459</v>
+        <v>954</v>
       </c>
       <c r="V351" t="s">
-        <v>99</v>
+        <v>744</v>
       </c>
       <c r="W351" t="s">
         <v>53</v>
@@ -68111,13 +68216,13 @@
         <v>53</v>
       </c>
       <c r="Z351">
-        <v>4591</v>
+        <v>24500</v>
       </c>
       <c r="AA351" t="s">
         <v>2172</v>
       </c>
       <c r="AB351" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC351" t="s">
         <v>2173</v>
@@ -68126,22 +68231,22 @@
         <v>1361</v>
       </c>
       <c r="AE351" s="1">
-        <v>46112</v>
+        <v>46094</v>
       </c>
       <c r="AF351" s="1">
-        <v>46236</v>
+        <v>46235</v>
       </c>
       <c r="AG351" s="1">
-        <v>46240</v>
+        <v>46375</v>
       </c>
       <c r="AH351">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="AI351" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ351">
-        <v>-3213.7</v>
+        <v>-24500</v>
       </c>
       <c r="AK351" t="s">
         <v>64</v>
@@ -68177,10 +68282,10 @@
         <v>53</v>
       </c>
       <c r="AV351" t="s">
-        <v>53</v>
+        <v>479</v>
       </c>
       <c r="AW351" t="s">
-        <v>53</v>
+        <v>2174</v>
       </c>
       <c r="AX351" t="s">
         <v>53</v>
@@ -68191,10 +68296,10 @@
     </row>
     <row r="352" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="B352" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="C352" t="s">
         <v>53</v>
@@ -68203,25 +68308,25 @@
         <v>53</v>
       </c>
       <c r="E352" t="s">
-        <v>165</v>
+        <v>53</v>
       </c>
       <c r="F352" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="G352" t="s">
-        <v>2177</v>
+        <v>53</v>
       </c>
       <c r="H352" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I352">
         <v>4</v>
       </c>
       <c r="J352">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K352">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L352" s="1" t="s">
         <v>53</v>
@@ -68236,13 +68341,13 @@
         <v>53</v>
       </c>
       <c r="P352" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="Q352" t="s">
-        <v>184</v>
+        <v>766</v>
       </c>
       <c r="R352" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="S352" t="s">
         <v>2178</v>
@@ -68251,10 +68356,10 @@
         <v>97</v>
       </c>
       <c r="U352" t="s">
-        <v>190</v>
+        <v>1459</v>
       </c>
       <c r="V352" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="W352" t="s">
         <v>53</v>
@@ -68266,13 +68371,13 @@
         <v>53</v>
       </c>
       <c r="Z352">
-        <v>3621.6</v>
+        <v>4591</v>
       </c>
       <c r="AA352" t="s">
         <v>2179</v>
       </c>
       <c r="AB352" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC352" t="s">
         <v>2180</v>
@@ -68281,22 +68386,22 @@
         <v>1361</v>
       </c>
       <c r="AE352" s="1">
-        <v>46145</v>
+        <v>46112</v>
       </c>
       <c r="AF352" s="1">
         <v>46236</v>
       </c>
       <c r="AG352" s="1">
-        <v>46243</v>
+        <v>46240</v>
       </c>
       <c r="AH352">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI352" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ352">
-        <v>-3621.6</v>
+        <v>-3213.7</v>
       </c>
       <c r="AK352" t="s">
         <v>64</v>
@@ -68304,8 +68409,8 @@
       <c r="AL352" t="s">
         <v>53</v>
       </c>
-      <c r="AM352">
-        <v>543.24</v>
+      <c r="AM352" t="s">
+        <v>53</v>
       </c>
       <c r="AN352" t="s">
         <v>53</v>
@@ -68358,25 +68463,25 @@
         <v>53</v>
       </c>
       <c r="E353" t="s">
+        <v>165</v>
+      </c>
+      <c r="F353" t="s">
         <v>2183</v>
       </c>
-      <c r="F353" t="s">
+      <c r="G353" t="s">
         <v>2184</v>
-      </c>
-      <c r="G353" t="s">
-        <v>2185</v>
       </c>
       <c r="H353" t="s">
         <v>86</v>
       </c>
       <c r="I353">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J353">
         <v>2</v>
       </c>
       <c r="K353">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L353" s="1" t="s">
         <v>53</v>
@@ -68400,7 +68505,7 @@
         <v>183</v>
       </c>
       <c r="S353" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="T353" t="s">
         <v>97</v>
@@ -68409,7 +68514,7 @@
         <v>190</v>
       </c>
       <c r="V353" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="W353" t="s">
         <v>53</v>
@@ -68421,37 +68526,37 @@
         <v>53</v>
       </c>
       <c r="Z353">
-        <v>1611.82</v>
+        <v>3621.6</v>
       </c>
       <c r="AA353" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="AB353" t="s">
         <v>180</v>
       </c>
       <c r="AC353" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="AD353" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE353" s="1">
-        <v>46131</v>
+        <v>46145</v>
       </c>
       <c r="AF353" s="1">
-        <v>46241</v>
+        <v>46236</v>
       </c>
       <c r="AG353" s="1">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="AH353">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI353" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ353">
-        <v>0</v>
+        <v>-3621.6</v>
       </c>
       <c r="AK353" t="s">
         <v>64</v>
@@ -68460,7 +68565,7 @@
         <v>53</v>
       </c>
       <c r="AM353">
-        <v>241.77</v>
+        <v>543.24</v>
       </c>
       <c r="AN353" t="s">
         <v>53</v>
@@ -68474,11 +68579,11 @@
       <c r="AQ353" t="s">
         <v>53</v>
       </c>
-      <c r="AR353" s="1">
-        <v>46131</v>
-      </c>
-      <c r="AS353" s="2">
-        <v>46131.51017361111</v>
+      <c r="AR353" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS353" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT353" s="1" t="s">
         <v>53</v>
@@ -68501,37 +68606,37 @@
     </row>
     <row r="354" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B354" t="s">
         <v>2189</v>
       </c>
-      <c r="B354" t="s">
+      <c r="C354" t="s">
+        <v>53</v>
+      </c>
+      <c r="D354" t="s">
+        <v>53</v>
+      </c>
+      <c r="E354" t="s">
         <v>2190</v>
-      </c>
-      <c r="C354" t="s">
-        <v>53</v>
-      </c>
-      <c r="D354" t="s">
-        <v>53</v>
-      </c>
-      <c r="E354" t="s">
-        <v>159</v>
       </c>
       <c r="F354" t="s">
         <v>2191</v>
       </c>
       <c r="G354" t="s">
-        <v>53</v>
+        <v>2192</v>
       </c>
       <c r="H354" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I354">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J354">
         <v>2</v>
       </c>
       <c r="K354">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L354" s="1" t="s">
         <v>53</v>
@@ -68546,22 +68651,22 @@
         <v>53</v>
       </c>
       <c r="P354" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="Q354" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="R354" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="S354" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="T354" t="s">
         <v>97</v>
       </c>
       <c r="U354" t="s">
-        <v>1006</v>
+        <v>190</v>
       </c>
       <c r="V354" t="s">
         <v>99</v>
@@ -68576,37 +68681,37 @@
         <v>53</v>
       </c>
       <c r="Z354">
-        <v>1627.68</v>
+        <v>1611.82</v>
       </c>
       <c r="AA354" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="AB354" t="s">
         <v>180</v>
       </c>
       <c r="AC354" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="AD354" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE354" s="1">
-        <v>46046</v>
+        <v>46131</v>
       </c>
       <c r="AF354" s="1">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="AG354" s="1">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="AH354">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AI354" t="s">
         <v>63</v>
       </c>
       <c r="AJ354">
-        <v>-1627.68</v>
+        <v>0</v>
       </c>
       <c r="AK354" t="s">
         <v>64</v>
@@ -68614,8 +68719,8 @@
       <c r="AL354" t="s">
         <v>53</v>
       </c>
-      <c r="AM354" t="s">
-        <v>53</v>
+      <c r="AM354">
+        <v>241.77</v>
       </c>
       <c r="AN354" t="s">
         <v>53</v>
@@ -68629,11 +68734,11 @@
       <c r="AQ354" t="s">
         <v>53</v>
       </c>
-      <c r="AR354" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS354" s="2" t="s">
-        <v>53</v>
+      <c r="AR354" s="1">
+        <v>46131</v>
+      </c>
+      <c r="AS354" s="2">
+        <v>46131.51017361111</v>
       </c>
       <c r="AT354" s="1" t="s">
         <v>53</v>
@@ -68656,10 +68761,10 @@
     </row>
     <row r="355" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="B355" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="C355" t="s">
         <v>53</v>
@@ -68668,10 +68773,10 @@
         <v>53</v>
       </c>
       <c r="E355" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="F355" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="G355" t="s">
         <v>53</v>
@@ -68680,10 +68785,10 @@
         <v>53</v>
       </c>
       <c r="I355">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J355">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K355">
         <v>0</v>
@@ -68701,16 +68806,16 @@
         <v>53</v>
       </c>
       <c r="P355" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="Q355" t="s">
-        <v>766</v>
+        <v>178</v>
       </c>
       <c r="R355" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="S355" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="T355" t="s">
         <v>97</v>
@@ -68731,37 +68836,37 @@
         <v>53</v>
       </c>
       <c r="Z355">
-        <v>7268.08</v>
+        <v>1627.68</v>
       </c>
       <c r="AA355" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="AB355" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC355" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="AD355" t="s">
         <v>1361</v>
       </c>
       <c r="AE355" s="1">
-        <v>46169</v>
+        <v>46046</v>
       </c>
       <c r="AF355" s="1">
         <v>46242</v>
       </c>
       <c r="AG355" s="1">
-        <v>46250</v>
+        <v>46248</v>
       </c>
       <c r="AH355">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI355" t="s">
         <v>63</v>
       </c>
       <c r="AJ355">
-        <v>-7268.08</v>
+        <v>-1627.68</v>
       </c>
       <c r="AK355" t="s">
         <v>64</v>
@@ -68811,10 +68916,10 @@
     </row>
     <row r="356" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="B356" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C356" t="s">
         <v>53</v>
@@ -68823,22 +68928,22 @@
         <v>53</v>
       </c>
       <c r="E356" t="s">
-        <v>220</v>
+        <v>53</v>
       </c>
       <c r="F356" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="G356" t="s">
-        <v>2204</v>
+        <v>53</v>
       </c>
       <c r="H356" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I356">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J356">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K356">
         <v>0</v>
@@ -68856,13 +68961,13 @@
         <v>53</v>
       </c>
       <c r="P356" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="Q356" t="s">
-        <v>68</v>
+        <v>766</v>
       </c>
       <c r="R356" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="S356" t="s">
         <v>2205</v>
@@ -68871,10 +68976,10 @@
         <v>97</v>
       </c>
       <c r="U356" t="s">
-        <v>190</v>
+        <v>1006</v>
       </c>
       <c r="V356" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="W356" t="s">
         <v>53</v>
@@ -68886,37 +68991,37 @@
         <v>53</v>
       </c>
       <c r="Z356">
-        <v>7616.7</v>
+        <v>7268.08</v>
       </c>
       <c r="AA356" t="s">
         <v>2206</v>
       </c>
       <c r="AB356" t="s">
-        <v>60</v>
+        <v>763</v>
       </c>
       <c r="AC356" t="s">
         <v>2207</v>
       </c>
       <c r="AD356" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE356" s="1">
-        <v>46173</v>
+        <v>46169</v>
       </c>
       <c r="AF356" s="1">
         <v>46242</v>
       </c>
       <c r="AG356" s="1">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="AH356">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AI356" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ356">
-        <v>0</v>
+        <v>-7268.08</v>
       </c>
       <c r="AK356" t="s">
         <v>64</v>
@@ -68924,8 +69029,8 @@
       <c r="AL356" t="s">
         <v>53</v>
       </c>
-      <c r="AM356">
-        <v>1142.51</v>
+      <c r="AM356" t="s">
+        <v>53</v>
       </c>
       <c r="AN356" t="s">
         <v>53</v>
@@ -68939,11 +69044,11 @@
       <c r="AQ356" t="s">
         <v>53</v>
       </c>
-      <c r="AR356" s="1">
-        <v>46183</v>
-      </c>
-      <c r="AS356" s="2">
-        <v>46183.99928240741</v>
+      <c r="AR356" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS356" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT356" s="1" t="s">
         <v>53</v>
@@ -68978,22 +69083,22 @@
         <v>53</v>
       </c>
       <c r="E357" t="s">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="F357" t="s">
         <v>2210</v>
       </c>
       <c r="G357" t="s">
-        <v>53</v>
+        <v>2211</v>
       </c>
       <c r="H357" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I357">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J357">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K357">
         <v>0</v>
@@ -69011,25 +69116,25 @@
         <v>53</v>
       </c>
       <c r="P357" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="Q357" t="s">
-        <v>766</v>
+        <v>68</v>
       </c>
       <c r="R357" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="S357" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="T357" t="s">
         <v>97</v>
       </c>
       <c r="U357" t="s">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="V357" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="W357" t="s">
         <v>53</v>
@@ -69041,34 +69146,34 @@
         <v>53</v>
       </c>
       <c r="Z357">
-        <v>11002.2</v>
+        <v>7616.7</v>
       </c>
       <c r="AA357" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="AB357" t="s">
-        <v>763</v>
+        <v>60</v>
       </c>
       <c r="AC357" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="AD357" t="s">
         <v>62</v>
       </c>
       <c r="AE357" s="1">
-        <v>46141</v>
+        <v>46173</v>
       </c>
       <c r="AF357" s="1">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="AG357" s="1">
         <v>46257</v>
       </c>
       <c r="AH357">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI357" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ357">
         <v>0</v>
@@ -69079,8 +69184,8 @@
       <c r="AL357" t="s">
         <v>53</v>
       </c>
-      <c r="AM357" t="s">
-        <v>53</v>
+      <c r="AM357">
+        <v>1142.51</v>
       </c>
       <c r="AN357" t="s">
         <v>53</v>
@@ -69095,10 +69200,10 @@
         <v>53</v>
       </c>
       <c r="AR357" s="1">
-        <v>46151</v>
+        <v>46183</v>
       </c>
       <c r="AS357" s="2">
-        <v>46151.583449074074</v>
+        <v>46183.99928240741</v>
       </c>
       <c r="AT357" s="1" t="s">
         <v>53</v>
@@ -69121,10 +69226,10 @@
     </row>
     <row r="358" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="B358" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="C358" t="s">
         <v>53</v>
@@ -69133,10 +69238,10 @@
         <v>53</v>
       </c>
       <c r="E358" t="s">
-        <v>165</v>
+        <v>53</v>
       </c>
       <c r="F358" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="G358" t="s">
         <v>53</v>
@@ -69145,10 +69250,10 @@
         <v>53</v>
       </c>
       <c r="I358">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J358">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K358">
         <v>0</v>
@@ -69175,13 +69280,13 @@
         <v>88</v>
       </c>
       <c r="S358" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="T358" t="s">
         <v>97</v>
       </c>
       <c r="U358" t="s">
-        <v>1006</v>
+        <v>300</v>
       </c>
       <c r="V358" t="s">
         <v>99</v>
@@ -69196,31 +69301,31 @@
         <v>53</v>
       </c>
       <c r="Z358">
-        <v>4336.2</v>
+        <v>11002.2</v>
       </c>
       <c r="AA358" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="AB358" t="s">
         <v>763</v>
       </c>
       <c r="AC358" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="AD358" t="s">
         <v>62</v>
       </c>
       <c r="AE358" s="1">
-        <v>46158</v>
+        <v>46141</v>
       </c>
       <c r="AF358" s="1">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="AG358" s="1">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="AH358">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AI358" t="s">
         <v>63</v>
@@ -69250,10 +69355,10 @@
         <v>53</v>
       </c>
       <c r="AR358" s="1">
-        <v>46160</v>
+        <v>46151</v>
       </c>
       <c r="AS358" s="2">
-        <v>46160.40216435185</v>
+        <v>46151.583449074074</v>
       </c>
       <c r="AT358" s="1" t="s">
         <v>53</v>
@@ -69262,7 +69367,7 @@
         <v>53</v>
       </c>
       <c r="AV358" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="AW358" t="s">
         <v>53</v>
@@ -69276,10 +69381,10 @@
     </row>
     <row r="359" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>2214</v>
+        <v>2221</v>
       </c>
       <c r="B359" t="s">
-        <v>2215</v>
+        <v>2222</v>
       </c>
       <c r="C359" t="s">
         <v>53</v>
@@ -69291,7 +69396,7 @@
         <v>165</v>
       </c>
       <c r="F359" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="G359" t="s">
         <v>53</v>
@@ -69330,7 +69435,7 @@
         <v>88</v>
       </c>
       <c r="S359" t="s">
-        <v>2221</v>
+        <v>2224</v>
       </c>
       <c r="T359" t="s">
         <v>97</v>
@@ -69351,31 +69456,31 @@
         <v>53</v>
       </c>
       <c r="Z359">
-        <v>7399.35</v>
+        <v>4336.2</v>
       </c>
       <c r="AA359" t="s">
-        <v>2222</v>
+        <v>2225</v>
       </c>
       <c r="AB359" t="s">
         <v>763</v>
       </c>
       <c r="AC359" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="AD359" t="s">
         <v>62</v>
       </c>
       <c r="AE359" s="1">
-        <v>46160</v>
+        <v>46158</v>
       </c>
       <c r="AF359" s="1">
         <v>46247</v>
       </c>
       <c r="AG359" s="1">
-        <v>46256</v>
+        <v>46252</v>
       </c>
       <c r="AH359">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AI359" t="s">
         <v>63</v>
@@ -69405,10 +69510,10 @@
         <v>53</v>
       </c>
       <c r="AR359" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="AS359" s="2">
-        <v>46170.66144675926</v>
+        <v>46160.40216435185</v>
       </c>
       <c r="AT359" s="1" t="s">
         <v>53</v>
@@ -69431,10 +69536,10 @@
     </row>
     <row r="360" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>2214</v>
+        <v>2221</v>
       </c>
       <c r="B360" t="s">
-        <v>2215</v>
+        <v>2222</v>
       </c>
       <c r="C360" t="s">
         <v>53</v>
@@ -69443,10 +69548,10 @@
         <v>53</v>
       </c>
       <c r="E360" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="F360" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="G360" t="s">
         <v>53</v>
@@ -69476,16 +69581,16 @@
         <v>53</v>
       </c>
       <c r="P360" t="s">
-        <v>804</v>
+        <v>88</v>
       </c>
       <c r="Q360" t="s">
-        <v>53</v>
+        <v>766</v>
       </c>
       <c r="R360" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="S360" t="s">
-        <v>2225</v>
+        <v>2228</v>
       </c>
       <c r="T360" t="s">
         <v>97</v>
@@ -69506,22 +69611,22 @@
         <v>53</v>
       </c>
       <c r="Z360">
-        <v>7398.81</v>
+        <v>7399.35</v>
       </c>
       <c r="AA360" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="AB360" t="s">
         <v>763</v>
       </c>
       <c r="AC360" t="s">
-        <v>2227</v>
+        <v>2230</v>
       </c>
       <c r="AD360" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE360" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="AF360" s="1">
         <v>46247</v>
@@ -69536,7 +69641,7 @@
         <v>63</v>
       </c>
       <c r="AJ360">
-        <v>-7398.81</v>
+        <v>0</v>
       </c>
       <c r="AK360" t="s">
         <v>64</v>
@@ -69559,11 +69664,11 @@
       <c r="AQ360" t="s">
         <v>53</v>
       </c>
-      <c r="AR360" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS360" s="2" t="s">
-        <v>53</v>
+      <c r="AR360" s="1">
+        <v>46170</v>
+      </c>
+      <c r="AS360" s="2">
+        <v>46170.66144675926</v>
       </c>
       <c r="AT360" s="1" t="s">
         <v>53</v>
@@ -69572,7 +69677,7 @@
         <v>53</v>
       </c>
       <c r="AV360" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="AW360" t="s">
         <v>53</v>
@@ -69586,10 +69691,10 @@
     </row>
     <row r="361" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>588</v>
+        <v>2221</v>
       </c>
       <c r="B361" t="s">
-        <v>2228</v>
+        <v>2222</v>
       </c>
       <c r="C361" t="s">
         <v>53</v>
@@ -69598,25 +69703,25 @@
         <v>53</v>
       </c>
       <c r="E361" t="s">
-        <v>498</v>
+        <v>53</v>
       </c>
       <c r="F361" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="G361" t="s">
-        <v>2230</v>
+        <v>53</v>
       </c>
       <c r="H361" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I361">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J361">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K361">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L361" s="1" t="s">
         <v>53</v>
@@ -69631,7 +69736,7 @@
         <v>53</v>
       </c>
       <c r="P361" t="s">
-        <v>189</v>
+        <v>804</v>
       </c>
       <c r="Q361" t="s">
         <v>53</v>
@@ -69640,16 +69745,16 @@
         <v>53</v>
       </c>
       <c r="S361" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="T361" t="s">
         <v>97</v>
       </c>
       <c r="U361" t="s">
-        <v>190</v>
+        <v>1006</v>
       </c>
       <c r="V361" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="W361" t="s">
         <v>53</v>
@@ -69661,37 +69766,37 @@
         <v>53</v>
       </c>
       <c r="Z361">
-        <v>8665</v>
+        <v>7398.81</v>
       </c>
       <c r="AA361" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="AB361" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC361" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="AD361" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE361" s="1">
-        <v>46030</v>
+        <v>46170</v>
       </c>
       <c r="AF361" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="AG361" s="1">
-        <v>46262</v>
+        <v>46256</v>
       </c>
       <c r="AH361">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AI361" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ361">
-        <v>0</v>
+        <v>-7398.81</v>
       </c>
       <c r="AK361" t="s">
         <v>64</v>
@@ -69699,8 +69804,8 @@
       <c r="AL361" t="s">
         <v>53</v>
       </c>
-      <c r="AM361">
-        <v>1299.75</v>
+      <c r="AM361" t="s">
+        <v>53</v>
       </c>
       <c r="AN361" t="s">
         <v>53</v>
@@ -69714,11 +69819,11 @@
       <c r="AQ361" t="s">
         <v>53</v>
       </c>
-      <c r="AR361" s="1">
-        <v>46032</v>
-      </c>
-      <c r="AS361" s="2">
-        <v>46032.64398148148</v>
+      <c r="AR361" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS361" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT361" s="1" t="s">
         <v>53</v>
@@ -69741,7 +69846,7 @@
     </row>
     <row r="362" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>2234</v>
+        <v>588</v>
       </c>
       <c r="B362" t="s">
         <v>2235</v>
@@ -69753,7 +69858,7 @@
         <v>53</v>
       </c>
       <c r="E362" t="s">
-        <v>165</v>
+        <v>498</v>
       </c>
       <c r="F362" t="s">
         <v>2236</v>
@@ -69765,13 +69870,13 @@
         <v>86</v>
       </c>
       <c r="I362">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J362">
         <v>2</v>
       </c>
       <c r="K362">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L362" s="1" t="s">
         <v>53</v>
@@ -69786,13 +69891,13 @@
         <v>53</v>
       </c>
       <c r="P362" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="Q362" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="R362" t="s">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="S362" t="s">
         <v>2238</v>
@@ -69804,7 +69909,7 @@
         <v>190</v>
       </c>
       <c r="V362" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="W362" t="s">
         <v>53</v>
@@ -69816,7 +69921,7 @@
         <v>53</v>
       </c>
       <c r="Z362">
-        <v>980</v>
+        <v>8665</v>
       </c>
       <c r="AA362" t="s">
         <v>2239</v>
@@ -69831,19 +69936,19 @@
         <v>62</v>
       </c>
       <c r="AE362" s="1">
-        <v>46048</v>
+        <v>46030</v>
       </c>
       <c r="AF362" s="1">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="AG362" s="1">
-        <v>46254</v>
+        <v>46262</v>
       </c>
       <c r="AH362">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AI362" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ362">
         <v>0</v>
@@ -69855,7 +69960,7 @@
         <v>53</v>
       </c>
       <c r="AM362">
-        <v>147</v>
+        <v>1299.75</v>
       </c>
       <c r="AN362" t="s">
         <v>53</v>
@@ -69870,10 +69975,10 @@
         <v>53</v>
       </c>
       <c r="AR362" s="1">
-        <v>46153</v>
+        <v>46032</v>
       </c>
       <c r="AS362" s="2">
-        <v>46153.715682870374</v>
+        <v>46032.64398148148</v>
       </c>
       <c r="AT362" s="1" t="s">
         <v>53</v>
@@ -69896,10 +70001,10 @@
     </row>
     <row r="363" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>1928</v>
+        <v>2241</v>
       </c>
       <c r="B363" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="C363" t="s">
         <v>53</v>
@@ -69911,10 +70016,10 @@
         <v>165</v>
       </c>
       <c r="F363" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="G363" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="H363" t="s">
         <v>86</v>
@@ -69944,13 +70049,13 @@
         <v>177</v>
       </c>
       <c r="Q363" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="R363" t="s">
         <v>177</v>
       </c>
       <c r="S363" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="T363" t="s">
         <v>97</v>
@@ -69971,28 +70076,28 @@
         <v>53</v>
       </c>
       <c r="Z363">
-        <v>982.77</v>
+        <v>980</v>
       </c>
       <c r="AA363" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="AB363" t="s">
         <v>180</v>
       </c>
       <c r="AC363" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="AD363" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE363" s="1">
-        <v>46115</v>
+        <v>46048</v>
       </c>
       <c r="AF363" s="1">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="AG363" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="AH363">
         <v>3</v>
@@ -70001,7 +70106,7 @@
         <v>63</v>
       </c>
       <c r="AJ363">
-        <v>-982.77</v>
+        <v>0</v>
       </c>
       <c r="AK363" t="s">
         <v>64</v>
@@ -70010,7 +70115,7 @@
         <v>53</v>
       </c>
       <c r="AM363">
-        <v>147.42</v>
+        <v>147</v>
       </c>
       <c r="AN363" t="s">
         <v>53</v>
@@ -70024,11 +70129,11 @@
       <c r="AQ363" t="s">
         <v>53</v>
       </c>
-      <c r="AR363" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS363" s="2" t="s">
-        <v>53</v>
+      <c r="AR363" s="1">
+        <v>46153</v>
+      </c>
+      <c r="AS363" s="2">
+        <v>46153.715682870374</v>
       </c>
       <c r="AT363" s="1" t="s">
         <v>53</v>
@@ -70051,7 +70156,7 @@
     </row>
     <row r="364" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>2247</v>
+        <v>1928</v>
       </c>
       <c r="B364" t="s">
         <v>2248</v>
@@ -70063,7 +70168,7 @@
         <v>53</v>
       </c>
       <c r="E364" t="s">
-        <v>312</v>
+        <v>165</v>
       </c>
       <c r="F364" t="s">
         <v>2249</v>
@@ -70075,10 +70180,10 @@
         <v>86</v>
       </c>
       <c r="I364">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J364">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K364">
         <v>0</v>
@@ -70096,13 +70201,13 @@
         <v>53</v>
       </c>
       <c r="P364" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Q364" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="R364" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="S364" t="s">
         <v>2251</v>
@@ -70114,7 +70219,7 @@
         <v>190</v>
       </c>
       <c r="V364" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="W364" t="s">
         <v>53</v>
@@ -70126,7 +70231,7 @@
         <v>53</v>
       </c>
       <c r="Z364">
-        <v>2599.95</v>
+        <v>982.77</v>
       </c>
       <c r="AA364" t="s">
         <v>2252</v>
@@ -70141,22 +70246,22 @@
         <v>1361</v>
       </c>
       <c r="AE364" s="1">
-        <v>46139</v>
+        <v>46115</v>
       </c>
       <c r="AF364" s="1">
-        <v>46259</v>
+        <v>46252</v>
       </c>
       <c r="AG364" s="1">
-        <v>46264</v>
+        <v>46255</v>
       </c>
       <c r="AH364">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI364" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ364">
-        <v>-2599.95</v>
+        <v>-982.77</v>
       </c>
       <c r="AK364" t="s">
         <v>64</v>
@@ -70165,7 +70270,7 @@
         <v>53</v>
       </c>
       <c r="AM364">
-        <v>389.99</v>
+        <v>147.42</v>
       </c>
       <c r="AN364" t="s">
         <v>53</v>
@@ -70218,22 +70323,22 @@
         <v>53</v>
       </c>
       <c r="E365" t="s">
-        <v>53</v>
+        <v>312</v>
       </c>
       <c r="F365" t="s">
         <v>2256</v>
       </c>
       <c r="G365" t="s">
-        <v>53</v>
+        <v>2257</v>
       </c>
       <c r="H365" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I365">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J365">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K365">
         <v>0</v>
@@ -70251,25 +70356,25 @@
         <v>53</v>
       </c>
       <c r="P365" t="s">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="Q365" t="s">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="R365" t="s">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="S365" t="s">
-        <v>53</v>
+        <v>2258</v>
       </c>
       <c r="T365" t="s">
         <v>97</v>
       </c>
       <c r="U365" t="s">
-        <v>736</v>
+        <v>190</v>
       </c>
       <c r="V365" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="W365" t="s">
         <v>53</v>
@@ -70281,37 +70386,37 @@
         <v>53</v>
       </c>
       <c r="Z365">
-        <v>0</v>
+        <v>2599.95</v>
       </c>
       <c r="AA365" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="AB365" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AC365" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="AD365" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE365" s="1">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="AF365" s="1">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="AG365" s="1">
-        <v>46556</v>
+        <v>46264</v>
       </c>
       <c r="AH365">
-        <v>290</v>
+        <v>5</v>
       </c>
       <c r="AI365" t="s">
         <v>112</v>
       </c>
       <c r="AJ365">
-        <v>0</v>
+        <v>-2599.95</v>
       </c>
       <c r="AK365" t="s">
         <v>64</v>
@@ -70319,8 +70424,8 @@
       <c r="AL365" t="s">
         <v>53</v>
       </c>
-      <c r="AM365" t="s">
-        <v>53</v>
+      <c r="AM365">
+        <v>389.99</v>
       </c>
       <c r="AN365" t="s">
         <v>53</v>
@@ -70334,11 +70439,11 @@
       <c r="AQ365" t="s">
         <v>53</v>
       </c>
-      <c r="AR365" s="1">
-        <v>46140</v>
-      </c>
-      <c r="AS365" s="2">
-        <v>46140.55385416667</v>
+      <c r="AR365" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS365" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT365" s="1" t="s">
         <v>53</v>
@@ -70347,7 +70452,7 @@
         <v>53</v>
       </c>
       <c r="AV365" t="s">
-        <v>479</v>
+        <v>53</v>
       </c>
       <c r="AW365" t="s">
         <v>53</v>
@@ -70361,10 +70466,10 @@
     </row>
     <row r="366" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>2254</v>
+        <v>2261</v>
       </c>
       <c r="B366" t="s">
-        <v>2255</v>
+        <v>2262</v>
       </c>
       <c r="C366" t="s">
         <v>53</v>
@@ -70373,16 +70478,16 @@
         <v>53</v>
       </c>
       <c r="E366" t="s">
-        <v>159</v>
+        <v>53</v>
       </c>
       <c r="F366" t="s">
-        <v>2259</v>
+        <v>2263</v>
       </c>
       <c r="G366" t="s">
-        <v>2260</v>
+        <v>53</v>
       </c>
       <c r="H366" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="I366">
         <v>1</v>
@@ -70409,10 +70514,10 @@
         <v>67</v>
       </c>
       <c r="Q366" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="R366" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="S366" t="s">
         <v>53</v>
@@ -70424,7 +70529,7 @@
         <v>736</v>
       </c>
       <c r="V366" t="s">
-        <v>2261</v>
+        <v>125</v>
       </c>
       <c r="W366" t="s">
         <v>53</v>
@@ -70436,19 +70541,19 @@
         <v>53</v>
       </c>
       <c r="Z366">
-        <v>62837.27</v>
+        <v>0</v>
       </c>
       <c r="AA366" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="AB366" t="s">
         <v>60</v>
       </c>
       <c r="AC366" t="s">
-        <v>2258</v>
+        <v>2265</v>
       </c>
       <c r="AD366" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE366" s="1">
         <v>46140</v>
@@ -70457,16 +70562,16 @@
         <v>46266</v>
       </c>
       <c r="AG366" s="1">
-        <v>46555</v>
+        <v>46556</v>
       </c>
       <c r="AH366">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI366" t="s">
         <v>112</v>
       </c>
       <c r="AJ366">
-        <v>-62837.27</v>
+        <v>0</v>
       </c>
       <c r="AK366" t="s">
         <v>64</v>
@@ -70489,11 +70594,11 @@
       <c r="AQ366" t="s">
         <v>53</v>
       </c>
-      <c r="AR366" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS366" s="2" t="s">
-        <v>53</v>
+      <c r="AR366" s="1">
+        <v>46140</v>
+      </c>
+      <c r="AS366" s="2">
+        <v>46140.55385416667</v>
       </c>
       <c r="AT366" s="1" t="s">
         <v>53</v>
@@ -70505,7 +70610,7 @@
         <v>479</v>
       </c>
       <c r="AW366" t="s">
-        <v>2263</v>
+        <v>53</v>
       </c>
       <c r="AX366" t="s">
         <v>53</v>
@@ -70516,10 +70621,10 @@
     </row>
     <row r="367" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="B367" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="C367" t="s">
         <v>53</v>
@@ -70537,13 +70642,13 @@
         <v>2267</v>
       </c>
       <c r="H367" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="I367">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J367">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K367">
         <v>0</v>
@@ -70561,25 +70666,25 @@
         <v>53</v>
       </c>
       <c r="P367" t="s">
-        <v>177</v>
+        <v>67</v>
       </c>
       <c r="Q367" t="s">
-        <v>178</v>
+        <v>68</v>
       </c>
       <c r="R367" t="s">
-        <v>177</v>
+        <v>67</v>
       </c>
       <c r="S367" t="s">
-        <v>2268</v>
+        <v>53</v>
       </c>
       <c r="T367" t="s">
         <v>97</v>
       </c>
       <c r="U367" t="s">
-        <v>190</v>
+        <v>736</v>
       </c>
       <c r="V367" t="s">
-        <v>99</v>
+        <v>2268</v>
       </c>
       <c r="W367" t="s">
         <v>53</v>
@@ -70591,37 +70696,37 @@
         <v>53</v>
       </c>
       <c r="Z367">
-        <v>974.7</v>
+        <v>62837.27</v>
       </c>
       <c r="AA367" t="s">
         <v>2269</v>
       </c>
       <c r="AB367" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AC367" t="s">
-        <v>2270</v>
+        <v>2265</v>
       </c>
       <c r="AD367" t="s">
         <v>1361</v>
       </c>
       <c r="AE367" s="1">
-        <v>46069</v>
+        <v>46140</v>
       </c>
       <c r="AF367" s="1">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="AG367" s="1">
-        <v>46271</v>
+        <v>46555</v>
       </c>
       <c r="AH367">
-        <v>3</v>
+        <v>289</v>
       </c>
       <c r="AI367" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ367">
-        <v>-974.7</v>
+        <v>-62837.27</v>
       </c>
       <c r="AK367" t="s">
         <v>64</v>
@@ -70629,8 +70734,8 @@
       <c r="AL367" t="s">
         <v>53</v>
       </c>
-      <c r="AM367">
-        <v>146.21</v>
+      <c r="AM367" t="s">
+        <v>53</v>
       </c>
       <c r="AN367" t="s">
         <v>53</v>
@@ -70657,10 +70762,10 @@
         <v>53</v>
       </c>
       <c r="AV367" t="s">
-        <v>53</v>
+        <v>479</v>
       </c>
       <c r="AW367" t="s">
-        <v>53</v>
+        <v>2270</v>
       </c>
       <c r="AX367" t="s">
         <v>53</v>
@@ -70683,7 +70788,7 @@
         <v>53</v>
       </c>
       <c r="E368" t="s">
-        <v>647</v>
+        <v>159</v>
       </c>
       <c r="F368" t="s">
         <v>2273</v>
@@ -70719,7 +70824,7 @@
         <v>177</v>
       </c>
       <c r="Q368" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="R368" t="s">
         <v>177</v>
@@ -70746,7 +70851,7 @@
         <v>53</v>
       </c>
       <c r="Z368">
-        <v>1092.96</v>
+        <v>974.7</v>
       </c>
       <c r="AA368" t="s">
         <v>2276</v>
@@ -70758,16 +70863,16 @@
         <v>2277</v>
       </c>
       <c r="AD368" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE368" s="1">
-        <v>46085</v>
+        <v>46069</v>
       </c>
       <c r="AF368" s="1">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="AG368" s="1">
-        <v>46275</v>
+        <v>46271</v>
       </c>
       <c r="AH368">
         <v>3</v>
@@ -70776,7 +70881,7 @@
         <v>63</v>
       </c>
       <c r="AJ368">
-        <v>0</v>
+        <v>-974.7</v>
       </c>
       <c r="AK368" t="s">
         <v>64</v>
@@ -70785,7 +70890,7 @@
         <v>53</v>
       </c>
       <c r="AM368">
-        <v>163.94</v>
+        <v>146.21</v>
       </c>
       <c r="AN368" t="s">
         <v>53</v>
@@ -70799,11 +70904,11 @@
       <c r="AQ368" t="s">
         <v>53</v>
       </c>
-      <c r="AR368" s="1">
-        <v>46088</v>
-      </c>
-      <c r="AS368" s="2">
-        <v>46088.145428240736</v>
+      <c r="AR368" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS368" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT368" s="1" t="s">
         <v>53</v>
@@ -70826,10 +70931,10 @@
     </row>
     <row r="369" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>2023</v>
+        <v>2278</v>
       </c>
       <c r="B369" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="C369" t="s">
         <v>53</v>
@@ -70838,22 +70943,22 @@
         <v>53</v>
       </c>
       <c r="E369" t="s">
-        <v>53</v>
+        <v>647</v>
       </c>
       <c r="F369" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="G369" t="s">
-        <v>53</v>
+        <v>2281</v>
       </c>
       <c r="H369" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I369">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J369">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K369">
         <v>0</v>
@@ -70871,25 +70976,25 @@
         <v>53</v>
       </c>
       <c r="P369" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="Q369" t="s">
-        <v>766</v>
+        <v>253</v>
       </c>
       <c r="R369" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="S369" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="T369" t="s">
         <v>97</v>
       </c>
       <c r="U369" t="s">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="V369" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="W369" t="s">
         <v>53</v>
@@ -70901,37 +71006,37 @@
         <v>53</v>
       </c>
       <c r="Z369">
-        <v>1892</v>
+        <v>1092.96</v>
       </c>
       <c r="AA369" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="AB369" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC369" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="AD369" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE369" s="1">
-        <v>46108</v>
+        <v>46085</v>
       </c>
       <c r="AF369" s="1">
+        <v>46272</v>
+      </c>
+      <c r="AG369" s="1">
         <v>46275</v>
       </c>
-      <c r="AG369" s="1">
-        <v>46279</v>
-      </c>
       <c r="AH369">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI369" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ369">
-        <v>-1892</v>
+        <v>0</v>
       </c>
       <c r="AK369" t="s">
         <v>64</v>
@@ -70939,8 +71044,8 @@
       <c r="AL369" t="s">
         <v>53</v>
       </c>
-      <c r="AM369" t="s">
-        <v>53</v>
+      <c r="AM369">
+        <v>163.94</v>
       </c>
       <c r="AN369" t="s">
         <v>53</v>
@@ -70954,11 +71059,11 @@
       <c r="AQ369" t="s">
         <v>53</v>
       </c>
-      <c r="AR369" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS369" s="2" t="s">
-        <v>53</v>
+      <c r="AR369" s="1">
+        <v>46088</v>
+      </c>
+      <c r="AS369" s="2">
+        <v>46088.145428240736</v>
       </c>
       <c r="AT369" s="1" t="s">
         <v>53</v>
@@ -70981,10 +71086,10 @@
     </row>
     <row r="370" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>2283</v>
+        <v>2023</v>
       </c>
       <c r="B370" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="C370" t="s">
         <v>53</v>
@@ -70996,7 +71101,7 @@
         <v>53</v>
       </c>
       <c r="F370" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="G370" t="s">
         <v>53</v>
@@ -71005,10 +71110,10 @@
         <v>53</v>
       </c>
       <c r="I370">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J370">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K370">
         <v>0</v>
@@ -71026,25 +71131,25 @@
         <v>53</v>
       </c>
       <c r="P370" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="Q370" t="s">
-        <v>184</v>
+        <v>766</v>
       </c>
       <c r="R370" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="S370" t="s">
-        <v>53</v>
+        <v>2287</v>
       </c>
       <c r="T370" t="s">
         <v>97</v>
       </c>
       <c r="U370" t="s">
-        <v>736</v>
+        <v>300</v>
       </c>
       <c r="V370" t="s">
-        <v>2286</v>
+        <v>58</v>
       </c>
       <c r="W370" t="s">
         <v>53</v>
@@ -71056,37 +71161,37 @@
         <v>53</v>
       </c>
       <c r="Z370">
-        <v>1594268</v>
+        <v>1892</v>
       </c>
       <c r="AA370" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="AB370" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC370" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="AD370" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE370" s="1">
-        <v>46078</v>
+        <v>46108</v>
       </c>
       <c r="AF370" s="1">
-        <v>46284</v>
+        <v>46275</v>
       </c>
       <c r="AG370" s="1">
-        <v>46544</v>
+        <v>46279</v>
       </c>
       <c r="AH370">
-        <v>260</v>
+        <v>4</v>
       </c>
       <c r="AI370" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="AJ370">
-        <v>0</v>
+        <v>-1892</v>
       </c>
       <c r="AK370" t="s">
         <v>64</v>
@@ -71109,11 +71214,11 @@
       <c r="AQ370" t="s">
         <v>53</v>
       </c>
-      <c r="AR370" s="1">
-        <v>46078</v>
-      </c>
-      <c r="AS370" s="2">
-        <v>46078.393645833334</v>
+      <c r="AR370" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS370" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT370" s="1" t="s">
         <v>53</v>
@@ -71122,7 +71227,7 @@
         <v>53</v>
       </c>
       <c r="AV370" t="s">
-        <v>479</v>
+        <v>53</v>
       </c>
       <c r="AW370" t="s">
         <v>53</v>
@@ -71136,10 +71241,10 @@
     </row>
     <row r="371" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>2283</v>
+        <v>2290</v>
       </c>
       <c r="B371" t="s">
-        <v>2284</v>
+        <v>2291</v>
       </c>
       <c r="C371" t="s">
         <v>53</v>
@@ -71151,7 +71256,7 @@
         <v>53</v>
       </c>
       <c r="F371" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="G371" t="s">
         <v>53</v>
@@ -71199,7 +71304,7 @@
         <v>736</v>
       </c>
       <c r="V371" t="s">
-        <v>2286</v>
+        <v>2293</v>
       </c>
       <c r="W371" t="s">
         <v>53</v>
@@ -71211,19 +71316,19 @@
         <v>53</v>
       </c>
       <c r="Z371">
-        <v>81900</v>
+        <v>1594268</v>
       </c>
       <c r="AA371" t="s">
-        <v>2290</v>
+        <v>2294</v>
       </c>
       <c r="AB371" t="s">
         <v>180</v>
       </c>
       <c r="AC371" t="s">
-        <v>2291</v>
+        <v>2295</v>
       </c>
       <c r="AD371" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE371" s="1">
         <v>46078</v>
@@ -71241,7 +71346,7 @@
         <v>37</v>
       </c>
       <c r="AJ371">
-        <v>-81900</v>
+        <v>0</v>
       </c>
       <c r="AK371" t="s">
         <v>64</v>
@@ -71264,11 +71369,11 @@
       <c r="AQ371" t="s">
         <v>53</v>
       </c>
-      <c r="AR371" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS371" s="2" t="s">
-        <v>53</v>
+      <c r="AR371" s="1">
+        <v>46078</v>
+      </c>
+      <c r="AS371" s="2">
+        <v>46078.393645833334</v>
       </c>
       <c r="AT371" s="1" t="s">
         <v>53</v>
@@ -71291,10 +71396,10 @@
     </row>
     <row r="372" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="B372" t="s">
-        <v>733</v>
+        <v>2291</v>
       </c>
       <c r="C372" t="s">
         <v>53</v>
@@ -71306,7 +71411,7 @@
         <v>53</v>
       </c>
       <c r="F372" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
       <c r="G372" t="s">
         <v>53</v>
@@ -71315,10 +71420,10 @@
         <v>53</v>
       </c>
       <c r="I372">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J372">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K372">
         <v>0</v>
@@ -71336,13 +71441,13 @@
         <v>53</v>
       </c>
       <c r="P372" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="Q372" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="R372" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="S372" t="s">
         <v>53</v>
@@ -71354,7 +71459,7 @@
         <v>736</v>
       </c>
       <c r="V372" t="s">
-        <v>2286</v>
+        <v>2293</v>
       </c>
       <c r="W372" t="s">
         <v>53</v>
@@ -71366,22 +71471,22 @@
         <v>53</v>
       </c>
       <c r="Z372">
-        <v>40957.8</v>
+        <v>81900</v>
       </c>
       <c r="AA372" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
       <c r="AB372" t="s">
         <v>180</v>
       </c>
       <c r="AC372" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="AD372" t="s">
         <v>1361</v>
       </c>
       <c r="AE372" s="1">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="AF372" s="1">
         <v>46284</v>
@@ -71396,7 +71501,7 @@
         <v>37</v>
       </c>
       <c r="AJ372">
-        <v>-40957.8</v>
+        <v>-81900</v>
       </c>
       <c r="AK372" t="s">
         <v>64</v>
@@ -71446,10 +71551,10 @@
     </row>
     <row r="373" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>2296</v>
+        <v>2299</v>
       </c>
       <c r="B373" t="s">
-        <v>2297</v>
+        <v>733</v>
       </c>
       <c r="C373" t="s">
         <v>53</v>
@@ -71461,7 +71566,7 @@
         <v>53</v>
       </c>
       <c r="F373" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="G373" t="s">
         <v>53</v>
@@ -71494,7 +71599,7 @@
         <v>177</v>
       </c>
       <c r="Q373" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="R373" t="s">
         <v>177</v>
@@ -71509,7 +71614,7 @@
         <v>736</v>
       </c>
       <c r="V373" t="s">
-        <v>2286</v>
+        <v>2293</v>
       </c>
       <c r="W373" t="s">
         <v>53</v>
@@ -71521,22 +71626,22 @@
         <v>53</v>
       </c>
       <c r="Z373">
-        <v>41080</v>
+        <v>40957.8</v>
       </c>
       <c r="AA373" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="AB373" t="s">
         <v>180</v>
       </c>
       <c r="AC373" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="AD373" t="s">
         <v>1361</v>
       </c>
       <c r="AE373" s="1">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="AF373" s="1">
         <v>46284</v>
@@ -71548,10 +71653,10 @@
         <v>260</v>
       </c>
       <c r="AI373" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="AJ373">
-        <v>-41080</v>
+        <v>-40957.8</v>
       </c>
       <c r="AK373" t="s">
         <v>64</v>
@@ -71601,10 +71706,10 @@
     </row>
     <row r="374" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>171</v>
+        <v>2303</v>
       </c>
       <c r="B374" t="s">
-        <v>79</v>
+        <v>2304</v>
       </c>
       <c r="C374" t="s">
         <v>53</v>
@@ -71616,7 +71721,7 @@
         <v>53</v>
       </c>
       <c r="F374" t="s">
-        <v>2301</v>
+        <v>2305</v>
       </c>
       <c r="G374" t="s">
         <v>53</v>
@@ -71646,25 +71751,25 @@
         <v>53</v>
       </c>
       <c r="P374" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="Q374" t="s">
-        <v>492</v>
+        <v>253</v>
       </c>
       <c r="R374" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="S374" t="s">
         <v>53</v>
       </c>
       <c r="T374" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="U374" t="s">
-        <v>53</v>
+        <v>736</v>
       </c>
       <c r="V374" t="s">
-        <v>58</v>
+        <v>2293</v>
       </c>
       <c r="W374" t="s">
         <v>53</v>
@@ -71676,37 +71781,37 @@
         <v>53</v>
       </c>
       <c r="Z374">
-        <v>1487</v>
+        <v>41080</v>
       </c>
       <c r="AA374" t="s">
-        <v>2302</v>
+        <v>2306</v>
       </c>
       <c r="AB374" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AC374" t="s">
-        <v>2303</v>
+        <v>2307</v>
       </c>
       <c r="AD374" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE374" s="1">
-        <v>46099</v>
+        <v>46134</v>
       </c>
       <c r="AF374" s="1">
-        <v>46286</v>
+        <v>46284</v>
       </c>
       <c r="AG374" s="1">
-        <v>46290</v>
+        <v>46544</v>
       </c>
       <c r="AH374">
-        <v>4</v>
+        <v>260</v>
       </c>
       <c r="AI374" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ374">
-        <v>0</v>
+        <v>-41080</v>
       </c>
       <c r="AK374" t="s">
         <v>64</v>
@@ -71729,11 +71834,11 @@
       <c r="AQ374" t="s">
         <v>53</v>
       </c>
-      <c r="AR374" s="1">
-        <v>46175</v>
-      </c>
-      <c r="AS374" s="2">
-        <v>46175.397372685184</v>
+      <c r="AR374" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS374" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT374" s="1" t="s">
         <v>53</v>
@@ -71742,7 +71847,7 @@
         <v>53</v>
       </c>
       <c r="AV374" t="s">
-        <v>53</v>
+        <v>479</v>
       </c>
       <c r="AW374" t="s">
         <v>53</v>
@@ -71756,10 +71861,10 @@
     </row>
     <row r="375" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>2304</v>
+        <v>171</v>
       </c>
       <c r="B375" t="s">
-        <v>2305</v>
+        <v>79</v>
       </c>
       <c r="C375" t="s">
         <v>53</v>
@@ -71771,7 +71876,7 @@
         <v>53</v>
       </c>
       <c r="F375" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="G375" t="s">
         <v>53</v>
@@ -71780,10 +71885,10 @@
         <v>53</v>
       </c>
       <c r="I375">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J375">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K375">
         <v>0</v>
@@ -71801,25 +71906,25 @@
         <v>53</v>
       </c>
       <c r="P375" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="Q375" t="s">
-        <v>766</v>
+        <v>492</v>
       </c>
       <c r="R375" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="S375" t="s">
-        <v>2307</v>
+        <v>53</v>
       </c>
       <c r="T375" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="U375" t="s">
-        <v>1006</v>
+        <v>53</v>
       </c>
       <c r="V375" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="W375" t="s">
         <v>53</v>
@@ -71831,37 +71936,37 @@
         <v>53</v>
       </c>
       <c r="Z375">
-        <v>13630.5</v>
+        <v>1487</v>
       </c>
       <c r="AA375" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="AB375" t="s">
-        <v>763</v>
+        <v>60</v>
       </c>
       <c r="AC375" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="AD375" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE375" s="1">
-        <v>46144</v>
+        <v>46099</v>
       </c>
       <c r="AF375" s="1">
         <v>46286</v>
       </c>
       <c r="AG375" s="1">
-        <v>46301</v>
+        <v>46290</v>
       </c>
       <c r="AH375">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AI375" t="s">
         <v>63</v>
       </c>
       <c r="AJ375">
-        <v>-13630.5</v>
+        <v>0</v>
       </c>
       <c r="AK375" t="s">
         <v>64</v>
@@ -71884,11 +71989,11 @@
       <c r="AQ375" t="s">
         <v>53</v>
       </c>
-      <c r="AR375" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS375" s="2" t="s">
-        <v>53</v>
+      <c r="AR375" s="1">
+        <v>46175</v>
+      </c>
+      <c r="AS375" s="2">
+        <v>46175.397372685184</v>
       </c>
       <c r="AT375" s="1" t="s">
         <v>53</v>
@@ -71911,10 +72016,10 @@
     </row>
     <row r="376" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="B376" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="C376" t="s">
         <v>53</v>
@@ -71923,16 +72028,16 @@
         <v>53</v>
       </c>
       <c r="E376" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F376" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="G376" t="s">
-        <v>2313</v>
+        <v>53</v>
       </c>
       <c r="H376" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I376">
         <v>2</v>
@@ -71956,13 +72061,13 @@
         <v>53</v>
       </c>
       <c r="P376" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="Q376" t="s">
-        <v>188</v>
+        <v>766</v>
       </c>
       <c r="R376" t="s">
-        <v>189</v>
+        <v>88</v>
       </c>
       <c r="S376" t="s">
         <v>2314</v>
@@ -71971,7 +72076,7 @@
         <v>97</v>
       </c>
       <c r="U376" t="s">
-        <v>190</v>
+        <v>1006</v>
       </c>
       <c r="V376" t="s">
         <v>99</v>
@@ -71986,13 +72091,13 @@
         <v>53</v>
       </c>
       <c r="Z376">
-        <v>918</v>
+        <v>13630.5</v>
       </c>
       <c r="AA376" t="s">
         <v>2315</v>
       </c>
       <c r="AB376" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC376" t="s">
         <v>2316</v>
@@ -72001,22 +72106,22 @@
         <v>1361</v>
       </c>
       <c r="AE376" s="1">
-        <v>46075</v>
+        <v>46144</v>
       </c>
       <c r="AF376" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="AG376" s="1">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="AH376">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AI376" t="s">
         <v>63</v>
       </c>
       <c r="AJ376">
-        <v>-918</v>
+        <v>-13630.5</v>
       </c>
       <c r="AK376" t="s">
         <v>64</v>
@@ -72024,8 +72129,8 @@
       <c r="AL376" t="s">
         <v>53</v>
       </c>
-      <c r="AM376">
-        <v>137.7</v>
+      <c r="AM376" t="s">
+        <v>53</v>
       </c>
       <c r="AN376" t="s">
         <v>53</v>
@@ -72066,10 +72171,10 @@
     </row>
     <row r="377" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>867</v>
+        <v>2317</v>
       </c>
       <c r="B377" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="C377" t="s">
         <v>53</v>
@@ -72078,22 +72183,22 @@
         <v>53</v>
       </c>
       <c r="E377" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F377" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="G377" t="s">
-        <v>53</v>
+        <v>2320</v>
       </c>
       <c r="H377" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I377">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J377">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K377">
         <v>0</v>
@@ -72111,22 +72216,22 @@
         <v>53</v>
       </c>
       <c r="P377" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Q377" t="s">
-        <v>53</v>
+        <v>188</v>
       </c>
       <c r="R377" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="S377" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="T377" t="s">
         <v>97</v>
       </c>
       <c r="U377" t="s">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="V377" t="s">
         <v>99</v>
@@ -72141,28 +72246,28 @@
         <v>53</v>
       </c>
       <c r="Z377">
-        <v>1395.99</v>
+        <v>918</v>
       </c>
       <c r="AA377" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="AB377" t="s">
         <v>180</v>
       </c>
       <c r="AC377" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="AD377" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE377" s="1">
-        <v>45989</v>
+        <v>46075</v>
       </c>
       <c r="AF377" s="1">
-        <v>46330</v>
+        <v>46290</v>
       </c>
       <c r="AG377" s="1">
-        <v>46333</v>
+        <v>46293</v>
       </c>
       <c r="AH377">
         <v>3</v>
@@ -72171,7 +72276,7 @@
         <v>63</v>
       </c>
       <c r="AJ377">
-        <v>0</v>
+        <v>-918</v>
       </c>
       <c r="AK377" t="s">
         <v>64</v>
@@ -72179,8 +72284,8 @@
       <c r="AL377" t="s">
         <v>53</v>
       </c>
-      <c r="AM377" t="s">
-        <v>53</v>
+      <c r="AM377">
+        <v>137.7</v>
       </c>
       <c r="AN377" t="s">
         <v>53</v>
@@ -72194,11 +72299,11 @@
       <c r="AQ377" t="s">
         <v>53</v>
       </c>
-      <c r="AR377" s="1">
-        <v>46040</v>
-      </c>
-      <c r="AS377" s="2">
-        <v>46040.82962962963</v>
+      <c r="AR377" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS377" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT377" s="1" t="s">
         <v>53</v>
@@ -72221,10 +72326,10 @@
     </row>
     <row r="378" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>2322</v>
+        <v>867</v>
       </c>
       <c r="B378" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="C378" t="s">
         <v>53</v>
@@ -72236,7 +72341,7 @@
         <v>53</v>
       </c>
       <c r="F378" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="G378" t="s">
         <v>53</v>
@@ -72266,16 +72371,16 @@
         <v>53</v>
       </c>
       <c r="P378" t="s">
-        <v>804</v>
+        <v>183</v>
       </c>
       <c r="Q378" t="s">
-        <v>808</v>
+        <v>53</v>
       </c>
       <c r="R378" t="s">
-        <v>804</v>
+        <v>53</v>
       </c>
       <c r="S378" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="T378" t="s">
         <v>97</v>
@@ -72284,7 +72389,7 @@
         <v>300</v>
       </c>
       <c r="V378" t="s">
-        <v>744</v>
+        <v>99</v>
       </c>
       <c r="W378" t="s">
         <v>53</v>
@@ -72296,37 +72401,37 @@
         <v>53</v>
       </c>
       <c r="Z378">
-        <v>1872.8</v>
+        <v>1395.99</v>
       </c>
       <c r="AA378" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="AB378" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC378" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="AD378" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE378" s="1">
-        <v>46120</v>
+        <v>45989</v>
       </c>
       <c r="AF378" s="1">
-        <v>46375</v>
+        <v>46330</v>
       </c>
       <c r="AG378" s="1">
-        <v>46379</v>
+        <v>46333</v>
       </c>
       <c r="AH378">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI378" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ378">
-        <v>-1872.8</v>
+        <v>0</v>
       </c>
       <c r="AK378" t="s">
         <v>64</v>
@@ -72349,11 +72454,11 @@
       <c r="AQ378" t="s">
         <v>53</v>
       </c>
-      <c r="AR378" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS378" s="2" t="s">
-        <v>53</v>
+      <c r="AR378" s="1">
+        <v>46040</v>
+      </c>
+      <c r="AS378" s="2">
+        <v>46040.82962962963</v>
       </c>
       <c r="AT378" s="1" t="s">
         <v>53</v>
@@ -72376,10 +72481,10 @@
     </row>
     <row r="379" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="B379" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="C379" t="s">
         <v>53</v>
@@ -72391,7 +72496,7 @@
         <v>53</v>
       </c>
       <c r="F379" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="G379" t="s">
         <v>53</v>
@@ -72421,16 +72526,16 @@
         <v>53</v>
       </c>
       <c r="P379" t="s">
-        <v>189</v>
+        <v>804</v>
       </c>
       <c r="Q379" t="s">
-        <v>188</v>
+        <v>808</v>
       </c>
       <c r="R379" t="s">
-        <v>189</v>
+        <v>804</v>
       </c>
       <c r="S379" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="T379" t="s">
         <v>97</v>
@@ -72439,7 +72544,7 @@
         <v>300</v>
       </c>
       <c r="V379" t="s">
-        <v>99</v>
+        <v>744</v>
       </c>
       <c r="W379" t="s">
         <v>53</v>
@@ -72451,28 +72556,28 @@
         <v>53</v>
       </c>
       <c r="Z379">
-        <v>3370</v>
+        <v>1872.8</v>
       </c>
       <c r="AA379" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="AB379" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC379" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="AD379" t="s">
         <v>1361</v>
       </c>
       <c r="AE379" s="1">
-        <v>46106</v>
+        <v>46120</v>
       </c>
       <c r="AF379" s="1">
-        <v>46385</v>
+        <v>46375</v>
       </c>
       <c r="AG379" s="1">
-        <v>46389</v>
+        <v>46379</v>
       </c>
       <c r="AH379">
         <v>4</v>
@@ -72481,7 +72586,7 @@
         <v>112</v>
       </c>
       <c r="AJ379">
-        <v>-3370</v>
+        <v>-1872.8</v>
       </c>
       <c r="AK379" t="s">
         <v>64</v>
@@ -72531,10 +72636,10 @@
     </row>
     <row r="380" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="B380" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="C380" t="s">
         <v>53</v>
@@ -72546,7 +72651,7 @@
         <v>53</v>
       </c>
       <c r="F380" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="G380" t="s">
         <v>53</v>
@@ -72576,16 +72681,16 @@
         <v>53</v>
       </c>
       <c r="P380" t="s">
-        <v>804</v>
+        <v>189</v>
       </c>
       <c r="Q380" t="s">
-        <v>808</v>
+        <v>188</v>
       </c>
       <c r="R380" t="s">
-        <v>804</v>
+        <v>189</v>
       </c>
       <c r="S380" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="T380" t="s">
         <v>97</v>
@@ -72594,7 +72699,7 @@
         <v>300</v>
       </c>
       <c r="V380" t="s">
-        <v>744</v>
+        <v>99</v>
       </c>
       <c r="W380" t="s">
         <v>53</v>
@@ -72606,37 +72711,37 @@
         <v>53</v>
       </c>
       <c r="Z380">
-        <v>1272</v>
+        <v>3370</v>
       </c>
       <c r="AA380" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="AB380" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC380" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="AD380" t="s">
         <v>1361</v>
       </c>
       <c r="AE380" s="1">
-        <v>46120</v>
+        <v>46106</v>
       </c>
       <c r="AF380" s="1">
         <v>46385</v>
       </c>
       <c r="AG380" s="1">
-        <v>46388</v>
+        <v>46389</v>
       </c>
       <c r="AH380">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI380" t="s">
         <v>112</v>
       </c>
       <c r="AJ380">
-        <v>-1272</v>
+        <v>-3370</v>
       </c>
       <c r="AK380" t="s">
         <v>64</v>
@@ -72686,10 +72791,10 @@
     </row>
     <row r="381" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="B381" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="C381" t="s">
         <v>53</v>
@@ -72701,7 +72806,7 @@
         <v>53</v>
       </c>
       <c r="F381" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="G381" t="s">
         <v>53</v>
@@ -72731,16 +72836,16 @@
         <v>53</v>
       </c>
       <c r="P381" t="s">
-        <v>189</v>
+        <v>804</v>
       </c>
       <c r="Q381" t="s">
-        <v>205</v>
+        <v>808</v>
       </c>
       <c r="R381" t="s">
-        <v>189</v>
+        <v>804</v>
       </c>
       <c r="S381" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="T381" t="s">
         <v>97</v>
@@ -72749,7 +72854,7 @@
         <v>300</v>
       </c>
       <c r="V381" t="s">
-        <v>99</v>
+        <v>744</v>
       </c>
       <c r="W381" t="s">
         <v>53</v>
@@ -72761,37 +72866,37 @@
         <v>53</v>
       </c>
       <c r="Z381">
-        <v>2300</v>
+        <v>1272</v>
       </c>
       <c r="AA381" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="AB381" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC381" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="AD381" t="s">
         <v>1361</v>
       </c>
       <c r="AE381" s="1">
-        <v>46141</v>
+        <v>46120</v>
       </c>
       <c r="AF381" s="1">
-        <v>46582</v>
+        <v>46385</v>
       </c>
       <c r="AG381" s="1">
-        <v>46586</v>
+        <v>46388</v>
       </c>
       <c r="AH381">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI381" t="s">
         <v>112</v>
       </c>
       <c r="AJ381">
-        <v>-2300</v>
+        <v>-1272</v>
       </c>
       <c r="AK381" t="s">
         <v>64</v>
@@ -72841,10 +72946,10 @@
     </row>
     <row r="382" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="B382" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="C382" t="s">
         <v>53</v>
@@ -72856,7 +72961,7 @@
         <v>53</v>
       </c>
       <c r="F382" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="G382" t="s">
         <v>53</v>
@@ -72865,10 +72970,10 @@
         <v>53</v>
       </c>
       <c r="I382">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J382">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K382">
         <v>0</v>
@@ -72895,7 +73000,7 @@
         <v>189</v>
       </c>
       <c r="S382" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="T382" t="s">
         <v>97</v>
@@ -72916,37 +73021,37 @@
         <v>53</v>
       </c>
       <c r="Z382">
-        <v>4829.94</v>
+        <v>2300</v>
       </c>
       <c r="AA382" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="AB382" t="s">
         <v>180</v>
       </c>
       <c r="AC382" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="AD382" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE382" s="1">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="AF382" s="1">
-        <v>46744</v>
+        <v>46582</v>
       </c>
       <c r="AG382" s="1">
-        <v>46753</v>
+        <v>46586</v>
       </c>
       <c r="AH382">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AI382" t="s">
         <v>112</v>
       </c>
       <c r="AJ382">
-        <v>0</v>
+        <v>-2300</v>
       </c>
       <c r="AK382" t="s">
         <v>64</v>
@@ -72969,28 +73074,183 @@
       <c r="AQ382" t="s">
         <v>53</v>
       </c>
-      <c r="AR382" s="1">
+      <c r="AR382" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS382" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AT382" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU382" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV382" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW382" t="s">
+        <v>53</v>
+      </c>
+      <c r="AX382" t="s">
+        <v>53</v>
+      </c>
+      <c r="AY382" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="383" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B383" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C383" t="s">
+        <v>53</v>
+      </c>
+      <c r="D383" t="s">
+        <v>53</v>
+      </c>
+      <c r="E383" t="s">
+        <v>53</v>
+      </c>
+      <c r="F383" t="s">
+        <v>2355</v>
+      </c>
+      <c r="G383" t="s">
+        <v>53</v>
+      </c>
+      <c r="H383" t="s">
+        <v>53</v>
+      </c>
+      <c r="I383">
+        <v>2</v>
+      </c>
+      <c r="J383">
+        <v>2</v>
+      </c>
+      <c r="K383">
+        <v>0</v>
+      </c>
+      <c r="L383" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M383" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N383" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O383" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P383" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q383" t="s">
+        <v>205</v>
+      </c>
+      <c r="R383" t="s">
+        <v>189</v>
+      </c>
+      <c r="S383" t="s">
+        <v>2356</v>
+      </c>
+      <c r="T383" t="s">
+        <v>97</v>
+      </c>
+      <c r="U383" t="s">
+        <v>300</v>
+      </c>
+      <c r="V383" t="s">
+        <v>99</v>
+      </c>
+      <c r="W383" t="s">
+        <v>53</v>
+      </c>
+      <c r="X383" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y383" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z383">
+        <v>4829.94</v>
+      </c>
+      <c r="AA383" t="s">
+        <v>2357</v>
+      </c>
+      <c r="AB383" t="s">
+        <v>180</v>
+      </c>
+      <c r="AC383" t="s">
+        <v>2358</v>
+      </c>
+      <c r="AD383" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE383" s="1">
         <v>46147</v>
       </c>
-      <c r="AS382" s="2">
+      <c r="AF383" s="1">
+        <v>46744</v>
+      </c>
+      <c r="AG383" s="1">
+        <v>46753</v>
+      </c>
+      <c r="AH383">
+        <v>9</v>
+      </c>
+      <c r="AI383" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ383">
+        <v>0</v>
+      </c>
+      <c r="AK383" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AM383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AN383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR383" s="1">
+        <v>46147</v>
+      </c>
+      <c r="AS383" s="2">
         <v>46147.538125</v>
       </c>
-      <c r="AT382" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AU382" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV382" t="s">
-        <v>53</v>
-      </c>
-      <c r="AW382" t="s">
-        <v>53</v>
-      </c>
-      <c r="AX382" t="s">
-        <v>53</v>
-      </c>
-      <c r="AY382" t="s">
+      <c r="AT383" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AX383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AY383" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14934" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14965" uniqueCount="2365">
   <si>
     <t>First name</t>
   </si>
@@ -9381,7 +9381,8 @@
     <t>Weiming</t>
   </si>
   <si>
-    <t xml:space="preserve">codes sent (auto)
+    <t xml:space="preserve">Post stay message sent (auto)
+codes sent (auto)
 Form chased 31/05/2026 (auto)
 approved
 moving from THREE
@@ -10355,7 +10356,8 @@
     <t>Alankar</t>
   </si>
   <si>
-    <t xml:space="preserve">codes sent (auto)
+    <t xml:space="preserve">Post stay message sent (auto)
+codes sent (auto)
 approved
 ----
 We're happy to confirm you can check-in early as 12:30PM! 
@@ -10448,7 +10450,8 @@
     <t>NZ</t>
   </si>
   <si>
-    <t xml:space="preserve">codes sent (asana)
+    <t xml:space="preserve">Early check-out confirmation sent (auto)
+codes sent (asana)
 Form chased 13/06/2026 (auto)
 IDENFO passed
 approved
@@ -10690,7 +10693,8 @@
     <t>Lopansri</t>
   </si>
   <si>
-    <t xml:space="preserve">codes sent (auto)
+    <t xml:space="preserve">Post stay message sent (auto)
+codes sent (auto)
 approved
 upgraded in order to accommodate long term bookings
 ----
@@ -10908,8 +10912,28 @@
     <t>XLXTLVYC</t>
   </si>
   <si>
-    <t xml:space="preserve">approved
-passed in IDENFO
+    <t xml:space="preserve">codes sent (auto)
+passed in IDENFO 
+approved
+----
+We're happy to confirm you can check in early as 1 PM!
+----
+KYC Status: Failed
+Person 1: Pass - CHARLOTTEGRACE MC CLURE
+ (dob: 2002-12-06, doe: 2032-12-19)
+Person 2: Pass - DOUGLAS BRYAN MC CLURE JR
+ (dob: 1970-05-03, doe: 2035-12-16)
+Person 3: Pass - DOUGLAS BRYAN MC CLURE JR
+ (dob: 1970-05-03, doe: 2035-12-16)
+Person 4: Pass - ANNE WILLIAMS MC CLURE
+ (dob: 1975-05-30, doe: 2034-03-25)
+Person 5: Pass - CHARLOTTEGRACE MC CLURE
+ (dob: 2002-12-06, doe: 2032-12-19)
+Person 6: Pass - ANNE WILLIAMS MC CLURE
+ (dob: 1975-05-30, doe: 2034-03-25)
+Person 7: Failed - Please upload a clear image
+Person 8: Failed - Please upload a clear image
+Checked at: 2026-06-18 00:28:33
 KYC Status: Failed
 Person 1: Pass - CHARLOTTEGRACE MC CLURE
  (dob: 2002-12-06, doe: 2032-12-19)
@@ -10919,10 +10943,9 @@
  (dob: 1970-05-03, doe: 2035-12-16)
 Person 4: Failed - Please upload a clear image
 Checked at: 2026-06-14 21:00:53
-placeholder
 Check-in form:
 https://checkin.stayatslo.com/?id=GVPPWDGJ-1
-Arrival time: 15:00
+Arrival time: 13:00
 Check out time: 11:00
 Flight/Train number:
 Special requests: 
@@ -10934,7 +10957,20 @@
 https://api.typeform.com/responses/files/d54f134cc9d7d44e8b7da0cdb969dd73c41b1c9c86892937484e50fc6d0cd133/IMG_8886.jpeg (Passport)
 https://api.typeform.com/responses/files/08dfa485356d6d94c00ee5f665e584a2774678728817addb8c93150a414350c5/IMG_1300.jpeg (Passport)
 https://api.typeform.com/responses/files/01c888d354c0afcb5f9e52c861ac1acd78e69e9acb9c1fc3539dd2b96b499b7a/IMG_8884.jpeg (Passport)
-https://api.typeform.com/responses/files/ab18aa853d0c7653aadcd5b5ef0de3fea61c51cccc48e80607e5f3b563fb17f4/IMG_8885.jpeg (Passport)</t>
+https://api.typeform.com/responses/files/ab18aa853d0c7653aadcd5b5ef0de3fea61c51cccc48e80607e5f3b563fb17f4/IMG_8885.jpeg (Passport)
+Arrival time: 13:00
+Check out time: 11:00
+Flight/Train number:
+Special requests: 
+Accessibility needs: No, I do not have any accessibility needs
+Consent: true
+WhatsApp: true
+Terms: true
+Number of guests: 4
+https://api.typeform.com/responses/files/97af086bbf890b63b8dfa0eda02ca14e96481ffc02f631ecca88c28d7b83c1c1/IMG_8886.jpeg (Passport)
+https://api.typeform.com/responses/files/9fd9c1eb61ad102d14114756ac38c948971dd449f5c30a6b95d50a03e478544b/IMG_8885.jpeg (Passport)
+https://api.typeform.com/responses/files/2a48c2d3aabbf3df0d6091c2332caabc3ed33f373668994ea595a6ebfdd46a22/IMG_8884.jpeg (Passport)
+https://api.typeform.com/responses/files/9d421bd2d15e78e6c01208c51e23a8a8526ed3de8824257d40f823871323dd59/IMG_1300.jpeg (Passport)</t>
   </si>
   <si>
     <t>smoking preference: Non-Smoking, The amount the guest prepaid to Booking.com is GBP 5021.80</t>
@@ -10955,7 +10991,8 @@
     <t>Mahdi</t>
   </si>
   <si>
-    <t xml:space="preserve">approved
+    <t xml:space="preserve">codes sent (auto)
+approved
 NOTE: copied and pasted there checkin form from the last booking, returning guest
 https://cleanings.stayatslo.com/?id=UCUOMERL-1
 Check-in form:
@@ -11147,7 +11184,8 @@
     <t>UZXNOVMZ</t>
   </si>
   <si>
-    <t xml:space="preserve">approved
+    <t xml:space="preserve">NOTE: CHANGE OF PLANS
+approved
 returning guest from Elizabeth
 his ID is already in IDENFO
 Check-in form:
@@ -11161,7 +11199,8 @@
 Accessibility needs: No, I do not have any accessibility needs
 Consent: true
 WhatsApp: true
-Terms: true</t>
+Terms: true
+https://cleanings.stayatslo.com/?id=NATVRXCG-1</t>
   </si>
   <si>
     <t>46254b07-c0a3-47a2-b23f-7e075e38a21d-1</t>
@@ -11179,7 +11218,10 @@
     <t>Lootah</t>
   </si>
   <si>
-    <t xml:space="preserve">placeholder
+    <t xml:space="preserve">KYC Status: Failed
+Person 1: Failed - Sorry, we couldn't detect any valid documents in the image you provided. Please ensure the document is clear and well-centered
+Checked at: 2026-06-18 12:49:58
+placeholder
 high chair pls
 IMPORTANT: There is a FM delivery under my name that arrived on reception on the 21st, please collect and place inside the apartment in a nice manner alongside our regular welcome pack 
 Guest is bringing her own baby cot please take note, has order it to be delivered to GCH - beds needs to be separated to twin beds.
@@ -11189,7 +11231,19 @@
 Remaining: 4
 https://cleanings.stayatslo.com/?id=EAOMBYPT-1
 Check-in form:
-https://checkin.stayatslo.com/?id=EAOMBYPT-1</t>
+https://checkin.stayatslo.com/?id=EAOMBYPT-1
+Arrival time: 19:00
+Check out time: 11:00
+Flight/Train number:
+Special requests: Guest wants 1st bedroom by door split into a twin bed because they will bring their own cot, and will be placed in the middle .
+They also requested  baby high-chair, and to put their empty luggage in storage.
+Additionally, was agreed that the grocery company will be there at 12pm on the 22nd, they will call when they are 5 mins away, just to drop off their shopping.
+Accessibility needs: No, I do not have any accessibility needs
+Consent: false
+WhatsApp: true
+Terms: true
+Number of guests: 1
+https://api.typeform.com/responses/files/4db488eb4d788d3e81b49074aed26ad27b9846f39d867fe7d6cb166677f40881/Rashed_ID.pdf (Driver's license (UK))</t>
   </si>
   <si>
     <t>EAOMBYPT-1</t>
@@ -12406,6 +12460,27 @@
   </si>
   <si>
     <t>ILYHIXRJ</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">placeholder
+Check-in form:
+https://checkin.nestorstay.com/?id=ZFEGBZRP-1
+https://cleanings.nestorstay.com/?id=ZFEGBZRP-1</t>
+  </si>
+  <si>
+    <t>smoking preference: Non-Smoking, The amount the guest prepaid to Booking.com is GBP 2178.90</t>
+  </si>
+  <si>
+    <t>6567959328|1</t>
+  </si>
+  <si>
+    <t>ZFEGBZRP-1</t>
+  </si>
+  <si>
+    <t>ZFEGBZRP</t>
   </si>
   <si>
     <t>Martine</t>
@@ -13872,7 +13947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AY383"/>
+  <dimension ref="A1:AY384"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="11" width="15" customWidth="1"/>
@@ -41896,7 +41971,7 @@
         <v>63</v>
       </c>
       <c r="AJ181">
-        <v>-22448.68</v>
+        <v>-9324.32</v>
       </c>
       <c r="AK181" t="s">
         <v>64</v>
@@ -48561,7 +48636,7 @@
         <v>112</v>
       </c>
       <c r="AJ224">
-        <v>-3672</v>
+        <v>0</v>
       </c>
       <c r="AK224" t="s">
         <v>64</v>
@@ -52059,11 +52134,11 @@
       <c r="M247" s="2">
         <v>46174.62662037037</v>
       </c>
-      <c r="N247" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O247" s="2" t="s">
-        <v>53</v>
+      <c r="N247" s="1">
+        <v>46192</v>
+      </c>
+      <c r="O247" s="2">
+        <v>46192.458761574075</v>
       </c>
       <c r="P247" t="s">
         <v>73</v>
@@ -52108,7 +52183,7 @@
         <v>1540</v>
       </c>
       <c r="AD247" t="s">
-        <v>1051</v>
+        <v>85</v>
       </c>
       <c r="AE247" s="1">
         <v>46165</v>
@@ -56089,11 +56164,11 @@
       <c r="M273" s="2">
         <v>46186.626493055555</v>
       </c>
-      <c r="N273" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O273" s="2" t="s">
-        <v>53</v>
+      <c r="N273" s="1">
+        <v>46191</v>
+      </c>
+      <c r="O273" s="2">
+        <v>46191.45893518519</v>
       </c>
       <c r="P273" t="s">
         <v>95</v>
@@ -56138,7 +56213,7 @@
         <v>1706</v>
       </c>
       <c r="AD273" t="s">
-        <v>1051</v>
+        <v>85</v>
       </c>
       <c r="AE273" s="1">
         <v>46181</v>
@@ -57484,11 +57559,11 @@
       <c r="M282" s="2">
         <v>46189.62652777778</v>
       </c>
-      <c r="N282" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O282" s="2" t="s">
-        <v>53</v>
+      <c r="N282" s="1">
+        <v>46192</v>
+      </c>
+      <c r="O282" s="2">
+        <v>46192.458750000005</v>
       </c>
       <c r="P282" t="s">
         <v>67</v>
@@ -57533,7 +57608,7 @@
         <v>1759</v>
       </c>
       <c r="AD282" t="s">
-        <v>1051</v>
+        <v>85</v>
       </c>
       <c r="AE282" s="1">
         <v>46175</v>
@@ -57676,7 +57751,7 @@
         <v>53</v>
       </c>
       <c r="Z283">
-        <v>3680</v>
+        <v>3807</v>
       </c>
       <c r="AA283" t="s">
         <v>1763</v>
@@ -58253,11 +58328,11 @@
       <c r="K287">
         <v>0</v>
       </c>
-      <c r="L287" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M287" s="2" t="s">
-        <v>53</v>
+      <c r="L287" s="1">
+        <v>46191</v>
+      </c>
+      <c r="M287" s="2">
+        <v>46191.62648148148</v>
       </c>
       <c r="N287" s="1" t="s">
         <v>53</v>
@@ -58308,7 +58383,7 @@
         <v>1784</v>
       </c>
       <c r="AD287" t="s">
-        <v>1361</v>
+        <v>1051</v>
       </c>
       <c r="AE287" s="1">
         <v>46189</v>
@@ -59691,7 +59766,7 @@
         <v>53</v>
       </c>
       <c r="Z296">
-        <v>2327</v>
+        <v>0</v>
       </c>
       <c r="AA296" t="s">
         <v>1839</v>
@@ -59703,7 +59778,7 @@
         <v>1840</v>
       </c>
       <c r="AD296" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE296" s="1">
         <v>46188</v>
@@ -59744,11 +59819,11 @@
       <c r="AQ296" t="s">
         <v>53</v>
       </c>
-      <c r="AR296" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS296" s="2" t="s">
-        <v>53</v>
+      <c r="AR296" s="1">
+        <v>46190</v>
+      </c>
+      <c r="AS296" s="2">
+        <v>46190.924317129626</v>
       </c>
       <c r="AT296" s="1" t="s">
         <v>53</v>
@@ -59783,7 +59858,7 @@
         <v>53</v>
       </c>
       <c r="E297" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="F297" t="s">
         <v>1842</v>
@@ -59876,7 +59951,7 @@
         <v>112</v>
       </c>
       <c r="AJ297">
-        <v>-65472</v>
+        <v>0</v>
       </c>
       <c r="AK297" t="s">
         <v>64</v>
@@ -63384,7 +63459,7 @@
         <v>88</v>
       </c>
       <c r="Q320" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="R320" t="s">
         <v>88</v>
@@ -66439,22 +66514,22 @@
         <v>2105</v>
       </c>
       <c r="B340" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C340" t="s">
+        <v>53</v>
+      </c>
+      <c r="D340" t="s">
+        <v>53</v>
+      </c>
+      <c r="E340" t="s">
+        <v>165</v>
+      </c>
+      <c r="F340" t="s">
         <v>2106</v>
       </c>
-      <c r="C340" t="s">
-        <v>53</v>
-      </c>
-      <c r="D340" t="s">
-        <v>53</v>
-      </c>
-      <c r="E340" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F340" t="s">
+      <c r="G340" t="s">
         <v>2107</v>
-      </c>
-      <c r="G340" t="s">
-        <v>2108</v>
       </c>
       <c r="H340" t="s">
         <v>86</v>
@@ -66490,7 +66565,7 @@
         <v>177</v>
       </c>
       <c r="S340" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="T340" t="s">
         <v>97</v>
@@ -66499,7 +66574,7 @@
         <v>190</v>
       </c>
       <c r="V340" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="W340" t="s">
         <v>53</v>
@@ -66511,37 +66586,37 @@
         <v>53</v>
       </c>
       <c r="Z340">
-        <v>1731.6</v>
+        <v>2178.9</v>
       </c>
       <c r="AA340" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="AB340" t="s">
         <v>180</v>
       </c>
       <c r="AC340" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="AD340" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE340" s="1">
-        <v>46056</v>
+        <v>46192</v>
       </c>
       <c r="AF340" s="1">
-        <v>46229</v>
+        <v>46228</v>
       </c>
       <c r="AG340" s="1">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="AH340">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI340" t="s">
         <v>112</v>
       </c>
       <c r="AJ340">
-        <v>0</v>
+        <v>-2178.9</v>
       </c>
       <c r="AK340" t="s">
         <v>64</v>
@@ -66550,7 +66625,7 @@
         <v>53</v>
       </c>
       <c r="AM340">
-        <v>259.74</v>
+        <v>326.83</v>
       </c>
       <c r="AN340" t="s">
         <v>53</v>
@@ -66564,11 +66639,11 @@
       <c r="AQ340" t="s">
         <v>53</v>
       </c>
-      <c r="AR340" s="1">
-        <v>46171</v>
-      </c>
-      <c r="AS340" s="2">
-        <v>46171.14560185185</v>
+      <c r="AR340" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS340" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT340" s="1" t="s">
         <v>53</v>
@@ -66591,25 +66666,25 @@
     </row>
     <row r="341" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B341" t="s">
         <v>2112</v>
       </c>
-      <c r="B341" t="s">
+      <c r="C341" t="s">
+        <v>53</v>
+      </c>
+      <c r="D341" t="s">
+        <v>53</v>
+      </c>
+      <c r="E341" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F341" t="s">
         <v>2113</v>
       </c>
-      <c r="C341" t="s">
-        <v>53</v>
-      </c>
-      <c r="D341" t="s">
-        <v>53</v>
-      </c>
-      <c r="E341" t="s">
-        <v>461</v>
-      </c>
-      <c r="F341" t="s">
+      <c r="G341" t="s">
         <v>2114</v>
-      </c>
-      <c r="G341" t="s">
-        <v>2115</v>
       </c>
       <c r="H341" t="s">
         <v>86</v>
@@ -66636,16 +66711,16 @@
         <v>53</v>
       </c>
       <c r="P341" t="s">
-        <v>73</v>
+        <v>177</v>
       </c>
       <c r="Q341" t="s">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="R341" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="S341" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="T341" t="s">
         <v>97</v>
@@ -66666,31 +66741,31 @@
         <v>53</v>
       </c>
       <c r="Z341">
-        <v>3983.66</v>
+        <v>1731.6</v>
       </c>
       <c r="AA341" t="s">
+        <v>2116</v>
+      </c>
+      <c r="AB341" t="s">
+        <v>180</v>
+      </c>
+      <c r="AC341" t="s">
         <v>2117</v>
-      </c>
-      <c r="AB341" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC341" t="s">
-        <v>2118</v>
       </c>
       <c r="AD341" t="s">
         <v>62</v>
       </c>
       <c r="AE341" s="1">
-        <v>46092</v>
+        <v>46056</v>
       </c>
       <c r="AF341" s="1">
         <v>46229</v>
       </c>
       <c r="AG341" s="1">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="AH341">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI341" t="s">
         <v>112</v>
@@ -66705,7 +66780,7 @@
         <v>53</v>
       </c>
       <c r="AM341">
-        <v>597.55</v>
+        <v>259.74</v>
       </c>
       <c r="AN341" t="s">
         <v>53</v>
@@ -66720,10 +66795,10 @@
         <v>53</v>
       </c>
       <c r="AR341" s="1">
-        <v>46187</v>
+        <v>46171</v>
       </c>
       <c r="AS341" s="2">
-        <v>46187.716319444444</v>
+        <v>46171.14560185185</v>
       </c>
       <c r="AT341" s="1" t="s">
         <v>53</v>
@@ -66746,7 +66821,7 @@
     </row>
     <row r="342" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>1339</v>
+        <v>2118</v>
       </c>
       <c r="B342" t="s">
         <v>2119</v>
@@ -66758,22 +66833,22 @@
         <v>53</v>
       </c>
       <c r="E342" t="s">
-        <v>570</v>
+        <v>461</v>
       </c>
       <c r="F342" t="s">
         <v>2120</v>
       </c>
       <c r="G342" t="s">
-        <v>53</v>
+        <v>2121</v>
       </c>
       <c r="H342" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I342">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J342">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K342">
         <v>0</v>
@@ -66791,25 +66866,25 @@
         <v>53</v>
       </c>
       <c r="P342" t="s">
-        <v>189</v>
+        <v>73</v>
       </c>
       <c r="Q342" t="s">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="R342" t="s">
-        <v>189</v>
+        <v>88</v>
       </c>
       <c r="S342" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="T342" t="s">
         <v>97</v>
       </c>
       <c r="U342" t="s">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="V342" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="W342" t="s">
         <v>53</v>
@@ -66821,37 +66896,37 @@
         <v>53</v>
       </c>
       <c r="Z342">
-        <v>2110.48</v>
+        <v>3983.66</v>
       </c>
       <c r="AA342" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="AB342" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AC342" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="AD342" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE342" s="1">
-        <v>46163</v>
+        <v>46092</v>
       </c>
       <c r="AF342" s="1">
         <v>46229</v>
       </c>
       <c r="AG342" s="1">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="AH342">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI342" t="s">
         <v>112</v>
       </c>
       <c r="AJ342">
-        <v>-2110.48</v>
+        <v>0</v>
       </c>
       <c r="AK342" t="s">
         <v>64</v>
@@ -66859,8 +66934,8 @@
       <c r="AL342" t="s">
         <v>53</v>
       </c>
-      <c r="AM342" t="s">
-        <v>53</v>
+      <c r="AM342">
+        <v>597.55</v>
       </c>
       <c r="AN342" t="s">
         <v>53</v>
@@ -66874,11 +66949,11 @@
       <c r="AQ342" t="s">
         <v>53</v>
       </c>
-      <c r="AR342" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS342" s="2" t="s">
-        <v>53</v>
+      <c r="AR342" s="1">
+        <v>46187</v>
+      </c>
+      <c r="AS342" s="2">
+        <v>46187.716319444444</v>
       </c>
       <c r="AT342" s="1" t="s">
         <v>53</v>
@@ -66887,7 +66962,7 @@
         <v>53</v>
       </c>
       <c r="AV342" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="AW342" t="s">
         <v>53</v>
@@ -66901,10 +66976,10 @@
     </row>
     <row r="343" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>2124</v>
+        <v>1339</v>
       </c>
       <c r="B343" t="s">
-        <v>79</v>
+        <v>2125</v>
       </c>
       <c r="C343" t="s">
         <v>53</v>
@@ -66913,25 +66988,25 @@
         <v>53</v>
       </c>
       <c r="E343" t="s">
-        <v>80</v>
+        <v>570</v>
       </c>
       <c r="F343" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="G343" t="s">
         <v>53</v>
       </c>
       <c r="H343" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I343">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J343">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K343">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L343" s="1" t="s">
         <v>53</v>
@@ -66946,49 +67021,49 @@
         <v>53</v>
       </c>
       <c r="P343" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="Q343" t="s">
-        <v>761</v>
+        <v>205</v>
       </c>
       <c r="R343" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="S343" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="T343" t="s">
         <v>97</v>
       </c>
       <c r="U343" t="s">
-        <v>98</v>
+        <v>300</v>
       </c>
       <c r="V343" t="s">
         <v>99</v>
       </c>
       <c r="W343" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="X343" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="Y343" t="s">
-        <v>1808</v>
+        <v>53</v>
       </c>
       <c r="Z343">
-        <v>5446</v>
+        <v>2110.48</v>
       </c>
       <c r="AA343" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="AB343" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC343" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="AD343" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE343" s="1">
         <v>46163</v>
@@ -67003,10 +67078,10 @@
         <v>4</v>
       </c>
       <c r="AI343" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ343">
-        <v>0</v>
+        <v>-2110.48</v>
       </c>
       <c r="AK343" t="s">
         <v>64</v>
@@ -67014,8 +67089,8 @@
       <c r="AL343" t="s">
         <v>53</v>
       </c>
-      <c r="AM343">
-        <v>1089.2</v>
+      <c r="AM343" t="s">
+        <v>53</v>
       </c>
       <c r="AN343" t="s">
         <v>53</v>
@@ -67029,11 +67104,11 @@
       <c r="AQ343" t="s">
         <v>53</v>
       </c>
-      <c r="AR343" s="1">
-        <v>46167</v>
-      </c>
-      <c r="AS343" s="2">
-        <v>46167.64277777778</v>
+      <c r="AR343" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS343" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT343" s="1" t="s">
         <v>53</v>
@@ -67042,7 +67117,7 @@
         <v>53</v>
       </c>
       <c r="AV343" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="AW343" t="s">
         <v>53</v>
@@ -67056,10 +67131,10 @@
     </row>
     <row r="344" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B344" t="s">
-        <v>2130</v>
+        <v>79</v>
       </c>
       <c r="C344" t="s">
         <v>53</v>
@@ -67068,7 +67143,7 @@
         <v>53</v>
       </c>
       <c r="E344" t="s">
-        <v>1079</v>
+        <v>80</v>
       </c>
       <c r="F344" t="s">
         <v>2131</v>
@@ -67077,16 +67152,16 @@
         <v>53</v>
       </c>
       <c r="H344" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I344">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J344">
         <v>2</v>
       </c>
       <c r="K344">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L344" s="1" t="s">
         <v>53</v>
@@ -67101,13 +67176,13 @@
         <v>53</v>
       </c>
       <c r="P344" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="Q344" t="s">
-        <v>787</v>
+        <v>761</v>
       </c>
       <c r="R344" t="s">
-        <v>786</v>
+        <v>88</v>
       </c>
       <c r="S344" t="s">
         <v>2132</v>
@@ -67116,28 +67191,28 @@
         <v>97</v>
       </c>
       <c r="U344" t="s">
-        <v>1006</v>
+        <v>98</v>
       </c>
       <c r="V344" t="s">
         <v>99</v>
       </c>
       <c r="W344" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="X344" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="Y344" t="s">
-        <v>53</v>
+        <v>1808</v>
       </c>
       <c r="Z344">
-        <v>1302.2</v>
+        <v>5446</v>
       </c>
       <c r="AA344" t="s">
         <v>2133</v>
       </c>
       <c r="AB344" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC344" t="s">
         <v>2134</v>
@@ -67146,13 +67221,13 @@
         <v>62</v>
       </c>
       <c r="AE344" s="1">
-        <v>46031</v>
+        <v>46163</v>
       </c>
       <c r="AF344" s="1">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="AG344" s="1">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="AH344">
         <v>4</v>
@@ -67169,8 +67244,8 @@
       <c r="AL344" t="s">
         <v>53</v>
       </c>
-      <c r="AM344" t="s">
-        <v>53</v>
+      <c r="AM344">
+        <v>1089.2</v>
       </c>
       <c r="AN344" t="s">
         <v>53</v>
@@ -67185,10 +67260,10 @@
         <v>53</v>
       </c>
       <c r="AR344" s="1">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="AS344" s="2">
-        <v>46161.58596064815</v>
+        <v>46167.64277777778</v>
       </c>
       <c r="AT344" s="1" t="s">
         <v>53</v>
@@ -67223,16 +67298,16 @@
         <v>53</v>
       </c>
       <c r="E345" t="s">
-        <v>53</v>
+        <v>1079</v>
       </c>
       <c r="F345" t="s">
         <v>2137</v>
       </c>
       <c r="G345" t="s">
-        <v>1641</v>
+        <v>53</v>
       </c>
       <c r="H345" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I345">
         <v>2</v>
@@ -67256,13 +67331,13 @@
         <v>53</v>
       </c>
       <c r="P345" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="Q345" t="s">
-        <v>408</v>
+        <v>787</v>
       </c>
       <c r="R345" t="s">
-        <v>67</v>
+        <v>786</v>
       </c>
       <c r="S345" t="s">
         <v>2138</v>
@@ -67271,52 +67346,52 @@
         <v>97</v>
       </c>
       <c r="U345" t="s">
-        <v>907</v>
+        <v>1006</v>
       </c>
       <c r="V345" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="W345" t="s">
+        <v>53</v>
+      </c>
+      <c r="X345" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y345" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z345">
+        <v>1302.2</v>
+      </c>
+      <c r="AA345" t="s">
         <v>2139</v>
       </c>
-      <c r="X345" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y345" t="s">
+      <c r="AB345" t="s">
+        <v>180</v>
+      </c>
+      <c r="AC345" t="s">
         <v>2140</v>
       </c>
-      <c r="Z345">
-        <v>5546.1</v>
-      </c>
-      <c r="AA345" t="s">
-        <v>2141</v>
-      </c>
-      <c r="AB345" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC345" t="s">
-        <v>2142</v>
-      </c>
       <c r="AD345" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE345" s="1">
-        <v>46188</v>
+        <v>46031</v>
       </c>
       <c r="AF345" s="1">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="AG345" s="1">
-        <v>46249</v>
+        <v>46234</v>
       </c>
       <c r="AH345">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AI345" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ345">
-        <v>-5546.1</v>
+        <v>0</v>
       </c>
       <c r="AK345" t="s">
         <v>64</v>
@@ -67339,11 +67414,11 @@
       <c r="AQ345" t="s">
         <v>53</v>
       </c>
-      <c r="AR345" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS345" s="2" t="s">
-        <v>53</v>
+      <c r="AR345" s="1">
+        <v>46161</v>
+      </c>
+      <c r="AS345" s="2">
+        <v>46161.58596064815</v>
       </c>
       <c r="AT345" s="1" t="s">
         <v>53</v>
@@ -67366,37 +67441,37 @@
     </row>
     <row r="346" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B346" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C346" t="s">
+        <v>53</v>
+      </c>
+      <c r="D346" t="s">
+        <v>53</v>
+      </c>
+      <c r="E346" t="s">
+        <v>53</v>
+      </c>
+      <c r="F346" t="s">
         <v>2143</v>
       </c>
-      <c r="B346" t="s">
-        <v>2144</v>
-      </c>
-      <c r="C346" t="s">
-        <v>53</v>
-      </c>
-      <c r="D346" t="s">
-        <v>53</v>
-      </c>
-      <c r="E346" t="s">
-        <v>220</v>
-      </c>
-      <c r="F346" t="s">
-        <v>2145</v>
-      </c>
       <c r="G346" t="s">
-        <v>2146</v>
+        <v>1641</v>
       </c>
       <c r="H346" t="s">
         <v>86</v>
       </c>
       <c r="I346">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J346">
         <v>2</v>
       </c>
       <c r="K346">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L346" s="1" t="s">
         <v>53</v>
@@ -67411,67 +67486,67 @@
         <v>53</v>
       </c>
       <c r="P346" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="Q346" t="s">
-        <v>188</v>
+        <v>408</v>
       </c>
       <c r="R346" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="S346" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="T346" t="s">
         <v>97</v>
       </c>
       <c r="U346" t="s">
-        <v>190</v>
+        <v>907</v>
       </c>
       <c r="V346" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="W346" t="s">
-        <v>53</v>
+        <v>2145</v>
       </c>
       <c r="X346" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="Y346" t="s">
-        <v>53</v>
+        <v>2146</v>
       </c>
       <c r="Z346">
-        <v>4013.08</v>
+        <v>5546.1</v>
       </c>
       <c r="AA346" t="s">
+        <v>2147</v>
+      </c>
+      <c r="AB346" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC346" t="s">
         <v>2148</v>
       </c>
-      <c r="AB346" t="s">
-        <v>180</v>
-      </c>
-      <c r="AC346" t="s">
-        <v>2149</v>
-      </c>
       <c r="AD346" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE346" s="1">
-        <v>46109</v>
+        <v>46188</v>
       </c>
       <c r="AF346" s="1">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="AG346" s="1">
-        <v>46241</v>
+        <v>46249</v>
       </c>
       <c r="AH346">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AI346" t="s">
         <v>112</v>
       </c>
       <c r="AJ346">
-        <v>0</v>
+        <v>-5546.1</v>
       </c>
       <c r="AK346" t="s">
         <v>64</v>
@@ -67479,8 +67554,8 @@
       <c r="AL346" t="s">
         <v>53</v>
       </c>
-      <c r="AM346">
-        <v>601.96</v>
+      <c r="AM346" t="s">
+        <v>53</v>
       </c>
       <c r="AN346" t="s">
         <v>53</v>
@@ -67494,11 +67569,11 @@
       <c r="AQ346" t="s">
         <v>53</v>
       </c>
-      <c r="AR346" s="1">
-        <v>46109</v>
-      </c>
-      <c r="AS346" s="2">
-        <v>46109.58243055556</v>
+      <c r="AR346" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS346" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT346" s="1" t="s">
         <v>53</v>
@@ -67521,10 +67596,10 @@
     </row>
     <row r="347" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>2143</v>
+        <v>2149</v>
       </c>
       <c r="B347" t="s">
-        <v>2144</v>
+        <v>2150</v>
       </c>
       <c r="C347" t="s">
         <v>53</v>
@@ -67536,22 +67611,22 @@
         <v>220</v>
       </c>
       <c r="F347" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="G347" t="s">
-        <v>1622</v>
+        <v>2152</v>
       </c>
       <c r="H347" t="s">
         <v>86</v>
       </c>
       <c r="I347">
+        <v>4</v>
+      </c>
+      <c r="J347">
         <v>2</v>
       </c>
-      <c r="J347">
-        <v>1</v>
-      </c>
       <c r="K347">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L347" s="1" t="s">
         <v>53</v>
@@ -67566,16 +67641,16 @@
         <v>53</v>
       </c>
       <c r="P347" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="Q347" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="R347" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="S347" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="T347" t="s">
         <v>97</v>
@@ -67596,16 +67671,16 @@
         <v>53</v>
       </c>
       <c r="Z347">
-        <v>1977.13</v>
+        <v>4013.08</v>
       </c>
       <c r="AA347" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="AB347" t="s">
         <v>180</v>
       </c>
       <c r="AC347" t="s">
-        <v>2149</v>
+        <v>2155</v>
       </c>
       <c r="AD347" t="s">
         <v>62</v>
@@ -67635,7 +67710,7 @@
         <v>53</v>
       </c>
       <c r="AM347">
-        <v>296.57</v>
+        <v>601.96</v>
       </c>
       <c r="AN347" t="s">
         <v>53</v>
@@ -67653,7 +67728,7 @@
         <v>46109</v>
       </c>
       <c r="AS347" s="2">
-        <v>46109.58244212963</v>
+        <v>46109.58243055556</v>
       </c>
       <c r="AT347" s="1" t="s">
         <v>53</v>
@@ -67676,10 +67751,10 @@
     </row>
     <row r="348" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>2143</v>
+        <v>2149</v>
       </c>
       <c r="B348" t="s">
-        <v>2144</v>
+        <v>2150</v>
       </c>
       <c r="C348" t="s">
         <v>53</v>
@@ -67691,7 +67766,7 @@
         <v>220</v>
       </c>
       <c r="F348" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="G348" t="s">
         <v>1622</v>
@@ -67700,13 +67775,13 @@
         <v>86</v>
       </c>
       <c r="I348">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J348">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K348">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L348" s="1" t="s">
         <v>53</v>
@@ -67721,16 +67796,16 @@
         <v>53</v>
       </c>
       <c r="P348" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Q348" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="R348" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="S348" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="T348" t="s">
         <v>97</v>
@@ -67751,16 +67826,16 @@
         <v>53</v>
       </c>
       <c r="Z348">
-        <v>3610.33</v>
+        <v>1977.13</v>
       </c>
       <c r="AA348" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="AB348" t="s">
         <v>180</v>
       </c>
       <c r="AC348" t="s">
-        <v>2149</v>
+        <v>2155</v>
       </c>
       <c r="AD348" t="s">
         <v>62</v>
@@ -67790,7 +67865,7 @@
         <v>53</v>
       </c>
       <c r="AM348">
-        <v>541.55</v>
+        <v>296.57</v>
       </c>
       <c r="AN348" t="s">
         <v>53</v>
@@ -67808,7 +67883,7 @@
         <v>46109</v>
       </c>
       <c r="AS348" s="2">
-        <v>46109.582453703704</v>
+        <v>46109.58244212963</v>
       </c>
       <c r="AT348" s="1" t="s">
         <v>53</v>
@@ -67831,10 +67906,10 @@
     </row>
     <row r="349" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>65</v>
+        <v>2149</v>
       </c>
       <c r="B349" t="s">
-        <v>2156</v>
+        <v>2150</v>
       </c>
       <c r="C349" t="s">
         <v>53</v>
@@ -67843,25 +67918,25 @@
         <v>53</v>
       </c>
       <c r="E349" t="s">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="F349" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="G349" t="s">
-        <v>53</v>
+        <v>1622</v>
       </c>
       <c r="H349" t="s">
         <v>86</v>
       </c>
       <c r="I349">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J349">
         <v>2</v>
       </c>
       <c r="K349">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L349" s="1" t="s">
         <v>53</v>
@@ -67876,37 +67951,37 @@
         <v>53</v>
       </c>
       <c r="P349" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="Q349" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="R349" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="S349" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="T349" t="s">
         <v>97</v>
       </c>
       <c r="U349" t="s">
-        <v>2159</v>
+        <v>190</v>
       </c>
       <c r="V349" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="W349" t="s">
-        <v>2160</v>
+        <v>53</v>
       </c>
       <c r="X349" t="s">
-        <v>526</v>
+        <v>53</v>
       </c>
       <c r="Y349" t="s">
         <v>53</v>
       </c>
       <c r="Z349">
-        <v>704.8</v>
+        <v>3610.33</v>
       </c>
       <c r="AA349" t="s">
         <v>2161</v>
@@ -67915,22 +67990,22 @@
         <v>180</v>
       </c>
       <c r="AC349" t="s">
-        <v>2162</v>
+        <v>2155</v>
       </c>
       <c r="AD349" t="s">
         <v>62</v>
       </c>
       <c r="AE349" s="1">
-        <v>46073</v>
+        <v>46109</v>
       </c>
       <c r="AF349" s="1">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="AG349" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="AH349">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI349" t="s">
         <v>112</v>
@@ -67944,8 +68019,8 @@
       <c r="AL349" t="s">
         <v>53</v>
       </c>
-      <c r="AM349" t="s">
-        <v>53</v>
+      <c r="AM349">
+        <v>541.55</v>
       </c>
       <c r="AN349" t="s">
         <v>53</v>
@@ -67960,10 +68035,10 @@
         <v>53</v>
       </c>
       <c r="AR349" s="1">
-        <v>46086</v>
+        <v>46109</v>
       </c>
       <c r="AS349" s="2">
-        <v>46086.16619212963</v>
+        <v>46109.582453703704</v>
       </c>
       <c r="AT349" s="1" t="s">
         <v>53</v>
@@ -67986,25 +68061,25 @@
     </row>
     <row r="350" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
+        <v>65</v>
+      </c>
+      <c r="B350" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C350" t="s">
+        <v>53</v>
+      </c>
+      <c r="D350" t="s">
+        <v>53</v>
+      </c>
+      <c r="E350" t="s">
+        <v>53</v>
+      </c>
+      <c r="F350" t="s">
         <v>2163</v>
       </c>
-      <c r="B350" t="s">
-        <v>2164</v>
-      </c>
-      <c r="C350" t="s">
-        <v>53</v>
-      </c>
-      <c r="D350" t="s">
-        <v>53</v>
-      </c>
-      <c r="E350" t="s">
-        <v>461</v>
-      </c>
-      <c r="F350" t="s">
-        <v>2165</v>
-      </c>
       <c r="G350" t="s">
-        <v>2166</v>
+        <v>53</v>
       </c>
       <c r="H350" t="s">
         <v>86</v>
@@ -68013,10 +68088,10 @@
         <v>2</v>
       </c>
       <c r="J350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K350">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L350" s="1" t="s">
         <v>53</v>
@@ -68031,61 +68106,61 @@
         <v>53</v>
       </c>
       <c r="P350" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="Q350" t="s">
-        <v>408</v>
+        <v>178</v>
       </c>
       <c r="R350" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="S350" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="T350" t="s">
         <v>97</v>
       </c>
       <c r="U350" t="s">
-        <v>190</v>
+        <v>2165</v>
       </c>
       <c r="V350" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="W350" t="s">
-        <v>53</v>
+        <v>2166</v>
       </c>
       <c r="X350" t="s">
-        <v>53</v>
+        <v>526</v>
       </c>
       <c r="Y350" t="s">
         <v>53</v>
       </c>
       <c r="Z350">
-        <v>6948.03</v>
+        <v>704.8</v>
       </c>
       <c r="AA350" t="s">
+        <v>2167</v>
+      </c>
+      <c r="AB350" t="s">
+        <v>180</v>
+      </c>
+      <c r="AC350" t="s">
         <v>2168</v>
-      </c>
-      <c r="AB350" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC350" t="s">
-        <v>2169</v>
       </c>
       <c r="AD350" t="s">
         <v>62</v>
       </c>
       <c r="AE350" s="1">
-        <v>46081</v>
+        <v>46073</v>
       </c>
       <c r="AF350" s="1">
         <v>46235</v>
       </c>
       <c r="AG350" s="1">
-        <v>46249</v>
+        <v>46238</v>
       </c>
       <c r="AH350">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AI350" t="s">
         <v>112</v>
@@ -68099,8 +68174,8 @@
       <c r="AL350" t="s">
         <v>53</v>
       </c>
-      <c r="AM350">
-        <v>1042.2</v>
+      <c r="AM350" t="s">
+        <v>53</v>
       </c>
       <c r="AN350" t="s">
         <v>53</v>
@@ -68115,10 +68190,10 @@
         <v>53</v>
       </c>
       <c r="AR350" s="1">
-        <v>46186</v>
+        <v>46086</v>
       </c>
       <c r="AS350" s="2">
-        <v>46186.88296296296</v>
+        <v>46086.16619212963</v>
       </c>
       <c r="AT350" s="1" t="s">
         <v>53</v>
@@ -68141,37 +68216,37 @@
     </row>
     <row r="351" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1166</v>
+        <v>2169</v>
       </c>
       <c r="B351" t="s">
-        <v>1078</v>
+        <v>2170</v>
       </c>
       <c r="C351" t="s">
         <v>53</v>
       </c>
       <c r="D351" t="s">
-        <v>988</v>
+        <v>53</v>
       </c>
       <c r="E351" t="s">
-        <v>159</v>
+        <v>461</v>
       </c>
       <c r="F351" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="G351" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="H351" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I351">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J351">
         <v>1</v>
       </c>
       <c r="K351">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L351" s="1" t="s">
         <v>53</v>
@@ -68186,25 +68261,25 @@
         <v>53</v>
       </c>
       <c r="P351" t="s">
-        <v>786</v>
+        <v>67</v>
       </c>
       <c r="Q351" t="s">
-        <v>787</v>
+        <v>408</v>
       </c>
       <c r="R351" t="s">
-        <v>786</v>
+        <v>67</v>
       </c>
       <c r="S351" t="s">
-        <v>53</v>
+        <v>2173</v>
       </c>
       <c r="T351" t="s">
         <v>97</v>
       </c>
       <c r="U351" t="s">
-        <v>954</v>
+        <v>190</v>
       </c>
       <c r="V351" t="s">
-        <v>744</v>
+        <v>125</v>
       </c>
       <c r="W351" t="s">
         <v>53</v>
@@ -68216,37 +68291,37 @@
         <v>53</v>
       </c>
       <c r="Z351">
-        <v>24500</v>
+        <v>6948.03</v>
       </c>
       <c r="AA351" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="AB351" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AC351" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="AD351" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE351" s="1">
-        <v>46094</v>
+        <v>46081</v>
       </c>
       <c r="AF351" s="1">
         <v>46235</v>
       </c>
       <c r="AG351" s="1">
-        <v>46375</v>
+        <v>46249</v>
       </c>
       <c r="AH351">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="AI351" t="s">
         <v>112</v>
       </c>
       <c r="AJ351">
-        <v>-24500</v>
+        <v>0</v>
       </c>
       <c r="AK351" t="s">
         <v>64</v>
@@ -68254,8 +68329,8 @@
       <c r="AL351" t="s">
         <v>53</v>
       </c>
-      <c r="AM351" t="s">
-        <v>53</v>
+      <c r="AM351">
+        <v>1042.2</v>
       </c>
       <c r="AN351" t="s">
         <v>53</v>
@@ -68269,11 +68344,11 @@
       <c r="AQ351" t="s">
         <v>53</v>
       </c>
-      <c r="AR351" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS351" s="2" t="s">
-        <v>53</v>
+      <c r="AR351" s="1">
+        <v>46186</v>
+      </c>
+      <c r="AS351" s="2">
+        <v>46186.88296296296</v>
       </c>
       <c r="AT351" s="1" t="s">
         <v>53</v>
@@ -68282,10 +68357,10 @@
         <v>53</v>
       </c>
       <c r="AV351" t="s">
-        <v>479</v>
+        <v>53</v>
       </c>
       <c r="AW351" t="s">
-        <v>2174</v>
+        <v>53</v>
       </c>
       <c r="AX351" t="s">
         <v>53</v>
@@ -68296,34 +68371,34 @@
     </row>
     <row r="352" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>2175</v>
+        <v>1166</v>
       </c>
       <c r="B352" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C352" t="s">
+        <v>53</v>
+      </c>
+      <c r="D352" t="s">
+        <v>988</v>
+      </c>
+      <c r="E352" t="s">
+        <v>159</v>
+      </c>
+      <c r="F352" t="s">
         <v>2176</v>
       </c>
-      <c r="C352" t="s">
-        <v>53</v>
-      </c>
-      <c r="D352" t="s">
-        <v>53</v>
-      </c>
-      <c r="E352" t="s">
-        <v>53</v>
-      </c>
-      <c r="F352" t="s">
+      <c r="G352" t="s">
         <v>2177</v>
       </c>
-      <c r="G352" t="s">
-        <v>53</v>
-      </c>
       <c r="H352" t="s">
         <v>53</v>
       </c>
       <c r="I352">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J352">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K352">
         <v>0</v>
@@ -68341,25 +68416,25 @@
         <v>53</v>
       </c>
       <c r="P352" t="s">
-        <v>88</v>
+        <v>786</v>
       </c>
       <c r="Q352" t="s">
-        <v>766</v>
+        <v>787</v>
       </c>
       <c r="R352" t="s">
-        <v>88</v>
+        <v>786</v>
       </c>
       <c r="S352" t="s">
-        <v>2178</v>
+        <v>53</v>
       </c>
       <c r="T352" t="s">
         <v>97</v>
       </c>
       <c r="U352" t="s">
-        <v>1459</v>
+        <v>954</v>
       </c>
       <c r="V352" t="s">
-        <v>99</v>
+        <v>744</v>
       </c>
       <c r="W352" t="s">
         <v>53</v>
@@ -68371,37 +68446,37 @@
         <v>53</v>
       </c>
       <c r="Z352">
-        <v>4591</v>
+        <v>24500</v>
       </c>
       <c r="AA352" t="s">
+        <v>2178</v>
+      </c>
+      <c r="AB352" t="s">
+        <v>180</v>
+      </c>
+      <c r="AC352" t="s">
         <v>2179</v>
-      </c>
-      <c r="AB352" t="s">
-        <v>763</v>
-      </c>
-      <c r="AC352" t="s">
-        <v>2180</v>
       </c>
       <c r="AD352" t="s">
         <v>1361</v>
       </c>
       <c r="AE352" s="1">
-        <v>46112</v>
+        <v>46094</v>
       </c>
       <c r="AF352" s="1">
-        <v>46236</v>
+        <v>46235</v>
       </c>
       <c r="AG352" s="1">
-        <v>46240</v>
+        <v>46375</v>
       </c>
       <c r="AH352">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="AI352" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ352">
-        <v>-3213.7</v>
+        <v>-24500</v>
       </c>
       <c r="AK352" t="s">
         <v>64</v>
@@ -68437,10 +68512,10 @@
         <v>53</v>
       </c>
       <c r="AV352" t="s">
-        <v>53</v>
+        <v>479</v>
       </c>
       <c r="AW352" t="s">
-        <v>53</v>
+        <v>2180</v>
       </c>
       <c r="AX352" t="s">
         <v>53</v>
@@ -68463,25 +68538,25 @@
         <v>53</v>
       </c>
       <c r="E353" t="s">
-        <v>165</v>
+        <v>53</v>
       </c>
       <c r="F353" t="s">
         <v>2183</v>
       </c>
       <c r="G353" t="s">
-        <v>2184</v>
+        <v>53</v>
       </c>
       <c r="H353" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I353">
         <v>4</v>
       </c>
       <c r="J353">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K353">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L353" s="1" t="s">
         <v>53</v>
@@ -68496,25 +68571,25 @@
         <v>53</v>
       </c>
       <c r="P353" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="Q353" t="s">
-        <v>184</v>
+        <v>766</v>
       </c>
       <c r="R353" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="S353" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="T353" t="s">
         <v>97</v>
       </c>
       <c r="U353" t="s">
-        <v>190</v>
+        <v>1459</v>
       </c>
       <c r="V353" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="W353" t="s">
         <v>53</v>
@@ -68526,37 +68601,37 @@
         <v>53</v>
       </c>
       <c r="Z353">
-        <v>3621.6</v>
+        <v>4591</v>
       </c>
       <c r="AA353" t="s">
+        <v>2185</v>
+      </c>
+      <c r="AB353" t="s">
+        <v>763</v>
+      </c>
+      <c r="AC353" t="s">
         <v>2186</v>
-      </c>
-      <c r="AB353" t="s">
-        <v>180</v>
-      </c>
-      <c r="AC353" t="s">
-        <v>2187</v>
       </c>
       <c r="AD353" t="s">
         <v>1361</v>
       </c>
       <c r="AE353" s="1">
-        <v>46145</v>
+        <v>46112</v>
       </c>
       <c r="AF353" s="1">
         <v>46236</v>
       </c>
       <c r="AG353" s="1">
-        <v>46243</v>
+        <v>46240</v>
       </c>
       <c r="AH353">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI353" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ353">
-        <v>-3621.6</v>
+        <v>-3213.7</v>
       </c>
       <c r="AK353" t="s">
         <v>64</v>
@@ -68564,8 +68639,8 @@
       <c r="AL353" t="s">
         <v>53</v>
       </c>
-      <c r="AM353">
-        <v>543.24</v>
+      <c r="AM353" t="s">
+        <v>53</v>
       </c>
       <c r="AN353" t="s">
         <v>53</v>
@@ -68606,37 +68681,37 @@
     </row>
     <row r="354" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B354" t="s">
         <v>2188</v>
       </c>
-      <c r="B354" t="s">
+      <c r="C354" t="s">
+        <v>53</v>
+      </c>
+      <c r="D354" t="s">
+        <v>53</v>
+      </c>
+      <c r="E354" t="s">
+        <v>165</v>
+      </c>
+      <c r="F354" t="s">
         <v>2189</v>
       </c>
-      <c r="C354" t="s">
-        <v>53</v>
-      </c>
-      <c r="D354" t="s">
-        <v>53</v>
-      </c>
-      <c r="E354" t="s">
+      <c r="G354" t="s">
         <v>2190</v>
-      </c>
-      <c r="F354" t="s">
-        <v>2191</v>
-      </c>
-      <c r="G354" t="s">
-        <v>2192</v>
       </c>
       <c r="H354" t="s">
         <v>86</v>
       </c>
       <c r="I354">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J354">
         <v>2</v>
       </c>
       <c r="K354">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L354" s="1" t="s">
         <v>53</v>
@@ -68660,7 +68735,7 @@
         <v>183</v>
       </c>
       <c r="S354" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="T354" t="s">
         <v>97</v>
@@ -68669,7 +68744,7 @@
         <v>190</v>
       </c>
       <c r="V354" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="W354" t="s">
         <v>53</v>
@@ -68681,37 +68756,37 @@
         <v>53</v>
       </c>
       <c r="Z354">
-        <v>1611.82</v>
+        <v>3621.6</v>
       </c>
       <c r="AA354" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="AB354" t="s">
         <v>180</v>
       </c>
       <c r="AC354" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="AD354" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE354" s="1">
-        <v>46131</v>
+        <v>46145</v>
       </c>
       <c r="AF354" s="1">
-        <v>46241</v>
+        <v>46236</v>
       </c>
       <c r="AG354" s="1">
-        <v>46244</v>
+        <v>46243</v>
       </c>
       <c r="AH354">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI354" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ354">
-        <v>0</v>
+        <v>-3621.6</v>
       </c>
       <c r="AK354" t="s">
         <v>64</v>
@@ -68720,7 +68795,7 @@
         <v>53</v>
       </c>
       <c r="AM354">
-        <v>241.77</v>
+        <v>543.24</v>
       </c>
       <c r="AN354" t="s">
         <v>53</v>
@@ -68734,11 +68809,11 @@
       <c r="AQ354" t="s">
         <v>53</v>
       </c>
-      <c r="AR354" s="1">
-        <v>46131</v>
-      </c>
-      <c r="AS354" s="2">
-        <v>46131.51017361111</v>
+      <c r="AR354" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS354" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT354" s="1" t="s">
         <v>53</v>
@@ -68761,37 +68836,37 @@
     </row>
     <row r="355" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B355" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C355" t="s">
+        <v>53</v>
+      </c>
+      <c r="D355" t="s">
+        <v>53</v>
+      </c>
+      <c r="E355" t="s">
         <v>2196</v>
       </c>
-      <c r="B355" t="s">
+      <c r="F355" t="s">
         <v>2197</v>
       </c>
-      <c r="C355" t="s">
-        <v>53</v>
-      </c>
-      <c r="D355" t="s">
-        <v>53</v>
-      </c>
-      <c r="E355" t="s">
-        <v>159</v>
-      </c>
-      <c r="F355" t="s">
+      <c r="G355" t="s">
         <v>2198</v>
       </c>
-      <c r="G355" t="s">
-        <v>53</v>
-      </c>
       <c r="H355" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I355">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J355">
         <v>2</v>
       </c>
       <c r="K355">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L355" s="1" t="s">
         <v>53</v>
@@ -68806,13 +68881,13 @@
         <v>53</v>
       </c>
       <c r="P355" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="Q355" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="R355" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="S355" t="s">
         <v>2199</v>
@@ -68821,7 +68896,7 @@
         <v>97</v>
       </c>
       <c r="U355" t="s">
-        <v>1006</v>
+        <v>190</v>
       </c>
       <c r="V355" t="s">
         <v>99</v>
@@ -68836,7 +68911,7 @@
         <v>53</v>
       </c>
       <c r="Z355">
-        <v>1627.68</v>
+        <v>1611.82</v>
       </c>
       <c r="AA355" t="s">
         <v>2200</v>
@@ -68848,25 +68923,25 @@
         <v>2201</v>
       </c>
       <c r="AD355" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE355" s="1">
-        <v>46046</v>
+        <v>46131</v>
       </c>
       <c r="AF355" s="1">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="AG355" s="1">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="AH355">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AI355" t="s">
         <v>63</v>
       </c>
       <c r="AJ355">
-        <v>-1627.68</v>
+        <v>0</v>
       </c>
       <c r="AK355" t="s">
         <v>64</v>
@@ -68874,8 +68949,8 @@
       <c r="AL355" t="s">
         <v>53</v>
       </c>
-      <c r="AM355" t="s">
-        <v>53</v>
+      <c r="AM355">
+        <v>241.77</v>
       </c>
       <c r="AN355" t="s">
         <v>53</v>
@@ -68889,11 +68964,11 @@
       <c r="AQ355" t="s">
         <v>53</v>
       </c>
-      <c r="AR355" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS355" s="2" t="s">
-        <v>53</v>
+      <c r="AR355" s="1">
+        <v>46131</v>
+      </c>
+      <c r="AS355" s="2">
+        <v>46131.51017361111</v>
       </c>
       <c r="AT355" s="1" t="s">
         <v>53</v>
@@ -68928,7 +69003,7 @@
         <v>53</v>
       </c>
       <c r="E356" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="F356" t="s">
         <v>2204</v>
@@ -68940,10 +69015,10 @@
         <v>53</v>
       </c>
       <c r="I356">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J356">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K356">
         <v>0</v>
@@ -68961,13 +69036,13 @@
         <v>53</v>
       </c>
       <c r="P356" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="Q356" t="s">
-        <v>766</v>
+        <v>178</v>
       </c>
       <c r="R356" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="S356" t="s">
         <v>2205</v>
@@ -68991,13 +69066,13 @@
         <v>53</v>
       </c>
       <c r="Z356">
-        <v>7268.08</v>
+        <v>1627.68</v>
       </c>
       <c r="AA356" t="s">
         <v>2206</v>
       </c>
       <c r="AB356" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC356" t="s">
         <v>2207</v>
@@ -69006,22 +69081,22 @@
         <v>1361</v>
       </c>
       <c r="AE356" s="1">
-        <v>46169</v>
+        <v>46046</v>
       </c>
       <c r="AF356" s="1">
         <v>46242</v>
       </c>
       <c r="AG356" s="1">
-        <v>46250</v>
+        <v>46248</v>
       </c>
       <c r="AH356">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI356" t="s">
         <v>63</v>
       </c>
       <c r="AJ356">
-        <v>-7268.08</v>
+        <v>-1627.68</v>
       </c>
       <c r="AK356" t="s">
         <v>64</v>
@@ -69083,22 +69158,22 @@
         <v>53</v>
       </c>
       <c r="E357" t="s">
-        <v>220</v>
+        <v>53</v>
       </c>
       <c r="F357" t="s">
         <v>2210</v>
       </c>
       <c r="G357" t="s">
-        <v>2211</v>
+        <v>53</v>
       </c>
       <c r="H357" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I357">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J357">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K357">
         <v>0</v>
@@ -69116,25 +69191,25 @@
         <v>53</v>
       </c>
       <c r="P357" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="Q357" t="s">
-        <v>68</v>
+        <v>766</v>
       </c>
       <c r="R357" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="S357" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="T357" t="s">
         <v>97</v>
       </c>
       <c r="U357" t="s">
-        <v>190</v>
+        <v>1006</v>
       </c>
       <c r="V357" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="W357" t="s">
         <v>53</v>
@@ -69146,37 +69221,37 @@
         <v>53</v>
       </c>
       <c r="Z357">
-        <v>7616.7</v>
+        <v>7268.08</v>
       </c>
       <c r="AA357" t="s">
+        <v>2212</v>
+      </c>
+      <c r="AB357" t="s">
+        <v>763</v>
+      </c>
+      <c r="AC357" t="s">
         <v>2213</v>
       </c>
-      <c r="AB357" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC357" t="s">
-        <v>2214</v>
-      </c>
       <c r="AD357" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE357" s="1">
-        <v>46173</v>
+        <v>46169</v>
       </c>
       <c r="AF357" s="1">
         <v>46242</v>
       </c>
       <c r="AG357" s="1">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="AH357">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AI357" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ357">
-        <v>0</v>
+        <v>-7268.08</v>
       </c>
       <c r="AK357" t="s">
         <v>64</v>
@@ -69184,8 +69259,8 @@
       <c r="AL357" t="s">
         <v>53</v>
       </c>
-      <c r="AM357">
-        <v>1142.51</v>
+      <c r="AM357" t="s">
+        <v>53</v>
       </c>
       <c r="AN357" t="s">
         <v>53</v>
@@ -69199,11 +69274,11 @@
       <c r="AQ357" t="s">
         <v>53</v>
       </c>
-      <c r="AR357" s="1">
-        <v>46183</v>
-      </c>
-      <c r="AS357" s="2">
-        <v>46183.99928240741</v>
+      <c r="AR357" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS357" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT357" s="1" t="s">
         <v>53</v>
@@ -69226,34 +69301,34 @@
     </row>
     <row r="358" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B358" t="s">
         <v>2215</v>
       </c>
-      <c r="B358" t="s">
+      <c r="C358" t="s">
+        <v>53</v>
+      </c>
+      <c r="D358" t="s">
+        <v>53</v>
+      </c>
+      <c r="E358" t="s">
+        <v>220</v>
+      </c>
+      <c r="F358" t="s">
         <v>2216</v>
       </c>
-      <c r="C358" t="s">
-        <v>53</v>
-      </c>
-      <c r="D358" t="s">
-        <v>53</v>
-      </c>
-      <c r="E358" t="s">
-        <v>53</v>
-      </c>
-      <c r="F358" t="s">
+      <c r="G358" t="s">
         <v>2217</v>
       </c>
-      <c r="G358" t="s">
-        <v>53</v>
-      </c>
       <c r="H358" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I358">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J358">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K358">
         <v>0</v>
@@ -69271,13 +69346,13 @@
         <v>53</v>
       </c>
       <c r="P358" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="Q358" t="s">
-        <v>766</v>
+        <v>68</v>
       </c>
       <c r="R358" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="S358" t="s">
         <v>2218</v>
@@ -69286,10 +69361,10 @@
         <v>97</v>
       </c>
       <c r="U358" t="s">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="V358" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="W358" t="s">
         <v>53</v>
@@ -69301,13 +69376,13 @@
         <v>53</v>
       </c>
       <c r="Z358">
-        <v>11002.2</v>
+        <v>7616.7</v>
       </c>
       <c r="AA358" t="s">
         <v>2219</v>
       </c>
       <c r="AB358" t="s">
-        <v>763</v>
+        <v>60</v>
       </c>
       <c r="AC358" t="s">
         <v>2220</v>
@@ -69316,19 +69391,19 @@
         <v>62</v>
       </c>
       <c r="AE358" s="1">
-        <v>46141</v>
+        <v>46173</v>
       </c>
       <c r="AF358" s="1">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="AG358" s="1">
         <v>46257</v>
       </c>
       <c r="AH358">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI358" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ358">
         <v>0</v>
@@ -69339,8 +69414,8 @@
       <c r="AL358" t="s">
         <v>53</v>
       </c>
-      <c r="AM358" t="s">
-        <v>53</v>
+      <c r="AM358">
+        <v>1142.51</v>
       </c>
       <c r="AN358" t="s">
         <v>53</v>
@@ -69355,10 +69430,10 @@
         <v>53</v>
       </c>
       <c r="AR358" s="1">
-        <v>46151</v>
+        <v>46183</v>
       </c>
       <c r="AS358" s="2">
-        <v>46151.583449074074</v>
+        <v>46183.99928240741</v>
       </c>
       <c r="AT358" s="1" t="s">
         <v>53</v>
@@ -69393,7 +69468,7 @@
         <v>53</v>
       </c>
       <c r="E359" t="s">
-        <v>165</v>
+        <v>53</v>
       </c>
       <c r="F359" t="s">
         <v>2223</v>
@@ -69405,10 +69480,10 @@
         <v>53</v>
       </c>
       <c r="I359">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J359">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K359">
         <v>0</v>
@@ -69441,7 +69516,7 @@
         <v>97</v>
       </c>
       <c r="U359" t="s">
-        <v>1006</v>
+        <v>300</v>
       </c>
       <c r="V359" t="s">
         <v>99</v>
@@ -69456,7 +69531,7 @@
         <v>53</v>
       </c>
       <c r="Z359">
-        <v>4336.2</v>
+        <v>11002.2</v>
       </c>
       <c r="AA359" t="s">
         <v>2225</v>
@@ -69471,16 +69546,16 @@
         <v>62</v>
       </c>
       <c r="AE359" s="1">
-        <v>46158</v>
+        <v>46141</v>
       </c>
       <c r="AF359" s="1">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="AG359" s="1">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="AH359">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AI359" t="s">
         <v>63</v>
@@ -69510,10 +69585,10 @@
         <v>53</v>
       </c>
       <c r="AR359" s="1">
-        <v>46160</v>
+        <v>46151</v>
       </c>
       <c r="AS359" s="2">
-        <v>46160.40216435185</v>
+        <v>46151.583449074074</v>
       </c>
       <c r="AT359" s="1" t="s">
         <v>53</v>
@@ -69522,7 +69597,7 @@
         <v>53</v>
       </c>
       <c r="AV359" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="AW359" t="s">
         <v>53</v>
@@ -69536,10 +69611,10 @@
     </row>
     <row r="360" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>2221</v>
+        <v>2227</v>
       </c>
       <c r="B360" t="s">
-        <v>2222</v>
+        <v>2228</v>
       </c>
       <c r="C360" t="s">
         <v>53</v>
@@ -69551,7 +69626,7 @@
         <v>165</v>
       </c>
       <c r="F360" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="G360" t="s">
         <v>53</v>
@@ -69590,7 +69665,7 @@
         <v>88</v>
       </c>
       <c r="S360" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="T360" t="s">
         <v>97</v>
@@ -69611,31 +69686,31 @@
         <v>53</v>
       </c>
       <c r="Z360">
-        <v>7399.35</v>
+        <v>4336.2</v>
       </c>
       <c r="AA360" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="AB360" t="s">
         <v>763</v>
       </c>
       <c r="AC360" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="AD360" t="s">
         <v>62</v>
       </c>
       <c r="AE360" s="1">
-        <v>46160</v>
+        <v>46158</v>
       </c>
       <c r="AF360" s="1">
         <v>46247</v>
       </c>
       <c r="AG360" s="1">
-        <v>46256</v>
+        <v>46252</v>
       </c>
       <c r="AH360">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AI360" t="s">
         <v>63</v>
@@ -69665,10 +69740,10 @@
         <v>53</v>
       </c>
       <c r="AR360" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="AS360" s="2">
-        <v>46170.66144675926</v>
+        <v>46160.40216435185</v>
       </c>
       <c r="AT360" s="1" t="s">
         <v>53</v>
@@ -69691,10 +69766,10 @@
     </row>
     <row r="361" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>2221</v>
+        <v>2227</v>
       </c>
       <c r="B361" t="s">
-        <v>2222</v>
+        <v>2228</v>
       </c>
       <c r="C361" t="s">
         <v>53</v>
@@ -69703,10 +69778,10 @@
         <v>53</v>
       </c>
       <c r="E361" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="F361" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="G361" t="s">
         <v>53</v>
@@ -69736,16 +69811,16 @@
         <v>53</v>
       </c>
       <c r="P361" t="s">
-        <v>804</v>
+        <v>88</v>
       </c>
       <c r="Q361" t="s">
-        <v>53</v>
+        <v>766</v>
       </c>
       <c r="R361" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="S361" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="T361" t="s">
         <v>97</v>
@@ -69766,22 +69841,22 @@
         <v>53</v>
       </c>
       <c r="Z361">
-        <v>7398.81</v>
+        <v>7399.35</v>
       </c>
       <c r="AA361" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="AB361" t="s">
         <v>763</v>
       </c>
       <c r="AC361" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="AD361" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE361" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="AF361" s="1">
         <v>46247</v>
@@ -69796,7 +69871,7 @@
         <v>63</v>
       </c>
       <c r="AJ361">
-        <v>-7398.81</v>
+        <v>0</v>
       </c>
       <c r="AK361" t="s">
         <v>64</v>
@@ -69819,11 +69894,11 @@
       <c r="AQ361" t="s">
         <v>53</v>
       </c>
-      <c r="AR361" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS361" s="2" t="s">
-        <v>53</v>
+      <c r="AR361" s="1">
+        <v>46170</v>
+      </c>
+      <c r="AS361" s="2">
+        <v>46170.66144675926</v>
       </c>
       <c r="AT361" s="1" t="s">
         <v>53</v>
@@ -69832,7 +69907,7 @@
         <v>53</v>
       </c>
       <c r="AV361" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="AW361" t="s">
         <v>53</v>
@@ -69846,10 +69921,10 @@
     </row>
     <row r="362" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>588</v>
+        <v>2227</v>
       </c>
       <c r="B362" t="s">
-        <v>2235</v>
+        <v>2228</v>
       </c>
       <c r="C362" t="s">
         <v>53</v>
@@ -69858,25 +69933,25 @@
         <v>53</v>
       </c>
       <c r="E362" t="s">
-        <v>498</v>
+        <v>53</v>
       </c>
       <c r="F362" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="G362" t="s">
-        <v>2237</v>
+        <v>53</v>
       </c>
       <c r="H362" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I362">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J362">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K362">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L362" s="1" t="s">
         <v>53</v>
@@ -69891,7 +69966,7 @@
         <v>53</v>
       </c>
       <c r="P362" t="s">
-        <v>189</v>
+        <v>804</v>
       </c>
       <c r="Q362" t="s">
         <v>53</v>
@@ -69906,10 +69981,10 @@
         <v>97</v>
       </c>
       <c r="U362" t="s">
-        <v>190</v>
+        <v>1006</v>
       </c>
       <c r="V362" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="W362" t="s">
         <v>53</v>
@@ -69921,37 +69996,37 @@
         <v>53</v>
       </c>
       <c r="Z362">
-        <v>8665</v>
+        <v>7398.81</v>
       </c>
       <c r="AA362" t="s">
         <v>2239</v>
       </c>
       <c r="AB362" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC362" t="s">
         <v>2240</v>
       </c>
       <c r="AD362" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE362" s="1">
-        <v>46030</v>
+        <v>46170</v>
       </c>
       <c r="AF362" s="1">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="AG362" s="1">
-        <v>46262</v>
+        <v>46256</v>
       </c>
       <c r="AH362">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AI362" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ362">
-        <v>0</v>
+        <v>-7398.81</v>
       </c>
       <c r="AK362" t="s">
         <v>64</v>
@@ -69959,8 +70034,8 @@
       <c r="AL362" t="s">
         <v>53</v>
       </c>
-      <c r="AM362">
-        <v>1299.75</v>
+      <c r="AM362" t="s">
+        <v>53</v>
       </c>
       <c r="AN362" t="s">
         <v>53</v>
@@ -69974,11 +70049,11 @@
       <c r="AQ362" t="s">
         <v>53</v>
       </c>
-      <c r="AR362" s="1">
-        <v>46032</v>
-      </c>
-      <c r="AS362" s="2">
-        <v>46032.64398148148</v>
+      <c r="AR362" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS362" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT362" s="1" t="s">
         <v>53</v>
@@ -70001,37 +70076,37 @@
     </row>
     <row r="363" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
+        <v>588</v>
+      </c>
+      <c r="B363" t="s">
         <v>2241</v>
       </c>
-      <c r="B363" t="s">
+      <c r="C363" t="s">
+        <v>53</v>
+      </c>
+      <c r="D363" t="s">
+        <v>53</v>
+      </c>
+      <c r="E363" t="s">
+        <v>498</v>
+      </c>
+      <c r="F363" t="s">
         <v>2242</v>
       </c>
-      <c r="C363" t="s">
-        <v>53</v>
-      </c>
-      <c r="D363" t="s">
-        <v>53</v>
-      </c>
-      <c r="E363" t="s">
-        <v>165</v>
-      </c>
-      <c r="F363" t="s">
+      <c r="G363" t="s">
         <v>2243</v>
-      </c>
-      <c r="G363" t="s">
-        <v>2244</v>
       </c>
       <c r="H363" t="s">
         <v>86</v>
       </c>
       <c r="I363">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J363">
         <v>2</v>
       </c>
       <c r="K363">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L363" s="1" t="s">
         <v>53</v>
@@ -70046,16 +70121,16 @@
         <v>53</v>
       </c>
       <c r="P363" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="Q363" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="R363" t="s">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="S363" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="T363" t="s">
         <v>97</v>
@@ -70064,7 +70139,7 @@
         <v>190</v>
       </c>
       <c r="V363" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="W363" t="s">
         <v>53</v>
@@ -70076,34 +70151,34 @@
         <v>53</v>
       </c>
       <c r="Z363">
-        <v>980</v>
+        <v>8665</v>
       </c>
       <c r="AA363" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="AB363" t="s">
         <v>180</v>
       </c>
       <c r="AC363" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="AD363" t="s">
         <v>62</v>
       </c>
       <c r="AE363" s="1">
-        <v>46048</v>
+        <v>46030</v>
       </c>
       <c r="AF363" s="1">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="AG363" s="1">
-        <v>46254</v>
+        <v>46262</v>
       </c>
       <c r="AH363">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AI363" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ363">
         <v>0</v>
@@ -70115,7 +70190,7 @@
         <v>53</v>
       </c>
       <c r="AM363">
-        <v>147</v>
+        <v>1299.75</v>
       </c>
       <c r="AN363" t="s">
         <v>53</v>
@@ -70130,10 +70205,10 @@
         <v>53</v>
       </c>
       <c r="AR363" s="1">
-        <v>46153</v>
+        <v>46032</v>
       </c>
       <c r="AS363" s="2">
-        <v>46153.715682870374</v>
+        <v>46032.64398148148</v>
       </c>
       <c r="AT363" s="1" t="s">
         <v>53</v>
@@ -70156,7 +70231,7 @@
     </row>
     <row r="364" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>1928</v>
+        <v>2247</v>
       </c>
       <c r="B364" t="s">
         <v>2248</v>
@@ -70204,7 +70279,7 @@
         <v>177</v>
       </c>
       <c r="Q364" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="R364" t="s">
         <v>177</v>
@@ -70231,7 +70306,7 @@
         <v>53</v>
       </c>
       <c r="Z364">
-        <v>982.77</v>
+        <v>980</v>
       </c>
       <c r="AA364" t="s">
         <v>2252</v>
@@ -70243,16 +70318,16 @@
         <v>2253</v>
       </c>
       <c r="AD364" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE364" s="1">
-        <v>46115</v>
+        <v>46048</v>
       </c>
       <c r="AF364" s="1">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="AG364" s="1">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="AH364">
         <v>3</v>
@@ -70261,7 +70336,7 @@
         <v>63</v>
       </c>
       <c r="AJ364">
-        <v>-982.77</v>
+        <v>0</v>
       </c>
       <c r="AK364" t="s">
         <v>64</v>
@@ -70270,7 +70345,7 @@
         <v>53</v>
       </c>
       <c r="AM364">
-        <v>147.42</v>
+        <v>147</v>
       </c>
       <c r="AN364" t="s">
         <v>53</v>
@@ -70284,11 +70359,11 @@
       <c r="AQ364" t="s">
         <v>53</v>
       </c>
-      <c r="AR364" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS364" s="2" t="s">
-        <v>53</v>
+      <c r="AR364" s="1">
+        <v>46153</v>
+      </c>
+      <c r="AS364" s="2">
+        <v>46153.715682870374</v>
       </c>
       <c r="AT364" s="1" t="s">
         <v>53</v>
@@ -70311,34 +70386,34 @@
     </row>
     <row r="365" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B365" t="s">
         <v>2254</v>
       </c>
-      <c r="B365" t="s">
+      <c r="C365" t="s">
+        <v>53</v>
+      </c>
+      <c r="D365" t="s">
+        <v>53</v>
+      </c>
+      <c r="E365" t="s">
+        <v>165</v>
+      </c>
+      <c r="F365" t="s">
         <v>2255</v>
       </c>
-      <c r="C365" t="s">
-        <v>53</v>
-      </c>
-      <c r="D365" t="s">
-        <v>53</v>
-      </c>
-      <c r="E365" t="s">
-        <v>312</v>
-      </c>
-      <c r="F365" t="s">
+      <c r="G365" t="s">
         <v>2256</v>
-      </c>
-      <c r="G365" t="s">
-        <v>2257</v>
       </c>
       <c r="H365" t="s">
         <v>86</v>
       </c>
       <c r="I365">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J365">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K365">
         <v>0</v>
@@ -70356,16 +70431,16 @@
         <v>53</v>
       </c>
       <c r="P365" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Q365" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="R365" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="S365" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="T365" t="s">
         <v>97</v>
@@ -70374,7 +70449,7 @@
         <v>190</v>
       </c>
       <c r="V365" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="W365" t="s">
         <v>53</v>
@@ -70386,37 +70461,37 @@
         <v>53</v>
       </c>
       <c r="Z365">
-        <v>2599.95</v>
+        <v>982.77</v>
       </c>
       <c r="AA365" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="AB365" t="s">
         <v>180</v>
       </c>
       <c r="AC365" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="AD365" t="s">
         <v>1361</v>
       </c>
       <c r="AE365" s="1">
-        <v>46139</v>
+        <v>46115</v>
       </c>
       <c r="AF365" s="1">
-        <v>46259</v>
+        <v>46252</v>
       </c>
       <c r="AG365" s="1">
-        <v>46264</v>
+        <v>46255</v>
       </c>
       <c r="AH365">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI365" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ365">
-        <v>-2599.95</v>
+        <v>-982.77</v>
       </c>
       <c r="AK365" t="s">
         <v>64</v>
@@ -70425,7 +70500,7 @@
         <v>53</v>
       </c>
       <c r="AM365">
-        <v>389.99</v>
+        <v>147.42</v>
       </c>
       <c r="AN365" t="s">
         <v>53</v>
@@ -70466,34 +70541,34 @@
     </row>
     <row r="366" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B366" t="s">
         <v>2261</v>
       </c>
-      <c r="B366" t="s">
+      <c r="C366" t="s">
+        <v>53</v>
+      </c>
+      <c r="D366" t="s">
+        <v>53</v>
+      </c>
+      <c r="E366" t="s">
+        <v>312</v>
+      </c>
+      <c r="F366" t="s">
         <v>2262</v>
       </c>
-      <c r="C366" t="s">
-        <v>53</v>
-      </c>
-      <c r="D366" t="s">
-        <v>53</v>
-      </c>
-      <c r="E366" t="s">
-        <v>53</v>
-      </c>
-      <c r="F366" t="s">
+      <c r="G366" t="s">
         <v>2263</v>
       </c>
-      <c r="G366" t="s">
-        <v>53</v>
-      </c>
       <c r="H366" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I366">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J366">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K366">
         <v>0</v>
@@ -70511,25 +70586,25 @@
         <v>53</v>
       </c>
       <c r="P366" t="s">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="Q366" t="s">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="R366" t="s">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="S366" t="s">
-        <v>53</v>
+        <v>2264</v>
       </c>
       <c r="T366" t="s">
         <v>97</v>
       </c>
       <c r="U366" t="s">
-        <v>736</v>
+        <v>190</v>
       </c>
       <c r="V366" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="W366" t="s">
         <v>53</v>
@@ -70541,37 +70616,37 @@
         <v>53</v>
       </c>
       <c r="Z366">
-        <v>0</v>
+        <v>2599.95</v>
       </c>
       <c r="AA366" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="AB366" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AC366" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="AD366" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE366" s="1">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="AF366" s="1">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="AG366" s="1">
-        <v>46556</v>
+        <v>46264</v>
       </c>
       <c r="AH366">
-        <v>290</v>
+        <v>5</v>
       </c>
       <c r="AI366" t="s">
         <v>112</v>
       </c>
       <c r="AJ366">
-        <v>0</v>
+        <v>-2599.95</v>
       </c>
       <c r="AK366" t="s">
         <v>64</v>
@@ -70579,8 +70654,8 @@
       <c r="AL366" t="s">
         <v>53</v>
       </c>
-      <c r="AM366" t="s">
-        <v>53</v>
+      <c r="AM366">
+        <v>389.99</v>
       </c>
       <c r="AN366" t="s">
         <v>53</v>
@@ -70594,11 +70669,11 @@
       <c r="AQ366" t="s">
         <v>53</v>
       </c>
-      <c r="AR366" s="1">
-        <v>46140</v>
-      </c>
-      <c r="AS366" s="2">
-        <v>46140.55385416667</v>
+      <c r="AR366" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS366" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT366" s="1" t="s">
         <v>53</v>
@@ -70607,7 +70682,7 @@
         <v>53</v>
       </c>
       <c r="AV366" t="s">
-        <v>479</v>
+        <v>53</v>
       </c>
       <c r="AW366" t="s">
         <v>53</v>
@@ -70621,10 +70696,10 @@
     </row>
     <row r="367" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>2261</v>
+        <v>2267</v>
       </c>
       <c r="B367" t="s">
-        <v>2262</v>
+        <v>2268</v>
       </c>
       <c r="C367" t="s">
         <v>53</v>
@@ -70633,16 +70708,16 @@
         <v>53</v>
       </c>
       <c r="E367" t="s">
-        <v>159</v>
+        <v>53</v>
       </c>
       <c r="F367" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="G367" t="s">
-        <v>2267</v>
+        <v>53</v>
       </c>
       <c r="H367" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="I367">
         <v>1</v>
@@ -70669,10 +70744,10 @@
         <v>67</v>
       </c>
       <c r="Q367" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="R367" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="S367" t="s">
         <v>53</v>
@@ -70684,7 +70759,7 @@
         <v>736</v>
       </c>
       <c r="V367" t="s">
-        <v>2268</v>
+        <v>125</v>
       </c>
       <c r="W367" t="s">
         <v>53</v>
@@ -70696,19 +70771,19 @@
         <v>53</v>
       </c>
       <c r="Z367">
-        <v>62837.27</v>
+        <v>0</v>
       </c>
       <c r="AA367" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="AB367" t="s">
         <v>60</v>
       </c>
       <c r="AC367" t="s">
-        <v>2265</v>
+        <v>2271</v>
       </c>
       <c r="AD367" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE367" s="1">
         <v>46140</v>
@@ -70717,16 +70792,16 @@
         <v>46266</v>
       </c>
       <c r="AG367" s="1">
-        <v>46555</v>
+        <v>46556</v>
       </c>
       <c r="AH367">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI367" t="s">
         <v>112</v>
       </c>
       <c r="AJ367">
-        <v>-62837.27</v>
+        <v>0</v>
       </c>
       <c r="AK367" t="s">
         <v>64</v>
@@ -70749,11 +70824,11 @@
       <c r="AQ367" t="s">
         <v>53</v>
       </c>
-      <c r="AR367" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS367" s="2" t="s">
-        <v>53</v>
+      <c r="AR367" s="1">
+        <v>46140</v>
+      </c>
+      <c r="AS367" s="2">
+        <v>46140.55385416667</v>
       </c>
       <c r="AT367" s="1" t="s">
         <v>53</v>
@@ -70765,7 +70840,7 @@
         <v>479</v>
       </c>
       <c r="AW367" t="s">
-        <v>2270</v>
+        <v>53</v>
       </c>
       <c r="AX367" t="s">
         <v>53</v>
@@ -70776,10 +70851,10 @@
     </row>
     <row r="368" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>2271</v>
+        <v>2267</v>
       </c>
       <c r="B368" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="C368" t="s">
         <v>53</v>
@@ -70791,19 +70866,19 @@
         <v>159</v>
       </c>
       <c r="F368" t="s">
+        <v>2272</v>
+      </c>
+      <c r="G368" t="s">
         <v>2273</v>
       </c>
-      <c r="G368" t="s">
-        <v>2274</v>
-      </c>
       <c r="H368" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="I368">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J368">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K368">
         <v>0</v>
@@ -70821,25 +70896,25 @@
         <v>53</v>
       </c>
       <c r="P368" t="s">
-        <v>177</v>
+        <v>67</v>
       </c>
       <c r="Q368" t="s">
-        <v>178</v>
+        <v>68</v>
       </c>
       <c r="R368" t="s">
-        <v>177</v>
+        <v>67</v>
       </c>
       <c r="S368" t="s">
-        <v>2275</v>
+        <v>53</v>
       </c>
       <c r="T368" t="s">
         <v>97</v>
       </c>
       <c r="U368" t="s">
-        <v>190</v>
+        <v>736</v>
       </c>
       <c r="V368" t="s">
-        <v>99</v>
+        <v>2274</v>
       </c>
       <c r="W368" t="s">
         <v>53</v>
@@ -70851,37 +70926,37 @@
         <v>53</v>
       </c>
       <c r="Z368">
-        <v>974.7</v>
+        <v>62837.27</v>
       </c>
       <c r="AA368" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="AB368" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AC368" t="s">
-        <v>2277</v>
+        <v>2271</v>
       </c>
       <c r="AD368" t="s">
         <v>1361</v>
       </c>
       <c r="AE368" s="1">
-        <v>46069</v>
+        <v>46140</v>
       </c>
       <c r="AF368" s="1">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="AG368" s="1">
-        <v>46271</v>
+        <v>46555</v>
       </c>
       <c r="AH368">
-        <v>3</v>
+        <v>289</v>
       </c>
       <c r="AI368" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ368">
-        <v>-974.7</v>
+        <v>-62837.27</v>
       </c>
       <c r="AK368" t="s">
         <v>64</v>
@@ -70889,8 +70964,8 @@
       <c r="AL368" t="s">
         <v>53</v>
       </c>
-      <c r="AM368">
-        <v>146.21</v>
+      <c r="AM368" t="s">
+        <v>53</v>
       </c>
       <c r="AN368" t="s">
         <v>53</v>
@@ -70917,10 +70992,10 @@
         <v>53</v>
       </c>
       <c r="AV368" t="s">
-        <v>53</v>
+        <v>479</v>
       </c>
       <c r="AW368" t="s">
-        <v>53</v>
+        <v>2276</v>
       </c>
       <c r="AX368" t="s">
         <v>53</v>
@@ -70931,25 +71006,25 @@
     </row>
     <row r="369" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B369" t="s">
         <v>2278</v>
       </c>
-      <c r="B369" t="s">
+      <c r="C369" t="s">
+        <v>53</v>
+      </c>
+      <c r="D369" t="s">
+        <v>53</v>
+      </c>
+      <c r="E369" t="s">
+        <v>159</v>
+      </c>
+      <c r="F369" t="s">
         <v>2279</v>
       </c>
-      <c r="C369" t="s">
-        <v>53</v>
-      </c>
-      <c r="D369" t="s">
-        <v>53</v>
-      </c>
-      <c r="E369" t="s">
-        <v>647</v>
-      </c>
-      <c r="F369" t="s">
+      <c r="G369" t="s">
         <v>2280</v>
-      </c>
-      <c r="G369" t="s">
-        <v>2281</v>
       </c>
       <c r="H369" t="s">
         <v>86</v>
@@ -70979,13 +71054,13 @@
         <v>177</v>
       </c>
       <c r="Q369" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="R369" t="s">
         <v>177</v>
       </c>
       <c r="S369" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="T369" t="s">
         <v>97</v>
@@ -71006,28 +71081,28 @@
         <v>53</v>
       </c>
       <c r="Z369">
-        <v>1092.96</v>
+        <v>974.7</v>
       </c>
       <c r="AA369" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="AB369" t="s">
         <v>180</v>
       </c>
       <c r="AC369" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="AD369" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE369" s="1">
-        <v>46085</v>
+        <v>46069</v>
       </c>
       <c r="AF369" s="1">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="AG369" s="1">
-        <v>46275</v>
+        <v>46271</v>
       </c>
       <c r="AH369">
         <v>3</v>
@@ -71036,7 +71111,7 @@
         <v>63</v>
       </c>
       <c r="AJ369">
-        <v>0</v>
+        <v>-974.7</v>
       </c>
       <c r="AK369" t="s">
         <v>64</v>
@@ -71045,7 +71120,7 @@
         <v>53</v>
       </c>
       <c r="AM369">
-        <v>163.94</v>
+        <v>146.21</v>
       </c>
       <c r="AN369" t="s">
         <v>53</v>
@@ -71059,11 +71134,11 @@
       <c r="AQ369" t="s">
         <v>53</v>
       </c>
-      <c r="AR369" s="1">
-        <v>46088</v>
-      </c>
-      <c r="AS369" s="2">
-        <v>46088.145428240736</v>
+      <c r="AR369" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS369" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT369" s="1" t="s">
         <v>53</v>
@@ -71086,7 +71161,7 @@
     </row>
     <row r="370" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>2023</v>
+        <v>2284</v>
       </c>
       <c r="B370" t="s">
         <v>2285</v>
@@ -71098,22 +71173,22 @@
         <v>53</v>
       </c>
       <c r="E370" t="s">
-        <v>53</v>
+        <v>647</v>
       </c>
       <c r="F370" t="s">
         <v>2286</v>
       </c>
       <c r="G370" t="s">
-        <v>53</v>
+        <v>2287</v>
       </c>
       <c r="H370" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I370">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J370">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K370">
         <v>0</v>
@@ -71131,25 +71206,25 @@
         <v>53</v>
       </c>
       <c r="P370" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="Q370" t="s">
-        <v>766</v>
+        <v>253</v>
       </c>
       <c r="R370" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="S370" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="T370" t="s">
         <v>97</v>
       </c>
       <c r="U370" t="s">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="V370" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="W370" t="s">
         <v>53</v>
@@ -71161,37 +71236,37 @@
         <v>53</v>
       </c>
       <c r="Z370">
-        <v>1892</v>
+        <v>1092.96</v>
       </c>
       <c r="AA370" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="AB370" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC370" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="AD370" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE370" s="1">
-        <v>46108</v>
+        <v>46085</v>
       </c>
       <c r="AF370" s="1">
+        <v>46272</v>
+      </c>
+      <c r="AG370" s="1">
         <v>46275</v>
       </c>
-      <c r="AG370" s="1">
-        <v>46279</v>
-      </c>
       <c r="AH370">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI370" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ370">
-        <v>-1892</v>
+        <v>0</v>
       </c>
       <c r="AK370" t="s">
         <v>64</v>
@@ -71199,8 +71274,8 @@
       <c r="AL370" t="s">
         <v>53</v>
       </c>
-      <c r="AM370" t="s">
-        <v>53</v>
+      <c r="AM370">
+        <v>163.94</v>
       </c>
       <c r="AN370" t="s">
         <v>53</v>
@@ -71214,11 +71289,11 @@
       <c r="AQ370" t="s">
         <v>53</v>
       </c>
-      <c r="AR370" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS370" s="2" t="s">
-        <v>53</v>
+      <c r="AR370" s="1">
+        <v>46088</v>
+      </c>
+      <c r="AS370" s="2">
+        <v>46088.145428240736</v>
       </c>
       <c r="AT370" s="1" t="s">
         <v>53</v>
@@ -71241,7 +71316,7 @@
     </row>
     <row r="371" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>2290</v>
+        <v>2023</v>
       </c>
       <c r="B371" t="s">
         <v>2291</v>
@@ -71265,10 +71340,10 @@
         <v>53</v>
       </c>
       <c r="I371">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J371">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K371">
         <v>0</v>
@@ -71286,25 +71361,25 @@
         <v>53</v>
       </c>
       <c r="P371" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="Q371" t="s">
-        <v>184</v>
+        <v>766</v>
       </c>
       <c r="R371" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="S371" t="s">
-        <v>53</v>
+        <v>2293</v>
       </c>
       <c r="T371" t="s">
         <v>97</v>
       </c>
       <c r="U371" t="s">
-        <v>736</v>
+        <v>300</v>
       </c>
       <c r="V371" t="s">
-        <v>2293</v>
+        <v>58</v>
       </c>
       <c r="W371" t="s">
         <v>53</v>
@@ -71316,37 +71391,37 @@
         <v>53</v>
       </c>
       <c r="Z371">
-        <v>1594268</v>
+        <v>1892</v>
       </c>
       <c r="AA371" t="s">
         <v>2294</v>
       </c>
       <c r="AB371" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC371" t="s">
         <v>2295</v>
       </c>
       <c r="AD371" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE371" s="1">
-        <v>46078</v>
+        <v>46108</v>
       </c>
       <c r="AF371" s="1">
-        <v>46284</v>
+        <v>46275</v>
       </c>
       <c r="AG371" s="1">
-        <v>46544</v>
+        <v>46279</v>
       </c>
       <c r="AH371">
-        <v>260</v>
+        <v>4</v>
       </c>
       <c r="AI371" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="AJ371">
-        <v>0</v>
+        <v>-1892</v>
       </c>
       <c r="AK371" t="s">
         <v>64</v>
@@ -71369,11 +71444,11 @@
       <c r="AQ371" t="s">
         <v>53</v>
       </c>
-      <c r="AR371" s="1">
-        <v>46078</v>
-      </c>
-      <c r="AS371" s="2">
-        <v>46078.393645833334</v>
+      <c r="AR371" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS371" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT371" s="1" t="s">
         <v>53</v>
@@ -71382,7 +71457,7 @@
         <v>53</v>
       </c>
       <c r="AV371" t="s">
-        <v>479</v>
+        <v>53</v>
       </c>
       <c r="AW371" t="s">
         <v>53</v>
@@ -71396,10 +71471,10 @@
     </row>
     <row r="372" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>2290</v>
+        <v>2296</v>
       </c>
       <c r="B372" t="s">
-        <v>2291</v>
+        <v>2297</v>
       </c>
       <c r="C372" t="s">
         <v>53</v>
@@ -71411,7 +71486,7 @@
         <v>53</v>
       </c>
       <c r="F372" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="G372" t="s">
         <v>53</v>
@@ -71459,7 +71534,7 @@
         <v>736</v>
       </c>
       <c r="V372" t="s">
-        <v>2293</v>
+        <v>2299</v>
       </c>
       <c r="W372" t="s">
         <v>53</v>
@@ -71471,19 +71546,19 @@
         <v>53</v>
       </c>
       <c r="Z372">
-        <v>81900</v>
+        <v>1594268</v>
       </c>
       <c r="AA372" t="s">
-        <v>2297</v>
+        <v>2300</v>
       </c>
       <c r="AB372" t="s">
         <v>180</v>
       </c>
       <c r="AC372" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="AD372" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE372" s="1">
         <v>46078</v>
@@ -71501,7 +71576,7 @@
         <v>37</v>
       </c>
       <c r="AJ372">
-        <v>-81900</v>
+        <v>0</v>
       </c>
       <c r="AK372" t="s">
         <v>64</v>
@@ -71524,11 +71599,11 @@
       <c r="AQ372" t="s">
         <v>53</v>
       </c>
-      <c r="AR372" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS372" s="2" t="s">
-        <v>53</v>
+      <c r="AR372" s="1">
+        <v>46078</v>
+      </c>
+      <c r="AS372" s="2">
+        <v>46078.393645833334</v>
       </c>
       <c r="AT372" s="1" t="s">
         <v>53</v>
@@ -71551,10 +71626,10 @@
     </row>
     <row r="373" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="B373" t="s">
-        <v>733</v>
+        <v>2297</v>
       </c>
       <c r="C373" t="s">
         <v>53</v>
@@ -71566,7 +71641,7 @@
         <v>53</v>
       </c>
       <c r="F373" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="G373" t="s">
         <v>53</v>
@@ -71575,10 +71650,10 @@
         <v>53</v>
       </c>
       <c r="I373">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J373">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K373">
         <v>0</v>
@@ -71596,13 +71671,13 @@
         <v>53</v>
       </c>
       <c r="P373" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="Q373" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="R373" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="S373" t="s">
         <v>53</v>
@@ -71614,7 +71689,7 @@
         <v>736</v>
       </c>
       <c r="V373" t="s">
-        <v>2293</v>
+        <v>2299</v>
       </c>
       <c r="W373" t="s">
         <v>53</v>
@@ -71626,22 +71701,22 @@
         <v>53</v>
       </c>
       <c r="Z373">
-        <v>40957.8</v>
+        <v>81900</v>
       </c>
       <c r="AA373" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="AB373" t="s">
         <v>180</v>
       </c>
       <c r="AC373" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="AD373" t="s">
         <v>1361</v>
       </c>
       <c r="AE373" s="1">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="AF373" s="1">
         <v>46284</v>
@@ -71656,7 +71731,7 @@
         <v>37</v>
       </c>
       <c r="AJ373">
-        <v>-40957.8</v>
+        <v>-81900</v>
       </c>
       <c r="AK373" t="s">
         <v>64</v>
@@ -71706,10 +71781,10 @@
     </row>
     <row r="374" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="B374" t="s">
-        <v>2304</v>
+        <v>733</v>
       </c>
       <c r="C374" t="s">
         <v>53</v>
@@ -71721,7 +71796,7 @@
         <v>53</v>
       </c>
       <c r="F374" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="G374" t="s">
         <v>53</v>
@@ -71754,7 +71829,7 @@
         <v>177</v>
       </c>
       <c r="Q374" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="R374" t="s">
         <v>177</v>
@@ -71769,7 +71844,7 @@
         <v>736</v>
       </c>
       <c r="V374" t="s">
-        <v>2293</v>
+        <v>2299</v>
       </c>
       <c r="W374" t="s">
         <v>53</v>
@@ -71781,22 +71856,22 @@
         <v>53</v>
       </c>
       <c r="Z374">
-        <v>41080</v>
+        <v>40957.8</v>
       </c>
       <c r="AA374" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="AB374" t="s">
         <v>180</v>
       </c>
       <c r="AC374" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="AD374" t="s">
         <v>1361</v>
       </c>
       <c r="AE374" s="1">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="AF374" s="1">
         <v>46284</v>
@@ -71808,10 +71883,10 @@
         <v>260</v>
       </c>
       <c r="AI374" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="AJ374">
-        <v>-41080</v>
+        <v>-40957.8</v>
       </c>
       <c r="AK374" t="s">
         <v>64</v>
@@ -71861,10 +71936,10 @@
     </row>
     <row r="375" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>171</v>
+        <v>2309</v>
       </c>
       <c r="B375" t="s">
-        <v>79</v>
+        <v>2310</v>
       </c>
       <c r="C375" t="s">
         <v>53</v>
@@ -71876,7 +71951,7 @@
         <v>53</v>
       </c>
       <c r="F375" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
       <c r="G375" t="s">
         <v>53</v>
@@ -71906,25 +71981,25 @@
         <v>53</v>
       </c>
       <c r="P375" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="Q375" t="s">
-        <v>492</v>
+        <v>253</v>
       </c>
       <c r="R375" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="S375" t="s">
         <v>53</v>
       </c>
       <c r="T375" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="U375" t="s">
-        <v>53</v>
+        <v>736</v>
       </c>
       <c r="V375" t="s">
-        <v>58</v>
+        <v>2299</v>
       </c>
       <c r="W375" t="s">
         <v>53</v>
@@ -71936,37 +72011,37 @@
         <v>53</v>
       </c>
       <c r="Z375">
-        <v>1487</v>
+        <v>41080</v>
       </c>
       <c r="AA375" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
       <c r="AB375" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AC375" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="AD375" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE375" s="1">
-        <v>46099</v>
+        <v>46134</v>
       </c>
       <c r="AF375" s="1">
-        <v>46286</v>
+        <v>46284</v>
       </c>
       <c r="AG375" s="1">
-        <v>46290</v>
+        <v>46544</v>
       </c>
       <c r="AH375">
-        <v>4</v>
+        <v>260</v>
       </c>
       <c r="AI375" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="AJ375">
-        <v>0</v>
+        <v>-41080</v>
       </c>
       <c r="AK375" t="s">
         <v>64</v>
@@ -71989,11 +72064,11 @@
       <c r="AQ375" t="s">
         <v>53</v>
       </c>
-      <c r="AR375" s="1">
-        <v>46175</v>
-      </c>
-      <c r="AS375" s="2">
-        <v>46175.397372685184</v>
+      <c r="AR375" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS375" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT375" s="1" t="s">
         <v>53</v>
@@ -72002,7 +72077,7 @@
         <v>53</v>
       </c>
       <c r="AV375" t="s">
-        <v>53</v>
+        <v>479</v>
       </c>
       <c r="AW375" t="s">
         <v>53</v>
@@ -72016,10 +72091,10 @@
     </row>
     <row r="376" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>2311</v>
+        <v>171</v>
       </c>
       <c r="B376" t="s">
-        <v>2312</v>
+        <v>79</v>
       </c>
       <c r="C376" t="s">
         <v>53</v>
@@ -72031,7 +72106,7 @@
         <v>53</v>
       </c>
       <c r="F376" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="G376" t="s">
         <v>53</v>
@@ -72040,10 +72115,10 @@
         <v>53</v>
       </c>
       <c r="I376">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J376">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K376">
         <v>0</v>
@@ -72061,25 +72136,25 @@
         <v>53</v>
       </c>
       <c r="P376" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="Q376" t="s">
-        <v>766</v>
+        <v>492</v>
       </c>
       <c r="R376" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="S376" t="s">
-        <v>2314</v>
+        <v>53</v>
       </c>
       <c r="T376" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="U376" t="s">
-        <v>1006</v>
+        <v>53</v>
       </c>
       <c r="V376" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="W376" t="s">
         <v>53</v>
@@ -72091,37 +72166,37 @@
         <v>53</v>
       </c>
       <c r="Z376">
-        <v>13630.5</v>
+        <v>1487</v>
       </c>
       <c r="AA376" t="s">
         <v>2315</v>
       </c>
       <c r="AB376" t="s">
-        <v>763</v>
+        <v>60</v>
       </c>
       <c r="AC376" t="s">
         <v>2316</v>
       </c>
       <c r="AD376" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE376" s="1">
-        <v>46144</v>
+        <v>46099</v>
       </c>
       <c r="AF376" s="1">
         <v>46286</v>
       </c>
       <c r="AG376" s="1">
-        <v>46301</v>
+        <v>46290</v>
       </c>
       <c r="AH376">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AI376" t="s">
         <v>63</v>
       </c>
       <c r="AJ376">
-        <v>-13630.5</v>
+        <v>0</v>
       </c>
       <c r="AK376" t="s">
         <v>64</v>
@@ -72144,11 +72219,11 @@
       <c r="AQ376" t="s">
         <v>53</v>
       </c>
-      <c r="AR376" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS376" s="2" t="s">
-        <v>53</v>
+      <c r="AR376" s="1">
+        <v>46175</v>
+      </c>
+      <c r="AS376" s="2">
+        <v>46175.397372685184</v>
       </c>
       <c r="AT376" s="1" t="s">
         <v>53</v>
@@ -72183,16 +72258,16 @@
         <v>53</v>
       </c>
       <c r="E377" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F377" t="s">
         <v>2319</v>
       </c>
       <c r="G377" t="s">
-        <v>2320</v>
+        <v>53</v>
       </c>
       <c r="H377" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I377">
         <v>2</v>
@@ -72216,22 +72291,22 @@
         <v>53</v>
       </c>
       <c r="P377" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="Q377" t="s">
-        <v>188</v>
+        <v>766</v>
       </c>
       <c r="R377" t="s">
-        <v>189</v>
+        <v>88</v>
       </c>
       <c r="S377" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="T377" t="s">
         <v>97</v>
       </c>
       <c r="U377" t="s">
-        <v>190</v>
+        <v>1006</v>
       </c>
       <c r="V377" t="s">
         <v>99</v>
@@ -72246,37 +72321,37 @@
         <v>53</v>
       </c>
       <c r="Z377">
-        <v>918</v>
+        <v>13630.5</v>
       </c>
       <c r="AA377" t="s">
+        <v>2321</v>
+      </c>
+      <c r="AB377" t="s">
+        <v>763</v>
+      </c>
+      <c r="AC377" t="s">
         <v>2322</v>
-      </c>
-      <c r="AB377" t="s">
-        <v>180</v>
-      </c>
-      <c r="AC377" t="s">
-        <v>2323</v>
       </c>
       <c r="AD377" t="s">
         <v>1361</v>
       </c>
       <c r="AE377" s="1">
-        <v>46075</v>
+        <v>46144</v>
       </c>
       <c r="AF377" s="1">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="AG377" s="1">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="AH377">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AI377" t="s">
         <v>63</v>
       </c>
       <c r="AJ377">
-        <v>-918</v>
+        <v>-13630.5</v>
       </c>
       <c r="AK377" t="s">
         <v>64</v>
@@ -72284,8 +72359,8 @@
       <c r="AL377" t="s">
         <v>53</v>
       </c>
-      <c r="AM377">
-        <v>137.7</v>
+      <c r="AM377" t="s">
+        <v>53</v>
       </c>
       <c r="AN377" t="s">
         <v>53</v>
@@ -72326,7 +72401,7 @@
     </row>
     <row r="378" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>867</v>
+        <v>2323</v>
       </c>
       <c r="B378" t="s">
         <v>2324</v>
@@ -72338,22 +72413,22 @@
         <v>53</v>
       </c>
       <c r="E378" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F378" t="s">
         <v>2325</v>
       </c>
       <c r="G378" t="s">
-        <v>53</v>
+        <v>2326</v>
       </c>
       <c r="H378" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I378">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J378">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K378">
         <v>0</v>
@@ -72371,22 +72446,22 @@
         <v>53</v>
       </c>
       <c r="P378" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="Q378" t="s">
-        <v>53</v>
+        <v>188</v>
       </c>
       <c r="R378" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="S378" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="T378" t="s">
         <v>97</v>
       </c>
       <c r="U378" t="s">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="V378" t="s">
         <v>99</v>
@@ -72401,28 +72476,28 @@
         <v>53</v>
       </c>
       <c r="Z378">
-        <v>1395.99</v>
+        <v>918</v>
       </c>
       <c r="AA378" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="AB378" t="s">
         <v>180</v>
       </c>
       <c r="AC378" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="AD378" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE378" s="1">
-        <v>45989</v>
+        <v>46075</v>
       </c>
       <c r="AF378" s="1">
-        <v>46330</v>
+        <v>46290</v>
       </c>
       <c r="AG378" s="1">
-        <v>46333</v>
+        <v>46293</v>
       </c>
       <c r="AH378">
         <v>3</v>
@@ -72431,7 +72506,7 @@
         <v>63</v>
       </c>
       <c r="AJ378">
-        <v>0</v>
+        <v>-918</v>
       </c>
       <c r="AK378" t="s">
         <v>64</v>
@@ -72439,8 +72514,8 @@
       <c r="AL378" t="s">
         <v>53</v>
       </c>
-      <c r="AM378" t="s">
-        <v>53</v>
+      <c r="AM378">
+        <v>137.7</v>
       </c>
       <c r="AN378" t="s">
         <v>53</v>
@@ -72454,11 +72529,11 @@
       <c r="AQ378" t="s">
         <v>53</v>
       </c>
-      <c r="AR378" s="1">
-        <v>46040</v>
-      </c>
-      <c r="AS378" s="2">
-        <v>46040.82962962963</v>
+      <c r="AR378" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS378" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="AT378" s="1" t="s">
         <v>53</v>
@@ -72481,7 +72556,7 @@
     </row>
     <row r="379" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>2329</v>
+        <v>867</v>
       </c>
       <c r="B379" t="s">
         <v>2330</v>
@@ -72526,13 +72601,13 @@
         <v>53</v>
       </c>
       <c r="P379" t="s">
-        <v>804</v>
+        <v>183</v>
       </c>
       <c r="Q379" t="s">
-        <v>808</v>
+        <v>53</v>
       </c>
       <c r="R379" t="s">
-        <v>804</v>
+        <v>53</v>
       </c>
       <c r="S379" t="s">
         <v>2332</v>
@@ -72544,7 +72619,7 @@
         <v>300</v>
       </c>
       <c r="V379" t="s">
-        <v>744</v>
+        <v>99</v>
       </c>
       <c r="W379" t="s">
         <v>53</v>
@@ -72556,37 +72631,37 @@
         <v>53</v>
       </c>
       <c r="Z379">
-        <v>1872.8</v>
+        <v>1395.99</v>
       </c>
       <c r="AA379" t="s">
         <v>2333</v>
       </c>
       <c r="AB379" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC379" t="s">
         <v>2334</v>
       </c>
       <c r="AD379" t="s">
-        <v>1361</v>
+        <v>62</v>
       </c>
       <c r="AE379" s="1">
-        <v>46120</v>
+        <v>45989</v>
       </c>
       <c r="AF379" s="1">
-        <v>46375</v>
+        <v>46330</v>
       </c>
       <c r="AG379" s="1">
-        <v>46379</v>
+        <v>46333</v>
       </c>
       <c r="AH379">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI379" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="AJ379">
-        <v>-1872.8</v>
+        <v>0</v>
       </c>
       <c r="AK379" t="s">
         <v>64</v>
@@ -72609,11 +72684,11 @@
       <c r="AQ379" t="s">
         <v>53</v>
       </c>
-      <c r="AR379" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS379" s="2" t="s">
-        <v>53</v>
+      <c r="AR379" s="1">
+        <v>46040</v>
+      </c>
+      <c r="AS379" s="2">
+        <v>46040.82962962963</v>
       </c>
       <c r="AT379" s="1" t="s">
         <v>53</v>
@@ -72681,13 +72756,13 @@
         <v>53</v>
       </c>
       <c r="P380" t="s">
-        <v>189</v>
+        <v>804</v>
       </c>
       <c r="Q380" t="s">
-        <v>188</v>
+        <v>808</v>
       </c>
       <c r="R380" t="s">
-        <v>189</v>
+        <v>804</v>
       </c>
       <c r="S380" t="s">
         <v>2338</v>
@@ -72699,7 +72774,7 @@
         <v>300</v>
       </c>
       <c r="V380" t="s">
-        <v>99</v>
+        <v>744</v>
       </c>
       <c r="W380" t="s">
         <v>53</v>
@@ -72711,13 +72786,13 @@
         <v>53</v>
       </c>
       <c r="Z380">
-        <v>3370</v>
+        <v>1872.8</v>
       </c>
       <c r="AA380" t="s">
         <v>2339</v>
       </c>
       <c r="AB380" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC380" t="s">
         <v>2340</v>
@@ -72726,13 +72801,13 @@
         <v>1361</v>
       </c>
       <c r="AE380" s="1">
-        <v>46106</v>
+        <v>46120</v>
       </c>
       <c r="AF380" s="1">
-        <v>46385</v>
+        <v>46375</v>
       </c>
       <c r="AG380" s="1">
-        <v>46389</v>
+        <v>46379</v>
       </c>
       <c r="AH380">
         <v>4</v>
@@ -72741,7 +72816,7 @@
         <v>112</v>
       </c>
       <c r="AJ380">
-        <v>-3370</v>
+        <v>-1872.8</v>
       </c>
       <c r="AK380" t="s">
         <v>64</v>
@@ -72836,13 +72911,13 @@
         <v>53</v>
       </c>
       <c r="P381" t="s">
-        <v>804</v>
+        <v>189</v>
       </c>
       <c r="Q381" t="s">
-        <v>808</v>
+        <v>188</v>
       </c>
       <c r="R381" t="s">
-        <v>804</v>
+        <v>189</v>
       </c>
       <c r="S381" t="s">
         <v>2344</v>
@@ -72854,7 +72929,7 @@
         <v>300</v>
       </c>
       <c r="V381" t="s">
-        <v>744</v>
+        <v>99</v>
       </c>
       <c r="W381" t="s">
         <v>53</v>
@@ -72866,13 +72941,13 @@
         <v>53</v>
       </c>
       <c r="Z381">
-        <v>1272</v>
+        <v>3370</v>
       </c>
       <c r="AA381" t="s">
         <v>2345</v>
       </c>
       <c r="AB381" t="s">
-        <v>763</v>
+        <v>180</v>
       </c>
       <c r="AC381" t="s">
         <v>2346</v>
@@ -72881,22 +72956,22 @@
         <v>1361</v>
       </c>
       <c r="AE381" s="1">
-        <v>46120</v>
+        <v>46106</v>
       </c>
       <c r="AF381" s="1">
         <v>46385</v>
       </c>
       <c r="AG381" s="1">
-        <v>46388</v>
+        <v>46389</v>
       </c>
       <c r="AH381">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI381" t="s">
         <v>112</v>
       </c>
       <c r="AJ381">
-        <v>-1272</v>
+        <v>-3370</v>
       </c>
       <c r="AK381" t="s">
         <v>64</v>
@@ -72991,13 +73066,13 @@
         <v>53</v>
       </c>
       <c r="P382" t="s">
-        <v>189</v>
+        <v>804</v>
       </c>
       <c r="Q382" t="s">
-        <v>205</v>
+        <v>808</v>
       </c>
       <c r="R382" t="s">
-        <v>189</v>
+        <v>804</v>
       </c>
       <c r="S382" t="s">
         <v>2350</v>
@@ -73009,7 +73084,7 @@
         <v>300</v>
       </c>
       <c r="V382" t="s">
-        <v>99</v>
+        <v>744</v>
       </c>
       <c r="W382" t="s">
         <v>53</v>
@@ -73021,13 +73096,13 @@
         <v>53</v>
       </c>
       <c r="Z382">
-        <v>2300</v>
+        <v>1272</v>
       </c>
       <c r="AA382" t="s">
         <v>2351</v>
       </c>
       <c r="AB382" t="s">
-        <v>180</v>
+        <v>763</v>
       </c>
       <c r="AC382" t="s">
         <v>2352</v>
@@ -73036,22 +73111,22 @@
         <v>1361</v>
       </c>
       <c r="AE382" s="1">
-        <v>46141</v>
+        <v>46120</v>
       </c>
       <c r="AF382" s="1">
-        <v>46582</v>
+        <v>46385</v>
       </c>
       <c r="AG382" s="1">
-        <v>46586</v>
+        <v>46388</v>
       </c>
       <c r="AH382">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI382" t="s">
         <v>112</v>
       </c>
       <c r="AJ382">
-        <v>-2300</v>
+        <v>-1272</v>
       </c>
       <c r="AK382" t="s">
         <v>64</v>
@@ -73125,10 +73200,10 @@
         <v>53</v>
       </c>
       <c r="I383">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J383">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K383">
         <v>0</v>
@@ -73176,7 +73251,7 @@
         <v>53</v>
       </c>
       <c r="Z383">
-        <v>4829.94</v>
+        <v>2300</v>
       </c>
       <c r="AA383" t="s">
         <v>2357</v>
@@ -73188,25 +73263,25 @@
         <v>2358</v>
       </c>
       <c r="AD383" t="s">
-        <v>62</v>
+        <v>1361</v>
       </c>
       <c r="AE383" s="1">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="AF383" s="1">
-        <v>46744</v>
+        <v>46582</v>
       </c>
       <c r="AG383" s="1">
-        <v>46753</v>
+        <v>46586</v>
       </c>
       <c r="AH383">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AI383" t="s">
         <v>112</v>
       </c>
       <c r="AJ383">
-        <v>0</v>
+        <v>-2300</v>
       </c>
       <c r="AK383" t="s">
         <v>64</v>
@@ -73229,28 +73304,183 @@
       <c r="AQ383" t="s">
         <v>53</v>
       </c>
-      <c r="AR383" s="1">
+      <c r="AR383" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AS383" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AT383" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AX383" t="s">
+        <v>53</v>
+      </c>
+      <c r="AY383" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="384" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B384" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C384" t="s">
+        <v>53</v>
+      </c>
+      <c r="D384" t="s">
+        <v>53</v>
+      </c>
+      <c r="E384" t="s">
+        <v>53</v>
+      </c>
+      <c r="F384" t="s">
+        <v>2361</v>
+      </c>
+      <c r="G384" t="s">
+        <v>53</v>
+      </c>
+      <c r="H384" t="s">
+        <v>53</v>
+      </c>
+      <c r="I384">
+        <v>2</v>
+      </c>
+      <c r="J384">
+        <v>2</v>
+      </c>
+      <c r="K384">
+        <v>0</v>
+      </c>
+      <c r="L384" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M384" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N384" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O384" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P384" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q384" t="s">
+        <v>205</v>
+      </c>
+      <c r="R384" t="s">
+        <v>189</v>
+      </c>
+      <c r="S384" t="s">
+        <v>2362</v>
+      </c>
+      <c r="T384" t="s">
+        <v>97</v>
+      </c>
+      <c r="U384" t="s">
+        <v>300</v>
+      </c>
+      <c r="V384" t="s">
+        <v>99</v>
+      </c>
+      <c r="W384" t="s">
+        <v>53</v>
+      </c>
+      <c r="X384" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y384" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z384">
+        <v>4829.94</v>
+      </c>
+      <c r="AA384" t="s">
+        <v>2363</v>
+      </c>
+      <c r="AB384" t="s">
+        <v>180</v>
+      </c>
+      <c r="AC384" t="s">
+        <v>2364</v>
+      </c>
+      <c r="AD384" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE384" s="1">
         <v>46147</v>
       </c>
-      <c r="AS383" s="2">
+      <c r="AF384" s="1">
+        <v>46744</v>
+      </c>
+      <c r="AG384" s="1">
+        <v>46753</v>
+      </c>
+      <c r="AH384">
+        <v>9</v>
+      </c>
+      <c r="AI384" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ384">
+        <v>0</v>
+      </c>
+      <c r="AK384" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL384" t="s">
+        <v>53</v>
+      </c>
+      <c r="AM384" t="s">
+        <v>53</v>
+      </c>
+      <c r="AN384" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO384" t="s">
+        <v>53</v>
+      </c>
+      <c r="AP384" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ384" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR384" s="1">
+        <v>46147</v>
+      </c>
+      <c r="AS384" s="2">
         <v>46147.538125</v>
       </c>
-      <c r="AT383" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AU383" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV383" t="s">
-        <v>53</v>
-      </c>
-      <c r="AW383" t="s">
-        <v>53</v>
-      </c>
-      <c r="AX383" t="s">
-        <v>53</v>
-      </c>
-      <c r="AY383" t="s">
+      <c r="AT384" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU384" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV384" t="s">
+        <v>53</v>
+      </c>
+      <c r="AW384" t="s">
+        <v>53</v>
+      </c>
+      <c r="AX384" t="s">
+        <v>53</v>
+      </c>
+      <c r="AY384" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -61909,7 +61909,7 @@
         <v>804</v>
       </c>
       <c r="Q310" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="R310" t="s">
         <v>88</v>
@@ -63459,7 +63459,7 @@
         <v>88</v>
       </c>
       <c r="Q320" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="R320" t="s">
         <v>88</v>
